--- a/watchlists/AI产业链.xlsx
+++ b/watchlists/AI产业链.xlsx
@@ -1152,7 +1152,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
+    <row r="2" ht="75" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>高速光模块</t>
@@ -1170,16 +1170,16 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>通过收购索尔思切入光模块（含光芯片），年报确认100G/200G PAM4 EML与10G-1.6T模块矩阵，同时有AI PCB协同；主板块由光芯片降为高速光模块，AI PCB放备注跟踪，风险是并购整合、负债和客户放量节奏。证据A。</t>
+          <t>2026H1正式中报（未经审计）：营收277.98亿元、归母29.57亿元、经营现金流23.84亿元（同比-4.65%）；光模块收入53.51亿元、毛利率39.33%；应收/存货105.98/114.18亿元，年初97.93/89.29亿元。高端AI PCB项目预算70亿元、进度27.02%；光模块产线预算18亿元、82.61%；泰国PCB/光模块配套预算13.12亿元、88.37%，均未视为投产/订单/收入。客户、订单、光芯片/AI PCB独立收入与毛利及认证范围=evidence_absent。证据A：CNINFO 2026-08-22。</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>已处理</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
+          <t>已处理；2026-08-22正式中报复核（未经审计）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>高速光模块</t>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>全球高速光模块龙头，2025年营收382.40亿元、归母净利107.97亿元，高速光模块、800G/1.6T放量已兑现；主板块保留高速光模块，风险是估值拥挤、客户集中、年降和物料约束。证据A。</t>
+          <t>2026H1正式中报（未经审计）：营收417.78亿元、归母136.51亿元、经营现金流18.00亿元（同比-44.08%）；光通信收发模块收入413.55亿元、毛利率46.59%；应收/存货150.01/198.26亿元，年初62.77/126.81亿元。800G/1.6T/硅光的客户、订单、独立收入/毛利及认证范围=evidence_absent。证据A：CNINFO 2026-08-22。</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>已处理；2026-08-22正式中报复核（未经审计）</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="60" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>新型光纤</t>
@@ -2126,12 +2126,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20更新：主营仍是“光棒—光纤—光缆”光传输产品。2025年光传输产品收入83.46亿元、占58.56%、毛利率35.90%；光互联组件收入31.44亿元、占22.06%、毛利率39.73%。2026H1预告归母净利润24—30亿元（同比+711%—914%）、扣非20—26亿元（同比+1349%—1784%）；据Q1归母4.95亿元推算，Q2归母约19.05—25.05亿元。公司称增量来自算力数据中心加速建设、国内外新型光纤光缆需求、核心客户拓展、产品结构优化及盈利能力提升。产品层：普通单模、预制棒及光缆仍是量的基本盘；G.654.E已超百万芯公里规模部署，OM4/OM4 Pro/OM5已规模商用；G.657.A2为成熟量产品种且对本轮高端光棒涨价敏感，但公司未披露其独立收入、ASP或毛利率；空芯/多芯仍偏产业化导入，不能视为当前利润主体。价格基准判断：A2及高端光棒2026H2仍偏强，2027H1涨幅钝化，名义高点更可能在2027Q2—Q3，2027H2—2028随有效产能释放而分化、回落风险上升。证据边界：行业A2报价及Corning海外长协不等于长飞实现售价、客户或订单；继续跟踪2026中报分产品收入/毛利率、现金流、存货及客户订单。来源：公司2026H1业绩预增公告、2025年报、2026-05-22业绩说明会；行业价格为二级证据。</t>
+          <t>2026H1正式中报（未经审计）：营收98.09亿元、归母29.25亿元、经营现金流18.26亿元；光传输/光互联组件收入约61.26/22.38亿元、毛利率63.11%/48.97%；应收/存货72.70/44.70亿元，年初59.50/31.53亿元。PMF/CPO及空芯光纤的客户、订单、独立收入/毛利及认证范围=evidence_absent。证据A：上交所2026-08-22。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>已处理；2026-06-28 光纤上游补充</t>
+          <t>已处理；2026-08-22正式中报复核（未经审计）</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="36" customHeight="1">
+    <row r="76" ht="75" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
           <t>高端高速铜箔</t>
@@ -3152,12 +3152,12 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>PCB级RTF/HVLP进展最直接，年报披露RTF-3/4认证并批量供货、HVLP1-3批量供货、HVLP4小规模放量、HVLP5完成样品认证并推进导入；主板块由高端铜箔细化为HVLP铜箔，风险是HVLP5多客户、收入和毛利率仍需量化。证据A/B。 2026-06-17 HVLP4/T-glass复核：放“交易弹性/条件式HVLP期权”；HVLP4/5从纯watch提高到watch_to_soft验证优先级，但需多客户批量、加工费、电子电路铜箔收入占比和毛利证据，不能混同锂电铜箔修复；官方追杀后，NVIDIA锁产/寄售/LTA/prepayment仍未闭环。</t>
+          <t>2026H1正式中报（未经审计）：营收91.97亿元、归母2.63亿元、经营现金流-6.13亿元；电子电路铜箔收入13.08亿元、毛利率4.85%；应收/存货35.84/26.80亿元，年初34.44/18.72亿元。H1启动5万吨AI高端电子电路铜箔项目（完全达产后年产5万吨为规划，非已达产）。HVLP/RTF/载体铜箔的客户、订单、独立收入/毛利及认证范围=evidence_absent。证据A：CNINFO 2026-08-22。</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>已处理；2026-06-17证据分层；2026-06-17官方锁产追杀仍未闭环</t>
+          <t>已处理；2026-08-22正式中报复核（未经审计）</t>
         </is>
       </c>
     </row>

--- a/watchlists/AI产业链.xlsx
+++ b/watchlists/AI产业链.xlsx
@@ -1115,7 +1115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E393"/>
+  <dimension ref="A1:E394"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1760,49 +1760,49 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>微光学耦合元件</t>
+          <t>FAU</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>688167</t>
+          <t>920045</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>炬光科技</t>
+          <t>蘅东光</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>光子技术平台，数据通信方向提供微透镜及阵列、V型槽阵列、FAU、ELSFP、NPO、CPO和OCS等场景的微光学解决方案，部分客户已批量交付；主板块改为微光学耦合元件，FAU和光模块封测耦合设备合并，风险是公司仍处亏损修复期、光通信收入基数小和客户认证转量产节奏。证据B。</t>
+          <t>无源光器件平台；2026H1披露应用于800G、1.6T光模块的无源内连光器件已规模交付。公司2025年度业绩说明会明确高速率无源内连器件包含单模FAU；CPO/NPO无源内连已完成产品开发，正处客户验证、小批量试产和量产准备，不能按CPO/NPO专用FAU量产、客户、订单或收入处理。主板块列FAU，风险是CPO/NPO验证转量产、客户认证及独立收入披露不足。证据A：北交所2026H1（2026-08-21）、公司2025年报业绩说明会（2026-05-11）。</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>已处理；2026-08-22研究更新</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>法拉第旋光片</t>
+          <t>微光学耦合元件</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>002222</t>
+          <t>688167</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>炬光科技</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>晶体元器件和精密光学元件平台，主营覆盖晶体、精密光学和激光器件，磁光晶体/法拉第旋光片可映射光通信光隔离器链条；主板块保留法拉第旋光片，但AI光模块客户、批量订单和收入占比仍需验证，风险是激光与光通信收入分散、AI链条业绩弹性不足。证据B/C。</t>
+          <t>光子技术平台，数据通信方向提供微透镜及阵列、V型槽阵列、FAU、ELSFP、NPO、CPO和OCS等场景的微光学解决方案，部分客户已批量交付；主板块改为微光学耦合元件，FAU和光模块封测耦合设备合并，风险是公司仍处亏损修复期、光通信收入基数小和客户认证转量产节奏。证据B。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -1814,22 +1814,22 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>薄膜滤波片</t>
+          <t>法拉第旋光片</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>688195</t>
+          <t>002222</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>腾景科技</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>精密光学和光纤器件平台，2025半年报披露数据中心CWDM滤光片可规模化低成本供应，并具备WSS关键球柱面镜、微透镜等能力；主板块改为薄膜滤波片，法拉第旋光片、OCS光交换和微透镜并入备注降级为相邻精密光学能力，风险是AI数据中心客户订单和收入占比披露不足。证据B。</t>
+          <t>晶体元器件和精密光学元件平台，主营覆盖晶体、精密光学和激光器件，磁光晶体/法拉第旋光片可映射光通信光隔离器链条；主板块保留法拉第旋光片，但AI光模块客户、批量订单和收入占比仍需验证，风险是激光与光通信收入分散、AI链条业绩弹性不足。证据B/C。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -1841,22 +1841,22 @@
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>微透镜</t>
+          <t>薄膜滤波片</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>603297</t>
+          <t>688195</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>永新光学</t>
+          <t>腾景科技</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>精密光学元组件和显微镜平台，2025年报披露半导体光学切入光刻机对准/照明系统并布局空间激光通信光学组件；AI光模块微透镜映射仍偏宽口径观察，主板块暂保留微透镜，风险是数据中心光通信客户、具体料号和收入占比证据不足。证据C/B。</t>
+          <t>精密光学和光纤器件平台，2025半年报披露数据中心CWDM滤光片可规模化低成本供应，并具备WSS关键球柱面镜、微透镜等能力；主板块改为薄膜滤波片，法拉第旋光片、OCS光交换和微透镜并入备注降级为相邻精密光学能力，风险是AI数据中心客户订单和收入占比披露不足。证据B。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1868,22 +1868,22 @@
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>光通信陶瓷管壳</t>
+          <t>微透镜</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>003031</t>
+          <t>603297</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>中瓷电子</t>
+          <t>永新光学</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>电子陶瓷平台叠加GaN通信器件、SiC功率模块业务；投关披露氮化铝多层薄厚膜已批量出货，产品用于400G、800G、1.6T高频高速光模块，AI数据中心光模块升级拉动较直接。主板块保留光通信陶瓷管壳，静电卡盘并入备注作为半导体设备陶瓷观察，风险是客户份额、产品价格和三代半业务周期。证据B。</t>
+          <t>精密光学元组件和显微镜平台，2025年报披露半导体光学切入光刻机对准/照明系统并布局空间激光通信光学组件；AI光模块微透镜映射仍偏宽口径观察，主板块暂保留微透镜，风险是数据中心光通信客户、具体料号和收入占比证据不足。证据C/B。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -1895,22 +1895,22 @@
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>光模块封测耦合设备</t>
+          <t>光通信陶瓷管壳</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>300757</t>
+          <t>003031</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>罗博特科</t>
+          <t>中瓷电子</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>通过ficonTEC切入光电子及半导体封测设备，年报披露设备用于硅光芯片、光模块、量子器件等微组装和测试，并进入多家全球头部科技公司供应链；可插拔光模块封装设备获同一集团客户约6亿元订单，CPO/OCS/OIO量产化升级带来高弹性。风险是并购整合、订单交付、亏损修复和光伏旧业务拖累。证据A。</t>
+          <t>电子陶瓷平台叠加GaN通信器件、SiC功率模块业务；投关披露氮化铝多层薄厚膜已批量出货，产品用于400G、800G、1.6T高频高速光模块，AI数据中心光模块升级拉动较直接。主板块保留光通信陶瓷管壳，静电卡盘并入备注作为半导体设备陶瓷观察，风险是客户份额、产品价格和三代半业务周期。证据B。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -1927,17 +1927,17 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>688097</t>
+          <t>300757</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>博众精工</t>
+          <t>罗博特科</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>自动化装备平台，年报/半年报披露半导体业务切入400G/800G/1.6T光模块场景，共晶贴片机等设备已在高速光模块规模化生产中批量应用并进入头部企业供应链；主板块保留光模块封测耦合设备，风险是光模块设备收入占比、订单连续性和3C/新能源业务波动。证据B。</t>
+          <t>通过ficonTEC切入光电子及半导体封测设备，年报披露设备用于硅光芯片、光模块、量子器件等微组装和测试，并进入多家全球头部科技公司供应链；可插拔光模块封装设备获同一集团客户约6亿元订单，CPO/OCS/OIO量产化升级带来高弹性。风险是并购整合、订单交付、亏损修复和光伏旧业务拖累。证据A。</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -1954,17 +1954,17 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>603203</t>
+          <t>688097</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>快克智能</t>
+          <t>博众精工</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>精密焊接、点胶、检测和自动化设备平台，2025年报披露光模块专用AOI可识别激光器芯片偏移、金线键合缺陷和光芯片波导亚微米级缺陷，并批量供应多家光模块龙头；主板块保留光模块封测耦合设备，AI眼镜激光焊接和TCB并入备注，风险是光模块设备放量、客户集中和先进封装证据仍弱。证据B。</t>
+          <t>自动化装备平台，年报/半年报披露半导体业务切入400G/800G/1.6T光模块场景，共晶贴片机等设备已在高速光模块规模化生产中批量应用并进入头部企业供应链；主板块保留光模块封测耦合设备，风险是光模块设备收入占比、订单连续性和3C/新能源业务波动。证据B。</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -1981,17 +1981,17 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>002957</t>
+          <t>603203</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>科瑞技术</t>
+          <t>快克智能</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>自动化装备公司，2025年报披露面向半导体及光模块推出光器件耦合设备、镜片/镜群耦合设备、光模块芯片AOI与COS AOI、光模块芯片共晶贴片和光纤打磨设备等，适配800G-3.2T光模块制造升级；主板块保留光模块封测耦合设备，风险是设备收入占比、头部客户订单和盈利修复。证据B。</t>
+          <t>精密焊接、点胶、检测和自动化设备平台，2025年报披露光模块专用AOI可识别激光器芯片偏移、金线键合缺陷和光芯片波导亚微米级缺陷，并批量供应多家光模块龙头；主板块保留光模块封测耦合设备，AI眼镜激光焊接和TCB并入备注，风险是光模块设备放量、客户集中和先进封装证据仍弱。证据B。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -2003,22 +2003,22 @@
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>光通信测试仪表</t>
+          <t>光模块封测耦合设备</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>688112</t>
+          <t>002957</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>鼎阳科技</t>
+          <t>科瑞技术</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>电子测试测量仪器平台，产品包括示波器、信号发生器、频谱分析仪、矢量网络分析仪等；年报和交流材料显示相关产品可用于光模块、高速连接器等数据中心基础设施研发与生产测试。主板块保留光模块高速测试仪表，风险是多为通用仪器、专用BERT/采样示波器能力和客户订单披露不足。证据B/C。</t>
+          <t>自动化装备公司，2025年报披露面向半导体及光模块推出光器件耦合设备、镜片/镜群耦合设备、光模块芯片AOI与COS AOI、光模块芯片共晶贴片和光纤打磨设备等，适配800G-3.2T光模块制造升级；主板块保留光模块封测耦合设备，风险是设备收入占比、头部客户订单和盈利修复。证据B。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -2035,17 +2035,17 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>688337</t>
+          <t>688112</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>普源精电</t>
+          <t>鼎阳科技</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>RIGOL电子测量仪器平台，核心产品覆盖数字示波器、微波射频、直流精密和模块化仪器，并提供通信等行业解决方案；2025年光通信领域核心大客户收入高增，说明光通信测试已进入业绩拉动。主板块保留光模块高速测试仪表，风险是毛利率压力、解决方案项目波动和高端仪器国产替代竞争。证据B。</t>
+          <t>电子测试测量仪器平台，产品包括示波器、信号发生器、频谱分析仪、矢量网络分析仪等；年报和交流材料显示相关产品可用于光模块、高速连接器等数据中心基础设施研发与生产测试。主板块保留光模块高速测试仪表，风险是多为通用仪器、专用BERT/采样示波器能力和客户订单披露不足。证据B/C。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -2062,17 +2062,17 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>688628</t>
+          <t>688337</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>优利德</t>
+          <t>普源精电</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>综合测试测量仪表平台，2026年公告拟收购信测通信51%股权，标的主营光网络建设维护、光功率计、光时域反射仪、光纤熔接机和电磁监测等，补齐光通信测试产品线；主板块收窄为光通信测试仪表，高速光模块产线测试证据不足，风险是收购落地、并表贡献和高端仪器能力验证。证据B/C。</t>
+          <t>RIGOL电子测量仪器平台，核心产品覆盖数字示波器、微波射频、直流精密和模块化仪器，并提供通信等行业解决方案；2025年光通信领域核心大客户收入高增，说明光通信测试已进入业绩拉动。主板块保留光模块高速测试仪表，风险是毛利率压力、解决方案项目波动和高端仪器国产替代竞争。证据B。</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -2084,22 +2084,22 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>光纤连接</t>
+          <t>光通信测试仪表</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>300570</t>
+          <t>688628</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>太辰光</t>
+          <t>优利德</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>光通信器件公司，MTP/MPO等高密度光连接产品直接受益数据中心高速互连需求，年报显示光通信器件主业延续增长；主板块改为光纤连接，FAU、陶瓷插芯和PM光纤并入备注，不再重复列板块，风险是北美客户集中、关税扰动和CPO商用节奏。证据A/B。</t>
+          <t>综合测试测量仪表平台，2026年公告拟收购信测通信51%股权，标的主营光网络建设维护、光功率计、光时域反射仪、光纤熔接机和电磁监测等，补齐光通信测试产品线；主板块收窄为光通信测试仪表，高速光模块产线测试证据不足，风险是收购落地、并表贡献和高端仪器能力验证。证据B/C。</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -2111,27 +2111,27 @@
     <row r="38" ht="60" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>新型光纤</t>
+          <t>光纤连接</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>601869</t>
+          <t>300570</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>长飞光纤</t>
+          <t>太辰光</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>2026H1正式中报（未经审计）：营收98.09亿元、归母29.25亿元、经营现金流18.26亿元；光传输/光互联组件收入约61.26/22.38亿元、毛利率63.11%/48.97%；应收/存货72.70/44.70亿元，年初59.50/31.53亿元。PMF/CPO及空芯光纤的客户、订单、独立收入/毛利及认证范围=evidence_absent。证据A：上交所2026-08-22。</t>
+          <t>光通信器件公司，MTP/MPO等高密度光连接产品直接受益数据中心高速互连需求，年报显示光通信器件主业延续增长；主板块改为光纤连接，FAU、陶瓷插芯和PM光纤并入备注，不再重复列板块，风险是北美客户集中、关税扰动和CPO商用节奏。证据A/B。</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>已处理；2026-08-22正式中报复核（未经审计）</t>
+          <t>已处理</t>
         </is>
       </c>
     </row>
@@ -2143,22 +2143,22 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>600487</t>
+          <t>601869</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>长飞光纤</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>光棒、光纤、光缆及海洋通信平台型公司，已披露空芯光纤成缆和商用线路推进，AI算力对低时延/高带宽光纤形成中长期拉动；主板块由光纤细化为新型光纤，电力电缆不作为AI链主板块，降级到电力/能源基建背景。风险是铜缆和能源业务摊薄、空芯规模化和毛利率波动。证据B。</t>
+          <t>2026H1正式中报（未经审计）：营收98.09亿元、归母29.25亿元、经营现金流18.26亿元；光传输/光互联组件收入约61.26/22.38亿元、毛利率63.11%/48.97%；应收/存货72.70/44.70亿元，年初59.50/31.53亿元。PMF/CPO及空芯光纤的客户、订单、独立收入/毛利及认证范围=evidence_absent。证据A：上交所2026-08-22。</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>已处理；2026-08-22正式中报复核（未经审计）</t>
         </is>
       </c>
     </row>
@@ -2170,17 +2170,17 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>600522</t>
+          <t>600487</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>中天科技</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>光纤光缆、特种光缆和通信网络平台，公开资料披露AI算力带动高性能特种光纤光缆需求，并有空芯光纤/数据中心互联进展；主板块由光纤细化为新型光纤，电力电缆删除为非本轮AI主线。风险是光纤价格周期、空芯光纤收入兑现和电力/海缆业务波动。证据A/B。</t>
+          <t>光棒、光纤、光缆及海洋通信平台型公司，已披露空芯光纤成缆和商用线路推进，AI算力对低时延/高带宽光纤形成中长期拉动；主板块由光纤细化为新型光纤，电力电缆不作为AI链主板块，降级到电力/能源基建背景。风险是铜缆和能源业务摊薄、空芯规模化和毛利率波动。证据B。</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -2192,27 +2192,27 @@
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>光纤级高纯四氯化硅</t>
+          <t>新型光纤</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>603938</t>
+          <t>600522</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>三孚股份</t>
+          <t>中天科技</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>6N/9N高纯四氯化硅直接用于光纤预制棒，现有高纯四氯化硅产能约3万吨/年，9N量小但可供应高端光棒/PCVD并出口欧洲特纤市场；AI数据中心光纤紧缺向光棒原料传导，属于当前更直接的外供标的。风险是9N实际销量、客户结构、涨价持续性和非光纤需求分流。证据A/B。新增：2026-06-28 光纤上游补充。</t>
+          <t>光纤光缆、特种光缆和通信网络平台，公开资料披露AI算力带动高性能特种光纤光缆需求，并有空芯光纤/数据中心互联进展；主板块由光纤细化为新型光纤，电力电缆删除为非本轮AI主线。风险是光纤价格周期、空芯光纤收入兑现和电力/海缆业务波动。证据A/B。</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>新增；2026-06-28 光纤上游补充</t>
+          <t>已处理</t>
         </is>
       </c>
     </row>
@@ -2224,17 +2224,17 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>600596</t>
+          <t>603938</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>新安股份</t>
+          <t>三孚股份</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>参股浙江亚格新安高纯四氯化硅项目，公开口径为规划4万吨、具备6N-9N能力，预计2026年投用；定位为新增供给观察，不等同当前已验证主供。风险是投产爬坡、客户认证、权益比例和利润归属。证据B/C。新增：2026-06-28 光纤上游补充。</t>
+          <t>6N/9N高纯四氯化硅直接用于光纤预制棒，现有高纯四氯化硅产能约3万吨/年，9N量小但可供应高端光棒/PCVD并出口欧洲特纤市场；AI数据中心光纤紧缺向光棒原料传导，属于当前更直接的外供标的。风险是9N实际销量、客户结构、涨价持续性和非光纤需求分流。证据A/B。新增：2026-06-28 光纤上游补充。</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -2251,17 +2251,17 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>603281</t>
+          <t>600596</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>江瀚新材</t>
+          <t>新安股份</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>功能性硅基前驱体项目规划光纤级6N四氯化硅，属于在建供给线索；若光棒扩产持续，后续弹性取决于投产、客户认证和实际供货。风险是项目进度、产品纯度等级、客户验证周期和收入占比。证据B/C。新增：2026-06-28 光纤上游补充。</t>
+          <t>参股浙江亚格新安高纯四氯化硅项目，公开口径为规划4万吨、具备6N-9N能力，预计2026年投用；定位为新增供给观察，不等同当前已验证主供。风险是投产爬坡、客户认证、权益比例和利润归属。证据B/C。新增：2026-06-28 光纤上游补充。</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -2278,17 +2278,17 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>605366</t>
+          <t>603281</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>宏柏新材</t>
+          <t>江瀚新材</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>规划高纯四氯化硅项目并对标9N级需求，但截至2026-06公开口径仍提示项目未开工/产能为零；只放observation/watch，不作为当前供应。风险是建设周期、环评/设备、客户认证和主题预期先行。证据B/C。新增：2026-06-28 光纤上游补充。</t>
+          <t>功能性硅基前驱体项目规划光纤级6N四氯化硅，属于在建供给线索；若光棒扩产持续，后续弹性取决于投产、客户认证和实际供货。风险是项目进度、产品纯度等级、客户验证周期和收入占比。证据B/C。新增：2026-06-28 光纤上游补充。</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -2300,22 +2300,22 @@
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>光纤级高纯石英材料</t>
+          <t>光纤级高纯四氯化硅</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>603688</t>
+          <t>605366</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>石英股份</t>
+          <t>宏柏新材</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>光纤级套管、衬管、炉芯管、石英管棒等是光纤预制棒和拉丝核心辅材，公司在高纯石英砂和石英制品端均有布局，光纤预制棒产能利用率提升带动光纤用高纯石英材料需求。风险是半导体/光伏石英周期扰动、光纤收入占比和订单持续性披露不足。证据A/B。新增：2026-06-28 光纤上游补充。</t>
+          <t>规划高纯四氯化硅项目并对标9N级需求，但截至2026-06公开口径仍提示项目未开工/产能为零；只放observation/watch，不作为当前供应。风险是建设周期、环评/设备、客户认证和主题预期先行。证据B/C。新增：2026-06-28 光纤上游补充。</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -2327,22 +2327,22 @@
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>合成高纯石英材料</t>
+          <t>光纤级高纯石英材料</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>600552</t>
+          <t>603688</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>凯盛科技</t>
+          <t>石英股份</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>合成高纯二氧化硅/高纯石英砂项目进入试生产和客户验证线索，可作为光纤级、半导体级高纯二氧化硅国产替代观察；与光纤套管、炉芯管等成品供应链的适配仍需验证。风险是验证周期、量产良率、客户结构和实际出货规模。证据B/C。新增：2026-06-28 光纤上游补充。</t>
+          <t>光纤级套管、衬管、炉芯管、石英管棒等是光纤预制棒和拉丝核心辅材，公司在高纯石英砂和石英制品端均有布局，光纤预制棒产能利用率提升带动光纤用高纯石英材料需求。风险是半导体/光伏石英周期扰动、光纤收入占比和订单持续性披露不足。证据A/B。新增：2026-06-28 光纤上游补充。</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -2354,27 +2354,27 @@
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>光模块液冷</t>
+          <t>合成高纯石英材料</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>688668</t>
+          <t>600552</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>鼎通科技</t>
+          <t>凯盛科技</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>按复核结论由224G高速背板连接器调整为光模块液冷：公司通信连接器仍是收入基本盘，但液冷CAGE是在现有CAGE基础上集成液冷板形成的光模块液冷散热模组，已取得核心客户认证并进入小批量交付；光模块散热/热沉/液冷CAGE是AI数据中心散热升级方向。风险是液冷CAGE仍处验证放量初期、客户集中和高速连接器周期波动。证据中强。</t>
+          <t>合成高纯二氧化硅/高纯石英砂项目进入试生产和客户验证线索，可作为光纤级、半导体级高纯二氧化硅国产替代观察；与光纤套管、炉芯管等成品供应链的适配仍需验证。风险是验证周期、量产良率、客户结构和实际出货规模。证据B/C。新增：2026-06-28 光纤上游补充。</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>新增；2026-06-28 光纤上游补充</t>
         </is>
       </c>
     </row>
@@ -2386,17 +2386,17 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>301123</t>
+          <t>688668</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>奕东电子</t>
+          <t>鼎通科技</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>按复核结论由光模块液冷组件统一为光模块液冷：公司具备光模块CAGE、连接器/结构件和热管理平台能力，OSFP 112G、OSFP-XD 224G、OverPass 224G等光模块CAGE产品已批量交货，液冷散热结构件已批量出货；适配液冷方案的CAGE已有出货，并推进CAGE+液冷一体化方案。风险是液冷CAGE/一体化方案仍处放量初期、客户认证节奏和传统消费电子业务波动。证据中强。</t>
+          <t>按复核结论由224G高速背板连接器调整为光模块液冷：公司通信连接器仍是收入基本盘，但液冷CAGE是在现有CAGE基础上集成液冷板形成的光模块液冷散热模组，已取得核心客户认证并进入小批量交付；光模块散热/热沉/液冷CAGE是AI数据中心散热升级方向。风险是液冷CAGE仍处验证放量初期、客户集中和高速连接器周期波动。证据中强。</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -2408,22 +2408,22 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>数据中心液冷系统</t>
+          <t>光模块液冷</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>002837</t>
+          <t>301123</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>奕东电子</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Coolinside全链条液冷覆盖冷板、快接头、Manifold、CDU、机柜、管路、冷源和工质，并有Intel平台验证等公开线索；主板块保留数据中心液冷系统，液冷检测和冷源行并入备注，风险是大客户节奏、交付毛利和海外扩张。证据A。</t>
+          <t>按复核结论由光模块液冷组件统一为光模块液冷：公司具备光模块CAGE、连接器/结构件和热管理平台能力，OSFP 112G、OSFP-XD 224G、OverPass 224G等光模块CAGE产品已批量交货，液冷散热结构件已批量出货；适配液冷方案的CAGE已有出货，并推进CAGE+液冷一体化方案。风险是液冷CAGE/一体化方案仍处放量初期、客户认证节奏和传统消费电子业务波动。证据中强。</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -2440,17 +2440,17 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>301018</t>
+          <t>002837</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>申菱环境</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>年报披露液冷系列覆盖CDU、Manifold、一体化冷源、干冷器、预制化管网、液冷门、快速接头和冷板，且在中国液冷数据中心CDU/智算市场排名靠前；主板块保留数据中心液冷系统，冷源行并入备注，风险是项目型交付、应收账款和订单持续性。证据A。</t>
+          <t>Coolinside全链条液冷覆盖冷板、快接头、Manifold、CDU、机柜、管路、冷源和工质，并有Intel平台验证等公开线索；主板块保留数据中心液冷系统，液冷检测和冷源行并入备注，风险是大客户节奏、交付毛利和海外扩张。证据A。</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>300990</t>
+          <t>301018</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>同飞股份</t>
+          <t>申菱环境</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>数据中心液冷方案覆盖CDU、Manifold、预制化管路、室外干冷器、集成冷站及浸没液冷箱体TANK，属于从工业温控切入AIDC液冷系统的直接映射；主板块保留数据中心液冷系统，背板空调和风墙作为过渡末端并入备注，风险是数据中心收入占比、订单连续性和项目毛利。证据A/B。</t>
+          <t>年报披露液冷系列覆盖CDU、Manifold、一体化冷源、干冷器、预制化管网、液冷门、快速接头和冷板，且在中国液冷数据中心CDU/智算市场排名靠前；主板块保留数据中心液冷系统，冷源行并入备注，风险是项目型交付、应收账款和订单持续性。证据A。</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -2494,17 +2494,17 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>300499</t>
+          <t>300990</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>同飞股份</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>信息与通信液冷产品覆盖冷板、流体连接部件、CDU、TANK和换热单元，已形成冷板式和浸没式解决方案并具备批量供货能力；主板块保留数据中心液冷系统，风险是AIDC订单兑现、客户集中和盈利修复。证据A。</t>
+          <t>数据中心液冷方案覆盖CDU、Manifold、预制化管路、室外干冷器、集成冷站及浸没液冷箱体TANK，属于从工业温控切入AIDC液冷系统的直接映射；主板块保留数据中心液冷系统，背板空调和风墙作为过渡末端并入备注，风险是数据中心收入占比、订单连续性和项目毛利。证据A/B。</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -2521,17 +2521,17 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>002126</t>
+          <t>300499</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>银轮股份</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>热管理平台公司，年报披露数据中心水-液和水-风液冷模块产品，并作为服务器液冷机柜液冷模块部件供应商切入；主板块保留数据中心液冷系统，但AI数据中心收入占比仍需拆分，风险是汽车主业周期和数据中心业务验证。证据B。</t>
+          <t>信息与通信液冷产品覆盖冷板、流体连接部件、CDU、TANK和换热单元，已形成冷板式和浸没式解决方案并具备批量供货能力；主板块保留数据中心液冷系统，风险是AIDC订单兑现、客户集中和盈利修复。证据A。</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -2548,17 +2548,17 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>603912</t>
+          <t>002126</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>佳力图</t>
+          <t>银轮股份</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>数据中心温控底盘上拓展集装箱式液冷、液冷机柜、2MW级CDU和液冷整机柜测试环境，主板块保留数据中心液冷系统；风墙、冷源和模块化数据中心并入备注，不单列重复板块，风险是项目型订单、规模化交付和利润率。证据A/B。</t>
+          <t>热管理平台公司，年报披露数据中心水-液和水-风液冷模块产品，并作为服务器液冷机柜液冷模块部件供应商切入；主板块保留数据中心液冷系统，但AI数据中心收入占比仍需拆分，风险是汽车主业周期和数据中心业务验证。证据B。</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -2570,22 +2570,22 @@
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>数据中心液冷热管理</t>
+          <t>数据中心液冷系统</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>002050</t>
+          <t>603912</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>三花智控</t>
+          <t>佳力图</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露制冷空调与汽车热管理为主业，公开资料显示公司积极开拓数据中心等新应用，核心产品包括阀、泵、换热器等；原“服务器风扇”不准确，改为数据中心液冷热管理，短期利润仍主要来自传统主业。</t>
+          <t>数据中心温控底盘上拓展集装箱式液冷、液冷机柜、2MW级CDU和液冷整机柜测试环境，主板块保留数据中心液冷系统；风墙、冷源和模块化数据中心并入备注，不单列重复板块，风险是项目型订单、规模化交付和利润率。证据A/B。</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -2597,22 +2597,22 @@
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>液冷检测</t>
+          <t>数据中心液冷热管理</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>300657</t>
+          <t>002050</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>弘信电子</t>
+          <t>三花智控</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>液冷漏液监测FPC应用方案取得头部AI算力服务器散热客户订单并量产出货，是FPC主业在AI服务器液冷监测小件上的直接映射；主板块保留液冷检测，AI眼镜、具身智能和AI服务器FPC并入备注，风险是单品价值量、客户集中和持续订单。证据A/B。</t>
+          <t>证据中：2025年报披露制冷空调与汽车热管理为主业，公开资料显示公司积极开拓数据中心等新应用，核心产品包括阀、泵、换热器等；原“服务器风扇”不准确，改为数据中心液冷热管理，短期利润仍主要来自传统主业。</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -2629,17 +2629,17 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>301128</t>
+          <t>300657</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>强瑞技术</t>
+          <t>弘信电子</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>液冷服务器检测设备订单放量，同时完成集成化AI服务器高端GPU水冷散热系统研发，更偏制造/测试设备而非运行时液冷部件；主板块保留液冷检测，光模块散热并入备注，风险是项目收入波动和客户设备投资节奏。证据B。</t>
+          <t>液冷漏液监测FPC应用方案取得头部AI算力服务器散热客户订单并量产出货，是FPC主业在AI服务器液冷监测小件上的直接映射；主板块保留液冷检测，AI眼镜、具身智能和AI服务器FPC并入备注，风险是单品价值量、客户集中和持续订单。证据A/B。</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2651,22 +2651,22 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>数据中心冷源</t>
+          <t>液冷检测</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>300249</t>
+          <t>301128</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>依米康</t>
+          <t>强瑞技术</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>数据中心温控和机房环境解决方案底盘明确，液冷机柜、冷源和氟泵自然冷却等可受益AIDC热密度提升；主板块保留数据中心冷源，风险是财务质量、项目回款和液冷订单纯度。证据B。</t>
+          <t>液冷服务器检测设备订单放量，同时完成集成化AI服务器高端GPU水冷散热系统研发，更偏制造/测试设备而非运行时液冷部件；主板块保留液冷检测，光模块散热并入备注，风险是项目收入波动和客户设备投资节奏。证据B。</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -2678,22 +2678,22 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浸没式液冷冷却液</t>
+          <t>数据中心冷源</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>600160</t>
+          <t>300249</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>巨化股份</t>
+          <t>依米康</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>氟化工平台龙头，年报披露JX系列氟液含高性能电子冷却液和浸没式冷却液，是冷却液材料端较有产品证据的映射；主板块保留浸没式液冷冷却液，风险是冷板/CDU仍为主流、浸没式渗透和数据中心客户验证。证据A。</t>
+          <t>数据中心温控和机房环境解决方案底盘明确，液冷机柜、冷源和氟泵自然冷却等可受益AIDC热密度提升；主板块保留数据中心冷源，风险是财务质量、项目回款和液冷订单纯度。证据B。</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2710,17 +2710,17 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>605020</t>
+          <t>600160</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>永和股份</t>
+          <t>巨化股份</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>氟化工和含氟高分子材料平台可观察电子氟化液/浸没冷却液方向，但公开数据中心客户和订单证据弱于巨化；主板块暂保留浸没式液冷冷却液，风险是产品认证、产能投放和主题兑现不足。证据C。</t>
+          <t>氟化工平台龙头，年报披露JX系列氟液含高性能电子冷却液和浸没式冷却液，是冷却液材料端较有产品证据的映射；主板块保留浸没式液冷冷却液，风险是冷板/CDU仍为主流、浸没式渗透和数据中心客户验证。证据A。</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>603379</t>
+          <t>605020</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>三美股份</t>
+          <t>永和股份</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>制冷剂和氟化工基础较强，浸没式冷却液更多是含氟材料主题迁移观察，公开数据中心冷却液产品、客户和订单证据不足；主板块暂保留浸没式液冷冷却液但证据弱，风险是AI链条相关性和业务兑现。证据C。</t>
+          <t>氟化工和含氟高分子材料平台可观察电子氟化液/浸没冷却液方向，但公开数据中心客户和订单证据弱于巨化；主板块暂保留浸没式液冷冷却液，风险是产品认证、产能投放和主题兑现不足。证据C。</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2764,17 +2764,17 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>002407</t>
+          <t>603379</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>多氟多</t>
+          <t>三美股份</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>氟化工、电子信息材料和新能源材料平台，年报披露高性能无机氟化物、电子信息材料及半导体级氢氟酸产能，但未见数据中心浸没冷却液客户、订单或收入披露；主板块暂保留浸没式液冷冷却液作材料端观察，真实受益弱于已有冷却液产品证据更强的公司，风险是冷却液产品化、客户验证和锂电材料周期。证据C。</t>
+          <t>制冷剂和氟化工基础较强，浸没式冷却液更多是含氟材料主题迁移观察，公开数据中心冷却液产品、客户和订单证据不足；主板块暂保留浸没式液冷冷却液但证据弱，风险是AI链条相关性和业务兑现。证据C。</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -2786,22 +2786,22 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>AI服务器散热材料</t>
+          <t>浸没式液冷冷却液</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>300684</t>
+          <t>002407</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>中石科技</t>
+          <t>多氟多</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>热管理材料和组件平台，导热界面材料、石墨散热、VC/热模组已向服务器、数据中心和北美大客户交付，AI服务器热源到冷板界面的TIM/导热材料是直接受益节点；主板块保留AI服务器散热材料，EMI屏蔽和光模块散热并入备注，风险是客户集中、毛利率和单机价值量波动。证据A/B。</t>
+          <t>氟化工、电子信息材料和新能源材料平台，年报披露高性能无机氟化物、电子信息材料及半导体级氢氟酸产能，但未见数据中心浸没冷却液客户、订单或收入披露；主板块暂保留浸没式液冷冷却液作材料端观察，真实受益弱于已有冷却液产品证据更强的公司，风险是冷却液产品化、客户验证和锂电材料周期。证据C。</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -2818,17 +2818,17 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>300684</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>飞荣达</t>
+          <t>中石科技</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>热管理、电磁屏蔽和结构件平台，液冷板、热管/VC、散热模组、导热材料和EMI屏蔽可覆盖AI服务器散热与屏蔽一体化；主板块保留AI服务器散热材料，EMI屏蔽、AI服务器机柜和液冷管路并入备注，风险是液冷客户认证、项目毛利和消费电子/新能源业务拖累。证据B。</t>
+          <t>热管理材料和组件平台，导热界面材料、石墨散热、VC/热模组已向服务器、数据中心和北美大客户交付，AI服务器热源到冷板界面的TIM/导热材料是直接受益节点；主板块保留AI服务器散热材料，EMI屏蔽和光模块散热并入备注，风险是客户集中、毛利率和单机价值量波动。证据A/B。</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -2845,17 +2845,17 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>301489</t>
+          <t>300602</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>思泉新材</t>
+          <t>飞荣达</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>热管理材料和散热组件公司，公开资料披露拓展AI服务器、光模块等场景，并布局高导热界面材料、冷板、Manifold、CDU等方向；主板块保留AI服务器散热材料，光模块散热并入备注，当前仍偏导入/样品和产线建设，风险是量产订单、客户集中和收入兑现。证据B/C。</t>
+          <t>热管理、电磁屏蔽和结构件平台，液冷板、热管/VC、散热模组、导热材料和EMI屏蔽可覆盖AI服务器散热与屏蔽一体化；主板块保留AI服务器散热材料，EMI屏蔽、AI服务器机柜和液冷管路并入备注，风险是液冷客户认证、项目毛利和消费电子/新能源业务拖累。证据B。</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -2867,22 +2867,22 @@
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>TEC</t>
+          <t>AI服务器散热材料</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>688662</t>
+          <t>301489</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>富信科技</t>
+          <t>思泉新材</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>半导体热电器件公司，Micro TEC已在通信领域头部企业实现批量稳定供货，适合映射高速光模块温控小件；主板块保留TEC，风险是单品价值量、通信客户放量、消费/工业温控业务波动和盈利修复。证据B。</t>
+          <t>热管理材料和散热组件公司，公开资料披露拓展AI服务器、光模块等场景，并布局高导热界面材料、冷板、Manifold、CDU等方向；主板块保留AI服务器散热材料，光模块散热并入备注，当前仍偏导入/样品和产线建设，风险是量产订单、客户集中和收入兑现。证据B/C。</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -2894,22 +2894,22 @@
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>服务器液冷板</t>
+          <t>TEC</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>300731</t>
+          <t>688662</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>科创新源</t>
+          <t>富信科技</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露创源智热开展数据中心散热结构件业务，产品含液冷板、虹吸式散热模组，四季度在台系散热结构件厂商、云计算服务商等客户端取得突破；删减“液冷管路”重复行，AI服务器机柜降级为应用场景。</t>
+          <t>半导体热电器件公司，Micro TEC已在通信领域头部企业实现批量稳定供货，适合映射高速光模块温控小件；主板块保留TEC，风险是单品价值量、通信客户放量、消费/工业温控业务波动和盈利修复。证据B。</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -2921,22 +2921,22 @@
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>服务器风扇</t>
+          <t>服务器液冷板</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>301226</t>
+          <t>300731</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>祥明智能</t>
+          <t>科创新源</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>证据弱：2025年报披露公司主营微特电机、风机及智能化组件，服务HVACR、交通车辆、通信系统、医疗健康等行业；未见明确AI服务器客户或订单，暂保留服务器风扇观察位，真实弹性需看数据中心风机客户验证。</t>
+          <t>证据中强：2025年报披露创源智热开展数据中心散热结构件业务，产品含液冷板、虹吸式散热模组，四季度在台系散热结构件厂商、云计算服务商等客户端取得突破；删减“液冷管路”重复行，AI服务器机柜降级为应用场景。</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -2948,22 +2948,22 @@
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>数据中心液冷管路</t>
+          <t>服务器风扇</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>300547</t>
+          <t>301226</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>川环科技</t>
+          <t>祥明智能</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露AI大模型提升数据中心散热需求，公司液冷服务器管路达V0并获UL认证、进入多家供应商体系；仍以汽车管路为基本盘，保留数据中心液冷管路并提示放量节奏待验证。</t>
+          <t>证据弱：2025年报披露公司主营微特电机、风机及智能化组件，服务HVACR、交通车辆、通信系统、医疗健康等行业；未见明确AI服务器客户或订单，暂保留服务器风扇观察位，真实弹性需看数据中心风机客户验证。</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -2975,22 +2975,22 @@
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>数据中心液冷泵</t>
+          <t>数据中心液冷管路</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>002536</t>
+          <t>300547</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>飞龙股份</t>
+          <t>川环科技</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>定位：汽车热管理主业＋数据中心液冷泵小批量期权。2025年传统发动机热管理两类收入合计82.91%；“新能源汽车及民用液冷”合并收入6.73亿元、毛利率15.61%，不可当作AI液冷收入。公司称电子液冷泵/温控阀已供货，并通过日本、台湾伙伴获得匿名N/W/G项目，但客户名称、终端、订单额和北美属性均未披露，不能认定为NVIDIA、Google或北美AI液冷链。2026H1预告归母净利0.68—0.80亿元，同比下降61.98%—67.69%，并明确液冷仅个别客户部分项目小批量落地、收入占比低、对业绩影响很小。按2026-07-22收盘48.05元及预告更新TTM利润测算，PE约148—158倍，当前估值主要交易液冷预期。风险：汽车降价、汇率/关税、原料上涨、客户集中、液冷放量不及预期及股东减持。证据分层：产品与小批量订单A；匿名终端/北美AI链C；规模收入未兑现。来源：2025年报、2026H1业绩预告、2026-06-25异动公告、2026-03-27业绩说明会。</t>
+          <t>证据中：2025年报披露AI大模型提升数据中心散热需求，公司液冷服务器管路达V0并获UL认证、进入多家供应商体系；仍以汽车管路为基本盘，保留数据中心液冷管路并提示放量节奏待验证。</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -3002,25 +3002,25 @@
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>低介电电子布</t>
+          <t>数据中心液冷泵</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>002080</t>
+          <t>002536</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>中材科技</t>
+          <t>飞龙股份</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>泰山玻纤掌握低介电超细纱及纤维布、低膨胀纤维布、超低损耗低介电纤维布等技术，特种纤维布已获头部客户认证并批量供货；集团业务较宽，AI PCB弹性弱于纯电子布标的。证据A。</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="inlineStr">
+          <t>定位：汽车热管理主业＋数据中心液冷泵小批量期权。2025年传统发动机热管理两类收入合计82.91%；“新能源汽车及民用液冷”合并收入6.73亿元、毛利率15.61%，不可当作AI液冷收入。公司称电子液冷泵/温控阀已供货，并通过日本、台湾伙伴获得匿名N/W/G项目，但客户名称、终端、订单额和北美属性均未披露，不能认定为NVIDIA、Google或北美AI液冷链。2026H1预告归母净利0.68—0.80亿元，同比下降61.98%—67.69%，并明确液冷仅个别客户部分项目小批量落地、收入占比低、对业绩影响很小。按2026-07-22收盘48.05元及预告更新TTM利润测算，PE约148—158倍，当前估值主要交易液冷预期。风险：汽车降价、汇率/关税、原料上涨、客户集中、液冷放量不及预期及股东减持。证据分层：产品与小批量订单A；匿名终端/北美AI链C；规模收入未兑现。来源：2025年报、2026H1业绩预告、2026-06-25异动公告、2026-03-27业绩说明会。</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
         <is>
           <t>已处理</t>
         </is>
@@ -3034,22 +3034,22 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>603256</t>
+          <t>002080</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>宏和科技</t>
+          <t>中材科技</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>高端电子布纯度高，港交所申请版本披露低Dk/Df、低CTE和石英布路线，并进入GPU/CPU等核心供应链；主线保留低介电电子布，石英布作为未来项，风险是估值拥挤和客户脱敏。证据A。 2026-06-17 HVLP4/T-glass复核：放“交易弹性/高优先观察”，不是基本面主受益；公司Low Dk/Low CTE电子布相关度高，但官方追杀后，NVIDIA直签/寄售/提前一年锁产能仍未闭环；DIGITIMES只支持NVIDIA接洽Co-Tech讨论长期产能规划，仍需分布种收入、客户认证、交期/allocation和毛利兑现。</t>
+          <t>泰山玻纤掌握低介电超细纱及纤维布、低膨胀纤维布、超低损耗低介电纤维布等技术，特种纤维布已获头部客户认证并批量供货；集团业务较宽，AI PCB弹性弱于纯电子布标的。证据A。</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>已处理；2026-06-17证据分层；2026-06-17官方锁产追杀仍未闭环</t>
+          <t>已处理</t>
         </is>
       </c>
     </row>
@@ -3061,44 +3061,44 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>301526</t>
+          <t>603256</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>国际复材</t>
+          <t>宏和科技</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>玻纤与电子布平台，低介电LDK一代/二代、高频高速电子纤维布项目和满产/订单线索支撑AI PCB材料映射；需区分普通玻纤周期修复与高端低介电布的真实利润贡献。证据B。</t>
+          <t>高端电子布纯度高，港交所申请版本披露低Dk/Df、低CTE和石英布路线，并进入GPU/CPU等核心供应链；主线保留低介电电子布，石英布作为未来项，风险是估值拥挤和客户脱敏。证据A。 2026-06-17 HVLP4/T-glass复核：放“交易弹性/高优先观察”，不是基本面主受益；公司Low Dk/Low CTE电子布相关度高，但官方追杀后，NVIDIA直签/寄售/提前一年锁产能仍未闭环；DIGITIMES只支持NVIDIA接洽Co-Tech讨论长期产能规划，仍需分布种收入、客户认证、交期/allocation和毛利兑现。</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>已处理；2026-06-17证据分层；2026-06-17官方锁产追杀仍未闭环</t>
         </is>
       </c>
     </row>
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>电子级玻纤</t>
+          <t>低介电电子布</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>600176</t>
+          <t>301526</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>中国巨石</t>
+          <t>国际复材</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>电子布销量规模大，低介电、低膨胀等特种电子布研发/认证推进；但公司主体仍是玻纤规模龙头，AI高端电子布收入占比和客户硬证据弱于纯标的，主板块由低介电电子布降为电子级玻纤。证据B。</t>
+          <t>玻纤与电子布平台，低介电LDK一代/二代、高频高速电子纤维布项目和满产/订单线索支撑AI PCB材料映射；需区分普通玻纤周期修复与高端低介电布的真实利润贡献。证据B。</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -3110,54 +3110,54 @@
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>石英电子布</t>
+          <t>电子级玻纤</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>300395</t>
+          <t>600176</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>中国巨石</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>石英材料/纤维一体化延伸到超薄石英电子布，2025年石英电子布收入9837.37万元，仍处客户端小批量测试和终端认证；主板块由低介电电子布细化为石英电子布，半导体石英材料作为基本面支撑放备注，不再单列AI主板块；风险是收入占比小和订单不确定。证据A/B。 2026-06-28 光纤上游补充：除石英电子布外，光通信/半导体石英材料可延伸到光纤预制棒支撑棒、把手棒、厚壁管、炉芯管等；与长盈通推进光纤配套衬管/套管项目，作为光棒上游高纯石英制品观察，不等同石英电子布主线。</t>
+          <t>电子布销量规模大，低介电、低膨胀等特种电子布研发/认证推进；但公司主体仍是玻纤规模龙头，AI高端电子布收入占比和客户硬证据弱于纯标的，主板块由低介电电子布降为电子级玻纤。证据B。</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>已处理；2026-06-28 光纤上游补充</t>
+          <t>已处理</t>
         </is>
       </c>
     </row>
     <row r="76" ht="75" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>高端高速铜箔</t>
+          <t>石英电子布</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>301511</t>
+          <t>300395</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>德福科技</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>2026H1正式中报（未经审计）：营收91.97亿元、归母2.63亿元、经营现金流-6.13亿元；电子电路铜箔收入13.08亿元、毛利率4.85%；应收/存货35.84/26.80亿元，年初34.44/18.72亿元。H1启动5万吨AI高端电子电路铜箔项目（完全达产后年产5万吨为规划，非已达产）。HVLP/RTF/载体铜箔的客户、订单、独立收入/毛利及认证范围=evidence_absent。证据A：CNINFO 2026-08-22。</t>
+          <t>石英材料/纤维一体化延伸到超薄石英电子布，2025年石英电子布收入9837.37万元，仍处客户端小批量测试和终端认证；主板块由低介电电子布细化为石英电子布，半导体石英材料作为基本面支撑放备注，不再单列AI主板块；风险是收入占比小和订单不确定。证据A/B。 2026-06-28 光纤上游补充：除石英电子布外，光通信/半导体石英材料可延伸到光纤预制棒支撑棒、把手棒、厚壁管、炉芯管等；与长盈通推进光纤配套衬管/套管项目，作为光棒上游高纯石英制品观察，不等同石英电子布主线。</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>已处理；2026-08-22正式中报复核（未经审计）</t>
+          <t>已处理；2026-06-28 光纤上游补充</t>
         </is>
       </c>
     </row>
@@ -3169,22 +3169,22 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>301217</t>
+          <t>301511</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>铜冠铜箔</t>
+          <t>德福科技</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>2026H1业绩预告：预计归母净利润2.05—2.25亿元（同比+486.49%—543.70%），扣非净利润2.00—2.20亿元（同比+724.05%—806.45%）；公司明确称聚焦头部客户需求，高频高速铜箔供不应求、销量同比增长，高附加值产品占比与加工费收入提升，降本带动毛利率改善，支持AI PCB材料景气已通过销量、结构和加工费进入利润表。仍未拆分HVLP代际、AI客户/收入占比及单吨加工费，且高频高速铜箔不等同全部AI收入；继续跟踪半年报分产品毛利和经营现金流。证据A。</t>
+          <t>2026H1正式中报（未经审计）：营收91.97亿元、归母2.63亿元、经营现金流-6.13亿元；电子电路铜箔收入13.08亿元、毛利率4.85%；应收/存货35.84/26.80亿元，年初34.44/18.72亿元。H1启动5万吨AI高端电子电路铜箔项目（完全达产后年产5万吨为规划，非已达产）。HVLP/RTF/载体铜箔的客户、订单、独立收入/毛利及认证范围=evidence_absent。证据A：CNINFO 2026-08-22。</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>已处理；2026-08-22正式中报复核（未经审计）</t>
         </is>
       </c>
     </row>
@@ -3196,17 +3196,17 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>600110</t>
+          <t>301217</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>诺德股份</t>
+          <t>铜冠铜箔</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>铜箔主业平台，布局HVLP、IC载板铜箔和高端电子标箔，但高附加值产品仍处市场导入期且公司2025年仍亏损；保留高端铜箔观察，不上调为HVLP主线，风险是盈利、现金流和客户验证不足。证据B。</t>
+          <t>2026H1业绩预告：预计归母净利润2.05—2.25亿元（同比+486.49%—543.70%），扣非净利润2.00—2.20亿元（同比+724.05%—806.45%）；公司明确称聚焦头部客户需求，高频高速铜箔供不应求、销量同比增长，高附加值产品占比与加工费收入提升，降本带动毛利率改善，支持AI PCB材料景气已通过销量、结构和加工费进入利润表。仍未拆分HVLP代际、AI客户/收入占比及单吨加工费，且高频高速铜箔不等同全部AI收入；继续跟踪半年报分产品毛利和经营现金流。证据A。</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -3223,17 +3223,17 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>688388</t>
+          <t>600110</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>嘉元科技</t>
+          <t>诺德股份</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>铜箔规模平台，围绕AI算力、IC载板等方向布局RTF、HVLP、载体铜箔等高端产品，2025经营修复；当前AI PCB客户批量、收入占比和毛利率证据仍弱，定位高端铜箔观察。证据B。</t>
+          <t>铜箔主业平台，布局HVLP、IC载板铜箔和高端电子标箔，但高附加值产品仍处市场导入期且公司2025年仍亏损；保留高端铜箔观察，不上调为HVLP主线，风险是盈利、现金流和客户验证不足。证据B。</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -3245,22 +3245,22 @@
     <row r="80" ht="36" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>载体铜箔</t>
+          <t>高端高速铜箔</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>688020</t>
+          <t>688388</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>方邦股份</t>
+          <t>嘉元科技</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>可剥离超薄载体铜箔面向IC载板/先进封装，部分规格通过载板厂和终端客户认证并持续小批量订单；主板块由高端铜箔改为载体铜箔，EMI屏蔽降级为非AI主线，不再单列，风险是规模收入和盈利兑现仍小。证据B。</t>
+          <t>铜箔规模平台，围绕AI算力、IC载板等方向布局RTF、HVLP、载体铜箔等高端产品，2025经营修复；当前AI PCB客户批量、收入占比和毛利率证据仍弱，定位高端铜箔观察。证据B。</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -3272,25 +3272,25 @@
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>高速电子树脂</t>
+          <t>载体铜箔</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>605589</t>
+          <t>688020</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>圣泉集团</t>
+          <t>方邦股份</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>电子级PPO/OPE/碳氢树脂等先进电子材料用于高频高速覆铜板，年报披露已与国际龙头及头部PCB/CCL厂联合开发与批量供货，应用于服务器、高速通信和AI算力设备；主板块保留高速电子树脂，风险是产能释放、价格和客户认证节奏。证据A。</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
+          <t>可剥离超薄载体铜箔面向IC载板/先进封装，部分规格通过载板厂和终端客户认证并持续小批量订单；主板块由高端铜箔改为载体铜箔，EMI屏蔽降级为非AI主线，不再单列，风险是规模收入和盈利兑现仍小。证据B。</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>已处理</t>
         </is>
@@ -3304,17 +3304,17 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>601208</t>
+          <t>605589</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>东材科技</t>
+          <t>圣泉集团</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>高性能电子树脂供应商定位明确，年报摘要披露联合开发适配高频、高速、高耐热、高导热覆铜板材料，并拓展新一代服务器等领域；主板块保留高速电子树脂，风险是高端品收入占比、客户认证和材料价格波动。证据B。</t>
+          <t>电子级PPO/OPE/碳氢树脂等先进电子材料用于高频高速覆铜板，年报披露已与国际龙头及头部PCB/CCL厂联合开发与批量供货，应用于服务器、高速通信和AI算力设备；主板块保留高速电子树脂，风险是产能释放、价格和客户认证节奏。证据A。</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>603002</t>
+          <t>601208</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>宏昌电子</t>
+          <t>东材科技</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>环氧树脂+覆铜板双主业，低介电聚醚树脂、无卤阻燃树脂和高频高速覆铜板可适配高端服务器与5G通信设备；主板块保留高速电子树脂，AI链条证据强于普通环氧但仍需看高端材料批量导入和利润率。证据B。</t>
+          <t>高性能电子树脂供应商定位明确，年报摘要披露联合开发适配高频、高速、高耐热、高导热覆铜板材料，并拓展新一代服务器等领域；主板块保留高速电子树脂，风险是高端品收入占比、客户认证和材料价格波动。证据B。</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -3358,17 +3358,17 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>300481</t>
+          <t>603002</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>濮阳惠成</t>
+          <t>宏昌电子</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>主营顺酐酸酐衍生物、功能材料中间体，应用于电子元器件封装、电气绝缘等；与AI高速CCL更偏上游配方材料观察，不直接等同核心高频高速树脂，主板块暂保留高速电子树脂但证据较弱，风险是利润下滑和AI收入不可见。证据C。</t>
+          <t>环氧树脂+覆铜板双主业，低介电聚醚树脂、无卤阻燃树脂和高频高速覆铜板可适配高端服务器与5G通信设备；主板块保留高速电子树脂，AI链条证据强于普通环氧但仍需看高端材料批量导入和利润率。证据B。</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -3380,27 +3380,27 @@
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>高端高速CCL</t>
+          <t>高速电子树脂</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>688519</t>
+          <t>300481</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>南亚新材</t>
+          <t>濮阳惠成</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>高频高速覆铜板主线，AI服务器/光模块用高速板材料明确，M8/M9/M10升级看客户认证、订单能见度和涨价传导；封装基板材料并入备注，不再单列主板块。证据B。2026-06-16 JPM补充：报告提示HPC CCL/PCB TAM由AI server、常规server、LEO共同推升，CCL TAM可按2.5-3倍近似外推PCB TAM，M9升级和载板用Q glass是新增验证方向；仍按B级卖方估算处理，需看分产品lead time、涨价、客户认证和收入毛利。</t>
+          <t>主营顺酐酸酐衍生物、功能材料中间体，应用于电子元器件封装、电气绝缘等；与AI高速CCL更偏上游配方材料观察，不直接等同核心高频高速树脂，主板块暂保留高速电子树脂但证据较弱，风险是利润下滑和AI收入不可见。证据C。</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>已处理；2026-06-16 JPM补充</t>
+          <t>已处理</t>
         </is>
       </c>
     </row>
@@ -3412,22 +3412,22 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>600183</t>
+          <t>688519</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>生益科技</t>
+          <t>南亚新材</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>大陆CCL龙头，高速覆铜板、封装材料和客户覆盖最完整，是AI服务器高速PCB与M9/M10材料升级的稳健映射；主板块保留高端高速CCL，封装基板材料放备注，风险是周期、价格传导和高端占比。证据A/B。2026-06-16 JPM补充：报告强化M8/M9高端CCL、HPC CCL与载板用CCL/Q glass需求，支持高端高速CCL soft_bottleneck+；但不能替代公司分产品订单、涨价和客户锁料证据。 2026-06-17 HVLP4/T-glass复核：放“基本面主受益/质量锚”；高速CCL/prepreg是板级PCB材料主线最稳映射，但NVIDIA M9独家/直供/锁产等说法在官方追杀后仍未闭环，仍需公司、客户或正式供应链文件确认。</t>
+          <t>高频高速覆铜板主线，AI服务器/光模块用高速板材料明确，M8/M9/M10升级看客户认证、订单能见度和涨价传导；封装基板材料并入备注，不再单列主板块。证据B。2026-06-16 JPM补充：报告提示HPC CCL/PCB TAM由AI server、常规server、LEO共同推升，CCL TAM可按2.5-3倍近似外推PCB TAM，M9升级和载板用Q glass是新增验证方向；仍按B级卖方估算处理，需看分产品lead time、涨价、客户认证和收入毛利。</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>已处理；2026-06-16 JPM补充；2026-06-17证据分层；2026-06-17官方锁产追杀仍未闭环</t>
+          <t>已处理；2026-06-16 JPM补充</t>
         </is>
       </c>
     </row>
@@ -3439,22 +3439,22 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>603186</t>
+          <t>600183</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>华正新材</t>
+          <t>生益科技</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>高频高速覆铜板和复合材料布局明确，服务器、交换机、光模块材料需求带来弹性；主板块保留高端高速CCL，封装基板材料降级并入备注，风险是客户和收入拆分弱于龙头。证据B。</t>
+          <t>大陆CCL龙头，高速覆铜板、封装材料和客户覆盖最完整，是AI服务器高速PCB与M9/M10材料升级的稳健映射；主板块保留高端高速CCL，封装基板材料放备注，风险是周期、价格传导和高端占比。证据A/B。2026-06-16 JPM补充：报告强化M8/M9高端CCL、HPC CCL与载板用CCL/Q glass需求，支持高端高速CCL soft_bottleneck+；但不能替代公司分产品订单、涨价和客户锁料证据。 2026-06-17 HVLP4/T-glass复核：放“基本面主受益/质量锚”；高速CCL/prepreg是板级PCB材料主线最稳映射，但NVIDIA M9独家/直供/锁产等说法在官方追杀后仍未闭环，仍需公司、客户或正式供应链文件确认。</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>已处理；2026-06-16 JPM补充；2026-06-17证据分层；2026-06-17官方锁产追杀仍未闭环</t>
         </is>
       </c>
     </row>
@@ -3466,49 +3466,49 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>300936</t>
+          <t>603186</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>中英科技</t>
+          <t>华正新材</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>小市值高频高速覆铜板标的，AI服务器高速PCB/CCL需求可带来弹性；主板块保留高端高速CCL，核心看量产规模、客户结构和盈利修复，证据强度弱于生益/南亚。证据B/C。 2026-06-17 HVLP4/T-glass复核：放“仅观察/PTFE-M10相邻线索”；PTFE高频覆铜板不属于HVLP4铜箔或T-glass直签锁产能主线，需AI server/M9-M10客户认证、量产收入和毛利证据后再上调。</t>
+          <t>高频高速覆铜板和复合材料布局明确，服务器、交换机、光模块材料需求带来弹性；主板块保留高端高速CCL，封装基板材料降级并入备注，风险是客户和收入拆分弱于龙头。证据B。</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>已处理；2026-06-17证据分层；2026-06-17官方锁产追杀仍未闭环</t>
+          <t>已处理</t>
         </is>
       </c>
     </row>
     <row r="89" ht="16.5" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>AI服务器高速PCB</t>
+          <t>高端高速CCL</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>300936</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>中英科技</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>高速通信/AI服务器PCB主线，数据中心交换机、服务器、加速卡等高多层高速板客户和产品验证最直接；主板块保留AI服务器高速PCB，风险是大客户节奏、毛利年降和扩产良率。证据A。2026-06-16 JPM补充：报告强调AI switch层数提升、HDI良率下降和M9升级可能使高层高速PCB供给落后需求，强化需求侧和复杂度证据；仍不证明具体客户订单或交期失控。</t>
+          <t>小市值高频高速覆铜板标的，AI服务器高速PCB/CCL需求可带来弹性；主板块保留高端高速CCL，核心看量产规模、客户结构和盈利修复，证据强度弱于生益/南亚。证据B/C。 2026-06-17 HVLP4/T-glass复核：放“仅观察/PTFE-M10相邻线索”；PTFE高频覆铜板不属于HVLP4铜箔或T-glass直签锁产能主线，需AI server/M9-M10客户认证、量产收入和毛利证据后再上调。</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>已处理；2026-06-16 JPM补充</t>
+          <t>已处理；2026-06-17证据分层；2026-06-17官方锁产追杀仍未闭环</t>
         </is>
       </c>
     </row>
@@ -3520,22 +3520,22 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>002916</t>
+          <t>002463</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>深南电路</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>PCB综合龙头，AI服务器/高速互连PCB与FC-BGA/BT载板能力共振；2026-06-16 ABF/IC载板复核后定位为“基本面质量锚”：深南电路具备数据中心PCB、封装基板平台和FC-BGA研发/打样能力，但不能直接写成NVIDIA/AMD高端GPU ABF载板订单。主板块保留AI服务器高速PCB，ABF/IC载板放备注跟踪，风险是封装基板收入占比、24层及以上进度、客户放量和毛利兑现。证据A/B。2026-06-16 JPM补充：报告估算IC载板UTR在2027e超过100%、AI server &amp; switch面积需求2028e占比75%，强化FC-BGA/ABF独立跟踪；深南仍需24层以上FC-BGA进展、大客户订单、收入和毛利验证。</t>
+          <t>高速通信/AI服务器PCB主线，数据中心交换机、服务器、加速卡等高多层高速板客户和产品验证最直接；主板块保留AI服务器高速PCB，风险是大客户节奏、毛利年降和扩产良率。证据A。2026-06-16 JPM补充：报告强调AI switch层数提升、HDI良率下降和M9升级可能使高层高速PCB供给落后需求，强化需求侧和复杂度证据；仍不证明具体客户订单或交期失控。</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>已处理；2026-06-16复核；2026-06-16 JPM补充</t>
+          <t>已处理；2026-06-16 JPM补充</t>
         </is>
       </c>
     </row>
@@ -3547,22 +3547,22 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>300476</t>
+          <t>002916</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>胜宏科技</t>
+          <t>深南电路</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>高多层PCB、HDI和AI服务器/交换机PCB是最直接主线，年报披露AI服务器相关HDI及18层以上多层板高景气，并强调深度绑定国际头部客户；主板块保留AI服务器高速PCB，风险是大客户集中、扩产良率和海外交付节奏。证据A/B。2026-06-16 JPM补充：报告从AI switch、midplane/HDI和高层PCB良率角度强化AI PCB价值量与制造难度，支持胜宏高层高速板需求侧；风险仍是扩产良率、客户集中和毛利年降。</t>
+          <t>PCB综合龙头，AI服务器/高速互连PCB与FC-BGA/BT载板能力共振；2026-06-16 ABF/IC载板复核后定位为“基本面质量锚”：深南电路具备数据中心PCB、封装基板平台和FC-BGA研发/打样能力，但不能直接写成NVIDIA/AMD高端GPU ABF载板订单。主板块保留AI服务器高速PCB，ABF/IC载板放备注跟踪，风险是封装基板收入占比、24层及以上进度、客户放量和毛利兑现。证据A/B。2026-06-16 JPM补充：报告估算IC载板UTR在2027e超过100%、AI server &amp; switch面积需求2028e占比75%，强化FC-BGA/ABF独立跟踪；深南仍需24层以上FC-BGA进展、大客户订单、收入和毛利验证。</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>已处理；2026-06-16 JPM补充</t>
+          <t>已处理；2026-06-16复核；2026-06-16 JPM补充</t>
         </is>
       </c>
     </row>
@@ -3574,17 +3574,17 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>688183</t>
+          <t>300476</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>生益电子</t>
+          <t>胜宏科技</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>AI服务器、OAM、UBB等高端PCB已大规模量产，2025年AI算力相关产品同比高增，是PCB环节纯度较高的标的；主板块保留AI服务器高速PCB，BT载板并入备注后不单列，风险是客户集中、产能爬坡和高端良率。证据A。2026-06-16 JPM补充：报告强化AI server/switch PCB复杂度与高端CCL需求，对生益电子的AI服务器、OAM、UBB等高端PCB形成需求侧佐证；仍需跟踪客户、毛利和产能爬坡。</t>
+          <t>高多层PCB、HDI和AI服务器/交换机PCB是最直接主线，年报披露AI服务器相关HDI及18层以上多层板高景气，并强调深度绑定国际头部客户；主板块保留AI服务器高速PCB，风险是大客户集中、扩产良率和海外交付节奏。证据A/B。2026-06-16 JPM补充：报告从AI switch、midplane/HDI和高层PCB良率角度强化AI PCB价值量与制造难度，支持胜宏高层高速板需求侧；风险仍是扩产良率、客户集中和毛利年降。</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -3601,22 +3601,22 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>002938</t>
+          <t>688183</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>鹏鼎控股</t>
+          <t>生益电子</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>全球PCB平台型龙头，年报将AI服务器、光模块等核心产品列为重点提升方向，FPC/SLP/HDI/RPCB平台有云-管-端协同；主板块保留AI服务器高速PCB，FC-BGA和AI服务器FPC并入备注，风险是消费电子占比高、AI收入拆分仍不够透明。证据B。</t>
+          <t>AI服务器、OAM、UBB等高端PCB已大规模量产，2025年AI算力相关产品同比高增，是PCB环节纯度较高的标的；主板块保留AI服务器高速PCB，BT载板并入备注后不单列，风险是客户集中、产能爬坡和高端良率。证据A。2026-06-16 JPM补充：报告强化AI server/switch PCB复杂度与高端CCL需求，对生益电子的AI服务器、OAM、UBB等高端PCB形成需求侧佐证；仍需跟踪客户、毛利和产能爬坡。</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>已处理；2026-06-16 JPM补充</t>
         </is>
       </c>
     </row>
@@ -3628,17 +3628,17 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>603228</t>
+          <t>002938</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>景旺电子</t>
+          <t>鹏鼎控股</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露AI服务器PCB经过多年蓄势后规模出货，高阶HDI、Birchstream平台高速PCB、PTFE刚挠结合板、高速FPC、1.6T光模块PCB等实现量产或突破；主板块由AI服务器FPC修正为覆盖业绩弹性的AI服务器PCB。</t>
+          <t>全球PCB平台型龙头，年报将AI服务器、光模块等核心产品列为重点提升方向，FPC/SLP/HDI/RPCB平台有云-管-端协同；主板块保留AI服务器高速PCB，FC-BGA和AI服务器FPC并入备注，风险是消费电子占比高、AI收入拆分仍不够透明。证据B。</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -3650,22 +3650,22 @@
     <row r="95" ht="16.5" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>PCB设备</t>
+          <t>AI服务器高速PCB</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>301200</t>
+          <t>603228</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>大族数控</t>
+          <t>景旺电子</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>PCB专用设备龙头，覆盖钻孔、成型、曝光、检测等关键工序；2025财务决算披露受AI服务器、高速交换机高多层板和高多层HDI扩产驱动，营收57.73亿元、同比增长72.68%，净利润同比增长173.68%。主板块改为PCB专用设备，PCB AOI和高多层PCB加工耗材并入备注，风险是下游扩产周期、客户集中和海外产能兑现。证据A。</t>
+          <t>证据强：2025年报披露AI服务器PCB经过多年蓄势后规模出货，高阶HDI、Birchstream平台高速PCB、PTFE刚挠结合板、高速FPC、1.6T光模块PCB等实现量产或突破；主板块由AI服务器FPC修正为覆盖业绩弹性的AI服务器PCB。</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -3682,17 +3682,17 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>688630</t>
+          <t>301200</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>芯碁微装</t>
+          <t>大族数控</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>直写光刻平台公司，2025年报披露在PCB领域主要应用于线路层和阻焊层曝光，2024年已成为全球最大PCB直接成像设备制造商，并布局激光钻孔设备；AI高多层/HDI和封装基板升级提升LDI门槛。主板块由PCB设备细化为PCB直接成像设备，风险是产能交付、海外竞争和泛半导体新业务兑现。证据A。</t>
+          <t>PCB专用设备龙头，覆盖钻孔、成型、曝光、检测等关键工序；2025财务决算披露受AI服务器、高速交换机高多层板和高多层HDI扩产驱动，营收57.73亿元、同比增长72.68%，净利润同比增长173.68%。主板块改为PCB专用设备，PCB AOI和高多层PCB加工耗材并入备注，风险是下游扩产周期、客户集中和海外产能兑现。证据A。</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -3709,17 +3709,17 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>002008</t>
+          <t>688630</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>芯碁微装</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>激光装备平台，2025年报披露AI算力PCB是未来PCB产业主要方向，CCD六轴钻孔、CO2/新型激光钻孔等方案已完成下一代AI服务器PCB加工认证并在多家高多层板龙头量产；主板块保留PCB设备，需注意与大族数控业务重叠和集团平台口径，风险是PCB设备周期、新能源设备波动和费用投入。证据A。</t>
+          <t>直写光刻平台公司，2025年报披露在PCB领域主要应用于线路层和阻焊层曝光，2024年已成为全球最大PCB直接成像设备制造商，并布局激光钻孔设备；AI高多层/HDI和封装基板升级提升LDI门槛。主板块由PCB设备细化为PCB直接成像设备，风险是产能交付、海外竞争和泛半导体新业务兑现。证据A。</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -3736,17 +3736,17 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>688170</t>
+          <t>002008</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>德龙激光</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>精密激光加工设备公司，2025年报披露PCB/FPC激光切割钻孔解决方案可加工AI服务器HDI高频材料、IC载板ABF膜、陶瓷基板和BT树脂等高端基板；主板块改为PCB激光加工设备，先进封装切割并入备注，风险是收入规模、客户量产验证和利润修复持续性。证据B。</t>
+          <t>激光装备平台，2025年报披露AI算力PCB是未来PCB产业主要方向，CCD六轴钻孔、CO2/新型激光钻孔等方案已完成下一代AI服务器PCB加工认证并在多家高多层板龙头量产；主板块保留PCB设备，需注意与大族数控业务重叠和集团平台口径，风险是PCB设备周期、新能源设备波动和费用投入。证据A。</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -3763,17 +3763,17 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>300802</t>
+          <t>688170</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>矩子科技</t>
+          <t>德龙激光</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>机器视觉设备公司，AOI、SPI等产品检测速度、精度和检出率为核心竞争力，可受益高层高密PCB良率控制需求；主板块保留PCB AOI，先进封装X-Ray并入备注降级，风险是AI PCB客户与收入占比披露不足、消费电子和海外订单波动。证据B/C。</t>
+          <t>精密激光加工设备公司，2025年报披露PCB/FPC激光切割钻孔解决方案可加工AI服务器HDI高频材料、IC载板ABF膜、陶瓷基板和BT树脂等高端基板；主板块改为PCB激光加工设备，先进封装切割并入备注，风险是收入规模、客户量产验证和利润修复持续性。证据B。</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3790,17 +3790,17 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>688700</t>
+          <t>300802</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>东威科技</t>
+          <t>矩子科技</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>PCB电镀设备龙头，2025年业绩预告/年报信息显示受PCB东南亚投资潮、AI和算力领域发展带动，PCB电镀设备订单持续增长；垂直连续电镀、水平三合一和VCP覆盖服务器、云存储、高阶HDI及IC载板。主板块保留PCB电镀设备，风险是订单交付、海外扩产节奏和新能源电镀业务波动。证据A/B。</t>
+          <t>机器视觉设备公司，AOI、SPI等产品检测速度、精度和检出率为核心竞争力，可受益高层高密PCB良率控制需求；主板块保留PCB AOI，先进封装X-Ray并入备注降级，风险是AI PCB客户与收入占比披露不足、消费电子和海外订单波动。证据B/C。</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3812,22 +3812,22 @@
     <row r="101" ht="16.5" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>PCB钻针</t>
+          <t>PCB设备</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>301377</t>
+          <t>688700</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>鼎泰高科</t>
+          <t>东威科技</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>PCB钻针和精密刀具龙头，2025年报披露受PCB基材硬化、板厚增加和布线密集化推动，微小径钻针、高长径比钻针和高端涂层钻针占比提升，0.20mm及以下微钻销量占比29.65%、涂层钻针39.40%。主板块保留PCB钻针，高多层PCB加工耗材并入备注，风险是估值拥挤、扩产消化和价格竞争。证据A。</t>
+          <t>PCB电镀设备龙头，2025年业绩预告/年报信息显示受PCB东南亚投资潮、AI和算力领域发展带动，PCB电镀设备订单持续增长；垂直连续电镀、水平三合一和VCP覆盖服务器、云存储、高阶HDI及IC载板。主板块保留PCB电镀设备，风险是订单交付、海外扩产节奏和新能源电镀业务波动。证据A/B。</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3844,17 +3844,17 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>000657</t>
+          <t>301377</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>中钨高新</t>
+          <t>鼎泰高科</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>硬质合金和钨材料平台，通过金洲公司切入PCB精密微型钻头及刀具；公告披露新增AI PCB用超长径精密微型刀具产能，并继续扩产印制电路板用高端微型精密刀具，匹配AI专用PCB层数多、厚度大、材料硬度高导致的钻孔刀具升级需求。主板块改为PCB钻针，PCB微型精密刀具/高端微钻/AI PCB超长径刀具并入备注，风险是金洲业务占比、扩产达产和钨价周期。证据A/B。</t>
+          <t>PCB钻针和精密刀具龙头，2025年报披露受PCB基材硬化、板厚增加和布线密集化推动，微小径钻针、高长径比钻针和高端涂层钻针占比提升，0.20mm及以下微钻销量占比29.65%、涂层钻针39.40%。主板块保留PCB钻针，高多层PCB加工耗材并入备注，风险是估值拥挤、扩产消化和价格竞争。证据A。</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3866,22 +3866,22 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>PCB湿化学</t>
+          <t>PCB钻针</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>688603</t>
+          <t>000657</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>天承科技</t>
+          <t>中钨高新</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>PCB专用电子化学品公司，产品覆盖沉铜、电镀、表面处理和棕化等湿制程，高层高密AI PCB、mSAP和封装基板升级提高药水纯度和工艺门槛；主板块保留PCB湿化学，风险是客户扩产周期、原料价格和海外市场验证。证据A。</t>
+          <t>硬质合金和钨材料平台，通过金洲公司切入PCB精密微型钻头及刀具；公告披露新增AI PCB用超长径精密微型刀具产能，并继续扩产印制电路板用高端微型精密刀具，匹配AI专用PCB层数多、厚度大、材料硬度高导致的钻孔刀具升级需求。主板块改为PCB钻针，PCB微型精密刀具/高端微钻/AI PCB超长径刀具并入备注，风险是金洲业务占比、扩产达产和钨价周期。证据A/B。</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3898,17 +3898,17 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>002741</t>
+          <t>688603</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>光华科技</t>
+          <t>天承科技</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>PCB化学品和电镀化学品平台，覆盖沉铜、电镀和表面处理等工序，可受益高端PCB湿制程材料国产替代；主板块保留PCB湿化学，但AI高多层板客户和高端产品占比证据弱于天承科技，风险是业务平台分散、毛利率和客户认证。证据B/C。</t>
+          <t>PCB专用电子化学品公司，产品覆盖沉铜、电镀、表面处理和棕化等湿制程，高层高密AI PCB、mSAP和封装基板升级提高药水纯度和工艺门槛；主板块保留PCB湿化学，风险是客户扩产周期、原料价格和海外市场验证。证据A。</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3920,22 +3920,22 @@
     <row r="105" ht="36" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>PCB光刻胶</t>
+          <t>PCB湿化学</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>300537</t>
+          <t>002741</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>广信材料</t>
+          <t>光华科技</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>感光材料平台，PCB阻焊油墨、湿膜/干膜光刻胶和电子材料是主线，AI高多层PCB图形精度提升带来材料升级观察；主板块由PCB湿化学改为PCB光刻胶，干膜并入备注，风险是高端PCB客户验证、国产替代进度和盈利修复。证据B/C。</t>
+          <t>PCB化学品和电镀化学品平台，覆盖沉铜、电镀和表面处理等工序，可受益高端PCB湿制程材料国产替代；主板块保留PCB湿化学，但AI高多层板客户和高端产品占比证据弱于天承科技，风险是业务平台分散、毛利率和客户认证。证据B/C。</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3952,17 +3952,17 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>300576</t>
+          <t>300537</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>容大感光</t>
+          <t>广信材料</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>PCB光刻胶为收入基本盘，液态阻焊/线路油墨确定性强，感光干膜是增量方向；AI高多层PCB带来图形精度和材料升级需求，但公司不是AI服务器部件直接供应商。主板块由干膜收敛为PCB光刻胶，干膜并入备注，风险是产品价格、客户认证和半导体/显示光刻胶放量不及预期。证据B。</t>
+          <t>感光材料平台，PCB阻焊油墨、湿膜/干膜光刻胶和电子材料是主线，AI高多层PCB图形精度提升带来材料升级观察；主板块由PCB湿化学改为PCB光刻胶，干膜并入备注，风险是高端PCB客户验证、国产替代进度和盈利修复。证据B/C。</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3974,22 +3974,22 @@
     <row r="107" ht="36" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>FPC测试设备</t>
+          <t>PCB光刻胶</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>688312</t>
+          <t>300576</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>燕麦科技</t>
+          <t>容大感光</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>FPC自动化测试设备供应商，年报披露核心仍是FPC/FPCA后段测试、组装和智能化设备；AI服务器高多层PCB检测证据不足，主板块由PCB AOI收窄为FPC测试设备，硅光/半导体测试仍属于待放量观察，风险是消费电子客户集中、新项目量产和AI链条相关性偏弱。证据B/C。</t>
+          <t>PCB光刻胶为收入基本盘，液态阻焊/线路油墨确定性强，感光干膜是增量方向；AI高多层PCB带来图形精度和材料升级需求，但公司不是AI服务器部件直接供应商。主板块由干膜收敛为PCB光刻胶，干膜并入备注，风险是产品价格、客户认证和半导体/显示光刻胶放量不及预期。证据B。</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -4001,22 +4001,22 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>高性能铜合金</t>
+          <t>FPC测试设备</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>601137</t>
+          <t>688312</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>博威合金</t>
+          <t>燕麦科技</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>证据中：公司高性能合金材料下游覆盖新能源汽车、算力服务器、智能手机和半导体芯片等，高强高导铜合金可映射引线框架、连接器和热管理材料；原“引线框架”过窄，改为材料端主板块。风险是2025年净利大幅下滑，新能源资产减值/海外政策扰动拖累整体基本面。</t>
+          <t>FPC自动化测试设备供应商，年报披露核心仍是FPC/FPCA后段测试、组装和智能化设备；AI服务器高多层PCB检测证据不足，主板块由PCB AOI收窄为FPC测试设备，硅光/半导体测试仍属于待放量观察，风险是消费电子客户集中、新项目量产和AI链条相关性偏弱。证据B/C。</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -4033,17 +4033,17 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>002171</t>
+          <t>601137</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>楚江新材</t>
+          <t>博威合金</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露公司聚焦新能源、5G通信、智能网联、机器人及AI算力等高增长赛道，精密铜带已批量应用于屏蔽罩、高速连接器、集成电路引线框架等关键部件；原“引线框架”过窄，调整为材料端主板块，AI弹性取决于高速连接器/服务器线缆等高端铜材放量。</t>
+          <t>证据中：公司高性能合金材料下游覆盖新能源汽车、算力服务器、智能手机和半导体芯片等，高强高导铜合金可映射引线框架、连接器和热管理材料；原“引线框架”过窄，改为材料端主板块。风险是2025年净利大幅下滑，新能源资产减值/海外政策扰动拖累整体基本面。</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -4055,22 +4055,22 @@
     <row r="110" ht="36" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>高速铜互连</t>
+          <t>高性能铜合金</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>300913</t>
+          <t>002171</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>兆龙互连</t>
+          <t>楚江新材</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>高速数据线缆/连接组件为主，覆盖10G至800G AOC并推进高速铜互连，AI服务器短距互连弹性来自DAC/ACC/AEC/AOC组合；主板块由AOC有源光缆改为高速铜互连，AOC放备注，风险是单价、客户认证和规模放量。证据B。</t>
+          <t>证据中：2025年报披露公司聚焦新能源、5G通信、智能网联、机器人及AI算力等高增长赛道，精密铜带已批量应用于屏蔽罩、高速连接器、集成电路引线框架等关键部件；原“引线框架”过窄，调整为材料端主板块，AI弹性取决于高速连接器/服务器线缆等高端铜材放量。</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -4087,17 +4087,17 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>300913</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>兆龙互连</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>数据中心业务覆盖DAC/ACC等高速铜缆、背板连接器、光模块、电源和热管理，AI算力最直接映射是铜光电热平台中的高速互连；主板块由高速连接器改为高速铜互连，大电流和224G背板降级进备注，风险是平台业务口径大、客户节奏和毛利兑现。证据A。</t>
+          <t>高速数据线缆/连接组件为主，覆盖10G至800G AOC并推进高速铜互连，AI服务器短距互连弹性来自DAC/ACC/AEC/AOC组合；主板块由AOC有源光缆改为高速铜互连，AOC放备注，风险是单价、客户认证和规模放量。证据B。</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -4114,17 +4114,17 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>002130</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>沃尔核材</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>通信线缆业务中高速通信线收入已明显放量，单通道224G产品稳定交付，448G样品验证、PCIe7.0小批量试产；主板块由高速连接器改为高速铜互连，EMI屏蔽仅作材料延伸不单列，风险是核心设备、客户认证和价格竞争。证据A。</t>
+          <t>数据中心业务覆盖DAC/ACC等高速铜缆、背板连接器、光模块、电源和热管理，AI算力最直接映射是铜光电热平台中的高速互连；主板块由高速连接器改为高速铜互连，大电流和224G背板降级进备注，风险是平台业务口径大、客户节奏和毛利兑现。证据A。</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -4141,17 +4141,17 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>688800</t>
+          <t>002130</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>瑞可达</t>
+          <t>沃尔核材</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>公司切入AI领域高速铜缆连接产品，AEC/DAC/ACC覆盖400G/800G并推进更高速率，同时有数据中心液冷UQD连接器项目；主板块由大电流连接改为高速铜互连，液冷快接头作为第二曲线并入备注，风险是小批量到规模交付、客户集中和盈利弹性不确定。证据B。</t>
+          <t>通信线缆业务中高速通信线收入已明显放量，单通道224G产品稳定交付，448G样品验证、PCIe7.0小批量试产；主板块由高速连接器改为高速铜互连，EMI屏蔽仅作材料延伸不单列，风险是核心设备、客户认证和价格竞争。证据A。</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
@@ -4168,17 +4168,17 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>300563</t>
+          <t>688800</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>神宇股份</t>
+          <t>瑞可达</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露AI服务器、云端存储普及推动高速数据线向高频、低损耗、高可靠升级，公司高速数据线业务规模和盈利水平提升；但主业仍为射频同轴电缆，AI服务器产品收入未单列。</t>
+          <t>公司切入AI领域高速铜缆连接产品，AEC/DAC/ACC覆盖400G/800G并推进更高速率，同时有数据中心液冷UQD连接器项目；主板块由大电流连接改为高速铜互连，液冷快接头作为第二曲线并入备注，风险是小批量到规模交付、客户集中和盈利弹性不确定。证据B。</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -4195,17 +4195,17 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>605277</t>
+          <t>300563</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>新亚电子</t>
+          <t>神宇股份</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露高频高速铜缆连接线通过安费诺进入国内外领先服务器制造商与数据中心运营商供应链，主要应用GB系列等AI服务器，终端覆盖戴尔、惠普、谷歌、亚马逊、微软等。</t>
+          <t>证据中：2025年报披露AI服务器、云端存储普及推动高速数据线向高频、低损耗、高可靠升级，公司高速数据线业务规模和盈利水平提升；但主业仍为射频同轴电缆，AI服务器产品收入未单列。</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -4217,22 +4217,22 @@
     <row r="116" ht="36" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>高速连接器</t>
+          <t>高速铜互连</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>688629</t>
+          <t>605277</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>华丰科技</t>
+          <t>新亚电子</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>数据中心、AI服务器和核心路由器需求拉动高速背板连接器、高速模组、线缆组件放量，112G已形成产品基础，224G处于样品/验证到量产爬坡阶段；主板块改为224G高速背板连接器，CPU Socket仅作高端连接器期权，风险是客户验证和批量稳定性。证据A/B。</t>
+          <t>证据强：2025年报披露高频高速铜缆连接线通过安费诺进入国内外领先服务器制造商与数据中心运营商供应链，主要应用GB系列等AI服务器，终端覆盖戴尔、惠普、谷歌、亚马逊、微软等。</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -4249,17 +4249,17 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>002179</t>
+          <t>688629</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>中航光电</t>
+          <t>华丰科技</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>数据中心产品矩阵覆盖电源、光传输、高速连接器/模组和液冷，高速背板、铜缆及标准接口是AI算力互连主线；主板块由大电流连接改为高速连接器，224G背板和液冷快接头并入备注，风险是防务底盘占比高、224G仍需验证、民品收入拆分有限。证据B。</t>
+          <t>数据中心、AI服务器和核心路由器需求拉动高速背板连接器、高速模组、线缆组件放量，112G已形成产品基础，224G处于样品/验证到量产爬坡阶段；主板块改为224G高速背板连接器，CPU Socket仅作高端连接器期权，风险是客户验证和批量稳定性。证据A/B。</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
@@ -4276,17 +4276,17 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>002897</t>
+          <t>002179</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>意华股份</t>
+          <t>中航光电</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>年报披露DSFP56、QSFP112-NPC 3.2T高速铜缆连接器、OSFP112 800G高速连接器等研发/小批量生产进展，AI数据中心映射更偏高速I/O连接器；主板块由MCIO-SlimSAS改为高速连接器，风险是批量规模、客户认证和通讯业务盈利弹性。证据A/B。</t>
+          <t>数据中心产品矩阵覆盖电源、光传输、高速连接器/模组和液冷，高速背板、铜缆及标准接口是AI算力互连主线；主板块由大电流连接改为高速连接器，224G背板和液冷快接头并入备注，风险是防务底盘占比高、224G仍需验证、民品收入拆分有限。证据B。</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -4303,17 +4303,17 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>301328</t>
+          <t>002897</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>维峰电子</t>
+          <t>意华股份</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>年报披露布局AI服务器、数据中心，并提供覆盖高速板端与高速线端的连接器研发生产；主板块由MCIO-SlimSAS改为高速连接器，现阶段AI收入纯度和客户仍需验证，风险是工控/汽车基本盘占比高。证据B。</t>
+          <t>年报披露DSFP56、QSFP112-NPC 3.2T高速铜缆连接器、OSFP112 800G高速连接器等研发/小批量生产进展，AI数据中心映射更偏高速I/O连接器；主板块由MCIO-SlimSAS改为高速连接器，风险是批量规模、客户认证和通讯业务盈利弹性。证据A/B。</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
@@ -4325,22 +4325,22 @@
     <row r="120" ht="16.5" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>MCIO-SlimSAS</t>
+          <t>高速连接器</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>300843</t>
+          <t>301328</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>胜蓝股份</t>
+          <t>维峰电子</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>数据通讯类连接器包括MCIO、Mini SAS HD、Slim SAS、SFP等，应用于路由器、服务器等通讯设备，受AI数据中心内部互连需求拉动；主板块保留MCIO-SlimSAS，风险是业务体量仍小、客户结构和消费电子基本盘波动。证据A/B。</t>
+          <t>年报披露布局AI服务器、数据中心，并提供覆盖高速板端与高速线端的连接器研发生产；主板块由MCIO-SlimSAS改为高速连接器，现阶段AI收入纯度和客户仍需验证，风险是工控/汽车基本盘占比高。证据B。</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -4352,52 +4352,52 @@
     <row r="121" ht="16.5" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>MCIO-SlimSAS</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>300843</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>暂无成熟A股纯标的</t>
+          <t>胜蓝股份</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>该环节主要由NVIDIA/Mellanox、Broadcom、Marvell、Intel等主导；A股网络设备公司不等同HCA/DPU芯片。</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="n"/>
+          <t>数据通讯类连接器包括MCIO、Mini SAS HD、Slim SAS、SFP等，应用于路由器、服务器等通讯设备，受AI数据中心内部互连需求拉动；主板块保留MCIO-SlimSAS，风险是业务体量仍小、客户结构和消费电子基本盘波动。证据A/B。</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>已处理</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>数据中心电源</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>300870</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>欧陆通</t>
+          <t>暂无成熟A股纯标的</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>数据中心电源已成为增长主线，2025年报披露数据中心电源收入20.15亿元、同比增长38.15%，高功率数据中心电源收入12.99亿元、同比增长66.52%；产品覆盖CRPS、GPU服务器电源、浸没式液冷电源和Power Shelf。主板块保留数据中心电源，风险是价格竞争、毛利率下滑、海外客户和新产能爬坡。证据A。</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>已处理</t>
-        </is>
-      </c>
+          <t>该环节主要由NVIDIA/Mellanox、Broadcom、Marvell、Intel等主导；A股网络设备公司不等同HCA/DPU芯片。</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -4407,22 +4407,22 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>002851</t>
+          <t>300870</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>麦格米特</t>
+          <t>欧陆通</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>电力电子平台，2026-06-16 800VDC复核后定位为“watch+ / catalyst_watch”：NVIDIA官方800VDC生态中可确认位于Power system components，公司年报/IR有推荐提供商、800VDC/SST/Sidecar/Power Shelf产品体系、小批量送测/试产和部分北美项目线索；但不能证明NVIDIA或Google直采订单。主板块保留数据中心电源，风险是AI电源研发投入、800VDC规模收入、订单金额、收入占比、毛利率和交付节奏兑现。证据A/B/C。</t>
+          <t>数据中心电源已成为增长主线，2025年报披露数据中心电源收入20.15亿元、同比增长38.15%，高功率数据中心电源收入12.99亿元、同比增长66.52%；产品覆盖CRPS、GPU服务器电源、浸没式液冷电源和Power Shelf。主板块保留数据中心电源，风险是价格竞争、毛利率下滑、海外客户和新产能爬坡。证据A。</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>已处理；2026-06-16复核</t>
+          <t>已处理</t>
         </is>
       </c>
     </row>
@@ -4434,22 +4434,22 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>002335</t>
+          <t>002851</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>科华数据</t>
+          <t>麦格米特</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>智算中心供电系统平台，产品覆盖UPS、HVDC、预制式电力模组、液冷微模块、精密列头柜和智能小母线，半年度报告披露以UPS、HVDC、液冷等核心产品推进认证和样机测试。主板块保留数据中心电源，模块化数据中心、数据中心储能和数据中心母线并入备注，风险是系统集成毛利、海外AI客户和项目回款。证据A/B。</t>
+          <t>电力电子平台，2026-06-16 800VDC复核后定位为“watch+ / catalyst_watch”：NVIDIA官方800VDC生态中可确认位于Power system components，公司年报/IR有推荐提供商、800VDC/SST/Sidecar/Power Shelf产品体系、小批量送测/试产和部分北美项目线索；但不能证明NVIDIA或Google直采订单。主板块保留数据中心电源，风险是AI电源研发投入、800VDC规模收入、订单金额、收入占比、毛利率和交付节奏兑现。证据A/B/C。</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>已处理；2026-06-16复核</t>
         </is>
       </c>
     </row>
@@ -4461,17 +4461,17 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>002518</t>
+          <t>002335</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>科士达</t>
+          <t>科华数据</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>UPS和数据中心关键基础设施供应商，2025年报披露智慧电源、数据中心产品收入约29.55亿元，占营收56.05%，并交付银行、通信、互联网和云计算数据中心项目；主板块保留数据中心电源，模块化数据中心和精密列头柜并入备注，Power Shelf/液冷CDU等仍需看订单。证据A/B。</t>
+          <t>智算中心供电系统平台，产品覆盖UPS、HVDC、预制式电力模组、液冷微模块、精密列头柜和智能小母线，半年度报告披露以UPS、HVDC、液冷等核心产品推进认证和样机测试。主板块保留数据中心电源，模块化数据中心、数据中心储能和数据中心母线并入备注，风险是系统集成毛利、海外AI客户和项目回款。证据A/B。</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
@@ -4488,17 +4488,17 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>002364</t>
+          <t>002518</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>中恒电气</t>
+          <t>科士达</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>数据中心电源产品矩阵覆盖HVDC 240V/336V/800V、Panama 240V/400V/800V、中低压配电、精密配电和服务器PSU，深度适配通用计算、AI与超算；年报披露阿里巴巴、腾讯等机房电源系统项目。主板块保留数据中心电源，STS/ATS并入备注，风险是订单交付、净利波动和海外拓展。证据A。</t>
+          <t>UPS和数据中心关键基础设施供应商，2025年报披露智慧电源、数据中心产品收入约29.55亿元，占营收56.05%，并交付银行、通信、互联网和云计算数据中心项目；主板块保留数据中心电源，模块化数据中心和精密列头柜并入备注，Power Shelf/液冷CDU等仍需看订单。证据A/B。</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -4515,17 +4515,17 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>300693</t>
+          <t>002364</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>盛弘股份</t>
+          <t>中恒电气</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>电能质量和电力电子设备平台，年报披露可向数据中心提供APF、SVG、UPS、UPQC和储能PCS，满足AI服务器对电力质量和备电的需求；主板块保留数据中心电源，电能质量、AIDC固态变压器和数据中心储能并入备注，SST/HVDC仍属研发和订单跟踪阶段。证据B。</t>
+          <t>数据中心电源产品矩阵覆盖HVDC 240V/336V/800V、Panama 240V/400V/800V、中低压配电、精密配电和服务器PSU，深度适配通用计算、AI与超算；年报披露阿里巴巴、腾讯等机房电源系统项目。主板块保留数据中心电源，STS/ATS并入备注，风险是订单交付、净利波动和海外拓展。证据A。</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
@@ -4537,22 +4537,22 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>AI服务器电源磁性件</t>
+          <t>数据中心电源</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>300811</t>
+          <t>300693</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>铂科新材</t>
+          <t>盛弘股份</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露以芯片电感为主的一体成型电感业务规模快速提升，成为第二增长曲线，并有适配AI等应用的超高功率密度模块用电感研发项目；主板块由GPU供电电感收敛为AI芯片电感。</t>
+          <t>电能质量和电力电子设备平台，年报披露可向数据中心提供APF、SVG、UPS、UPQC和储能PCS，满足AI服务器对电力质量和备电的需求；主板块保留数据中心电源，电能质量、AIDC固态变压器和数据中心储能并入备注，SST/HVDC仍属研发和订单跟踪阶段。证据B。</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -4569,17 +4569,17 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>002138</t>
+          <t>300811</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>顺络电子</t>
+          <t>铂科新材</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025半年报/公开资料披露AI、数据中心等战略市场持续高增长，数据中心订单显著增长，公司推出超薄钽电容、铜磁共烧电感等AI服务器/GPU垂直供电相关产品；删减MLCC重复行。</t>
+          <t>证据强：2025年报披露以芯片电感为主的一体成型电感业务规模快速提升，成为第二增长曲线，并有适配AI等应用的超高功率密度模块用电感研发项目；主板块由GPU供电电感收敛为AI芯片电感。</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
@@ -4596,17 +4596,17 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>002885</t>
+          <t>002138</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>京泉华</t>
+          <t>顺络电子</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露磁性器件和电源产品可用于AI服务器集群、GPU电源模块、数据中心高压直流供电系统，但收入仍由磁性元器件、电源、特种变压器共同构成；主线保留AI服务器电源磁性件。</t>
+          <t>证据中强：2025半年报/公开资料披露AI、数据中心等战略市场持续高增长，数据中心订单显著增长，公司推出超薄钽电容、铜磁共烧电感等AI服务器/GPU垂直供电相关产品；删减MLCC重复行。</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -4623,17 +4623,17 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>002782</t>
+          <t>002885</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>可立克</t>
+          <t>京泉华</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露磁性元件用于AI服务器电源等领域，磁性元件收入占比高，业绩增长较快；数据中心领域已有多款磁性元件量产并研发5.5kW/8.5kW高功率密度产品，需继续跟踪AI客户占比。</t>
+          <t>证据中：2025年报披露磁性器件和电源产品可用于AI服务器集群、GPU电源模块、数据中心高压直流供电系统，但收入仍由磁性元器件、电源、特种变压器共同构成；主线保留AI服务器电源磁性件。</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
@@ -4645,22 +4645,22 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>数据中心变压器</t>
+          <t>AI服务器电源磁性件</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>002922</t>
+          <t>002782</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>伊戈尔</t>
+          <t>可立克</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司处于变压器设备及照明领域，数据中心变压设备市场扩容；公开点评显示数据中心产品收入约2.4亿元、同比高增，产品拓展至干式/油浸式等。主板块由移相变压器调整为更完整的数据中心变压器。</t>
+          <t>证据中：2025年报披露磁性元件用于AI服务器电源等领域，磁性元件收入占比高，业绩增长较快；数据中心领域已有多款磁性元件量产并研发5.5kW/8.5kW高功率密度产品，需继续跟踪AI客户占比。</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -4672,22 +4672,22 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>数据中心STS/ATS</t>
+          <t>数据中心变压器</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>002927</t>
+          <t>002922</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>泰永长征</t>
+          <t>伊戈尔</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露中低压ATSE产品升级，TBBQ12中压自动转换开关已在运营商数据中心项目商用；数据中心移相整流变压器仍处验证阶段，固态断路器偏直流配电技术储备，故合并删减“移相变压器、固态断路器”重复行。</t>
+          <t>证据中强：2025年报披露公司处于变压器设备及照明领域，数据中心变压设备市场扩容；公开点评显示数据中心产品收入约2.4亿元、同比高增，产品拓展至干式/油浸式等。主板块由移相变压器调整为更完整的数据中心变压器。</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
@@ -4699,22 +4699,22 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>数据中心配电母线</t>
+          <t>数据中心STS/ATS</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>688226</t>
+          <t>002927</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>威腾电气</t>
+          <t>泰永长征</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报及再融资材料披露公司以低压母线为核心，产品应用于数据中心等场所，并推进数据中心相关电源模块、机柜和列头柜认证；但2025利润大幅下滑，保留数据中心配电母线并降低盈利确定性。</t>
+          <t>证据中强：2025年报披露中低压ATSE产品升级，TBBQ12中压自动转换开关已在运营商数据中心项目商用；数据中心移相整流变压器仍处验证阶段，固态断路器偏直流配电技术储备，故合并删减“移相变压器、固态断路器”重复行。</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -4726,22 +4726,22 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>数据中心电力监控</t>
+          <t>数据中心配电母线</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>300286</t>
+          <t>688226</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>安科瑞</t>
+          <t>威腾电气</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>公司是用户侧能效管理和用电安全系统集成商，投资者记录披露数据中心方案包括蓄电池监测、动环监控、谐波治理、无功补偿、智能小母线监控和精密配电管理。主板块由DCIM细化为数据中心电力监控，精密列头柜和数据中心母线并入备注。风险是项目型订单波动、海外开拓、软硬件集成毛利和数据中心收入占比披露不足。证据A/B。</t>
+          <t>证据中：2025年报及再融资材料披露公司以低压母线为核心，产品应用于数据中心等场所，并推进数据中心相关电源模块、机柜和列头柜认证；但2025利润大幅下滑，保留数据中心配电母线并降低盈利确定性。</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
@@ -4753,22 +4753,22 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>AIDC电力设备</t>
+          <t>数据中心电力监控</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>688676</t>
+          <t>300286</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>金盘科技</t>
+          <t>安科瑞</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>干式变压器、数据中心电源模块、HVDC和固态变压器是AI数据中心供电链条的直接设备节点；2025年报披露AIDC/IDC数据中心收入高增，客户覆盖互联网与运营商数据中心项目。主板块由数据中心电力细化为AIDC电力设备，风险是AIDC订单持续性、应收回款、海外交付和新型电源技术量产。证据A。</t>
+          <t>公司是用户侧能效管理和用电安全系统集成商，投资者记录披露数据中心方案包括蓄电池监测、动环监控、谐波治理、无功补偿、智能小母线监控和精密配电管理。主板块由DCIM细化为数据中心电力监控，精密列头柜和数据中心母线并入备注。风险是项目型订单波动、海外开拓、软硬件集成毛利和数据中心收入占比披露不足。证据A/B。</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -4780,22 +4780,22 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>AIDC电力电缆</t>
+          <t>AIDC电力设备</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>603606</t>
+          <t>688676</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>东方电缆</t>
+          <t>金盘科技</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>公司强项是海缆、高压电缆和电力工程线缆，真实业绩弹性主要来自海风、海缆出海和电力互联；AI数据中心只通过电力基础设施扩建间接受益。主板块由电力电缆细化为高压电缆，风险是数据中心直接关联弱、海风交付节奏、应收和项目毛利波动。证据B/C。</t>
+          <t>干式变压器、数据中心电源模块、HVDC和固态变压器是AI数据中心供电链条的直接设备节点；2025年报披露AIDC/IDC数据中心收入高增，客户覆盖互联网与运营商数据中心项目。主板块由数据中心电力细化为AIDC电力设备，风险是AIDC订单持续性、应收回款、海外交付和新型电源技术量产。证据A。</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
@@ -4812,17 +4812,17 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>600973</t>
+          <t>603606</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>宝胜股份</t>
+          <t>东方电缆</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>电线电缆、裸导体、电力电缆和特种线缆平台，数据中心园区配电建设可形成需求映射，但公司2025年仍亏损、裸导体低毛利占比高，AI受益逻辑偏弱。主板块保留电力电缆，风险是盈利能力、铜价传导、应收/减值和数据中心客户证据不足。证据C。</t>
+          <t>公司强项是海缆、高压电缆和电力工程线缆，真实业绩弹性主要来自海风、海缆出海和电力互联；AI数据中心只通过电力基础设施扩建间接受益。主板块由电力电缆细化为高压电缆，风险是数据中心直接关联弱、海风交付节奏、应收和项目毛利波动。证据B/C。</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -4834,22 +4834,22 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>AIDC低压电器</t>
+          <t>AIDC电力电缆</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>002706</t>
+          <t>600973</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>良信股份</t>
+          <t>宝胜股份</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>低压电器和智能配电方案是主业，年报披露产品广泛应用于智算中心，智算中心/电网/工控等数字能源业务约占收入20%；投资者记录显示数据中心当前集中在HVDC、UPS等配电设备。主板块由中低压开关柜细化为AIDC低压电器，高压直流保护和数据中心母线并入备注。风险是金属材料成本、数据中心客户放量、海外算力项目认证和毛利率修复。证据A/B。</t>
+          <t>电线电缆、裸导体、电力电缆和特种线缆平台，数据中心园区配电建设可形成需求映射，但公司2025年仍亏损、裸导体低毛利占比高，AI受益逻辑偏弱。主板块保留电力电缆，风险是盈利能力、铜价传导、应收/减值和数据中心客户证据不足。证据C。</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
@@ -4866,17 +4866,17 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>601877</t>
+          <t>002706</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>正泰电器</t>
+          <t>良信股份</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>低压电器龙头，低压电器业务收入规模大，年报将新能源、数据中心、通信等列为低压电器增长新动能；但公开资料未充分拆出数据中心订单和收入占比。主板块由中低压开关柜收敛为低压电器，高压直流保护并入备注并降级为产品方向。风险是光伏业务波动、数据中心纯度不足、海外竞争和渠道库存。证据B/C。</t>
+          <t>低压电器和智能配电方案是主业，年报披露产品广泛应用于智算中心，智算中心/电网/工控等数字能源业务约占收入20%；投资者记录显示数据中心当前集中在HVDC、UPS等配电设备。主板块由中低压开关柜细化为AIDC低压电器，高压直流保护和数据中心母线并入备注。风险是金属材料成本、数据中心客户放量、海外算力项目认证和毛利率修复。证据A/B。</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -4888,22 +4888,22 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>AIDC配电设备</t>
+          <t>AIDC低压电器</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>603861</t>
+          <t>601877</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>白云电器</t>
+          <t>正泰电器</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>成套开关设备、变压器、无功补偿和中低压配电设备是主线，年报明确聚焦数据中心及智算中心，并推进一体化电源、HVDC、直流供配电、智能小母线等产品批量生产。主板块由中低压开关柜细化为AIDC配电设备。风险是智算中心订单兑现、传统电网/轨交业务波动、海外拓展和应收回款。证据A。</t>
+          <t>低压电器龙头，低压电器业务收入规模大，年报将新能源、数据中心、通信等列为低压电器增长新动能；但公开资料未充分拆出数据中心订单和收入占比。主板块由中低压开关柜收敛为低压电器，高压直流保护并入备注并降级为产品方向。风险是光伏业务波动、数据中心纯度不足、海外竞争和渠道库存。证据B/C。</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
@@ -4915,22 +4915,22 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>中低压开关柜</t>
+          <t>AIDC配电设备</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>300444</t>
+          <t>603861</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>双杰电气</t>
+          <t>白云电器</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>公司核心为配电设备、变压器、箱变和新能源智能装备，高低压成套开关柜具备迁移到数据中心配电的可能；但公开资料中AI数据中心客户和订单证据不足，当前业绩更多来自新能源建设开发和电气设备。主板块保留中低压开关柜，AI链定位为低证据配电设备观察。风险是新能源EPC毛利、订单结构、数据中心客户导入和现金流。证据C。</t>
+          <t>成套开关设备、变压器、无功补偿和中低压配电设备是主线，年报明确聚焦数据中心及智算中心，并推进一体化电源、HVDC、直流供配电、智能小母线等产品批量生产。主板块由中低压开关柜细化为AIDC配电设备。风险是智算中心订单兑现、传统电网/轨交业务波动、海外拓展和应收回款。证据A。</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -4942,22 +4942,22 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>高压直流继电器</t>
+          <t>中低压开关柜</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>600885</t>
+          <t>300444</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>宏发股份</t>
+          <t>双杰电气</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报显示公司为全球继电器龙头，高压直流业务受新能源车、储能等拉动并拓展数据中心等场景；互动平台披露高压直流继电器及配套产品可用于数据中心高压直流供电系统。AI链条真实但收入未单列，合并删减“高压直流保护”重复行。</t>
+          <t>公司核心为配电设备、变压器、箱变和新能源智能装备，高低压成套开关柜具备迁移到数据中心配电的可能；但公开资料中AI数据中心客户和订单证据不足，当前业绩更多来自新能源建设开发和电气设备。主板块保留中低压开关柜，AI链定位为低证据配电设备观察。风险是新能源EPC毛利、订单结构、数据中心客户导入和现金流。证据C。</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
@@ -4974,17 +4974,17 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>300932</t>
+          <t>600885</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>三友联众</t>
+          <t>宏发股份</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报显示公司主业为继电器，产品用于新能源、光伏、AI算力数据中心等领域，并推进高压直流继电器研发和应用覆盖；但AI数据中心客户、订单和收入未单列，主板块保留高压直流继电器并降级为场景弹性。</t>
+          <t>证据中强：2025年报显示公司为全球继电器龙头，高压直流业务受新能源车、储能等拉动并拓展数据中心等场景；互动平台披露高压直流继电器及配套产品可用于数据中心高压直流供电系统。AI链条真实但收入未单列，合并删减“高压直流保护”重复行。</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -4996,22 +4996,22 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>AI服务器功率器件</t>
+          <t>高压直流继电器</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>600745</t>
+          <t>300932</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>闻泰科技</t>
+          <t>三友联众</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露MOSFET等进入全球头部AI服务器/AI PC ODM供应体系，AI服务器价值量高于传统云服务器；但安世境外控制权受限、审计意见和ST风险显著，保留AI服务器功率半导体并强化风险备注。</t>
+          <t>证据中：2025年报显示公司主业为继电器，产品用于新能源、光伏、AI算力数据中心等领域，并推进高压直流继电器研发和应用覆盖；但AI数据中心客户、订单和收入未单列，主板块保留高压直流继电器并降级为场景弹性。</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr">
@@ -5028,17 +5028,17 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>605111</t>
+          <t>600745</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>新洁能</t>
+          <t>闻泰科技</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露MOSFET/IGBT/SiC可用于AI服务器及数据中心PSU、VRM、HVDC、SST等关键环节，功率器件平台较全；未见明确客户或订单，主板块由泛功率半导体收敛为AI服务器功率器件。</t>
+          <t>证据中强：2025年报披露MOSFET等进入全球头部AI服务器/AI PC ODM供应体系，AI服务器价值量高于传统云服务器；但安世境外控制权受限、审计意见和ST风险显著，保留AI服务器功率半导体并强化风险备注。</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
@@ -5050,22 +5050,22 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>服务器电源MOSFET</t>
+          <t>AI服务器功率器件</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>688261</t>
+          <t>605111</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>东微半导</t>
+          <t>新洁能</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报摘要及披露材料显示公司超级结MOSFET等用于服务器、通信和基站电源，导入维谛、台达、超聚变、欧陆通等客户，算力服务器电源相关产品逐步量产；主板块收敛为服务器电源MOSFET。</t>
+          <t>证据中强：2025年报披露MOSFET/IGBT/SiC可用于AI服务器及数据中心PSU、VRM、HVDC、SST等关键环节，功率器件平台较全；未见明确客户或订单，主板块由泛功率半导体收敛为AI服务器功率器件。</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
@@ -5077,22 +5077,22 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>AI服务器电源管理芯片</t>
+          <t>服务器电源MOSFET</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>600460</t>
+          <t>688261</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>士兰微</t>
+          <t>东微半导</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露服务器DrMOS、Efuse和多项控制器电路已在客户端测试或导入量产，公司IDM平台和功率/电源管理能力支撑该节点；由泛功率半导体收敛为服务器电源管理芯片。</t>
+          <t>证据强：2025年报摘要及披露材料显示公司超级结MOSFET等用于服务器、通信和基站电源，导入维谛、台达、超聚变、欧陆通等客户，算力服务器电源相关产品逐步量产；主板块收敛为服务器电源MOSFET。</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
@@ -5109,17 +5109,17 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>688141</t>
+          <t>600460</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>杰华特</t>
+          <t>士兰微</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露高集成度电源管理芯片在服务器领域渗透率提升，公开互动显示DrMOS、多相控制器、eFuse等已形成PC-服务器-AI产品矩阵；合并删减eFuse、多相DC-DC重复行。</t>
+          <t>证据中强：2025年报披露服务器DrMOS、Efuse和多项控制器电路已在客户端测试或导入量产，公司IDM平台和功率/电源管理能力支撑该节点；由泛功率半导体收敛为服务器电源管理芯片。</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr">
@@ -5136,17 +5136,17 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>688368</t>
+          <t>688141</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>晶丰明源</t>
+          <t>杰华特</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报明确大电流降压型DC/DC、负载点电源应用于AI数据中心、AIC显卡和服务器，并指出数字多相控制器与DrMOS是AI服务器供电系统标配；保留多相DC-DC主线。</t>
+          <t>证据中强：2025年报披露高集成度电源管理芯片在服务器领域渗透率提升，公开互动显示DrMOS、多相控制器、eFuse等已形成PC-服务器-AI产品矩阵；合并删减eFuse、多相DC-DC重复行。</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
@@ -5163,17 +5163,17 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>688484</t>
+          <t>688368</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>南芯科技</t>
+          <t>晶丰明源</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年业绩说明披露智能算力收入占比提升，并在AI服务器方向开发高性能多相控制器、DrMOS、大电流DC-DC和PMIC；当前更多是产品开发和客户机会，确定性低于已量产同业。</t>
+          <t>证据强：2025年报明确大电流降压型DC/DC、负载点电源应用于AI数据中心、AIC显卡和服务器，并指出数字多相控制器与DrMOS是AI服务器供电系统标配；保留多相DC-DC主线。</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
@@ -5190,17 +5190,17 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>688508</t>
+          <t>688484</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>芯朋微</t>
+          <t>南芯科技</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>证据强：2026提质增效方案披露2025年推出12款AI计算能源核心新品，覆盖800V HVDC、SiC/GaN驱动、8/12/16相VRM、DrMOS、eFuse、PoL等，完成服务器一二三次电源全链路布局。</t>
+          <t>证据中：2025年业绩说明披露智能算力收入占比提升，并在AI服务器方向开发高性能多相控制器、DrMOS、大电流DC-DC和PMIC；当前更多是产品开发和客户机会，确定性低于已量产同业。</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -5212,22 +5212,22 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>IGBT/SiC功率模块</t>
+          <t>AI服务器电源管理芯片</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>603290</t>
+          <t>688508</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>斯达半导</t>
+          <t>芯朋微</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报显示IGBT模块收入占主营约83.7%，车规IGBT/SiC模块获多个平台定点并拓展工业及电源场景；AI服务器/数据中心仍属新兴开拓，主板块由泛功率半导体收敛为IGBT/SiC功率模块。</t>
+          <t>证据强：2026提质增效方案披露2025年推出12款AI计算能源核心新品，覆盖800V HVDC、SiC/GaN驱动、8/12/16相VRM、DrMOS、eFuse、PoL等，完成服务器一二三次电源全链路布局。</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
@@ -5244,17 +5244,17 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>688711</t>
+          <t>603290</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>宏微科技</t>
+          <t>斯达半导</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露公司稳固硅基IGBT/FRD基本盘，同时推进SiC、GaN量产转化，下游覆盖工业控制、新能源汽车、AI服务器电源等；AI链受益更多是电源功率器件增量，直接订单证据仍不足。</t>
+          <t>证据中强：2025年报显示IGBT模块收入占主营约83.7%，车规IGBT/SiC模块获多个平台定点并拓展工业及电源场景；AI服务器/数据中心仍属新兴开拓，主板块由泛功率半导体收敛为IGBT/SiC功率模块。</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
@@ -5266,22 +5266,22 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>SiC功率器件</t>
+          <t>IGBT/SiC功率模块</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>300373</t>
+          <t>688711</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>扬杰科技</t>
+          <t>宏微科技</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司覆盖材料、晶圆、封装及硅基/碳化硅功率器件，SiC芯片工厂推进650V-1700V产品迭代，产品应用含汽车电子、AI数据中心、5G通信；主线从泛功率半导体收敛为SiC功率器件。</t>
+          <t>证据中：2025年报披露公司稳固硅基IGBT/FRD基本盘，同时推进SiC、GaN量产转化，下游覆盖工业控制、新能源汽车、AI服务器电源等；AI链受益更多是电源功率器件增量，直接订单证据仍不足。</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr">
@@ -5293,22 +5293,22 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>AI服务器隔离驱动芯片</t>
+          <t>SiC功率器件</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>688052</t>
+          <t>300373</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>纳芯微</t>
+          <t>扬杰科技</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报/点评显示AI服务器电源需求带动公司高压GaN驱动、隔离芯片、MCU等批量发货或量产突破；数字隔离和电流传感更多为汽车/工业通用能力，合并删减重复行。</t>
+          <t>证据中强：2025年报披露公司覆盖材料、晶圆、封装及硅基/碳化硅功率器件，SiC芯片工厂推进650V-1700V产品迭代，产品应用含汽车电子、AI数据中心、5G通信；主线从泛功率半导体收敛为SiC功率器件。</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
@@ -5320,22 +5320,22 @@
     <row r="157" ht="16.5" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>AI服务器高端电容</t>
+          <t>AI服务器隔离驱动芯片</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>603989</t>
+          <t>688052</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>艾华集团</t>
+          <t>纳芯微</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露新能源及AI数据中心成为行业增长引擎，公司叠层铝电容等高端产品进入通信、数据中心市场，并计划深耕AI服务器电源；保留高端电容并明确AI服务器应用。</t>
+          <t>证据强：2025年报/点评显示AI服务器电源需求带动公司高压GaN驱动、隔离芯片、MCU等批量发货或量产突破；数字隔离和电流传感更多为汽车/工业通用能力，合并删减重复行。</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
@@ -5347,22 +5347,22 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>高端薄膜电容</t>
+          <t>AI服务器高端电容</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>600563</t>
+          <t>603989</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>法拉电子</t>
+          <t>艾华集团</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露薄膜电容为绝对主业且营收、净利稳增；AI数据中心800V HVDC/服务器电源是增量场景但公开客户订单不强，主板块从泛高端电容收敛为高端薄膜电容。</t>
+          <t>证据中强：2025年报披露新能源及AI数据中心成为行业增长引擎，公司叠层铝电容等高端产品进入通信、数据中心市场，并计划深耕AI服务器电源；保留高端电容并明确AI服务器应用。</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
@@ -5374,22 +5374,22 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>高可靠钽电容</t>
+          <t>高端薄膜电容</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>300726</t>
+          <t>600563</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>宏达电子</t>
+          <t>法拉电子</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报及公开披露显示高可靠电子元器件为基本盘，民品收入高增，民用钽电容进入国产服务器供应链并在AI服务器、数据中心批量应用；保留高可靠钽电容。</t>
+          <t>证据中强：2025年报披露薄膜电容为绝对主业且营收、净利稳增；AI数据中心800V HVDC/服务器电源是增量场景但公开客户订单不强，主板块从泛高端电容收敛为高端薄膜电容。</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
@@ -5401,22 +5401,22 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>AI服务器超级电容</t>
+          <t>高可靠钽电容</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>300726</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>江海股份</t>
+          <t>宏达电子</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>证据中：公司公告披露超级电容/MLPC在AI服务器电源端应用仍小，2026Q1 AI服务器电源应用约1200万元；原高可靠钽电容不贴合主业，改为AI服务器超级电容，处早期放量。</t>
+          <t>证据中强：2025年报及公开披露显示高可靠电子元器件为基本盘，民品收入高增，民用钽电容进入国产服务器供应链并在AI服务器、数据中心批量应用；保留高可靠钽电容。</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
@@ -5428,27 +5428,27 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>MLCC</t>
+          <t>AI服务器超级电容</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>300408</t>
+          <t>002484</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>三环集团</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>电子陶瓷材料平台，2026-06-16 MLCC复核后定位为AI server高端MLCC“main_candidate / 主受益候选”：年报披露数据中心领域多尺寸高容MLCC和48V电源系统高容MLCC，2026Q1盈利质量较强，光通信陶瓷件也有增量。风险是未披露AI server客户名单、具体高端MLCC ASP涨价、AI server收入拆分，估值已反映部分景气。证据A/B。2026-06-16 JPM补充：报告估算AI server MLCC TAM 150%+ CAGR，并指出高端MLCC产能消耗会挤压低阶/中阶供给；三环仍需用高容/高压/高可靠MLCC客户、ASP、收入占比和毛利率验证。</t>
+          <t>证据中：公司公告披露超级电容/MLPC在AI服务器电源端应用仍小，2026Q1 AI服务器电源应用约1200万元；原高可靠钽电容不贴合主业，改为AI服务器超级电容，处早期放量。</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr">
         <is>
-          <t>已处理；2026-06-16复核；2026-06-16 JPM补充</t>
+          <t>已处理</t>
         </is>
       </c>
     </row>
@@ -5460,17 +5460,17 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>000636</t>
+          <t>300408</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>风华高科</t>
+          <t>三环集团</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>高端MLCC国产替代标的，2026-06-16 MLCC复核后定位为“watch+ / event_trade”：公司披露极限高容MLCC应用于AI服务器等领域，多个MLCC产品完成客户编码认定并批量交付，但已明确目前尚未直接供货英伟达。交易弹性高于基本面确定性，需跟踪AI服务器MLCC批量规模、涨价执行、客户编码数量和净利率改善。证据A/B。2026-06-16 JPM补充：报告强化AI server高端MLCC需求和低阶供给挤压，但海外锚主要是YAGEO/Murata/Samsung；风华仍按watch+ / event_trade处理，需验证AI服务器MLCC批量规模、涨价执行和客户编码。</t>
+          <t>电子陶瓷材料平台，2026-06-16 MLCC复核后定位为AI server高端MLCC“main_candidate / 主受益候选”：年报披露数据中心领域多尺寸高容MLCC和48V电源系统高容MLCC，2026Q1盈利质量较强，光通信陶瓷件也有增量。风险是未披露AI server客户名单、具体高端MLCC ASP涨价、AI server收入拆分，估值已反映部分景气。证据A/B。2026-06-16 JPM补充：报告估算AI server MLCC TAM 150%+ CAGR，并指出高端MLCC产能消耗会挤压低阶/中阶供给；三环仍需用高容/高压/高可靠MLCC客户、ASP、收入占比和毛利率验证。</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -5482,49 +5482,49 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>MLCC材料</t>
+          <t>MLCC</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>300285</t>
+          <t>000636</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>国瓷材料</t>
+          <t>风华高科</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>电子陶瓷材料平台，年报披露重点聚焦AI服务器及车规用MLCC介质粉体，并推进扩产，部分新产品在核心客户取得突破；覆铜板填充材料和光模块陶瓷基板也可观察，但AI链条最清晰的是MLCC介质粉体。主板块由高端封装填料改为MLCC材料，风险是MLCC景气、客户认证和利润弹性偏稳。证据A/B。</t>
+          <t>高端MLCC国产替代标的，2026-06-16 MLCC复核后定位为“watch+ / event_trade”：公司披露极限高容MLCC应用于AI服务器等领域，多个MLCC产品完成客户编码认定并批量交付，但已明确目前尚未直接供货英伟达。交易弹性高于基本面确定性，需跟踪AI服务器MLCC批量规模、涨价执行、客户编码数量和净利率改善。证据A/B。2026-06-16 JPM补充：报告强化AI server高端MLCC需求和低阶供给挤压，但海外锚主要是YAGEO/Murata/Samsung；风华仍按watch+ / event_trade处理，需验证AI服务器MLCC批量规模、涨价执行和客户编码。</t>
         </is>
       </c>
       <c r="E163" s="6" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>已处理；2026-06-16复核；2026-06-16 JPM补充</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>输变电主设备</t>
+          <t>MLCC材料</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>002028</t>
+          <t>300285</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>思源电气</t>
+          <t>国瓷材料</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>GIS、开关、变压器、保护自动化和电力电子产品构成输配电设备平台，AI数据中心拉动来自并网、园区供电、储能/超级电容和全球电网升级；主板块由数据中心电力收敛为输变电设备，电网自动化并入备注。风险是数据中心订单占比未单独披露、海外交付、毛利率和电力电子竞争。证据A/B。</t>
+          <t>电子陶瓷材料平台，年报披露重点聚焦AI服务器及车规用MLCC介质粉体，并推进扩产，部分新产品在核心客户取得突破；覆铜板填充材料和光模块陶瓷基板也可观察，但AI链条最清晰的是MLCC介质粉体。主板块由高端封装填料改为MLCC材料，风险是MLCC景气、客户认证和利润弹性偏稳。证据A/B。</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
@@ -5541,17 +5541,17 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>600089</t>
+          <t>002028</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>特变电工</t>
+          <t>思源电气</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>大型变压器、电抗器、特高压和线缆是电网与大型电力基础设施主设备，AI数据中心电力扩容属于间接受益增量；公司盈利还受多晶硅、煤炭、新能源电站等周期业务影响。主板块由数据中心电力改为输变电主设备，风险是数据中心收入不透明、周期业务拖累、海外订单执行和原材料价格。证据B/C。</t>
+          <t>GIS、开关、变压器、保护自动化和电力电子产品构成输配电设备平台，AI数据中心拉动来自并网、园区供电、储能/超级电容和全球电网升级；主板块由数据中心电力收敛为输变电设备，电网自动化并入备注。风险是数据中心订单占比未单独披露、海外交付、毛利率和电力电子竞争。证据A/B。</t>
         </is>
       </c>
       <c r="E165" s="6" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>601179</t>
+          <t>600089</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>中国西电</t>
+          <t>特变电工</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>高压开关、变压器、电力电子和输配电成套装备是主线，受益电网投资、特高压与大型负荷并网；数据中心固态变压器和供电装备属于新兴观察但不是当前收入核心。主板块由数据中心电力改为输变电主设备，风险是国网招标节奏、海外毛利、新业务量产和数据中心收入占比。证据B。</t>
+          <t>大型变压器、电抗器、特高压和线缆是电网与大型电力基础设施主设备，AI数据中心电力扩容属于间接受益增量；公司盈利还受多晶硅、煤炭、新能源电站等周期业务影响。主板块由数据中心电力改为输变电主设备，风险是数据中心收入不透明、周期业务拖累、海外订单执行和原材料价格。证据B/C。</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
@@ -5590,22 +5590,22 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>电网自动化</t>
+          <t>输变电主设备</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>600406</t>
+          <t>601179</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>国电南瑞</t>
+          <t>中国西电</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>电网调度自动化、继电保护、变电站自动化和数能融合平台是核心，AI数据中心电力瓶颈传导到并网调度、能源管理和数字化管控；主板块保留电网自动化，DCIM并入备注并降级为数据中心能源管理场景。风险是数据中心项目占比、国网投资节奏、软件平台竞争和项目验收周期。证据A/B。</t>
+          <t>高压开关、变压器、电力电子和输配电成套装备是主线，受益电网投资、特高压与大型负荷并网；数据中心固态变压器和供电装备属于新兴观察但不是当前收入核心。主板块由数据中心电力改为输变电主设备，风险是国网招标节奏、海外毛利、新业务量产和数据中心收入占比。证据B。</t>
         </is>
       </c>
       <c r="E167" s="6" t="inlineStr">
@@ -5622,17 +5622,17 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>000400</t>
+          <t>600406</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>许继电气</t>
+          <t>国电南瑞</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>电力自动化、保护控制、换流输配电设备和电能质量治理是主线，AI数据中心映射在园区配电可靠性、无功补偿、电能质量和并网控制；主板块保留电网自动化，电能质量并入备注。风险是营收增速承压、EPC业务压缩、数据中心直接订单披露不足和国网招标节奏。证据B/C。</t>
+          <t>电网调度自动化、继电保护、变电站自动化和数能融合平台是核心，AI数据中心电力瓶颈传导到并网调度、能源管理和数字化管控；主板块保留电网自动化，DCIM并入备注并降级为数据中心能源管理场景。风险是数据中心项目占比、国网投资节奏、软件平台竞争和项目验收周期。证据A/B。</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
@@ -5649,17 +5649,17 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>601126</t>
+          <t>000400</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>许继电气</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>继电保护、自动化与控制系统、电力电子和智慧用电方案是主线，年报披露参与中国移动呼和浩特数据中心、京津算力产业园、芜湖字节跳动火山引擎算力中心等项目，AI数据中心电力管理证据强于多数自动化公司。主板块保留电网自动化，风险是数据中心项目规模占比、海外拓展和工业自动化毛利。证据A。</t>
+          <t>电力自动化、保护控制、换流输配电设备和电能质量治理是主线，AI数据中心映射在园区配电可靠性、无功补偿、电能质量和并网控制；主板块保留电网自动化，电能质量并入备注。风险是营收增速承压、EPC业务压缩、数据中心直接订单披露不足和国网招标节奏。证据B/C。</t>
         </is>
       </c>
       <c r="E169" s="6" t="inlineStr">
@@ -5671,22 +5671,22 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>能源物联网</t>
+          <t>电网自动化</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>688100</t>
+          <t>601126</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>威胜信息</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>公司主线是能源数字化、用电信息采集、通信模块和电力物联网解决方案，受益配用电数字化和新型电力系统建设；数据中心精细化电力监控属于间接映射，缺少DCIM专项收入和客户证据。主板块由DCIM改为能源物联网。风险是国网/南网招标节奏、海外项目、芯片/模块毛利和数据中心场景纯度不足。证据B/C。</t>
+          <t>继电保护、自动化与控制系统、电力电子和智慧用电方案是主线，年报披露参与中国移动呼和浩特数据中心、京津算力产业园、芜湖字节跳动火山引擎算力中心等项目，AI数据中心电力管理证据强于多数自动化公司。主板块保留电网自动化，风险是数据中心项目规模占比、海外拓展和工业自动化毛利。证据A。</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -5698,22 +5698,22 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>电能质量</t>
+          <t>能源物联网</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>688663</t>
+          <t>688100</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>新风光</t>
+          <t>威胜信息</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>SVG、PCS、高压变频器和电力电子控制是核心，年报指出AI大模型和数据中心增长将带动无功补偿等电力基础设施需求，调研资料披露SVG等产品已用于数据中心场景；SST是后续弹性。主板块保留电能质量。风险是数据中心订单规模、煤矿/工业周期、SST量产和价格竞争。证据A/B。</t>
+          <t>公司主线是能源数字化、用电信息采集、通信模块和电力物联网解决方案，受益配用电数字化和新型电力系统建设；数据中心精细化电力监控属于间接映射，缺少DCIM专项收入和客户证据。主板块由DCIM改为能源物联网。风险是国网/南网招标节奏、海外项目、芯片/模块毛利和数据中心场景纯度不足。证据B/C。</t>
         </is>
       </c>
       <c r="E171" s="6" t="inlineStr">
@@ -5725,22 +5725,22 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>数据中心备用发电</t>
+          <t>电能质量</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>300153</t>
+          <t>688663</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>科泰电源</t>
+          <t>新风光</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>证据强：主营发电机组/备用电源，2025年报披露备用电源覆盖算力中心、数据中心，且新增互联网客户、海外数据中心大规模交付；AI相关性在数据中心电力保障，不是算力核心设备，跟踪订单、毛利率和交付回款。</t>
+          <t>SVG、PCS、高压变频器和电力电子控制是核心，年报指出AI大模型和数据中心增长将带动无功补偿等电力基础设施需求，调研资料披露SVG等产品已用于数据中心场景；SST是后续弹性。主板块保留电能质量。风险是数据中心订单规模、煤矿/工业周期、SST量产和价格竞争。证据A/B。</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
@@ -5757,17 +5757,17 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>000880</t>
+          <t>300153</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>潍柴重机</t>
+          <t>科泰电源</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>证据中：公司主业为船舶动力和发电机组，年报披露受AI和数据中心需求拉动，数据中心高可靠性发电机组市场需求提升；相比纯数据中心设备商，业务仍更偏发动机/能源电力通用平台，跟踪数据中心收入占比和利润弹性。</t>
+          <t>证据强：主营发电机组/备用电源，2025年报披露备用电源覆盖算力中心、数据中心，且新增互联网客户、海外数据中心大规模交付；AI相关性在数据中心电力保障，不是算力核心设备，跟踪订单、毛利率和交付回款。</t>
         </is>
       </c>
       <c r="E173" s="6" t="inlineStr">
@@ -5784,17 +5784,17 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>600710</t>
+          <t>000880</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>苏美达</t>
+          <t>潍柴重机</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露柴油发电机组收入16.77亿元、同比增长41.56%，核心需求来自算力中心、数据中心、运营商和工业企业备用电源；但公司还有供应链、纺服、船舶等大盘业务，AI弹性需看发电机组占比、毛利和订单持续性。</t>
+          <t>证据中：公司主业为船舶动力和发电机组，年报披露受AI和数据中心需求拉动，数据中心高可靠性发电机组市场需求提升；相比纯数据中心设备商，业务仍更偏发动机/能源电力通用平台，跟踪数据中心收入占比和利润弹性。</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -5806,22 +5806,22 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>AIDC储能电池系统</t>
+          <t>数据中心备用发电</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>300207</t>
+          <t>600710</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>欣旺达</t>
+          <t>苏美达</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报明确生成式AI推动AIDC规模扩张，公司将推出适配AIDC的锂电池产品，搭载6C/10C高倍率电池系统与800V高压架构，覆盖大型储能、园区备电、机柜备电和BBU毫秒级备电；利润短期受诉讼和汇兑扰动。</t>
+          <t>证据强：2025年报披露柴油发电机组收入16.77亿元、同比增长41.56%，核心需求来自算力中心、数据中心、运营商和工业企业备用电源；但公司还有供应链、纺服、船舶等大盘业务，AI弹性需看发电机组占比、毛利和订单持续性。</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
@@ -5833,22 +5833,22 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>数据中心储能</t>
+          <t>AIDC储能电池系统</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>300207</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>欣旺达</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报/公司公告显示宁德时代储能业务和零碳场景持续扩张，并将电动化边界延伸至数据中心等多元场景；但公司收入主轴仍是动力电池和通用储能，AIDC储能收入未单列，按数据中心储能保留但标注为增量场景。</t>
+          <t>证据强：2025年报明确生成式AI推动AIDC规模扩张，公司将推出适配AIDC的锂电池产品，搭载6C/10C高倍率电池系统与800V高压架构，覆盖大型储能、园区备电、机柜备电和BBU毫秒级备电；利润短期受诉讼和汇兑扰动。</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
@@ -5860,22 +5860,22 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>工商业储能系统</t>
+          <t>数据中心储能</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>688063</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>派能科技</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报显示公司储能产品出货和收入恢复增长，并提到AI算力爆发、数据中心和工商业园区等场景推动储能需求；但公司主业仍以户用/工商业储能为核心，数据中心客户和收入未单列，原数据中心储能降级为工商业储能系统。</t>
+          <t>证据中：2025年报/公司公告显示宁德时代储能业务和零碳场景持续扩张，并将电动化边界延伸至数据中心等多元场景；但公司收入主轴仍是动力电池和通用储能，AIDC储能收入未单列，按数据中心储能保留但标注为增量场景。</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
@@ -5887,22 +5887,22 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>储能电池</t>
+          <t>工商业储能系统</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>300014</t>
+          <t>688063</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>亿纬锂能</t>
+          <t>派能科技</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报显示公司储能出货快速增长、储能电池产品定义行业标杆，大容量磷酸铁锂储能电池是主要弹性来源；数据中心/AIDC是储能下游增量场景之一，但未见单列客户或收入，故由数据中心储能收敛为储能电池。</t>
+          <t>证据中：2025年报显示公司储能产品出货和收入恢复增长，并提到AI算力爆发、数据中心和工商业园区等场景推动储能需求；但公司主业仍以户用/工商业储能为核心，数据中心客户和收入未单列，原数据中心储能降级为工商业储能系统。</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
@@ -5914,22 +5914,22 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>AIDC电路保护</t>
+          <t>储能电池</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>301031</t>
+          <t>300014</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>中熔电气</t>
+          <t>亿纬锂能</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露激励熔断器、智能熔断器及继电器在光伏、储能及数据中心需求涌现，公司面向智算/超算AIDC从UPS到HVDC再到SST提供一站式电路保护方案；合并删减“数据中心母线”重复行。</t>
+          <t>证据中强：2025年报显示公司储能出货快速增长、储能电池产品定义行业标杆，大容量磷酸铁锂储能电池是主要弹性来源；数据中心/AIDC是储能下游增量场景之一，但未见单列客户或收入，故由数据中心储能收敛为储能电池。</t>
         </is>
       </c>
       <c r="E179" s="6" t="inlineStr">
@@ -5941,22 +5941,22 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>数据中心消防</t>
+          <t>AIDC电路保护</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>002960</t>
+          <t>301031</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>青鸟消防</t>
+          <t>中熔电气</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>消防报警、智慧消防、储能消防和数据中心消防方案齐全，2025年报披露数据中心消防业务发货额超1.7亿元并受益智算中心与大型IDC项目密集投建；储能消防为另一高景气增量。主板块保留数据中心消防。风险是消防新旧国标切换、价格竞争、数据中心项目交付节奏和海外认证。证据A。</t>
+          <t>证据强：2025年报披露激励熔断器、智能熔断器及继电器在光伏、储能及数据中心需求涌现，公司面向智算/超算AIDC从UPS到HVDC再到SST提供一站式电路保护方案；合并删减“数据中心母线”重复行。</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -5968,22 +5968,22 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>储能消防</t>
+          <t>数据中心消防</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>300902</t>
+          <t>002960</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>国安达</t>
+          <t>青鸟消防</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>公司核心业务更集中在储能消防、电力电网消防和交通运输消防，储能消防收入近年快速增长；公开资料显示新型能源消防方案可应用于数据中心/算力中心，并推进消防与液冷融合方案，数据中心仍偏延伸场景。主板块由数据中心消防改为储能消防，数据中心消防降级并入备注。风险是数据中心收入占比不明、储能消防价格竞争、客户集中和新业务投入。证据B/C。</t>
+          <t>消防报警、智慧消防、储能消防和数据中心消防方案齐全，2025年报披露数据中心消防业务发货额超1.7亿元并受益智算中心与大型IDC项目密集投建；储能消防为另一高景气增量。主板块保留数据中心消防。风险是消防新旧国标切换、价格竞争、数据中心项目交付节奏和海外认证。证据A。</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
@@ -5995,22 +5995,22 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>先进封装</t>
+          <t>储能消防</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>600584</t>
+          <t>300902</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>长电科技</t>
+          <t>国安达</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>国内封测平台龙头，WLP、2.5D/3D、SiP、倒装等先进封装应用于AI和高性能计算；2025年先进封装收入创高，XDFOI光引擎完成客户样品交付并通过测试但仍属早期增量。主板块改为先进封装，CPO光电合封降级并入备注，风险是高端产能爬坡、客户放量节奏和利润率。证据A/B。</t>
+          <t>公司核心业务更集中在储能消防、电力电网消防和交通运输消防，储能消防收入近年快速增长；公开资料显示新型能源消防方案可应用于数据中心/算力中心，并推进消防与液冷融合方案，数据中心仍偏延伸场景。主板块由数据中心消防改为储能消防，数据中心消防降级并入备注。风险是数据中心收入占比不明、储能消防价格竞争、客户集中和新业务投入。证据B/C。</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
@@ -6027,17 +6027,17 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>002156</t>
+          <t>600584</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>通富微电</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>证据强：封测平台绑定AMD等高性能计算客户，年报披露chiplet高密度封装研发产业化、FCBGA等先进封装能力，AI/数据中心需求带动中高端产品收入；跟踪先进封装产能利用率、折旧压力和大客户集中度。</t>
+          <t>国内封测平台龙头，WLP、2.5D/3D、SiP、倒装等先进封装应用于AI和高性能计算；2025年先进封装收入创高，XDFOI光引擎完成客户样品交付并通过测试但仍属早期增量。主板块改为先进封装，CPO光电合封降级并入备注，风险是高端产能爬坡、客户放量节奏和利润率。证据A/B。</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
@@ -6054,17 +6054,17 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>688362</t>
+          <t>002156</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>甬矽电子</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>证据中强：产品以QFN/LGA/BGA/FlipChip/Bumping/WLCSP等中高端先进封装为主，具备Bumping+CP+FC+FT一站式能力，布局SiP、FC、RDL/Interposer等；AI/HPC为行业驱动力，但公司体量和高端客户验证仍需跟踪。</t>
+          <t>证据强：封测平台绑定AMD等高性能计算客户，年报披露chiplet高密度封装研发产业化、FCBGA等先进封装能力，AI/数据中心需求带动中高端产品收入；跟踪先进封装产能利用率、折旧压力和大客户集中度。</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -6081,17 +6081,17 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>002185</t>
+          <t>688362</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>华天科技</t>
+          <t>甬矽电子</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>证据中强：主营集成电路封测，已掌握SiP、FC、TSV、Bumping、FO、WLP、PLP、2.5D/3D等先进封装技术，并披露聚焦国内CPU/GPU客户；AI映射成立，但高端AI封装纯度和盈利弹性弱于头部绑定客户公司。</t>
+          <t>证据中强：产品以QFN/LGA/BGA/FlipChip/Bumping/WLCSP等中高端先进封装为主，具备Bumping+CP+FC+FT一站式能力，布局SiP、FC、RDL/Interposer等；AI/HPC为行业驱动力，但公司体量和高端客户验证仍需跟踪。</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
@@ -6103,76 +6103,76 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>FC-BGA载板</t>
+          <t>先进封装</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>002436</t>
+          <t>002185</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>兴森科技</t>
+          <t>华天科技</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>证据中强：IC封装基板收入高增，FCBGA/ABF项目面向服务器、AI芯片、交换机晶片等应用并处小批量生产/客户导入阶段；2026-06-16 ABF复核后定位为“watch+ / event_trade_option”，更像订单突破期权而非当前基本面主受益。风险是大批量量产取决于客户进展和供应商管理策略，FCBGA过去仍拖累利润，需跟踪客户层级、单季收入和毛利改善。证据A/B。2026-06-16 JPM补充：报告估算载板UTR在2027e超过100%，AI server &amp; switch面积需求从2024年2,448 bn mm2升至2028e 21,522 bn mm2，占比升至75%；兴森仍是FC-BGA/ABF订单突破期权，需大客户、量产、收入和毛利验证。</t>
+          <t>证据中强：主营集成电路封测，已掌握SiP、FC、TSV、Bumping、FO、WLP、PLP、2.5D/3D等先进封装技术，并披露聚焦国内CPU/GPU客户；AI映射成立，但高端AI封装纯度和盈利弹性弱于头部绑定客户公司。</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>已处理；2026-06-16复核；2026-06-16 JPM补充</t>
+          <t>已处理</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>电子封装载带</t>
+          <t>FC-BGA载板</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>002859</t>
+          <t>002436</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>洁美科技</t>
+          <t>兴森科技</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>证据中：主营纸质/塑料载带、电子胶带、离型膜、IC-tray等电子封装材料，2025年报显示电子封装材料库存下降、电子级薄膜和IC-tray备货增长；AI相关性偏电子元器件和半导体封装耗材补链，直接度低于先进封装。</t>
+          <t>证据中强：IC封装基板收入高增，FCBGA/ABF项目面向服务器、AI芯片、交换机晶片等应用并处小批量生产/客户导入阶段；2026-06-16 ABF复核后定位为“watch+ / event_trade_option”，更像订单突破期权而非当前基本面主受益。风险是大批量量产取决于客户进展和供应商管理策略，FCBGA过去仍拖累利润，需跟踪客户层级、单季收入和毛利改善。证据A/B。2026-06-16 JPM补充：报告估算载板UTR在2027e超过100%，AI server &amp; switch面积需求从2024年2,448 bn mm2升至2028e 21,522 bn mm2，占比升至75%；兴森仍是FC-BGA/ABF订单突破期权，需大客户、量产、收入和毛利验证。</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>已处理；2026-06-16复核；2026-06-16 JPM补充</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>引线框架</t>
+          <t>电子封装载带</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>002119</t>
+          <t>002859</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>康强电子</t>
+          <t>洁美科技</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>证据中：公司专业从事半导体封装材料引线框架、键合丝开发生产销售，2025年利润改善且深耕引线框架核心业务；属于传统封装材料国产供应链，和HBM/CoWoS等高端AI先进封装主线相关性偏弱。</t>
+          <t>证据中：主营纸质/塑料载带、电子胶带、离型膜、IC-tray等电子封装材料，2025年报显示电子封装材料库存下降、电子级薄膜和IC-tray备货增长；AI相关性偏电子元器件和半导体封装耗材补链，直接度低于先进封装。</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -6184,22 +6184,22 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>先进封装电镀液</t>
+          <t>引线框架</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>300236</t>
+          <t>002119</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>上海新阳</t>
+          <t>康强电子</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报显示公司聚焦集成电路制造及先进封装关键工艺材料，半导体业务收入同比高增，晶圆制造及先进封装用电镀液及添加剂市场份额提升、销售额同比增长约40%；合并删减“先进封装工艺材料”泛标签重复行。</t>
+          <t>证据中：公司专业从事半导体封装材料引线框架、键合丝开发生产销售，2025年利润改善且深耕引线框架核心业务；属于传统封装材料国产供应链，和HBM/CoWoS等高端AI先进封装主线相关性偏弱。</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
@@ -6211,22 +6211,22 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>高端封装填料</t>
+          <t>先进封装电镀液</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>688300</t>
+          <t>300236</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>联瑞新材</t>
+          <t>上海新阳</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>功能性粉体材料龙头，年报披露聚焦AI/5G/HPC高端芯片封装、Chiplet/HBM异构集成和M8/M9/M10高速覆铜板，Low-alpha球硅/球铝及低损耗球硅是先进封装和高速基板关键填料。主板块保留高端封装填料，封装基板材料并入备注，风险是客户认证、价格竞争和高端新品占比。证据A。</t>
+          <t>证据强：2025年报显示公司聚焦集成电路制造及先进封装关键工艺材料，半导体业务收入同比高增，晶圆制造及先进封装用电镀液及添加剂市场份额提升、销售额同比增长约40%；合并删减“先进封装工艺材料”泛标签重复行。</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
@@ -6243,71 +6243,71 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>688733</t>
+          <t>688300</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>壹石通</t>
+          <t>联瑞新材</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>电子功能粉体材料方向中，Low-alpha球形氧化铝面向高端芯片封装，可满足高算力芯片散热和低α射线需求；2025年披露仍在多批次客户验证和样品级销售阶段。主板块保留高端封装填料但证据弱于联瑞，风险是客户导入、规模收入和新能源材料主业波动。证据B/C。 2026-06-28 光纤上游补充：人工合成高纯石英砂/高纯二氧化硅处客户验证和小批量预期阶段，可作光纤级/半导体级高纯材料国产替代watch；当前证据弱于已量产石英套管、炉芯管供应商，需跟踪客户认证和实际出货。</t>
+          <t>功能性粉体材料龙头，年报披露聚焦AI/5G/HPC高端芯片封装、Chiplet/HBM异构集成和M8/M9/M10高速覆铜板，Low-alpha球硅/球铝及低损耗球硅是先进封装和高速基板关键填料。主板块保留高端封装填料，封装基板材料并入备注，风险是客户认证、价格竞争和高端新品占比。证据A。</t>
         </is>
       </c>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t>已处理；2026-06-28 光纤上游补充</t>
+          <t>已处理</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>先进封装热界面材料</t>
+          <t>高端封装填料</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>688035</t>
+          <t>688733</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>德邦科技</t>
+          <t>壹石通</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>电子封装材料平台，导热界面材料、芯片级散热盖粘接胶、导电/绝缘固晶胶和DAF/CDAF覆盖高密度、异构集成先进封装及服务器/交换机散热材料；主板块由AI服务器散热材料收敛为先进封装热界面材料，Die Attach并入备注，风险是半导体客户认证、先进封装订单和产品毛利。证据A/B。</t>
+          <t>电子功能粉体材料方向中，Low-alpha球形氧化铝面向高端芯片封装，可满足高算力芯片散热和低α射线需求；2025年披露仍在多批次客户验证和样品级销售阶段。主板块保留高端封装填料但证据弱于联瑞，风险是客户导入、规模收入和新能源材料主业波动。证据B/C。 2026-06-28 光纤上游补充：人工合成高纯石英砂/高纯二氧化硅处客户验证和小批量预期阶段，可作光纤级/半导体级高纯材料国产替代watch；当前证据弱于已量产石英套管、炉芯管供应商，需跟踪客户认证和实际出货。</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>已处理；2026-06-28 光纤上游补充</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>先进封装材料</t>
+          <t>先进封装热界面材料</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>002409</t>
+          <t>688035</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>雅克科技</t>
+          <t>德邦科技</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>电子材料平台，半导体前驱体、封装材料和UP Chemical相关产品是AI先进封装/HBM材料映射的核心；年报明确跟踪先进制程薄膜沉积和人工智能先进封装复杂芯片组所需前驱体材料。主板块由HBM封装材料收敛为先进封装材料，ALD-CVD前驱体并入备注；HBM具体客户、TC-NCF收入占比仍需持续验证。风险是海外客户认证、韩国子公司汇率、封装材料放量节奏和传统阻燃剂/LNG材料波动。证据A/B。</t>
+          <t>电子封装材料平台，导热界面材料、芯片级散热盖粘接胶、导电/绝缘固晶胶和DAF/CDAF覆盖高密度、异构集成先进封装及服务器/交换机散热材料；主板块由AI服务器散热材料收敛为先进封装热界面材料，Die Attach并入备注，风险是半导体客户认证、先进封装订单和产品毛利。证据A/B。</t>
         </is>
       </c>
       <c r="E193" s="6" t="inlineStr">
@@ -6324,17 +6324,17 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>300398</t>
+          <t>002409</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>飞凯材料</t>
+          <t>雅克科技</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露半导体材料覆盖锡球、环氧塑封料、光刻胶、湿电子化学品等，先进封装Fan-out键合胶多款产品进入量产/客户验证，厚膜负性光刻胶适配2.5D/3D先进封装；合并Die Attach、封装胶、临时键合胶、半导体光刻胶重复行。</t>
+          <t>电子材料平台，半导体前驱体、封装材料和UP Chemical相关产品是AI先进封装/HBM材料映射的核心；年报明确跟踪先进制程薄膜沉积和人工智能先进封装复杂芯片组所需前驱体材料。主板块由HBM封装材料收敛为先进封装材料，ALD-CVD前驱体并入备注；HBM具体客户、TC-NCF收入占比仍需持续验证。风险是海外客户认证、韩国子公司汇率、封装材料放量节奏和传统阻燃剂/LNG材料波动。证据A/B。</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
@@ -6351,17 +6351,17 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>300054</t>
+          <t>300398</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>鼎龙股份</t>
+          <t>飞凯材料</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露半导体先进封装材料中封装PI、临时键合胶2025年实现销售放量、收入1176万元，主流封测厂和晶圆厂验证导入深化；显示PSPI收入更大但AI链条较间接，合并PSPI、临时键合胶、RDL-Bumping等重复行。</t>
+          <t>证据中强：2025年报披露半导体材料覆盖锡球、环氧塑封料、光刻胶、湿电子化学品等，先进封装Fan-out键合胶多款产品进入量产/客户验证，厚膜负性光刻胶适配2.5D/3D先进封装；合并Die Attach、封装胶、临时键合胶、半导体光刻胶重复行。</t>
         </is>
       </c>
       <c r="E195" s="6" t="inlineStr">
@@ -6373,22 +6373,22 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>先进封装塑封料</t>
+          <t>先进封装材料</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>688535</t>
+          <t>300054</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>华海诚科</t>
+          <t>鼎龙股份</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司主营环氧塑封料和电子胶黏剂，先进封装用颗粒状环氧塑封料、FC底填胶、液态塑封料等是重点，FOWLP/FOPLP颗粒料装备与产业化推进明确；合并Die Attach、封装胶、临时键合胶重复行。</t>
+          <t>证据中：2025年报披露半导体先进封装材料中封装PI、临时键合胶2025年实现销售放量、收入1176万元，主流封测厂和晶圆厂验证导入深化；显示PSPI收入更大但AI链条较间接，合并PSPI、临时键合胶、RDL-Bumping等重复行。</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
@@ -6400,22 +6400,22 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>先进封装光刻胶</t>
+          <t>先进封装塑封料</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>688720</t>
+          <t>688535</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>艾森股份</t>
+          <t>华海诚科</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露电镀液覆盖TSV/RDL/Bumping等，先进封装光刻胶覆盖RDL/Bumping/TSV并推进PSPI验证或小量产；合并“先进封装电镀液”和“RDL-Bumping”，主板块保留更能体现先进封装增量的先进封装光刻胶，电镀液作为辅线。</t>
+          <t>证据强：2025年报披露公司主营环氧塑封料和电子胶黏剂，先进封装用颗粒状环氧塑封料、FC底填胶、液态塑封料等是重点，FOWLP/FOPLP颗粒料装备与产业化推进明确；合并Die Attach、封装胶、临时键合胶重复行。</t>
         </is>
       </c>
       <c r="E197" s="6" t="inlineStr">
@@ -6427,22 +6427,22 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>先进封装X-Ray检测</t>
+          <t>先进封装光刻胶</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>688531</t>
+          <t>688720</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>日联科技</t>
+          <t>艾森股份</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司形成X射线源、AI软件算法、3D/CT等工业检测能力，集成电路X射线精密检测系统面向传统封装及先进封装内部制程缺陷检测；AI链条主要来自先进封装检测需求，主板块保留先进封装X-Ray检测。</t>
+          <t>证据强：2025年报披露电镀液覆盖TSV/RDL/Bumping等，先进封装光刻胶覆盖RDL/Bumping/TSV并推进PSPI验证或小量产；合并“先进封装电镀液”和“RDL-Bumping”，主板块保留更能体现先进封装增量的先进封装光刻胶，电镀液作为辅线。</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
@@ -6454,72 +6454,72 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>TCB</t>
+          <t>先进封装X-Ray检测</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>暂无成熟A股纯标的</t>
+          <t>688531</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>暂无成熟A股纯标的</t>
+          <t>日联科技</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>高端TCB主要由Besi、ASMPT等海外厂商主导，A股目前缺成熟纯标的。</t>
-        </is>
-      </c>
-      <c r="E199" s="6" t="n"/>
+          <t>证据中强：2025年报披露公司形成X射线源、AI软件算法、3D/CT等工业检测能力，集成电路X射线精密检测系统面向传统封装及先进封装内部制程缺陷检测；AI链条主要来自先进封装检测需求，主板块保留先进封装X-Ray检测。</t>
+        </is>
+      </c>
+      <c r="E199" s="6" t="inlineStr">
+        <is>
+          <t>已处理</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>TGV玻璃基板</t>
+          <t>TCB</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>603773</t>
+          <t>暂无成熟A股纯标的</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>沃格光电</t>
+          <t>暂无成熟A股纯标的</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露通格微推进全玻璃基多层互联/GCP、TGV玻璃基板，并与北极雄芯围绕异构芯粒与玻璃基板AI计算芯片合作；但公司仍亏损，相关业务多处于验证或送样阶段，需跟踪规模化兑现。</t>
-        </is>
-      </c>
-      <c r="E200" s="6" t="inlineStr">
-        <is>
-          <t>已处理</t>
-        </is>
-      </c>
+          <t>高端TCB主要由Besi、ASMPT等海外厂商主导，A股目前缺成熟纯标的。</t>
+        </is>
+      </c>
+      <c r="E200" s="6" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>TGV激光微孔设备</t>
+          <t>TGV玻璃基板</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>300776</t>
+          <t>603773</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>帝尔激光</t>
+          <t>沃格光电</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露TGV设备已完成晶圆级和板级玻璃基板通孔设备出货，实现TGV封装激光技术覆盖；公司本质是设备供应商而非玻璃基板厂，主板块由玻璃基板修正为TGV激光微孔设备。</t>
+          <t>证据中：2025年报披露通格微推进全玻璃基多层互联/GCP、TGV玻璃基板，并与北极雄芯围绕异构芯粒与玻璃基板AI计算芯片合作；但公司仍亏损，相关业务多处于验证或送样阶段，需跟踪规模化兑现。</t>
         </is>
       </c>
       <c r="E201" s="6" t="inlineStr">
@@ -6531,22 +6531,22 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>AI芯片IP平台</t>
+          <t>TGV激光微孔设备</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>688521</t>
+          <t>300776</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>芯原股份</t>
+          <t>帝尔激光</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露AI算力业务成为增长引擎，NPU IP已被91家客户用于140余款AI芯片，GPU/VPU/SerDes等IP和Chiplet-UCIe接口均有进展；合并删减Chiplet-UCIe、GPU/GPGPU、NPU、AI子系统、高速接口IP重复行。</t>
+          <t>证据中强：2025年报披露TGV设备已完成晶圆级和板级玻璃基板通孔设备出货，实现TGV封装激光技术覆盖；公司本质是设备供应商而非玻璃基板厂，主板块由玻璃基板修正为TGV激光微孔设备。</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
@@ -6558,22 +6558,22 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>芯片定制设计服务</t>
+          <t>AI芯片IP平台</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>688691</t>
+          <t>688521</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>灿芯股份</t>
+          <t>芯原股份</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>证据中弱：2025年报显示公司为一站式芯片定制服务企业，芯片设计业务和流片项目有所恢复，但全年收入下降、归母亏损1.1亿元；未见Chiplet-UCIe成为核心收入或订单主线，故由Chiplet-UCIe降级为芯片定制设计服务。</t>
+          <t>证据强：2025年报披露AI算力业务成为增长引擎，NPU IP已被91家客户用于140余款AI芯片，GPU/VPU/SerDes等IP和Chiplet-UCIe接口均有进展；合并删减Chiplet-UCIe、GPU/GPGPU、NPU、AI子系统、高速接口IP重复行。</t>
         </is>
       </c>
       <c r="E203" s="6" t="inlineStr">
@@ -6585,22 +6585,22 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>国产EDA平台</t>
+          <t>芯片定制设计服务</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>301269</t>
+          <t>688691</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>华大九天</t>
+          <t>灿芯股份</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报摘要披露公司EDA软件收入占比高，构建3DIC全流程、先进工艺支持、AI+EDA等关键解决方案，并称为国内唯一3DIC设计验证全流程EDA提供商；合并删减3DIC物理验证、存储芯片设计EDA、DTCO-PDK开发重复行。</t>
+          <t>证据中弱：2025年报显示公司为一站式芯片定制服务企业，芯片设计业务和流片项目有所恢复，但全年收入下降、归母亏损1.1亿元；未见Chiplet-UCIe成为核心收入或订单主线，故由Chiplet-UCIe降级为芯片定制设计服务。</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
@@ -6612,22 +6612,22 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>电路仿真EDA</t>
+          <t>国产EDA平台</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>688206</t>
+          <t>301269</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>概伦电子</t>
+          <t>华大九天</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报显示公司主营EDA软件及解决方案，核心围绕器件建模、SPICE/FastSPICE仿真和设计-工艺协同优化，境内主营收入增长；PDK/PCell属于同一EDA能力链，合并删减重复行。</t>
+          <t>证据强：2025年报摘要披露公司EDA软件收入占比高，构建3DIC全流程、先进工艺支持、AI+EDA等关键解决方案，并称为国内唯一3DIC设计验证全流程EDA提供商；合并删减3DIC物理验证、存储芯片设计EDA、DTCO-PDK开发重复行。</t>
         </is>
       </c>
       <c r="E205" s="6" t="inlineStr">
@@ -6639,22 +6639,22 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>良率管理EDA</t>
+          <t>电路仿真EDA</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>301095</t>
+          <t>688206</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>广立微</t>
+          <t>概伦电子</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报/公开披露显示公司营收和利润增长，业务围绕DFM/DFT、测试芯片、WAT晶圆级电性测试及良率提升闭环；WAT和功能安全仿真作为能力补充并入备注，合并删减重复行。</t>
+          <t>证据中强：2025年报显示公司主营EDA软件及解决方案，核心围绕器件建模、SPICE/FastSPICE仿真和设计-工艺协同优化，境内主营收入增长；PDK/PCell属于同一EDA能力链，合并删减重复行。</t>
         </is>
       </c>
       <c r="E206" s="6" t="inlineStr">
@@ -6666,22 +6666,22 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>晶圆代工</t>
+          <t>良率管理EDA</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>688981</t>
+          <t>301095</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>中芯国际</t>
+          <t>广立微</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司为中国大陆集成电路晶圆代工领导者、全球纯晶圆代工第二，8英寸和12英寸产能及客户基础稳固；AI受益主要来自端侧AI、国产芯片供应链和本土代工需求，非直接GPU先进制程暴露。</t>
+          <t>证据中强：2025年报/公开披露显示公司营收和利润增长，业务围绕DFM/DFT、测试芯片、WAT晶圆级电性测试及良率提升闭环；WAT和功能安全仿真作为能力补充并入备注，合并删减重复行。</t>
         </is>
       </c>
       <c r="E207" s="6" t="inlineStr">
@@ -6693,22 +6693,22 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>特色工艺晶圆代工</t>
+          <t>晶圆代工</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>688347</t>
+          <t>688981</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>华虹公司</t>
+          <t>中芯国际</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司为全球领先特色工艺晶圆代工企业，聚焦嵌入式/独立式非易失性存储器、功率器件、模拟与电源管理、逻辑与射频等平台；AI链条偏电源管理、功率、边缘/端侧配套，较中芯国际更偏特色工艺。</t>
+          <t>证据强：2025年报披露公司为中国大陆集成电路晶圆代工领导者、全球纯晶圆代工第二，8英寸和12英寸产能及客户基础稳固；AI受益主要来自端侧AI、国产芯片供应链和本土代工需求，非直接GPU先进制程暴露。</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
@@ -6720,22 +6720,22 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>晶圆硅片</t>
+          <t>特色工艺晶圆代工</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>688126</t>
+          <t>688347</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>沪硅产业</t>
+          <t>华虹公司</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>主要产品为300mm及以下半导体硅片和SOI硅片，300mm硅片是收入增长核心并覆盖逻辑、存储等高端应用；SOI硅光材料已向射频、功率和硅光客户送样但仍处验证/导入阶段。主板块改为晶圆硅片，SOI硅光衬底并入备注作为高端材料观察，风险是硅片价格竞争、产能爬坡费用和盈利承压。证据B。</t>
+          <t>证据强：2025年报披露公司为全球领先特色工艺晶圆代工企业，聚焦嵌入式/独立式非易失性存储器、功率器件、模拟与电源管理、逻辑与射频等平台；AI链条偏电源管理、功率、边缘/端侧配套，较中芯国际更偏特色工艺。</t>
         </is>
       </c>
       <c r="E209" s="6" t="inlineStr">
@@ -6752,17 +6752,17 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>605358</t>
+          <t>688126</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>立昂微</t>
+          <t>沪硅产业</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>半导体硅片、功率器件和化合物半导体平台，2025年报披露6-12英寸硅抛光片/外延片和12英寸产能建设是主线；VCSEL收入增速高但金额仍小，且更多已在激光雷达等场景验证，AI光模块映射不足。主板块改为晶圆硅片，VCSEL并入备注，风险是产能折旧、存货减值和硅片价格周期。证据B/C。</t>
+          <t>主要产品为300mm及以下半导体硅片和SOI硅片，300mm硅片是收入增长核心并覆盖逻辑、存储等高端应用；SOI硅光材料已向射频、功率和硅光客户送样但仍处验证/导入阶段。主板块改为晶圆硅片，SOI硅光衬底并入备注作为高端材料观察，风险是硅片价格竞争、产能爬坡费用和盈利承压。证据B。</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
@@ -6774,22 +6774,22 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>半导体光掩膜版</t>
+          <t>晶圆硅片</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>688401</t>
+          <t>605358</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>路维光电</t>
+          <t>立昂微</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司平板显示与半导体掩膜版增长，G11、HTM、PSM等高端产品推进，AI算力、先进封装、AMOLED、Micro-LED等新兴领域带动高精度掩膜版需求；半导体占比仍需跟踪，主板块由泛光掩膜版收敛为高端掩膜版。</t>
+          <t>半导体硅片、功率器件和化合物半导体平台，2025年报披露6-12英寸硅抛光片/外延片和12英寸产能建设是主线；VCSEL收入增速高但金额仍小，且更多已在激光雷达等场景验证，AI光模块映射不足。主板块改为晶圆硅片，VCSEL并入备注，风险是产能折旧、存货减值和硅片价格周期。证据B/C。</t>
         </is>
       </c>
       <c r="E211" s="6" t="inlineStr">
@@ -6806,17 +6806,17 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>688138</t>
+          <t>688401</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>清溢光电</t>
+          <t>路维光电</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报显示公司主要从事掩膜版研发、设计、生产和销售，产品用于平板显示、半导体芯片、触控和电路板等；半导体国产替代和AI带动晶圆产能扩张构成间接受益，收入仍较依赖显示与综合掩膜版需求。</t>
+          <t>证据中强：2025年报披露公司平板显示与半导体掩膜版增长，G11、HTM、PSM等高端产品推进，AI算力、先进封装、AMOLED、Micro-LED等新兴领域带动高精度掩膜版需求；半导体占比仍需跟踪，主板块由泛光掩膜版收敛为高端掩膜版。</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
@@ -6833,17 +6833,17 @@
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>688721</t>
+          <t>688138</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>龙图光罩</t>
+          <t>清溢光电</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司聚焦半导体掩模版，高端制程及关键客户开发持续推进、珠海工厂投产爬坡；但2025年净利润明显下滑，竞争、折旧和研发费用压制弹性，主板块保留半导体光掩膜版。</t>
+          <t>证据中：2025年报显示公司主要从事掩膜版研发、设计、生产和销售，产品用于平板显示、半导体芯片、触控和电路板等；半导体国产替代和AI带动晶圆产能扩张构成间接受益，收入仍较依赖显示与综合掩膜版需求。</t>
         </is>
       </c>
       <c r="E213" s="6" t="inlineStr">
@@ -6855,22 +6855,22 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>半导体前道设备</t>
+          <t>半导体光掩膜版</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>002371</t>
+          <t>688721</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>北方华创</t>
+          <t>龙图光罩</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露电子工艺装备收入高增，刻蚀、薄膜沉积、热处理、湿法清洗等主力设备放量，离子注入、电镀、混合键合等新品推进；MFC和清洗设备只是平台产品/子环节，合并删减重复行。</t>
+          <t>证据中强：2025年报披露公司聚焦半导体掩模版，高端制程及关键客户开发持续推进、珠海工厂投产爬坡；但2025年净利润明显下滑，竞争、折旧和研发费用压制弹性，主板块保留半导体光掩膜版。</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
@@ -6882,22 +6882,22 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>离子注入设备/电子材料</t>
+          <t>半导体前道设备</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>600641</t>
+          <t>002371</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>先导基电</t>
+          <t>北方华创</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>证据A：原万业企业的主线为凯世通半导体离子注入设备；2026年7月以增资方式投资控股广东先导微电子，后续纳入合并范围，新增GaAs/Ge衬底、高纯金属、前驱体和电子特气等电子材料布局。其配套模拟审计报告假设先导微电子将InP业务相关资产、负债转至广东先锐，并自先导微电子模拟口径剔除相关资产、负债、收入、费用；因此不再按InP衬底资产或业绩处理。核心映射是晶圆厂半导体资本开支的间接受益，不属于800G/1.6T光互连的直接InP标的；风险是整合、融资及InP剥离交割边界。</t>
+          <t>证据强：2025年报披露电子工艺装备收入高增，刻蚀、薄膜沉积、热处理、湿法清洗等主力设备放量，离子注入、电镀、混合键合等新品推进；MFC和清洗设备只是平台产品/子环节，合并删减重复行。</t>
         </is>
       </c>
       <c r="E215" s="6" t="inlineStr">
@@ -6909,22 +6909,22 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>刻蚀设备</t>
+          <t>离子注入设备/电子材料</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>688012</t>
+          <t>600641</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>中微公司</t>
+          <t>先导基电</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报/公开资料显示公司营收创新高，刻蚀设备为最大收入来源，LPCVD/ALD、MOCVD等新产品加速放量；先进封装TSV刻蚀等提供AI先进封装延伸，但主业和业绩弹性仍以刻蚀设备为核心。</t>
+          <t>证据A：原万业企业的主线为凯世通半导体离子注入设备；2026年7月以增资方式投资控股广东先导微电子，后续纳入合并范围，新增GaAs/Ge衬底、高纯金属、前驱体和电子特气等电子材料布局。其配套模拟审计报告假设先导微电子将InP业务相关资产、负债转至广东先锐，并自先导微电子模拟口径剔除相关资产、负债、收入、费用；因此不再按InP衬底资产或业绩处理。核心映射是晶圆厂半导体资本开支的间接受益，不属于800G/1.6T光互连的直接InP标的；风险是整合、融资及InP剥离交割边界。</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
@@ -6936,22 +6936,22 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>薄膜沉积设备</t>
+          <t>刻蚀设备</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>688072</t>
+          <t>688012</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>拓荆科技</t>
+          <t>中微公司</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报显示PECVD、ALD、SACVD、HDPCVD等先进工艺设备在先进存储、先进逻辑规模化量产，在手订单较高；先进键合/三维集成设备已有突破但仍属扩展线，合并删减“先进封装设备”重复行。</t>
+          <t>证据强：2025年报/公开资料显示公司营收创新高，刻蚀设备为最大收入来源，LPCVD/ALD、MOCVD等新产品加速放量；先进封装TSV刻蚀等提供AI先进封装延伸，但主业和业绩弹性仍以刻蚀设备为核心。</t>
         </is>
       </c>
       <c r="E217" s="6" t="inlineStr">
@@ -6963,22 +6963,22 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>半导体清洗设备</t>
+          <t>薄膜沉积设备</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>688082</t>
+          <t>688072</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>盛美上海</t>
+          <t>拓荆科技</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露半导体清洗设备收入占比最高，清洗、电镀、立式炉管、先进封装湿法设备等多产品增长；先进封装湿法设备适配2.5D/3D封装和Chiplet但收入占比较小，合并删减“先进封装设备”重复行。</t>
+          <t>证据强：2025年报显示PECVD、ALD、SACVD、HDPCVD等先进工艺设备在先进存储、先进逻辑规模化量产，在手订单较高；先进键合/三维集成设备已有突破但仍属扩展线，合并删减“先进封装设备”重复行。</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
@@ -6990,22 +6990,22 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>涂胶显影清洗设备</t>
+          <t>半导体清洗设备</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>688037</t>
+          <t>688082</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>芯源微</t>
+          <t>盛美上海</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报显示公司以光刻工序涂胶显影、单片式湿法清洗及先进封装湿法设备为主，前道晶圆加工与后道先进封装设备收入均增长；先进封装设备是AI/HBM链条延伸，主业弹性仍来自涂胶显影清洗平台，合并删减“先进封装设备”重复行。</t>
+          <t>证据强：2025年报披露半导体清洗设备收入占比最高，清洗、电镀、立式炉管、先进封装湿法设备等多产品增长；先进封装湿法设备适配2.5D/3D封装和Chiplet但收入占比较小，合并删减“先进封装设备”重复行。</t>
         </is>
       </c>
       <c r="E219" s="6" t="inlineStr">
@@ -7017,22 +7017,22 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>CMP与减薄设备</t>
+          <t>涂胶显影清洗设备</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>688120</t>
+          <t>688037</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>华海清科</t>
+          <t>芯源微</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司CMP装备市场地位稳固，并突破先进封装减薄抛光设备、离子注入等新产品，CMP、减薄、划切、边抛等覆盖先进制程/先进封装/HBM需求；合并删减“晶圆减薄”重复行。</t>
+          <t>证据强：2025年报显示公司以光刻工序涂胶显影、单片式湿法清洗及先进封装湿法设备为主，前道晶圆加工与后道先进封装设备收入均增长；先进封装设备是AI/HBM链条延伸，主业弹性仍来自涂胶显影清洗平台，合并删减“先进封装设备”重复行。</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
@@ -7044,22 +7044,22 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>封测切割减薄设备</t>
+          <t>CMP与减薄设备</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>300480</t>
+          <t>688120</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>光力科技</t>
+          <t>华海清科</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司半导体封测装备覆盖晶圆切割、封装体切割、晶圆减薄等环节，部分划切设备已在先进封装中批量应用；晶圆减薄和先进封装切割属于同一封测装备链，合并删减重复行。</t>
+          <t>证据强：2025年报披露公司CMP装备市场地位稳固，并突破先进封装减薄抛光设备、离子注入等新产品，CMP、减薄、划切、边抛等覆盖先进制程/先进封装/HBM需求；合并删减“晶圆减薄”重复行。</t>
         </is>
       </c>
       <c r="E221" s="6" t="inlineStr">
@@ -7071,22 +7071,22 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>精密磨削设备</t>
+          <t>封测切割减薄设备</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>002903</t>
+          <t>300480</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>宇环数控</t>
+          <t>光力科技</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>证据弱中：2025年报显示公司主业仍为数控磨削抛光设备，全年亏损；晶圆减薄属于潜在高精密磨削应用，但半导体客户、订单和收入证据不足，原晶圆减薄降级为精密磨削设备并保留观察。</t>
+          <t>证据中强：2025年报披露公司半导体封测装备覆盖晶圆切割、封装体切割、晶圆减薄等环节，部分划切设备已在先进封装中批量应用；晶圆减薄和先进封装切割属于同一封测装备链，合并删减重复行。</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
@@ -7098,22 +7098,22 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>半导体工艺温控</t>
+          <t>精密磨削设备</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>688652</t>
+          <t>002903</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>京仪装备</t>
+          <t>宇环数控</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司主营半导体专用温控设备，产品覆盖刻蚀、薄膜沉积、离子注入、清洗等核心制程，主要客户为国内头部晶圆厂和设备厂；工艺废气处理和AMHS为业务外延，合并进备注并删除重复行。</t>
+          <t>证据弱中：2025年报显示公司主业仍为数控磨削抛光设备，全年亏损；晶圆减薄属于潜在高精密磨削应用，但半导体客户、订单和收入证据不足，原晶圆减薄降级为精密磨削设备并保留观察。</t>
         </is>
       </c>
       <c r="E223" s="6" t="inlineStr">
@@ -7125,22 +7125,22 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>半导体真空泵</t>
+          <t>半导体工艺温控</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>002158</t>
+          <t>688652</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>汉钟精机</t>
+          <t>京仪装备</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报显示公司真空产品已应用于半导体、太阳能、锂电等领域，半导体真空泵是真实AI链条节点；工艺温控并非公司半导体主线，合并删减“半导体工艺温控”重复行。短期需跟踪半导体客户认证和收入占比。</t>
+          <t>证据强：2025年报披露公司主营半导体专用温控设备，产品覆盖刻蚀、薄膜沉积、离子注入、清洗等核心制程，主要客户为国内头部晶圆厂和设备厂；工艺废气处理和AMHS为业务外延，合并进备注并删除重复行。</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
@@ -7157,67 +7157,67 @@
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>暂无成熟A股纯标的</t>
+          <t>002158</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>高端干泵/涡轮分子泵纯标的不足</t>
+          <t>汉钟精机</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>高端半导体干泵和涡轮分子泵仍由Edwards、Pfeiffer、Ebara等海外厂商主导，A股除汉钟等配套外缺成熟纯标的。</t>
-        </is>
-      </c>
-      <c r="E225" s="6" t="n"/>
+          <t>证据中强：2025年报显示公司真空产品已应用于半导体、太阳能、锂电等领域，半导体真空泵是真实AI链条节点；工艺温控并非公司半导体主线，合并删减“半导体工艺温控”重复行。短期需跟踪半导体客户认证和收入占比。</t>
+        </is>
+      </c>
+      <c r="E225" s="6" t="inlineStr">
+        <is>
+          <t>已处理</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>半导体射频电源</t>
+          <t>半导体真空泵</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>300820</t>
+          <t>暂无成熟A股纯标的</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>英杰电气</t>
+          <t>高端干泵/涡轮分子泵纯标的不足</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报显示公司半导体等电子材料设备电源收入增长，射频电源、RPS远程等离子源等产品用于刻蚀/沉积/清洗等前道设备；公司不是离子注入设备商，合并删减“离子注入、RPS远程等离子源”重复行，主线收敛为半导体射频电源。</t>
-        </is>
-      </c>
-      <c r="E226" s="6" t="inlineStr">
-        <is>
-          <t>已处理</t>
-        </is>
-      </c>
+          <t>高端半导体干泵和涡轮分子泵仍由Edwards、Pfeiffer、Ebara等海外厂商主导，A股除汉钟等配套外缺成熟纯标的。</t>
+        </is>
+      </c>
+      <c r="E226" s="6" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>晶圆传输设备</t>
+          <t>半导体射频电源</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>300024</t>
+          <t>300820</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>英杰电气</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报显示公司半导体装备业务围绕晶圆搬运、真空机器人、EFEM、Load Port等产品，服务前道和后道设备厂商；原“半导体AMHS”过宽，主板块收敛为晶圆传输设备，AI受益来自国产半导体设备配套。</t>
+          <t>证据中强：2025年报显示公司半导体等电子材料设备电源收入增长，射频电源、RPS远程等离子源等产品用于刻蚀/沉积/清洗等前道设备；公司不是离子注入设备商，合并删减“离子注入、RPS远程等离子源”重复行，主线收敛为半导体射频电源。</t>
         </is>
       </c>
       <c r="E227" s="6" t="inlineStr">
@@ -7229,22 +7229,22 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>半导体设备零部件</t>
+          <t>晶圆传输设备</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>688409</t>
+          <t>300024</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>富创精密</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司为半导体设备精密零部件平台，覆盖金属结构件、腔体、管路、模组等，并推进静电卡盘等高价值产品；静电卡盘是重要升级方向但不是唯一主线，合并删减“静电卡盘”重复行。</t>
+          <t>证据中强：2025年报显示公司半导体装备业务围绕晶圆搬运、真空机器人、EFEM、Load Port等产品，服务前道和后道设备厂商；原“半导体AMHS”过宽，主板块收敛为晶圆传输设备，AI受益来自国产半导体设备配套。</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
@@ -7256,27 +7256,27 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>半导体测试设备</t>
+          <t>半导体设备零部件</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>300604</t>
+          <t>688409</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>长川科技</t>
+          <t>富创精密</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报/公开资料显示公司已形成测试机、分选机、探针台、AOI等平台型产品矩阵，测试机成为核心收入来源，AI芯片复杂度提升、存储扩产和国产替代共同拉动高端测试设备需求；合并并删减“半导体测试分选机”重复行。2026-06-16 JPM补充：报告把GPU FT/SLT测试时间延长、TDP提升列为测试设备需求驱动，海外锚为Chroma；长川受益需验证高端SoC/SLT平台订单和AI客户收入，不泛化为所有测试机。</t>
+          <t>证据强：2025年报披露公司为半导体设备精密零部件平台，覆盖金属结构件、腔体、管路、模组等，并推进静电卡盘等高价值产品；静电卡盘是重要升级方向但不是唯一主线，合并删减“静电卡盘”重复行。</t>
         </is>
       </c>
       <c r="E229" s="6" t="inlineStr">
         <is>
-          <t>已处理；2026-06-16 JPM补充</t>
+          <t>已处理</t>
         </is>
       </c>
     </row>
@@ -7288,22 +7288,22 @@
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>688200</t>
+          <t>300604</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>华峰测控</t>
+          <t>长川科技</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司主营半导体自动化测试系统，收入和利润高增；AI相关弹性主要来自SoC/混合信号等高端测试平台放量与国产替代，现阶段仍以测试设备主业为核心，不单列为AI专用设备。</t>
+          <t>证据强：2025年报/公开资料显示公司已形成测试机、分选机、探针台、AOI等平台型产品矩阵，测试机成为核心收入来源，AI芯片复杂度提升、存储扩产和国产替代共同拉动高端测试设备需求；合并并删减“半导体测试分选机”重复行。2026-06-16 JPM补充：报告把GPU FT/SLT测试时间延长、TDP提升列为测试设备需求驱动，海外锚为Chroma；长川受益需验证高端SoC/SLT平台订单和AI客户收入，不泛化为所有测试机。</t>
         </is>
       </c>
       <c r="E230" s="6" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>已处理；2026-06-16 JPM补充</t>
         </is>
       </c>
     </row>
@@ -7315,17 +7315,17 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>688001</t>
+          <t>688200</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>华兴源创</t>
+          <t>华峰测控</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露公司为工业自动化测试设备与整线系统方案商，产品用于消费电子、半导体集成电路和新能源汽车等；半导体侧包括SiP/芯片测试平台等研发，但AI业绩弹性未单列，合并删减“IC测试板、SiP系统模块测试、半导体测试分选机”重复行。</t>
+          <t>证据中强：2025年报披露公司主营半导体自动化测试系统，收入和利润高增；AI相关弹性主要来自SoC/混合信号等高端测试平台放量与国产替代，现阶段仍以测试设备主业为核心，不单列为AI专用设备。</t>
         </is>
       </c>
       <c r="E231" s="6" t="inlineStr">
@@ -7337,22 +7337,22 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>功率半导体测试设备</t>
+          <t>半导体测试设备</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>301369</t>
+          <t>688001</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>联动科技</t>
+          <t>华兴源创</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报显示公司聚焦功率半导体、小信号分立器件测试系统及激光打标设备，并提到紧抓大功率器件、第三代半导体、人工智能产业机遇向SoC测试拓展；AI链条较间接，主板块由泛半导体测试收敛为功率半导体测试设备。</t>
+          <t>证据中：2025年报披露公司为工业自动化测试设备与整线系统方案商，产品用于消费电子、半导体集成电路和新能源汽车等；半导体侧包括SiP/芯片测试平台等研发，但AI业绩弹性未单列，合并删减“IC测试板、SiP系统模块测试、半导体测试分选机”重复行。</t>
         </is>
       </c>
       <c r="E232" s="6" t="inlineStr">
@@ -7364,76 +7364,76 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>AI系统级测试设备</t>
+          <t>功率半导体测试设备</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>301369</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>暂无成熟A股纯标的（海外锚：致茂电子 2360.TW）</t>
+          <t>联动科技</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>J.P. Morgan Asia Components 2026-06 中文整理版把Chroma的SLT、光通信/CPO、数据中心电源测试标注为三条100%+ CAGR方向；A股映射需拆到长川科技、华峰测控、华兴源创、伟测科技、精智达等子环节逐项验证，当前仅作new_watch，不等同普通半导体测试设备受益。证据B。</t>
+          <t>证据中：2025年报显示公司聚焦功率半导体、小信号分立器件测试系统及激光打标设备，并提到紧抓大功率器件、第三代半导体、人工智能产业机遇向SoC测试拓展；AI链条较间接，主板块由泛半导体测试收敛为功率半导体测试设备。</t>
         </is>
       </c>
       <c r="E233" s="6" t="inlineStr">
         <is>
-          <t>新增；2026-06-16 JPM补充</t>
+          <t>已处理</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>半导体测试探针</t>
+          <t>AI系统级测试设备</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>688661</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>和林微纳</t>
+          <t>暂无成熟A股纯标的（海外锚：致茂电子 2360.TW）</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报/公开资料显示半导体测试探针业务成为增长引擎，收入同比高增并带动扭亏；公开证据更直接指向测试探针平台，HBM专用探针客户和收入未充分披露，故将“HBM测试探针”降级为半导体测试探针。</t>
+          <t>J.P. Morgan Asia Components 2026-06 中文整理版把Chroma的SLT、光通信/CPO、数据中心电源测试标注为三条100%+ CAGR方向；A股映射需拆到长川科技、华峰测控、华兴源创、伟测科技、精智达等子环节逐项验证，当前仅作new_watch，不等同普通半导体测试设备受益。证据B。</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>新增；2026-06-16 JPM补充</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>晶圆探针台</t>
+          <t>半导体测试探针</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>301629</t>
+          <t>688661</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>矽电股份</t>
+          <t>和林微纳</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司是中国大陆首家实现12英寸晶圆探针台产业化应用的厂商，产品面向SOC、Memory、CIS、功率器件等测试领域；AI/HBM是行业需求驱动而非已披露专用探针收入，原“HBM测试探针”修正为晶圆探针台。</t>
+          <t>证据中强：2025年报/公开资料显示半导体测试探针业务成为增长引擎，收入同比高增并带动扭亏；公开证据更直接指向测试探针平台，HBM专用探针客户和收入未充分披露，故将“HBM测试探针”降级为半导体测试探针。</t>
         </is>
       </c>
       <c r="E235" s="6" t="inlineStr">
@@ -7445,22 +7445,22 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>半导体测试分选设备</t>
+          <t>晶圆探针台</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>603061</t>
+          <t>301629</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>金海通</t>
+          <t>矽电股份</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司专注半导体芯片测试设备，三温测试分选机及大平台超多工位测试分选机需求持续增长、产品销量提升；AI算力芯片和先进封装属于复杂测试应用场景，主板块保留半导体测试分选机。</t>
+          <t>证据强：2025年报披露公司是中国大陆首家实现12英寸晶圆探针台产业化应用的厂商，产品面向SOC、Memory、CIS、功率器件等测试领域；AI/HBM是行业需求驱动而非已披露专用探针收入，原“HBM测试探针”修正为晶圆探针台。</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
@@ -7477,17 +7477,17 @@
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>688328</t>
+          <t>603061</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>深科达</t>
+          <t>金海通</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报/公告显示公司半导体设备业务增长，转塔式和平移式测试分选机实现批量订单交付，子公司深科达半导体贡献利润；未见TCB热压键合为核心收入，故由TCB修正为半导体测试分选设备。</t>
+          <t>证据强：2025年报披露公司专注半导体芯片测试设备，三温测试分选机及大平台超多工位测试分选机需求持续增长、产品销量提升；AI算力芯片和先进封装属于复杂测试应用场景，主板块保留半导体测试分选机。</t>
         </is>
       </c>
       <c r="E237" s="6" t="inlineStr">
@@ -7499,22 +7499,22 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>半导体检测量测设备</t>
+          <t>半导体测试分选设备</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>688361</t>
+          <t>688328</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>中科飞测</t>
+          <t>深科达</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露检测设备和量测设备收入增长，暗场纳米图形晶圆缺陷检测、无图形晶圆缺陷检测、套刻精度量测等产品贡献提升，并拓展电子束/X光技术；先进封装X-Ray作为能力补充并入备注，删除重复行。</t>
+          <t>证据中：2025年报/公告显示公司半导体设备业务增长，转塔式和平移式测试分选机实现批量订单交付，子公司深科达半导体贡献利润；未见TCB热压键合为核心收入，故由TCB修正为半导体测试分选设备。</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
@@ -7526,22 +7526,22 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>半导体测试服务</t>
+          <t>半导体检测量测设备</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>688135</t>
+          <t>688361</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>利扬芯片</t>
+          <t>中科飞测</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报显示公司主业为集成电路测试方案开发、晶圆测试和成品测试服务，营收创新高且亏损收窄，增长受高算力、存储、汽车电子等芯片测试需求和新客户/新产品导入带动；AI链条为后道测试服务弹性，客户与AI芯片收入未单列。</t>
+          <t>证据强：2025年报披露检测设备和量测设备收入增长，暗场纳米图形晶圆缺陷检测、无图形晶圆缺陷检测、套刻精度量测等产品贡献提升，并拓展电子束/X光技术；先进封装X-Ray作为能力补充并入备注，删除重复行。</t>
         </is>
       </c>
       <c r="E239" s="6" t="inlineStr">
@@ -7558,17 +7558,17 @@
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>430139</t>
+          <t>688135</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>华岭股份</t>
+          <t>利扬芯片</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报显示测试服务仍为核心收入来源，并建设高算力应用芯片开放式测试创新服务平台；但公司2025年亏损扩大，AI/高算力测试仍处研发和客户拓展阶段，主线保留半导体测试服务，备注降级AI兑现强度。</t>
+          <t>证据中强：2025年报显示公司主业为集成电路测试方案开发、晶圆测试和成品测试服务，营收创新高且亏损收窄，增长受高算力、存储、汽车电子等芯片测试需求和新客户/新产品导入带动；AI链条为后道测试服务弹性，客户与AI芯片收入未单列。</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
@@ -7585,17 +7585,17 @@
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>688372</t>
+          <t>430139</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>伟测科技</t>
+          <t>华岭股份</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报明确公司聚焦中高端晶圆及成品测试，拓展高算力产品测试，服务CPU/GPU/AI/FPGA、SoC/Chiplet/SiP等测试需求，并披露TSV工艺高性能AI产品整体测试方案研发；主板块由泛半导体测试收敛为高算力芯片测试服务。</t>
+          <t>证据中：2025年报显示测试服务仍为核心收入来源，并建设高算力应用芯片开放式测试创新服务平台；但公司2025年亏损扩大，AI/高算力测试仍处研发和客户拓展阶段，主线保留半导体测试服务，备注降级AI兑现强度。</t>
         </is>
       </c>
       <c r="E241" s="6" t="inlineStr">
@@ -7607,22 +7607,22 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>存储芯片测试设备</t>
+          <t>半导体测试服务</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>688627</t>
+          <t>688372</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>精智达</t>
+          <t>伟测科技</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报/公开资料显示半导体存储测试设备业务快速放量，并签订两笔约3.2亿元级半导体重大订单；公司推进高速FT测试机、老化测试修复设备、探针卡及HBM测试设备研发，HBM BI属于未来强化方向，主板块收敛为存储芯片测试设备。</t>
+          <t>证据强：2025年报明确公司聚焦中高端晶圆及成品测试，拓展高算力产品测试，服务CPU/GPU/AI/FPGA、SoC/Chiplet/SiP等测试需求，并披露TSV工艺高性能AI产品整体测试方案研发；主板块由泛半导体测试收敛为高算力芯片测试服务。</t>
         </is>
       </c>
       <c r="E242" s="6" t="inlineStr">
@@ -7634,22 +7634,22 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>半导体洁净室</t>
+          <t>存储芯片测试设备</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>603929</t>
+          <t>688627</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>亚翔集成</t>
+          <t>精智达</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司为IC半导体、光电、云计算中心等建厂工程提供洁净室、机电和建筑工程服务，净利润同比高增；AI受益路径来自半导体/存储扩产与厂务资本开支，属于配套基础设施而非芯片产品直接弹性。</t>
+          <t>证据强：2025年报/公开资料显示半导体存储测试设备业务快速放量，并签订两笔约3.2亿元级半导体重大订单；公司推进高速FT测试机、老化测试修复设备、探针卡及HBM测试设备研发，HBM BI属于未来强化方向，主板块收敛为存储芯片测试设备。</t>
         </is>
       </c>
       <c r="E243" s="6" t="inlineStr">
@@ -7666,17 +7666,17 @@
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>601133</t>
+          <t>603929</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>柏诚股份</t>
+          <t>亚翔集成</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报/摘要显示公司主要从事高等级洁净系统集成服务，覆盖半导体及泛半导体、新型显示、生命科学等；2025营收和利润承压且应收/合同资产占比较高，AI链条为晶圆厂扩产配套，保留半导体洁净室但降低弹性强度。</t>
+          <t>证据中强：2025年报披露公司为IC半导体、光电、云计算中心等建厂工程提供洁净室、机电和建筑工程服务，净利润同比高增；AI受益路径来自半导体/存储扩产与厂务资本开支，属于配套基础设施而非芯片产品直接弹性。</t>
         </is>
       </c>
       <c r="E244" s="6" t="inlineStr">
@@ -7693,17 +7693,17 @@
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>603163</t>
+          <t>601133</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>圣晖集成</t>
+          <t>柏诚股份</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报显示公司继续专注洁净室系统集成工程，覆盖设计、采购、施工和维护全链条，主要客户集中在半导体、电子等高科技行业，营收和利润高增；AI受益路径来自晶圆厂/先进封装/存储扩产的厂务资本开支。</t>
+          <t>证据中：2025年报/摘要显示公司主要从事高等级洁净系统集成服务，覆盖半导体及泛半导体、新型显示、生命科学等；2025营收和利润承压且应收/合同资产占比较高，AI链条为晶圆厂扩产配套，保留半导体洁净室但降低弹性强度。</t>
         </is>
       </c>
       <c r="E245" s="6" t="inlineStr">
@@ -7715,22 +7715,22 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>洁净过滤材料</t>
+          <t>半导体洁净室</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>603601</t>
+          <t>603163</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>再升科技</t>
+          <t>圣晖集成</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露公司干净空气材料包括高效空气滤材、PTFE膜等，是FFU、新风系统等核心部件，用于工业电子、生物医药等洁净场景；半导体洁净室链条为间接受益，且2025收入利润承压，故由半导体洁净过滤降级为洁净过滤材料。</t>
+          <t>证据强：2025年报显示公司继续专注洁净室系统集成工程，覆盖设计、采购、施工和维护全链条，主要客户集中在半导体、电子等高科技行业，营收和利润高增；AI受益路径来自晶圆厂/先进封装/存储扩产的厂务资本开支。</t>
         </is>
       </c>
       <c r="E246" s="6" t="inlineStr">
@@ -7742,22 +7742,22 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>半导体洁净过滤</t>
+          <t>洁净过滤材料</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>688376</t>
+          <t>603601</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>美埃科技</t>
+          <t>再升科技</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司聚焦工业级超洁净技术，风机过滤单元、过滤器和空气净化设备用于半导体等洁净厂房，并通过收购延伸洁净室墙壁和天花板系统；但2025净利润下滑，半导体项目延期压制业绩弹性。</t>
+          <t>证据中：2025年报披露公司干净空气材料包括高效空气滤材、PTFE膜等，是FFU、新风系统等核心部件，用于工业电子、生物医药等洁净场景；半导体洁净室链条为间接受益，且2025收入利润承压，故由半导体洁净过滤降级为洁净过滤材料。</t>
         </is>
       </c>
       <c r="E247" s="6" t="inlineStr">
@@ -7769,22 +7769,22 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>半导体高纯工艺系统</t>
+          <t>半导体洁净过滤</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>688376</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>新莱应材</t>
+          <t>美埃科技</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露泛半导体/高纯及超高纯应用材料收入增长，真空和UHP等级管道、管件、阀门、腔体、精密零部件用于半导体制程及厂务；液冷管路属于新布局且规模仍小，合并删减“液冷管路”重复行。</t>
+          <t>证据中强：2025年报披露公司聚焦工业级超洁净技术，风机过滤单元、过滤器和空气净化设备用于半导体等洁净厂房，并通过收购延伸洁净室墙壁和天花板系统；但2025净利润下滑，半导体项目延期压制业绩弹性。</t>
         </is>
       </c>
       <c r="E248" s="6" t="inlineStr">
@@ -7801,17 +7801,17 @@
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>603690</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>至纯科技</t>
+          <t>新莱应材</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报摘要披露公司业务围绕高纯工艺系统、制程设备、电子材料、零部件和专业服务，服务晶圆厂建设投产和运营量产；AI链条来自半导体扩产，但2025归母亏损扩大，湿法设备和高纯系统订单修复需继续验证。</t>
+          <t>证据中强：2025年报披露泛半导体/高纯及超高纯应用材料收入增长，真空和UHP等级管道、管件、阀门、腔体、精密零部件用于半导体制程及厂务；液冷管路属于新布局且规模仍小，合并删减“液冷管路”重复行。</t>
         </is>
       </c>
       <c r="E249" s="6" t="inlineStr">
@@ -7828,17 +7828,17 @@
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>688596</t>
+          <t>603690</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>正帆科技</t>
+          <t>至纯科技</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司稳固“制程关键系统、核心工艺材料与零组件、专业服务”三位一体定位，制程关键系统覆盖多数国内一线晶圆厂，GasBox等设备零部件获头部设备厂商采用；合并删减“半导体核心零部件”重复行。</t>
+          <t>证据中：2025年报摘要披露公司业务围绕高纯工艺系统、制程设备、电子材料、零部件和专业服务，服务晶圆厂建设投产和运营量产；AI链条来自半导体扩产，但2025归母亏损扩大，湿法设备和高纯系统订单修复需继续验证。</t>
         </is>
       </c>
       <c r="E250" s="6" t="inlineStr">
@@ -7850,22 +7850,22 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>半导体工艺废气处理</t>
+          <t>半导体高纯工艺系统</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>603324</t>
+          <t>688596</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>盛剑环境</t>
+          <t>正帆科技</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>证据中：公开简称盛剑科技，2025年报显示公司围绕半导体等泛半导体客户提供工艺废气治理、湿电子化学品供应与绿色厂务系统服务；AI受益来自晶圆厂扩产和厂务环保配套，非芯片设备直接弹性。</t>
+          <t>证据中强：2025年报披露公司稳固“制程关键系统、核心工艺材料与零组件、专业服务”三位一体定位，制程关键系统覆盖多数国内一线晶圆厂，GasBox等设备零部件获头部设备厂商采用；合并删减“半导体核心零部件”重复行。</t>
         </is>
       </c>
       <c r="E251" s="6" t="inlineStr">
@@ -7882,17 +7882,17 @@
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>301030</t>
+          <t>603324</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>仕净科技</t>
+          <t>盛剑环境</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>证据弱中：公司有泛半导体/光伏等制程污染防控与废气处理经验，但2025年受光伏客户和资产减值拖累出现大额亏损，半导体AI链条订单和收入证据不足；保留工艺废气处理，但在备注中降级为观察型厂务环保标的。</t>
+          <t>证据中：公开简称盛剑科技，2025年报显示公司围绕半导体等泛半导体客户提供工艺废气治理、湿电子化学品供应与绿色厂务系统服务；AI受益来自晶圆厂扩产和厂务环保配套，非芯片设备直接弹性。</t>
         </is>
       </c>
       <c r="E252" s="6" t="inlineStr">
@@ -7904,22 +7904,22 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>高纯湿电子化学品</t>
+          <t>半导体工艺废气处理</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>688549</t>
+          <t>301030</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>中巨芯-U</t>
+          <t>仕净科技</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报显示公司同时覆盖电子湿化学品、电子特种气体和前驱体材料，其中电子湿化学品收入占比约72.5%，电子特气及前驱体占比约23.9%；公司仍亏损，故由ALD-CVD前驱体修正为电子湿化学品。</t>
+          <t>证据弱中：公司有泛半导体/光伏等制程污染防控与废气处理经验，但2025年受光伏客户和资产减值拖累出现大额亏损，半导体AI链条订单和收入证据不足；保留工艺废气处理，但在备注中降级为观察型厂务环保标的。</t>
         </is>
       </c>
       <c r="E253" s="6" t="inlineStr">
@@ -7936,17 +7936,17 @@
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>300655</t>
+          <t>688549</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>晶瑞电材</t>
+          <t>中巨芯-U</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报显示公司扭亏并净利润大幅增长，业绩改善主要来自高纯湿化学品量价齐升，光刻胶业务稳健发展且KrF产品已有订单；原半导体光刻胶标签偏窄，收敛为更能解释业绩的高纯湿电子化学品。</t>
+          <t>证据中：2025年报显示公司同时覆盖电子湿化学品、电子特种气体和前驱体材料，其中电子湿化学品收入占比约72.5%，电子特气及前驱体占比约23.9%；公司仍亏损，故由ALD-CVD前驱体修正为电子湿化学品。</t>
         </is>
       </c>
       <c r="E254" s="6" t="inlineStr">
@@ -7958,22 +7958,22 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>光刻胶上游材料</t>
+          <t>高纯湿电子化学品</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>300429</t>
+          <t>300655</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>强力新材</t>
+          <t>晶瑞电材</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>公司核心是PCB/LCD/半导体光刻胶光引发剂等电子材料，PSPI先进封装材料项目提供AI先进封装可选弹性；主板块由干膜改为光刻胶上游材料，PSPI并入备注，先进封装电镀液证据不足降级删除。风险是PSPI量产节奏、库存减值、下游竞争和盈利修复。证据B/C。</t>
+          <t>证据中强：2025年报显示公司扭亏并净利润大幅增长，业绩改善主要来自高纯湿化学品量价齐升，光刻胶业务稳健发展且KrF产品已有订单；原半导体光刻胶标签偏窄，收敛为更能解释业绩的高纯湿电子化学品。</t>
         </is>
       </c>
       <c r="E255" s="6" t="inlineStr">
@@ -7985,22 +7985,22 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>半导体光刻胶</t>
+          <t>光刻胶上游材料</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>603650</t>
+          <t>300429</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>彤程新材</t>
+          <t>强力新材</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露半导体光刻胶业务高速增长，ArF光刻胶收入实现超800%突破，同时显示光刻胶规模优势稳固；RDL-Bumping属于先进封装光刻材料延伸，合并删减重复行。</t>
+          <t>公司核心是PCB/LCD/半导体光刻胶光引发剂等电子材料，PSPI先进封装材料项目提供AI先进封装可选弹性；主板块由干膜改为光刻胶上游材料，PSPI并入备注，先进封装电镀液证据不足降级删除。风险是PSPI量产节奏、库存减值、下游竞争和盈利修复。证据B/C。</t>
         </is>
       </c>
       <c r="E256" s="6" t="inlineStr">
@@ -8012,22 +8012,22 @@
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>CMP抛光材料</t>
+          <t>半导体光刻胶</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>688019</t>
+          <t>603650</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>安集科技</t>
+          <t>彤程新材</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司围绕CMP抛光液、功能性湿电子化学品、电镀液及核心原材料形成“3+1”平台，先进封装用TSV、混合键合、聚合物等抛光液在国内客户中作为首选供应商并销售上量；主板块由泛先进封装工艺材料收敛为CMP抛光材料。</t>
+          <t>证据强：2025年报披露半导体光刻胶业务高速增长，ArF光刻胶收入实现超800%突破，同时显示光刻胶规模优势稳固；RDL-Bumping属于先进封装光刻材料延伸，合并删减重复行。</t>
         </is>
       </c>
       <c r="E257" s="6" t="inlineStr">
@@ -8039,22 +8039,22 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>半导体电子特气</t>
+          <t>CMP抛光材料</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>688268</t>
+          <t>688019</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>华特气体</t>
+          <t>安集科技</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报摘要披露公司特种气体品种数量位居国内前列，已实现57个产品进口替代，覆盖国内8/12英寸集成电路制造厂商超90%客户，并切入全球顶尖半导体供应链；先进封装需求体现在电子特气增量，合并删减泛“先进封装工艺材料”重复行。</t>
+          <t>证据强：2025年报披露公司围绕CMP抛光液、功能性湿电子化学品、电镀液及核心原材料形成“3+1”平台，先进封装用TSV、混合键合、聚合物等抛光液在国内客户中作为首选供应商并销售上量；主板块由泛先进封装工艺材料收敛为CMP抛光材料。</t>
         </is>
       </c>
       <c r="E258" s="6" t="inlineStr">
@@ -8071,22 +8071,22 @@
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>688146</t>
+          <t>688268</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>中船特气</t>
+          <t>华特气体</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16 WF6复核后列为“main_candidate / 主受益候选”：公司具备直接WF6合成产能、6N产品能力、较高产能利用率和2027年新增产能规划，AI链条来自3D NAND/HBM/先进逻辑CVD钨沉积需求以及钨出口许可、APT/钨粉、WF6价格链。边界是Kanto Denka/Central Glass“2026-07-01永久停产”未获官方确认，公司也提示未签署新的长期或大额实质性订单，不能把WF6涨价线性外推为业绩。证据A/B/C。</t>
+          <t>证据强：2025年报摘要披露公司特种气体品种数量位居国内前列，已实现57个产品进口替代，覆盖国内8/12英寸集成电路制造厂商超90%客户，并切入全球顶尖半导体供应链；先进封装需求体现在电子特气增量，合并删减泛“先进封装工艺材料”重复行。</t>
         </is>
       </c>
       <c r="E259" s="6" t="inlineStr">
         <is>
-          <t>已处理；2026-06-16复核</t>
+          <t>已处理</t>
         </is>
       </c>
     </row>
@@ -8098,22 +8098,22 @@
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>600378</t>
+          <t>688146</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>昊华科技</t>
+          <t>中船特气</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>证据中强：昊华气体官网披露电子级六氟化钨5N产品，公开互动口径称WF6产能约600吨/年；AI链条来自先进制程/存储芯片CVD钨沉积用电子特气需求，确定性和客户验证透明度弱于中船特气，需跟踪6N升级、客户认证、出口订单和钨粉成本传导。</t>
+          <t>2026-06-16 WF6复核后列为“main_candidate / 主受益候选”：公司具备直接WF6合成产能、6N产品能力、较高产能利用率和2027年新增产能规划，AI链条来自3D NAND/HBM/先进逻辑CVD钨沉积需求以及钨出口许可、APT/钨粉、WF6价格链。边界是Kanto Denka/Central Glass“2026-07-01永久停产”未获官方确认，公司也提示未签署新的长期或大额实质性订单，不能把WF6涨价线性外推为业绩。证据A/B/C。</t>
         </is>
       </c>
       <c r="E260" s="6" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>已处理；2026-06-16复核</t>
         </is>
       </c>
     </row>
@@ -8125,17 +8125,17 @@
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>688106</t>
+          <t>600378</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>金宏气体</t>
+          <t>昊华科技</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露电子特种气体国内市占率约2.81%，电子大宗载气提纯、现场制气及多个半导体/显示项目持续导入；但公司2025年增收不增利、应收较高，主板块由单一电子特气扩为半导体电子气体。</t>
+          <t>证据中强：昊华气体官网披露电子级六氟化钨5N产品，公开互动口径称WF6产能约600吨/年；AI链条来自先进制程/存储芯片CVD钨沉积用电子特气需求，确定性和客户验证透明度弱于中船特气，需跟踪6N升级、客户认证、出口订单和钨粉成本传导。</t>
         </is>
       </c>
       <c r="E261" s="6" t="inlineStr">
@@ -8147,22 +8147,22 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>半导体前驱体材料</t>
+          <t>半导体电子特气</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>300346</t>
+          <t>688106</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>南大光电</t>
+          <t>金宏气体</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报显示公司围绕先进前驱体、电子特气、光刻胶及配套材料三大核心半导体材料发展，业绩连续增长；光刻胶有产业化突破但收入规模仍需跟踪，主线从光刻胶/ALD-CVD前驱体重复标签收敛为半导体前驱体材料。</t>
+          <t>证据中强：2025年报披露电子特种气体国内市占率约2.81%，电子大宗载气提纯、现场制气及多个半导体/显示项目持续导入；但公司2025年增收不增利、应收较高，主板块由单一电子特气扩为半导体电子气体。</t>
         </is>
       </c>
       <c r="E262" s="6" t="inlineStr">
@@ -8174,22 +8174,22 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>半导体高纯金属靶材</t>
+          <t>半导体前驱体材料</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>300666</t>
+          <t>300346</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>江丰电子</t>
+          <t>南大光电</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报显示公司核心产品为超高纯金属溅射靶材，覆盖先进制程及存储、逻辑、功率等客户，半导体靶材收入占比高；HBM TSV金属材料属于先进封装/存储升级延伸，证据仍弱于靶材主业，合并删减“HBM TSV金属材料”重复行。</t>
+          <t>证据中强：2025年报显示公司围绕先进前驱体、电子特气、光刻胶及配套材料三大核心半导体材料发展，业绩连续增长；光刻胶有产业化突破但收入规模仍需跟踪，主线从光刻胶/ALD-CVD前驱体重复标签收敛为半导体前驱体材料。</t>
         </is>
       </c>
       <c r="E263" s="6" t="inlineStr">
@@ -8206,17 +8206,17 @@
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>600206</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>有研新材</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司聚焦电子薄膜及贵金属材料等新材料，集成电路及半导体薄膜材料国产化需求持续；高纯金属靶材是更确定主线，HBM TSV金属材料属于先进存储/封装延伸，当前公开证据不足以作为主板块。</t>
+          <t>证据强：2025年报显示公司核心产品为超高纯金属溅射靶材，覆盖先进制程及存储、逻辑、功率等客户，半导体靶材收入占比高；HBM TSV金属材料属于先进封装/存储升级延伸，证据仍弱于靶材主业，合并删减“HBM TSV金属材料”重复行。</t>
         </is>
       </c>
       <c r="E264" s="6" t="inlineStr">
@@ -8228,22 +8228,22 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>半导体先进陶瓷部件</t>
+          <t>半导体高纯金属靶材</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>301611</t>
+          <t>600206</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>珂玛科技</t>
+          <t>有研新材</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司以半导体先进陶瓷零部件为核心，陶瓷加热器已大批量交付，静电卡盘8/12英寸产品通过客户验证并小规模量产；静电卡盘弹性清晰但收入仍小，主板块由单一静电卡盘修正为半导体先进陶瓷部件。</t>
+          <t>证据中强：2025年报披露公司聚焦电子薄膜及贵金属材料等新材料，集成电路及半导体薄膜材料国产化需求持续；高纯金属靶材是更确定主线，HBM TSV金属材料属于先进存储/封装延伸，当前公开证据不足以作为主板块。</t>
         </is>
       </c>
       <c r="E265" s="6" t="inlineStr">
@@ -8255,22 +8255,22 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>碳化硅衬底</t>
+          <t>半导体先进陶瓷部件</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>688234</t>
+          <t>301611</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>天岳先进</t>
+          <t>珂玛科技</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司主营碳化硅衬底，导电型SiC衬底全球份额27.6%、8英寸份额51.3%；AI数据中心拉动SiC材料应用是中长期变量，但2025收入下滑并亏损，需跟踪价格和产能利用率。</t>
+          <t>证据中强：2025年报披露公司以半导体先进陶瓷零部件为核心，陶瓷加热器已大批量交付，静电卡盘8/12英寸产品通过客户验证并小规模量产；静电卡盘弹性清晰但收入仍小，主板块由单一静电卡盘修正为半导体先进陶瓷部件。</t>
         </is>
       </c>
       <c r="E266" s="6" t="inlineStr">
@@ -8282,22 +8282,22 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>内存接口芯片</t>
+          <t>碳化硅衬底</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>688008</t>
+          <t>688234</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>澜起科技</t>
+          <t>天岳先进</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>DDR5 RCD/DB、MRCD/MDB、CKD是AI服务器高带宽内存互连核心节点，PCIe Retimer、CXL MXC扩展高速互连第二曲线；主板块收敛为内存接口芯片，HBM、DDR5 SPD、SOCAMM、CXL和CXL内存扩展模组均并入备注或删除，避免误当存储模组/HBM厂商。风险是海外竞争、服务器平台迭代和新品放量节奏。证据A。</t>
+          <t>证据强：2025年报披露公司主营碳化硅衬底，导电型SiC衬底全球份额27.6%、8英寸份额51.3%；AI数据中心拉动SiC材料应用是中长期变量，但2025收入下滑并亏损，需跟踪价格和产能利用率。</t>
         </is>
       </c>
       <c r="E267" s="6" t="inlineStr">
@@ -8309,22 +8309,22 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>DDR5 SPD</t>
+          <t>内存接口芯片</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>688123</t>
+          <t>688008</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>聚辰股份</t>
+          <t>澜起科技</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>公司具备DDR2/3/4/5内存模组配套SPD、TS等芯片产品，DDR5 SPD受益AI服务器内存模组数量提升，是明确的小芯片弹性节点；主板块保留DDR5 SPD，SOCAMM作为下游内存模组形态并入备注，不单列。风险是DDR5渗透节奏、客户导入、EEPROM周期和价格竞争。证据A。</t>
+          <t>DDR5 RCD/DB、MRCD/MDB、CKD是AI服务器高带宽内存互连核心节点，PCIe Retimer、CXL MXC扩展高速互连第二曲线；主板块收敛为内存接口芯片，HBM、DDR5 SPD、SOCAMM、CXL和CXL内存扩展模组均并入备注或删除，避免误当存储模组/HBM厂商。风险是海外竞争、服务器平台迭代和新品放量节奏。证据A。</t>
         </is>
       </c>
       <c r="E268" s="6" t="inlineStr">
@@ -8336,22 +8336,22 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>高端存储分销</t>
+          <t>DDR5 SPD</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>688123</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>聚辰股份</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>公司以SK海力士核心代理分销为基本盘，向国内云服务器龙头和大型ODM提供存储解决方案；HBM/DDR5紧缺带来强周期弹性，但本质不是HBM制造商。自主海普存储企业级SSD/DRAM开始贡献增量。主板块由HBM改为高端存储分销，风险是存储价格周期、供应商授权、分销毛利和库存。证据A/B。</t>
+          <t>公司具备DDR2/3/4/5内存模组配套SPD、TS等芯片产品，DDR5 SPD受益AI服务器内存模组数量提升，是明确的小芯片弹性节点；主板块保留DDR5 SPD，SOCAMM作为下游内存模组形态并入备注，不单列。风险是DDR5渗透节奏、客户导入、EEPROM周期和价格竞争。证据A。</t>
         </is>
       </c>
       <c r="E269" s="6" t="inlineStr">
@@ -8363,22 +8363,22 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>企业级存储模组</t>
+          <t>高端存储分销</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>688525</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>佰维存储</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>公司企业级存储方案覆盖PCIe/SATA SSD、DDR4/DDR5 RDIMM和CXL内存扩展模组，服务数据中心、服务器和AI工作负载；主板块由DDR5 SPD改为企业级存储模组，SOCAMM、企业级SSD、SSD主控、UFS、晶圆级封测和CXL并入备注或降级。风险是NAND/DRAM价格周期、库存、客户认证和自研控制器/封测兑现。证据B。</t>
+          <t>公司以SK海力士核心代理分销为基本盘，向国内云服务器龙头和大型ODM提供存储解决方案；HBM/DDR5紧缺带来强周期弹性，但本质不是HBM制造商。自主海普存储企业级SSD/DRAM开始贡献增量。主板块由HBM改为高端存储分销，风险是存储价格周期、供应商授权、分销毛利和库存。证据A/B。</t>
         </is>
       </c>
       <c r="E270" s="6" t="inlineStr">
@@ -8395,17 +8395,17 @@
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>688525</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>佰维存储</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>公司企业级eSSD和RDIMM已在互联网、运营商等客户完成验证并批量出货，SOCAMM2、CXL内存扩展、MRDIMM等构成AI服务器存储升级可选项；主板块由SOCAMM改为企业级存储模组，端侧UFS、eMMC、SSD主控、SPU、HLC-iSA、mSSD和CXL并入备注。SOCAMM2仍需收入贡献验证。证据A/B。</t>
+          <t>公司企业级存储方案覆盖PCIe/SATA SSD、DDR4/DDR5 RDIMM和CXL内存扩展模组，服务数据中心、服务器和AI工作负载；主板块由DDR5 SPD改为企业级存储模组，SOCAMM、企业级SSD、SSD主控、UFS、晶圆级封测和CXL并入备注或降级。风险是NAND/DRAM价格周期、库存、客户认证和自研控制器/封测兑现。证据B。</t>
         </is>
       </c>
       <c r="E271" s="6" t="inlineStr">
@@ -8417,22 +8417,22 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>企业级SSD</t>
+          <t>企业级存储模组</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报摘要披露AI浪潮下公司加快向高容量、高性能固态硬盘拓展，重点聚焦QLC NAND企业级应用方向；自研主控是能力基础，但表格保留最贴近收入承载的“企业级SSD”，删减企业级SSD主控、QLC SSD、AI场景化存储方案重复行。风险是存储价格周期和经营现金流波动。</t>
+          <t>公司企业级eSSD和RDIMM已在互联网、运营商等客户完成验证并批量出货，SOCAMM2、CXL内存扩展、MRDIMM等构成AI服务器存储升级可选项；主板块由SOCAMM改为企业级存储模组，端侧UFS、eMMC、SSD主控、SPU、HLC-iSA、mSSD和CXL并入备注。SOCAMM2仍需收入贡献验证。证据A/B。</t>
         </is>
       </c>
       <c r="E272" s="6" t="inlineStr">
@@ -8444,22 +8444,22 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>企业级SSD主控</t>
+          <t>企业级SSD</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>300672</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>国科微</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>证据中偏弱：公司固态存储主控芯片实现国产替代，同时布局端侧AI、车载电子、智慧视觉等多条芯片线；AI数据中心企业级SSD客户、收入占比和订单仍未充分披露，保留为SSD主控国产替代观察，基本面需关注2025亏损后毛利修复和研发投入转化。</t>
+          <t>证据中强：2025年报摘要披露AI浪潮下公司加快向高容量、高性能固态硬盘拓展，重点聚焦QLC NAND企业级应用方向；自研主控是能力基础，但表格保留最贴近收入承载的“企业级SSD”，删减企业级SSD主控、QLC SSD、AI场景化存储方案重复行。风险是存储价格周期和经营现金流波动。</t>
         </is>
       </c>
       <c r="E273" s="6" t="inlineStr">
@@ -8476,17 +8476,17 @@
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>688449</t>
+          <t>300672</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>联芸科技</t>
+          <t>国科微</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露SSD主控覆盖SATA、PCIe3.0/4.0/5.0，企业级PCIe Gen5 SSD主控已进入量产测试阶段，并规划PCIe Gen6/Gen7切入数据中心；删减UFS主控重复行，UFS偏终端嵌入式，AI算力弹性以企业级SSD主控为主。</t>
+          <t>证据中偏弱：公司固态存储主控芯片实现国产替代，同时布局端侧AI、车载电子、智慧视觉等多条芯片线；AI数据中心企业级SSD客户、收入占比和订单仍未充分披露，保留为SSD主控国产替代观察，基本面需关注2025亏损后毛利修复和研发投入转化。</t>
         </is>
       </c>
       <c r="E274" s="6" t="inlineStr">
@@ -8498,22 +8498,22 @@
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>AI存储</t>
+          <t>企业级SSD主控</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>300302</t>
+          <t>688449</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>同有科技</t>
+          <t>联芸科技</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露高端存储在AI智算中心、高性能计算等核心场景推进，NVMe/RDMA高性能分布式文件存储用于智算领域高并发、低延迟需求；主板块保留AI存储，跟踪标杆方案复制、国产化替代和毛利率。</t>
+          <t>证据强：2025年报披露SSD主控覆盖SATA、PCIe3.0/4.0/5.0，企业级PCIe Gen5 SSD主控已进入量产测试阶段，并规划PCIe Gen6/Gen7切入数据中心；删减UFS主控重复行，UFS偏终端嵌入式，AI算力弹性以企业级SSD主控为主。</t>
         </is>
       </c>
       <c r="E275" s="6" t="inlineStr">
@@ -8525,30 +8525,34 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>HBF高带宽闪存</t>
+          <t>AI存储</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>300302</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>暂无成熟A股纯标的</t>
+          <t>同有科技</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>德明利2025半年报提到闪迪HBF结合3D NAND与HBM、适合读取密集型AI推理任务；A股暂无成熟高带宽闪存纯标的。</t>
-        </is>
-      </c>
-      <c r="E276" s="6" t="n"/>
+          <t>证据强：2025年报披露高端存储在AI智算中心、高性能计算等核心场景推进，NVMe/RDMA高性能分布式文件存储用于智算领域高并发、低延迟需求；主板块保留AI存储，跟踪标杆方案复制、国产化替代和毛利率。</t>
+        </is>
+      </c>
+      <c r="E276" s="6" t="inlineStr">
+        <is>
+          <t>已处理</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>Nearline HDD</t>
+          <t>HBF高带宽闪存</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
@@ -8563,7 +8567,7 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>希捷和西部数据官方披露AI数据增长推动数据中心exabyte级低成本存储需求；近线HDD仍主要由海外双寡头主导。</t>
+          <t>德明利2025半年报提到闪迪HBF结合3D NAND与HBM、适合读取密集型AI推理任务；A股暂无成熟高带宽闪存纯标的。</t>
         </is>
       </c>
       <c r="E277" s="6" t="n"/>
@@ -8571,7 +8575,7 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>HAMR-ePMR高容量HDD</t>
+          <t>Nearline HDD</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -8586,7 +8590,7 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>希捷披露HAMR Mozaic放量，西部数据披露40TB UltraSMR ePMR验证和HAMR 100TB路线；A股暂无成熟HDD主线标的。</t>
+          <t>希捷和西部数据官方披露AI数据增长推动数据中心exabyte级低成本存储需求；近线HDD仍主要由海外双寡头主导。</t>
         </is>
       </c>
       <c r="E278" s="6" t="n"/>
@@ -8594,7 +8598,7 @@
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>高带宽HDD</t>
+          <t>HAMR-ePMR高容量HDD</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -8609,7 +8613,7 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>西部数据2026 Innovation Day披露High Bandwidth Drive与Dual Pivot提升HDD带宽/IO，服务AI温冷数据层，A股暂无对应纯标的。</t>
+          <t>希捷披露HAMR Mozaic放量，西部数据披露40TB UltraSMR ePMR验证和HAMR 100TB路线；A股暂无成熟HDD主线标的。</t>
         </is>
       </c>
       <c r="E279" s="6" t="n"/>
@@ -8617,7 +8621,7 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>CXL</t>
+          <t>高带宽HDD</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -8632,7 +8636,7 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Astera/Broadcom/Marvell主导高速互连芯片，A股除澜起接口芯片外不宜硬凑纯Retimer/PCIe switch标的。</t>
+          <t>西部数据2026 Innovation Day披露High Bandwidth Drive与Dual Pivot提升HDD带宽/IO，服务AI温冷数据层，A股暂无对应纯标的。</t>
         </is>
       </c>
       <c r="E280" s="6" t="n"/>
@@ -8640,22 +8644,22 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>CXL内存扩展模组</t>
+          <t>CXL</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
           <t>暂无成熟A股纯标的</t>
         </is>
       </c>
-      <c r="C281" s="2" t="inlineStr">
-        <is>
-          <t>CXL Switch暂无成熟A股纯标的</t>
-        </is>
-      </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>CXL交换/池化控制仍主要由Marvell等海外厂商推进，A股目前缺成熟CXL Switch纯标的。</t>
+          <t>Astera/Broadcom/Marvell主导高速互连芯片，A股除澜起接口芯片外不宜硬凑纯Retimer/PCIe switch标的。</t>
         </is>
       </c>
       <c r="E281" s="6" t="n"/>
@@ -8663,49 +8667,45 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>HBM BI</t>
+          <t>CXL内存扩展模组</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>300567</t>
+          <t>暂无成熟A股纯标的</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>精测电子</t>
+          <t>CXL Switch暂无成熟A股纯标的</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>检测设备平台，2025年报摘要披露推出JH5520 HBM BI测试系统以满足HBM高端存储测试需求，半导体量检测覆盖前道、后道电测和先进封装；主板块改为HBM BI，PCB AOI、半导体量测和先进封装X-Ray并入备注，风险是半导体业务收入占比、客户认证和设备订单兑现。证据A/B。</t>
-        </is>
-      </c>
-      <c r="E282" s="6" t="inlineStr">
-        <is>
-          <t>已处理</t>
-        </is>
-      </c>
+          <t>CXL交换/池化控制仍主要由Marvell等海外厂商推进，A股目前缺成熟CXL Switch纯标的。</t>
+        </is>
+      </c>
+      <c r="E282" s="6" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>AI服务器整机</t>
+          <t>HBM BI</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>300567</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>精测电子</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>证据中强：公司核心是高端计算机、智能计算和算力服务，2025年报披露继续围绕AI算力、液冷散热、高速互联等核心领域投入；AI存储和推理板卡只是配套能力，删减AI存储、AI推理板卡、AI服务器ODM重复行，保留更准确的AI服务器整机/智算底座定位。</t>
+          <t>检测设备平台，2025年报摘要披露推出JH5520 HBM BI测试系统以满足HBM高端存储测试需求，半导体量检测覆盖前道、后道电测和先进封装；主板块改为HBM BI，PCB AOI、半导体量测和先进封装X-Ray并入备注，风险是半导体业务收入占比、客户认证和设备订单兑现。证据A/B。</t>
         </is>
       </c>
       <c r="E283" s="6" t="inlineStr">
@@ -8722,17 +8722,17 @@
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>000977</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>浪潮信息</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露总营收1647.82亿元、同比增长43.25%，主要由服务器产品销售增长驱动；存储交换类收入占比小，删减AI存储重复行，主板块改为AI服务器整机。风险是服务器高增但毛利率偏低，GPU/核心器件供应和价格压力影响利润弹性。</t>
+          <t>证据中强：公司核心是高端计算机、智能计算和算力服务，2025年报披露继续围绕AI算力、液冷散热、高速互联等核心领域投入；AI存储和推理板卡只是配套能力，删减AI存储、AI推理板卡、AI服务器ODM重复行，保留更准确的AI服务器整机/智算底座定位。</t>
         </is>
       </c>
       <c r="E284" s="6" t="inlineStr">
@@ -8749,17 +8749,17 @@
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>000034</t>
+          <t>000977</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>神州数码</t>
+          <t>浪潮信息</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露AI相关业务收入330.3亿元、同比增长47.7%，神州鲲泰服务器基于鲲鹏CPU+昇腾NPU支持DeepSeek等大模型私有化部署，并开放国产技术栈AI智算OpenLab；主线是国产算力整机和方案。</t>
+          <t>证据强：2025年报披露总营收1647.82亿元、同比增长43.25%，主要由服务器产品销售增长驱动；存储交换类收入占比小，删减AI存储重复行，主板块改为AI服务器整机。风险是服务器高增但毛利率偏低，GPU/核心器件供应和价格压力影响利润弹性。</t>
         </is>
       </c>
       <c r="E285" s="6" t="inlineStr">
@@ -8776,17 +8776,17 @@
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>002261</t>
+          <t>000034</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>拓维信息</t>
+          <t>神州数码</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报摘要披露公司基于“鲲鹏+昇腾AI”算力底座，推出中心侧高性能服务器、推理服务器和边端终端侧产品；主板块从国产AI服务器收敛为昇腾AI服务器，风险是收入下滑、利润体量仍小。</t>
+          <t>证据中强：2025年报披露AI相关业务收入330.3亿元、同比增长47.7%，神州鲲泰服务器基于鲲鹏CPU+昇腾NPU支持DeepSeek等大模型私有化部署，并开放国产技术栈AI智算OpenLab；主线是国产算力整机和方案。</t>
         </is>
       </c>
       <c r="E286" s="6" t="inlineStr">
@@ -8798,22 +8798,22 @@
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>AI服务器ODM</t>
+          <t>AI服务器整机</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>601138</t>
+          <t>002261</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>工业富联</t>
+          <t>拓维信息</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司与全球头部客户协同下一代AI服务器及液冷技术，云服务商AI服务器收入同比大增，GPU与ASIC方案产品快速增长；删减“AI服务器机柜”重复行，机柜/液冷作为ODM系统能力纳入备注。</t>
+          <t>证据中：2025年报摘要披露公司基于“鲲鹏+昇腾AI”算力底座，推出中心侧高性能服务器、推理服务器和边端终端侧产品；主板块从国产AI服务器收敛为昇腾AI服务器，风险是收入下滑、利润体量仍小。</t>
         </is>
       </c>
       <c r="E287" s="6" t="inlineStr">
@@ -8830,17 +8830,17 @@
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>603296</t>
+          <t>601138</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>华勤技术</t>
+          <t>工业富联</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露华勤数据中心业务形成AI服务器、通用服务器、交换机等全栈产品组合，数据中心业务收入754.75亿元、同比增长51.93%；主板块保留AI服务器ODM，AI PC和终端ODM作为附属受益。</t>
+          <t>证据强：2025年报披露公司与全球头部客户协同下一代AI服务器及液冷技术，云服务商AI服务器收入同比大增，GPU与ASIC方案产品快速增长；删减“AI服务器机柜”重复行，机柜/液冷作为ODM系统能力纳入备注。</t>
         </is>
       </c>
       <c r="E288" s="6" t="inlineStr">
@@ -8852,22 +8852,22 @@
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>算力服务器结构件</t>
+          <t>AI服务器ODM</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>002965</t>
+          <t>603296</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>祥鑫科技</t>
+          <t>华勤技术</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>证据中弱：2025年报披露公司在通信设备领域可供应通讯插箱、交换机箱、算力服务器等产品和服务，但汽车业务仍占收入主体且净利润下滑；主板块由AI服务器机柜收敛为算力服务器结构件，AI订单强度需继续验证。</t>
+          <t>证据强：2025年报披露华勤数据中心业务形成AI服务器、通用服务器、交换机等全栈产品组合，数据中心业务收入754.75亿元、同比增长51.93%；主板块保留AI服务器ODM，AI PC和终端ODM作为附属受益。</t>
         </is>
       </c>
       <c r="E289" s="6" t="inlineStr">
@@ -8879,22 +8879,22 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>智能算力产品及服务</t>
+          <t>算力服务器结构件</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>300857</t>
+          <t>002965</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>协创数据</t>
+          <t>祥鑫科技</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露智能算力产品及服务收入27.61亿元、同比增长1727.17%、占总收入22.57%，成为第二大收入支柱；原IDC标签不准确，改为智能算力产品及服务。</t>
+          <t>证据中弱：2025年报披露公司在通信设备领域可供应通讯插箱、交换机箱、算力服务器等产品和服务，但汽车业务仍占收入主体且净利润下滑；主板块由AI服务器机柜收敛为算力服务器结构件，AI订单强度需继续验证。</t>
         </is>
       </c>
       <c r="E290" s="6" t="inlineStr">
@@ -8906,22 +8906,22 @@
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>国产AI加速芯片</t>
+          <t>智能算力产品及服务</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>688256</t>
+          <t>300857</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>寒武纪</t>
+          <t>协创数据</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司云边端智能芯片及板卡矩阵，云端产品线面向服务器和数据中心AI处理，收入大增并首次全年盈利；删减“AI推理板卡”重复行，板卡是产品形态，主板块归入国产AI加速芯片。</t>
+          <t>证据强：2025年报披露智能算力产品及服务收入27.61亿元、同比增长1727.17%、占总收入22.57%，成为第二大收入支柱；原IDC标签不准确，改为智能算力产品及服务。</t>
         </is>
       </c>
       <c r="E291" s="6" t="inlineStr">
@@ -8933,22 +8933,22 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>国产CPU-DCU芯片</t>
+          <t>国产AI加速芯片</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>688041</t>
+          <t>688256</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>寒武纪</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报及公开资料显示海光坚持CPU+DCU双芯战略，DCU软件栈适配大模型训练推理并在多行业场景落地；删减“AI推理板卡”重复行，核心价值在国产高端处理器和DCU算力平台。</t>
+          <t>证据强：2025年报披露公司云边端智能芯片及板卡矩阵，云端产品线面向服务器和数据中心AI处理，收入大增并首次全年盈利；删减“AI推理板卡”重复行，板卡是产品形态，主板块归入国产AI加速芯片。</t>
         </is>
       </c>
       <c r="E292" s="6" t="inlineStr">
@@ -8960,22 +8960,22 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>国产GPU芯片</t>
+          <t>国产CPU-DCU芯片</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>300474</t>
+          <t>688041</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>景嘉微</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露公司推进“高性能GPU+边端侧AI SoC芯片”双轮驱动，景宏系列智算模块及整机产品瞄准AI训练和推理；删减“AI推理板卡”重复行，当前仍以国产GPU芯片为主线，亏损和商业化规模是主要风险。</t>
+          <t>证据强：2025年报及公开资料显示海光坚持CPU+DCU双芯战略，DCU软件栈适配大模型训练推理并在多行业场景落地；删减“AI推理板卡”重复行，核心价值在国产高端处理器和DCU算力平台。</t>
         </is>
       </c>
       <c r="E293" s="6" t="inlineStr">
@@ -8987,22 +8987,22 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>AI推理芯片</t>
+          <t>国产GPU芯片</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>688343</t>
+          <t>300474</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>云天励飞</t>
+          <t>景嘉微</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司构建应用、算法、芯片全栈能力，自研AI推理芯片适配国产大模型、操作系统和推理框架，并推出大模型一体机；一体机为产品化形态，主板块保留AI推理芯片。</t>
+          <t>证据中：2025年报披露公司推进“高性能GPU+边端侧AI SoC芯片”双轮驱动，景宏系列智算模块及整机产品瞄准AI训练和推理；删减“AI推理板卡”重复行，当前仍以国产GPU芯片为主线，亏损和商业化规模是主要风险。</t>
         </is>
       </c>
       <c r="E294" s="6" t="inlineStr">
@@ -9014,22 +9014,22 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>智算网络设备</t>
+          <t>AI推理芯片</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>000938</t>
+          <t>688343</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>紫光股份</t>
+          <t>云天励飞</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>证据强：新华三深度覆盖云、网、安、算、存、端，但公司披露中国数据中心交换机份额居前，并在智算网络、800G/CPO交换机和AI算力基础设施上持续推进；删减AI存储、AI服务器ODM重复行，主板块保留最能体现差异化和份额优势的智算交换机。</t>
+          <t>证据中强：2025年报披露公司构建应用、算法、芯片全栈能力，自研AI推理芯片适配国产大模型、操作系统和推理框架，并推出大模型一体机；一体机为产品化形态，主板块保留AI推理芯片。</t>
         </is>
       </c>
       <c r="E295" s="6" t="inlineStr">
@@ -9046,17 +9046,17 @@
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>301165</t>
+          <t>000938</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>锐捷网络</t>
+          <t>紫光股份</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露AI智算中心网络方案已服务中国移动、阿里、字节、百度、腾讯等训练/推理大模型场景，数据中心交换机订单加速交付；IDC数据显示中国数据中心交换机市占率第三。</t>
+          <t>证据强：新华三深度覆盖云、网、安、算、存、端，但公司披露中国数据中心交换机份额居前，并在智算网络、800G/CPO交换机和AI算力基础设施上持续推进；删减AI存储、AI服务器ODM重复行，主板块保留最能体现差异化和份额优势的智算交换机。</t>
         </is>
       </c>
       <c r="E296" s="6" t="inlineStr">
@@ -9073,17 +9073,17 @@
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>000063</t>
+          <t>301165</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>中兴通讯</t>
+          <t>锐捷网络</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报及公司新闻披露算力业务收入同比约150%，服务器及存储同比超200%，数据中心产品同比增长；公司以自研AI大容量交换芯片支撑智算超节点和万卡级智算中心，主板块从交换机扩展为智算网络设备。</t>
+          <t>证据强：2025年报披露AI智算中心网络方案已服务中国移动、阿里、字节、百度、腾讯等训练/推理大模型场景，数据中心交换机订单加速交付；IDC数据显示中国数据中心交换机市占率第三。</t>
         </is>
       </c>
       <c r="E297" s="6" t="inlineStr">
@@ -9095,22 +9095,22 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>以太网交换芯片</t>
+          <t>智算网络设备</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>688702</t>
+          <t>000063</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>盛科通信-U</t>
+          <t>中兴通讯</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司主营以太网交换芯片及配套产品，交换芯片收入8.31亿元、占营收72.26%，交换机收入占比较低；删减“智算交换机”重复行，保留最能体现价值量的以太网交换芯片，风险是亏损扩大和高端产品放量节奏。</t>
+          <t>证据强：2025年报及公司新闻披露算力业务收入同比约150%，服务器及存储同比超200%，数据中心产品同比增长；公司以自研AI大容量交换芯片支撑智算超节点和万卡级智算中心，主板块从交换机扩展为智算网络设备。</t>
         </is>
       </c>
       <c r="E298" s="6" t="inlineStr">
@@ -9122,22 +9122,22 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>以太网PHY-交换芯片</t>
+          <t>以太网交换芯片</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>688515</t>
+          <t>688702</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>裕太微</t>
+          <t>盛科通信-U</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露公司专注高速有线通信芯片，网通PHY、交换机芯片、网卡芯片已规模量产，网通类产品销量约1.4亿颗，并向数据中心与基站等高价值场景延伸；AI数据中心直接收入仍需跟踪。</t>
+          <t>证据中强：2025年报披露公司主营以太网交换芯片及配套产品，交换芯片收入8.31亿元、占营收72.26%，交换机收入占比较低；删减“智算交换机”重复行，保留最能体现价值量的以太网交换芯片，风险是亏损扩大和高端产品放量节奏。</t>
         </is>
       </c>
       <c r="E299" s="6" t="inlineStr">
@@ -9149,30 +9149,34 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>PCIe Switch</t>
+          <t>以太网PHY-交换芯片</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>暂无成熟A股纯标的</t>
+          <t>688515</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>暂无成熟A股纯标的</t>
+          <t>裕太微</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>GPU集群内PCIe Switch、NVSwitch和高端交换ASIC主要由NVIDIA、Broadcom、Microchip、Astera等海外厂商主导，A股不硬凑。</t>
-        </is>
-      </c>
-      <c r="E300" s="6" t="n"/>
+          <t>证据中：2025年报披露公司专注高速有线通信芯片，网通PHY、交换机芯片、网卡芯片已规模量产，网通类产品销量约1.4亿颗，并向数据中心与基站等高价值场景延伸；AI数据中心直接收入仍需跟踪。</t>
+        </is>
+      </c>
+      <c r="E300" s="6" t="inlineStr">
+        <is>
+          <t>已处理</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>BMC</t>
+          <t>PCIe Switch</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">
@@ -9187,7 +9191,7 @@
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>AI服务器BMC/远程管理芯片以海外和台湾厂商为主，A股目前缺成熟纯标的，先列系统级空白。</t>
+          <t>GPU集群内PCIe Switch、NVSwitch和高端交换ASIC主要由NVIDIA、Broadcom、Microchip、Astera等海外厂商主导，A股不硬凑。</t>
         </is>
       </c>
       <c r="E301" s="6" t="n"/>
@@ -9195,49 +9199,45 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>Edge BMC管理芯片</t>
+          <t>BMC</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>688595</t>
+          <t>暂无成熟A股纯标的</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>芯海科技</t>
+          <t>暂无成熟A股纯标的</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报摘要披露面向边缘计算及服务器市场的轻量级edge BMC管理芯片已上市并量产销售，同时EC芯片在AI PC量产；保留BMC但改为Edge BMC管理芯片，风险是公司仍亏损且BMC收入规模未单列。</t>
-        </is>
-      </c>
-      <c r="E302" s="6" t="inlineStr">
-        <is>
-          <t>已处理</t>
-        </is>
-      </c>
+          <t>AI服务器BMC/远程管理芯片以海外和台湾厂商为主，A股目前缺成熟纯标的，先列系统级空白。</t>
+        </is>
+      </c>
+      <c r="E302" s="6" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>低抖动时钟源</t>
+          <t>Edge BMC管理芯片</t>
         </is>
       </c>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>603738</t>
+          <t>688595</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>泰晶科技</t>
+          <t>芯海科技</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报/半年报披露公司开发面向AI数据中心基础设施的312.5MHz差分输出温补振荡器和低抖动可编程振荡器，满足AI数据中心、3.2T光模块、AI算力等需求；主板块保留低抖动时钟源。</t>
+          <t>证据中：2025年报摘要披露面向边缘计算及服务器市场的轻量级edge BMC管理芯片已上市并量产销售，同时EC芯片在AI PC量产；保留BMC但改为Edge BMC管理芯片，风险是公司仍亏损且BMC收入规模未单列。</t>
         </is>
       </c>
       <c r="E303" s="6" t="inlineStr">
@@ -9249,22 +9249,22 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>高频晶振</t>
+          <t>低抖动时钟源</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>300460</t>
+          <t>603738</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>惠伦晶体</t>
+          <t>泰晶科技</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>证据弱：2025半年报披露公司主营石英晶体元器件，高频产品和服务器等领域方案商认证具备基础支撑价值；但2025年仍亏损且未见明确AI服务器低抖动订单，主板块由低抖动时钟源降级为高频晶振观察。</t>
+          <t>证据中强：2025年报/半年报披露公司开发面向AI数据中心基础设施的312.5MHz差分输出温补振荡器和低抖动可编程振荡器，满足AI数据中心、3.2T光模块、AI算力等需求；主板块保留低抖动时钟源。</t>
         </is>
       </c>
       <c r="E304" s="6" t="inlineStr">
@@ -9276,22 +9276,22 @@
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>IDC</t>
+          <t>高频晶振</t>
         </is>
       </c>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>600845</t>
+          <t>300460</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>宝信软件</t>
+          <t>惠伦晶体</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>工业软件和IDC双主业，宝之云IDC、华北基地、人工智能算力资源池等资产构成算力基础设施运营侧真实映射；DCIM不是公司最核心的AI受益解释。主板块由DCIM改为IDC，原IDC重复行合并删除。风险是钢铁行业软件需求承压、IDC资本开支和上架率、电力成本、AI算力资源池回报周期。证据A/B。</t>
+          <t>证据弱：2025半年报披露公司主营石英晶体元器件，高频产品和服务器等领域方案商认证具备基础支撑价值；但2025年仍亏损且未见明确AI服务器低抖动订单，主板块由低抖动时钟源降级为高频晶振观察。</t>
         </is>
       </c>
       <c r="E305" s="6" t="inlineStr">
@@ -9303,22 +9303,22 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>AIDC智算中心</t>
+          <t>IDC</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>300442</t>
+          <t>600845</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>润泽科技</t>
+          <t>宝信软件</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报显示AIDC收入25.1亿元、占总收入44.24%，新增交付算力规模220MW且含单体100MW智算中心；合并IDC/算力中心运维，主线改为AIDC智算中心。</t>
+          <t>工业软件和IDC双主业，宝之云IDC、华北基地、人工智能算力资源池等资产构成算力基础设施运营侧真实映射；DCIM不是公司最核心的AI受益解释。主板块由DCIM改为IDC，原IDC重复行合并删除。风险是钢铁行业软件需求承压、IDC资本开支和上架率、电力成本、AI算力资源池回报周期。证据A/B。</t>
         </is>
       </c>
       <c r="E306" s="6" t="inlineStr">
@@ -9330,22 +9330,22 @@
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>IDC及算力租赁</t>
+          <t>AIDC智算中心</t>
         </is>
       </c>
       <c r="B307" s="3" t="inlineStr">
         <is>
-          <t>300738</t>
+          <t>300442</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>奥飞数据</t>
+          <t>润泽科技</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露业务为IDC及互联网综合服务，报告期新项目投产并继续推进算力租赁和相关设备销售；AI链受益来自机柜上架和算力需求，保留IDC及算力租赁。</t>
+          <t>证据强：2025年报显示AIDC收入25.1亿元、占总收入44.24%，新增交付算力规模220MW且含单体100MW智算中心；合并IDC/算力中心运维，主线改为AIDC智算中心。</t>
         </is>
       </c>
       <c r="E307" s="6" t="inlineStr">
@@ -9357,22 +9357,22 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>IDC云计算基础设施</t>
+          <t>IDC及算力租赁</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>300383</t>
+          <t>300738</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>光环新网</t>
+          <t>奥飞数据</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露主营仍是IDC及云计算，AI爆发带动数据中心与云计算需求，并与格灵深瞳合作AI+行业智算云；直接算力运营收入未充分拆分，保留IDC云计算基础设施。</t>
+          <t>证据中：2025年报披露业务为IDC及互联网综合服务，报告期新项目投产并继续推进算力租赁和相关设备销售；AI链受益来自机柜上架和算力需求，保留IDC及算力租赁。</t>
         </is>
       </c>
       <c r="E308" s="6" t="inlineStr">
@@ -9384,22 +9384,22 @@
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>算力中心运维</t>
+          <t>IDC云计算基础设施</t>
         </is>
       </c>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>002929</t>
+          <t>300383</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>润建股份</t>
+          <t>光环新网</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露算力网络业务增长、算力中心管理运维和智算云服务推进，但AI及算力收入占比仍较小且归母净利下滑；保留算力中心运维并下调盈利确定性。</t>
+          <t>证据中：2025年报披露主营仍是IDC及云计算，AI爆发带动数据中心与云计算需求，并与格灵深瞳合作AI+行业智算云；直接算力运营收入未充分拆分，保留IDC云计算基础设施。</t>
         </is>
       </c>
       <c r="E309" s="6" t="inlineStr">
@@ -9411,22 +9411,22 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>算力设备交付运维</t>
+          <t>算力中心运维</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>301085</t>
+          <t>002929</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>亚康股份</t>
+          <t>润建股份</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报摘要披露向富士康、英业达、华勤、浪潮等算力服务器制造商提供交付及售后维保，并从传统数据中心向AI智算中心运维升级；公司亏损，主线为算力设备交付运维。</t>
+          <t>证据中：2025年报披露算力网络业务增长、算力中心管理运维和智算云服务推进，但AI及算力收入占比仍较小且归母净利下滑；保留算力中心运维并下调盈利确定性。</t>
         </is>
       </c>
       <c r="E310" s="6" t="inlineStr">
@@ -9438,22 +9438,22 @@
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>AI智能终端ODM</t>
+          <t>算力设备交付运维</t>
         </is>
       </c>
       <c r="B311" s="3" t="inlineStr">
         <is>
-          <t>603341</t>
+          <t>301085</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>龙旗科技</t>
+          <t>亚康股份</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露AI PC实现全平台产品设计与量产落地并获得全球头部客户订单，智能眼镜实现多场景、多品类规模化量产，AIoT业务覆盖智能手表/手环和智能眼镜；主板块从智能终端ODM细化为AI智能终端ODM。风险是手机/平板仍占大盘，新业务弹性需看AI PC、智能眼镜收入占比和毛利。</t>
+          <t>证据中：2025年报摘要披露向富士康、英业达、华勤、浪潮等算力服务器制造商提供交付及售后维保，并从传统数据中心向AI智算中心运维升级；公司亏损，主线为算力设备交付运维。</t>
         </is>
       </c>
       <c r="E311" s="6" t="inlineStr">
@@ -9465,27 +9465,27 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>端侧AI SoC</t>
+          <t>AI智能终端ODM</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>603341</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>龙旗科技</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>证据强：2026年一季报及2026年半年度业绩预告显示，公司采用“AIoT SoC算力平台+AI协处理器”双轨路线，RK3588、RK3576、RV11系列持续高速增长，RK182X已量产并预计下半年开始放量；以RK3588为例，芯片集成CPU、GPU、6TOPS自研NPU、ISP及8K音视频编解码能力，终端覆盖机器人、机器视觉/安防、工业控制、智能座舱、商显/办公、智能家居及教育娱乐等消费电子。2026H1预告营收28.70—29.10亿元、归母净利润8.50—9.10亿元、扣非净利润8.30—8.90亿元（均未经审计）。主板块归入端侧AI SoC；风险是存储及载板等原材料涨价/短缺、消费类终端承压，以及新品导入和放量不及预期。</t>
+          <t>证据中强：2025年报披露AI PC实现全平台产品设计与量产落地并获得全球头部客户订单，智能眼镜实现多场景、多品类规模化量产，AIoT业务覆盖智能手表/手环和智能眼镜；主板块从智能终端ODM细化为AI智能终端ODM。风险是手机/平板仍占大盘，新业务弹性需看AI PC、智能眼镜收入占比和毛利。</t>
         </is>
       </c>
       <c r="E312" s="6" t="inlineStr">
         <is>
-          <t>更新；2026-07-25</t>
+          <t>已处理</t>
         </is>
       </c>
     </row>
@@ -9497,22 +9497,22 @@
       </c>
       <c r="B313" s="3" t="inlineStr">
         <is>
-          <t>300458</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>全志科技</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司实现CPU、GPU、NPU、DSP及RISC-V协处理器复杂异构芯片规模化量产，智能终端应用处理器是核心业务；删减AI眼镜应用处理器重复行，AI眼镜只是下游应用之一，主板块保留端侧AI SoC。</t>
+          <t>证据强：2026年一季报及2026年半年度业绩预告显示，公司采用“AIoT SoC算力平台+AI协处理器”双轨路线，RK3588、RK3576、RV11系列持续高速增长，RK182X已量产并预计下半年开始放量；以RK3588为例，芯片集成CPU、GPU、6TOPS自研NPU、ISP及8K音视频编解码能力，终端覆盖机器人、机器视觉/安防、工业控制、智能座舱、商显/办公、智能家居及教育娱乐等消费电子。2026H1预告营收28.70—29.10亿元、归母净利润8.50—9.10亿元、扣非净利润8.30—8.90亿元（均未经审计）。主板块归入端侧AI SoC；风险是存储及载板等原材料涨价/短缺、消费类终端承压，以及新品导入和放量不及预期。</t>
         </is>
       </c>
       <c r="E313" s="6" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>更新；2026-07-25</t>
         </is>
       </c>
     </row>
@@ -9524,17 +9524,17 @@
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>688099</t>
+          <t>300458</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>晶晨股份</t>
+          <t>全志科技</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露智能多媒体及显示SoC仍是核心收入来源，AIoT SoC收入16.40亿元、同比增长8.50%，AIoT SoC集成NPU、DSP、视觉处理单元、ISP及编解码器并获Google EDLA认证；主板块从端侧AIoT SoC收敛为端侧AI SoC，跟踪端侧大模型适配、头部客户新品和经营现金流修复。</t>
+          <t>证据中强：2025年报披露公司实现CPU、GPU、NPU、DSP及RISC-V协处理器复杂异构芯片规模化量产，智能终端应用处理器是核心业务；删减AI眼镜应用处理器重复行，AI眼镜只是下游应用之一，主板块保留端侧AI SoC。</t>
         </is>
       </c>
       <c r="E314" s="6" t="inlineStr">
@@ -9551,71 +9551,71 @@
       </c>
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>301536</t>
+          <t>688099</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>星宸科技</t>
+          <t>晶晨股份</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>证据强（截至2026-07-25）：公司以视觉AI SoC为核心，核心芯片集成ISP、NPU、编解码、音频/显示等IP；主要产品/目标终端包括IPC/NVR（SSR670G）、家用服务及户外等机器人、智能家居/办公/工业、智能穿戴和车载记录仪/DMS/OMS/CMS/L0-L2辅助驾驶，另布局SPAD 3D感知与蓝牙。已形成收入：2025年智能安防19.35亿元/65.10%、智能物联6.58亿元/22.14%、智能车载3.18亿元/10.69%；2026H1预告收入26.2—27.2亿元、归母8.2—9.0亿元、扣非7.0—7.8亿元（未经审计；7月22日公告称无需修正），SSR670系列公司称已大规模商用。商业化边界：AI眼镜SSC309QL仅小规模量产，另有5—6家客户开发中，订单/独立收入N/A；机器人2025年出货超1,000万颗但独立收入N/A，具身“小脑/大脑”仍在研；SS901公司IR称已在国内一线自主品牌主力车型量产上车，其他车载/3D项目的导入或规划不等于订单/收入。PE(TTM，用户口径)=24.4—28.4x：总市值555.82亿元（东方财富，2026-07-24收盘）÷[(2026H1扣非预告7.0—7.8亿元−2026Q1扣非2.0998亿元)×4]，非标准近四季PE。证据状态：财务/分部=confirmed_official；产品/客户进展=company_claim；估值=market_data_vendor；annualized_core_gap_status=insufficient、formal_surprise_status=N/A（缺公告前FY归母点时共识）。风险：半年度预告待8月27日正式半年报验证，毛利率、现金流、存货、价量与新品放量持续性待核。</t>
+          <t>证据中强：2025年报披露智能多媒体及显示SoC仍是核心收入来源，AIoT SoC收入16.40亿元、同比增长8.50%，AIoT SoC集成NPU、DSP、视觉处理单元、ISP及编解码器并获Google EDLA认证；主板块从端侧AIoT SoC收敛为端侧AI SoC，跟踪端侧大模型适配、头部客户新品和经营现金流修复。</t>
         </is>
       </c>
       <c r="E315" s="6" t="inlineStr">
         <is>
-          <t>更新；2026-07-25</t>
+          <t>已处理</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>AI眼镜主控SoC</t>
+          <t>端侧AI SoC</t>
         </is>
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>688608</t>
+          <t>301536</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>恒玄科技</t>
+          <t>星宸科技</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司主营低功耗无线计算SoC，芯片集成CPU、嵌入式NPU、ISP、DSP、蓝牙/Wi-Fi等模块；BES6100面向智能眼镜等低功耗终端，6nm工艺，集成多核Cortex-A、NPU、GPU，可运行Linux/Android并支持端侧AI推理。风险是AI眼镜SoC仍处放量早期，需跟踪客户导入和量产节奏。</t>
+          <t>证据强（截至2026-07-25）：公司以视觉AI SoC为核心，核心芯片集成ISP、NPU、编解码、音频/显示等IP；主要产品/目标终端包括IPC/NVR（SSR670G）、家用服务及户外等机器人、智能家居/办公/工业、智能穿戴和车载记录仪/DMS/OMS/CMS/L0-L2辅助驾驶，另布局SPAD 3D感知与蓝牙。已形成收入：2025年智能安防19.35亿元/65.10%、智能物联6.58亿元/22.14%、智能车载3.18亿元/10.69%；2026H1预告收入26.2—27.2亿元、归母8.2—9.0亿元、扣非7.0—7.8亿元（未经审计；7月22日公告称无需修正），SSR670系列公司称已大规模商用。商业化边界：AI眼镜SSC309QL仅小规模量产，另有5—6家客户开发中，订单/独立收入N/A；机器人2025年出货超1,000万颗但独立收入N/A，具身“小脑/大脑”仍在研；SS901公司IR称已在国内一线自主品牌主力车型量产上车，其他车载/3D项目的导入或规划不等于订单/收入。PE(TTM，用户口径)=24.4—28.4x：总市值555.82亿元（东方财富，2026-07-24收盘）÷[(2026H1扣非预告7.0—7.8亿元−2026Q1扣非2.0998亿元)×4]，非标准近四季PE。证据状态：财务/分部=confirmed_official；产品/客户进展=company_claim；估值=market_data_vendor；annualized_core_gap_status=insufficient、formal_surprise_status=N/A（缺公告前FY归母点时共识）。风险：半年度预告待8月27日正式半年报验证，毛利率、现金流、存货、价量与新品放量持续性待核。</t>
         </is>
       </c>
       <c r="E316" s="6" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>更新；2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>智能穿戴SoC</t>
+          <t>AI眼镜主控SoC</t>
         </is>
       </c>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>688049</t>
+          <t>688608</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>炬芯科技</t>
+          <t>恒玄科技</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报摘要披露公司构建低功耗大算力芯片硬件架构、端侧AI开发工具和存内计算CIM，CPU+DSP+NPU架构提升端侧AI能效；智能穿戴SoC覆盖手表/手环、AI眼镜等，主板块保留智能穿戴SoC，AI眼镜属于穿戴场景扩展而非单独主线。</t>
+          <t>证据强：2025年报披露公司主营低功耗无线计算SoC，芯片集成CPU、嵌入式NPU、ISP、DSP、蓝牙/Wi-Fi等模块；BES6100面向智能眼镜等低功耗终端，6nm工艺，集成多核Cortex-A、NPU、GPU，可运行Linux/Android并支持端侧AI推理。风险是AI眼镜SoC仍处放量早期，需跟踪客户导入和量产节奏。</t>
         </is>
       </c>
       <c r="E317" s="6" t="inlineStr">
@@ -9627,22 +9627,22 @@
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>端侧音视频SoC</t>
+          <t>智能穿戴SoC</t>
         </is>
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>688332</t>
+          <t>688049</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>中科蓝讯</t>
+          <t>炬芯科技</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>证据中：公司专注低功耗无线音频SoC，2025年报披露形成蓝牙耳机、智能穿戴、AIoT、AI语音识别、Wi-Fi、视频芯片等产品线，并向AI玩具、AI眼镜、AI音箱扩展；主板块保留端侧音视频SoC。风险是2025净利高增主要受投资公允价值影响，扣非和主业毛利需单独跟踪。</t>
+          <t>证据中强：2025年报摘要披露公司构建低功耗大算力芯片硬件架构、端侧AI开发工具和存内计算CIM，CPU+DSP+NPU架构提升端侧AI能效；智能穿戴SoC覆盖手表/手环、AI眼镜等，主板块保留智能穿戴SoC，AI眼镜属于穿戴场景扩展而非单独主线。</t>
         </is>
       </c>
       <c r="E318" s="6" t="inlineStr">
@@ -9654,22 +9654,22 @@
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>端侧AI MCU</t>
+          <t>端侧音视频SoC</t>
         </is>
       </c>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>688018</t>
+          <t>688332</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>乐鑫科技</t>
+          <t>中科蓝讯</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司以AIoT为核心，芯片、模组和开发套件保持增长；官方ESP32-P4为双核RISC-V高性能MCU，具备AI指令扩展、先进内存子系统和高速外设，面向HMI、边缘计算、视觉AI等嵌入式场景。风险是AI算力较SoC/NPU平台更轻量，需跟踪高端新品放量和客户结构。</t>
+          <t>证据中：公司专注低功耗无线音频SoC，2025年报披露形成蓝牙耳机、智能穿戴、AIoT、AI语音识别、Wi-Fi、视频芯片等产品线，并向AI玩具、AI眼镜、AI音箱扩展；主板块保留端侧音视频SoC。风险是2025净利高增主要受投资公允价值影响，扣非和主业毛利需单独跟踪。</t>
         </is>
       </c>
       <c r="E319" s="6" t="inlineStr">
@@ -9681,22 +9681,22 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>端侧AI蜂窝模组</t>
+          <t>端侧AI MCU</t>
         </is>
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>603236</t>
+          <t>688018</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>移远通信</t>
+          <t>乐鑫科技</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露物联网需求回暖，边缘计算、混合现实、大模型与物联网融合加速；公司推出支持主流AI大模型端侧部署的5G智能座舱模组，并依托智能模组、AI大模型、主控板、算力卡和自研算法打造多层级端侧AI方案。主板块保留端侧AI蜂窝模组，跟踪AI模组收入占比和毛利提升。</t>
+          <t>证据中强：2025年报披露公司以AIoT为核心，芯片、模组和开发套件保持增长；官方ESP32-P4为双核RISC-V高性能MCU，具备AI指令扩展、先进内存子系统和高速外设，面向HMI、边缘计算、视觉AI等嵌入式场景。风险是AI算力较SoC/NPU平台更轻量，需跟踪高端新品放量和客户结构。</t>
         </is>
       </c>
       <c r="E320" s="6" t="inlineStr">
@@ -9708,22 +9708,22 @@
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>高算力智能模组</t>
+          <t>端侧AI蜂窝模组</t>
         </is>
       </c>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>002881</t>
+          <t>603236</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>美格智能</t>
+          <t>移远通信</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露无线通信模组正向智能模组、高算力模组升级，公司的智能模组和高算力模组是物联网终端侧、边缘侧计算能力承载平台，并推动端侧AI在物联网领域落地；主板块从端侧AI蜂窝模组细化为高算力智能模组，跟踪海外收入、车载/AR/VR等大颗粒市场和毛利修复。</t>
+          <t>证据强：2025年报披露物联网需求回暖，边缘计算、混合现实、大模型与物联网融合加速；公司推出支持主流AI大模型端侧部署的5G智能座舱模组，并依托智能模组、AI大模型、主控板、算力卡和自研算法打造多层级端侧AI方案。主板块保留端侧AI蜂窝模组，跟踪AI模组收入占比和毛利提升。</t>
         </is>
       </c>
       <c r="E321" s="6" t="inlineStr">
@@ -9735,22 +9735,22 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>端侧AI模组</t>
+          <t>高算力智能模组</t>
         </is>
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>300638</t>
+          <t>002881</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>广和通</t>
+          <t>美格智能</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司发布Fibocom AI Stack端侧AI解决方案及覆盖1T-50T算力的“星云”AI模组矩阵，支持不同参数端侧大模型部署，应用于AI玩具、机器人等终端；主板块保留端侧AI模组，跟踪星云系列出货、AI解决方案收入占比和客户落地。</t>
+          <t>证据中强：2025年报披露无线通信模组正向智能模组、高算力模组升级，公司的智能模组和高算力模组是物联网终端侧、边缘侧计算能力承载平台，并推动端侧AI在物联网领域落地；主板块从端侧AI蜂窝模组细化为高算力智能模组，跟踪海外收入、车载/AR/VR等大颗粒市场和毛利修复。</t>
         </is>
       </c>
       <c r="E322" s="6" t="inlineStr">
@@ -9762,22 +9762,22 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>AIOS端侧智能</t>
+          <t>端侧AI模组</t>
         </is>
       </c>
       <c r="B323" s="3" t="inlineStr">
         <is>
-          <t>300496</t>
+          <t>300638</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>中科创达</t>
+          <t>广和通</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司以AIOS为核心战略，覆盖端云协同、AI智能体和行业AI，并在智能汽车、AI眼镜、机器人等端侧场景落地；主板块由端侧智能OS升级为AIOS端侧智能。</t>
+          <t>证据强：2025年报披露公司发布Fibocom AI Stack端侧AI解决方案及覆盖1T-50T算力的“星云”AI模组矩阵，支持不同参数端侧大模型部署，应用于AI玩具、机器人等终端；主板块保留端侧AI模组，跟踪星云系列出货、AI解决方案收入占比和客户落地。</t>
         </is>
       </c>
       <c r="E323" s="6" t="inlineStr">
@@ -9789,22 +9789,22 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>AR光波导</t>
+          <t>AIOS端侧智能</t>
         </is>
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>300496</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>中科创达</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>精密镀膜、微纳光学和光电封测能力较强，AR/VR领域反射光波导及核心光学元件为公司重点工程，AI眼镜是更直接的未来映射；主板块改为AR光波导，微透镜并入备注，CPO硅透镜研发仅作远期观察，风险是AR大客户量产节奏、消费电子大客户依赖和光通信收入兑现。证据B。</t>
+          <t>证据强：2025年报披露公司以AIOS为核心战略，覆盖端云协同、AI智能体和行业AI，并在智能汽车、AI眼镜、机器人等端侧场景落地；主板块由端侧智能OS升级为AIOS端侧智能。</t>
         </is>
       </c>
       <c r="E324" s="6" t="inlineStr">
@@ -9816,22 +9816,22 @@
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>AI眼镜光学模组</t>
+          <t>AR光波导</t>
         </is>
       </c>
       <c r="B325" s="3" t="inlineStr">
         <is>
-          <t>300433</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>蓝思科技</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司是AI硬件全产业链一站式精密制造解决方案提供商，AI眼镜领域具备材料、光学、结构件到整机组装全栈能力，已实现国内头部客户整机组装和海外头部客户精密零组件规模化交付，并在光波导镜片高精度自动化组装等领域突破；主板块从AI眼镜光波导扩展为AI眼镜光学模组。</t>
+          <t>精密镀膜、微纳光学和光电封测能力较强，AR/VR领域反射光波导及核心光学元件为公司重点工程，AI眼镜是更直接的未来映射；主板块改为AR光波导，微透镜并入备注，CPO硅透镜研发仅作远期观察，风险是AR大客户量产节奏、消费电子大客户依赖和光通信收入兑现。证据B。</t>
         </is>
       </c>
       <c r="E325" s="6" t="inlineStr">
@@ -9843,22 +9843,22 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>AR投影光机</t>
+          <t>AI眼镜光学模组</t>
         </is>
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>688010</t>
+          <t>300433</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>福光股份</t>
+          <t>蓝思科技</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露公司主营特种及民用光学镜头、光电系统和光学元组件，研发项目中M003 MicroLED AR显示模组处于产业化推广，应用于AR领域；投影光机可用于AR/可穿戴设备。主板块保留AR投影光机，但AI眼镜收入纯度和客户放量仍需继续验证，扣非盈利仍承压。</t>
+          <t>证据强：2025年报披露公司是AI硬件全产业链一站式精密制造解决方案提供商，AI眼镜领域具备材料、光学、结构件到整机组装全栈能力，已实现国内头部客户整机组装和海外头部客户精密零组件规模化交付，并在光波导镜片高精度自动化组装等领域突破；主板块从AI眼镜光波导扩展为AI眼镜光学模组。</t>
         </is>
       </c>
       <c r="E326" s="6" t="inlineStr">
@@ -9870,22 +9870,22 @@
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>硅基OLED微显示</t>
+          <t>AR投影光机</t>
         </is>
       </c>
       <c r="B327" s="3" t="inlineStr">
         <is>
-          <t>688496</t>
+          <t>688010</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>清越科技</t>
+          <t>福光股份</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露公司形成PMOLED、电子纸模组与硅基OLED微显示器三大业务，硅基OLED用于AR智能眼镜、VR头显等近眼显示；Micro-OLED高亮高效结构器件等项目继续推进。主板块保留硅基OLED微显示，但公司2025亏损扩大，需跟踪硅基OLED量产客户和盈利拐点。</t>
+          <t>证据中：2025年报披露公司主营特种及民用光学镜头、光电系统和光学元组件，研发项目中M003 MicroLED AR显示模组处于产业化推广，应用于AR领域；投影光机可用于AR/可穿戴设备。主板块保留AR投影光机，但AI眼镜收入纯度和客户放量仍需继续验证，扣非盈利仍承压。</t>
         </is>
       </c>
       <c r="E327" s="6" t="inlineStr">
@@ -9897,22 +9897,22 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>AI眼镜MicroLED光机</t>
+          <t>硅基OLED微显示</t>
         </is>
       </c>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>300296</t>
+          <t>688496</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>利亚德</t>
+          <t>清越科技</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年度总经理工作报告披露公司已推出基于MicroLED光机的AR眼镜，并发布AI玩具等大众消费AI创新产品；MicroLED仍是新战略周期重点增长方向。主板块保留AI眼镜MicroLED光机，风险是公司收入主体仍为LED显示和文旅，AI眼镜商业化仍早期。</t>
+          <t>证据中：2025年报披露公司形成PMOLED、电子纸模组与硅基OLED微显示器三大业务，硅基OLED用于AR智能眼镜、VR头显等近眼显示；Micro-OLED高亮高效结构器件等项目继续推进。主板块保留硅基OLED微显示，但公司2025亏损扩大，需跟踪硅基OLED量产客户和盈利拐点。</t>
         </is>
       </c>
       <c r="E328" s="6" t="inlineStr">
@@ -9924,22 +9924,22 @@
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>AI眼镜MicroLED微显示</t>
+          <t>AI眼镜MicroLED光机</t>
         </is>
       </c>
       <c r="B329" s="3" t="inlineStr">
         <is>
-          <t>300323</t>
+          <t>300296</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>京东方华灿</t>
+          <t>利亚德</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025投资者关系记录披露MicroLED技术可用于具备显示功能的AI眼镜，公司配合不同客户需求提供解决方案并提升性能与良率；2025年报披露MicroLED技术研发及产业化项目推进高亮度、高对比度、高色彩饱和度芯片。主板块保留AI眼镜MicroLED微显示，风险是公司仍亏损，产业化和客户放量需跟踪。</t>
+          <t>证据中强：2025年度总经理工作报告披露公司已推出基于MicroLED光机的AR眼镜，并发布AI玩具等大众消费AI创新产品；MicroLED仍是新战略周期重点增长方向。主板块保留AI眼镜MicroLED光机，风险是公司收入主体仍为LED显示和文旅，AI眼镜商业化仍早期。</t>
         </is>
       </c>
       <c r="E329" s="6" t="inlineStr">
@@ -9951,22 +9951,22 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>MicroLED芯片</t>
+          <t>AI眼镜MicroLED微显示</t>
         </is>
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>600703</t>
+          <t>300323</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>三安光电</t>
+          <t>京东方华灿</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露Mini/Micro LED高端产品占比提升，Micro LED芯片在中大型显示增长，并切入AR眼镜、AI数据中心光互连等应用；删减“化合物半导体”重复行，SiC/GaN等平台能力在备注降级说明。</t>
+          <t>证据中：2025投资者关系记录披露MicroLED技术可用于具备显示功能的AI眼镜，公司配合不同客户需求提供解决方案并提升性能与良率；2025年报披露MicroLED技术研发及产业化项目推进高亮度、高对比度、高色彩饱和度芯片。主板块保留AI眼镜MicroLED微显示，风险是公司仍亏损，产业化和客户放量需跟踪。</t>
         </is>
       </c>
       <c r="E330" s="6" t="inlineStr">
@@ -9978,22 +9978,22 @@
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>OLED-MicroLED显示</t>
+          <t>MicroLED芯片</t>
         </is>
       </c>
       <c r="B331" s="3" t="inlineStr">
         <is>
-          <t>002387</t>
+          <t>600703</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>维信诺</t>
+          <t>三安光电</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露维信诺围绕AI新场景推进智能终端、智能影像、智慧家居等显示供货，并持续推进ViP、Micro-LED等显示技术；真实受益节点是AI终端显示，MicroLED更多体现技术储备和参股生态。</t>
+          <t>证据中强：2025年报披露Mini/Micro LED高端产品占比提升，Micro LED芯片在中大型显示增长，并切入AR眼镜、AI数据中心光互连等应用；删减“化合物半导体”重复行，SiC/GaN等平台能力在备注降级说明。</t>
         </is>
       </c>
       <c r="E331" s="6" t="inlineStr">
@@ -10005,22 +10005,22 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>AI眼镜CIS</t>
+          <t>OLED-MicroLED显示</t>
         </is>
       </c>
       <c r="B332" s="3" t="inlineStr">
         <is>
-          <t>688213</t>
+          <t>002387</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>思特威</t>
+          <t>维信诺</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司推出1200万像素AI眼镜应用CMOS图像传感器SC1200IOT，官网还披露SC1200IOT/SC1220IOT具备小封装、低功耗、高感度、Always-On等特性，适用于AI眼镜及AR/VR微型摄像头模组；主板块保留AI眼镜CIS，跟踪量产客户和高像素新品。</t>
+          <t>证据中：2025年报披露维信诺围绕AI新场景推进智能终端、智能影像、智慧家居等显示供货，并持续推进ViP、Micro-LED等显示技术；真实受益节点是AI终端显示，MicroLED更多体现技术储备和参股生态。</t>
         </is>
       </c>
       <c r="E332" s="6" t="inlineStr">
@@ -10037,17 +10037,17 @@
       </c>
       <c r="B333" s="3" t="inlineStr">
         <is>
-          <t>688728</t>
+          <t>688213</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>格科微</t>
+          <t>思特威</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司主营CIS与DDIC，高像素CIS放量；公告口径显示公司持续关注AI眼镜等新兴市场，500万和800万像素CIS已在AI眼镜项目量产。主板块保留AI眼镜CIS，但整体利润承压，需跟踪AI眼镜CIS是否能改善产品结构和毛利。</t>
+          <t>证据强：2025年报披露公司推出1200万像素AI眼镜应用CMOS图像传感器SC1200IOT，官网还披露SC1200IOT/SC1220IOT具备小封装、低功耗、高感度、Always-On等特性，适用于AI眼镜及AR/VR微型摄像头模组；主板块保留AI眼镜CIS，跟踪量产客户和高像素新品。</t>
         </is>
       </c>
       <c r="E333" s="6" t="inlineStr">
@@ -10059,22 +10059,22 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>AI眼镜视觉算法</t>
+          <t>AI眼镜CIS</t>
         </is>
       </c>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>688088</t>
+          <t>688728</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>虹软科技</t>
+          <t>格科微</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报/业绩快报披露AI眼镜影像与视觉算法持续升级，围绕复杂光照、动态场景、低照度和视频防抖推进平台适配；公开资料显示方案已在雷鸟、Rokid、夸克等AI眼镜落地。删减“端侧视觉AI底座”重复行，保留最直接的AI眼镜视觉算法。</t>
+          <t>证据中强：2025年报披露公司主营CIS与DDIC，高像素CIS放量；公告口径显示公司持续关注AI眼镜等新兴市场，500万和800万像素CIS已在AI眼镜项目量产。主板块保留AI眼镜CIS，但整体利润承压，需跟踪AI眼镜CIS是否能改善产品结构和毛利。</t>
         </is>
       </c>
       <c r="E334" s="6" t="inlineStr">
@@ -10086,22 +10086,22 @@
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>AI眼镜模拟芯片</t>
+          <t>AI眼镜视觉算法</t>
         </is>
       </c>
       <c r="B335" s="3" t="inlineStr">
         <is>
-          <t>688798</t>
+          <t>688088</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>艾为电子</t>
+          <t>虹软科技</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司高性能数模混合芯片覆盖音频功放、触觉反馈、马达驱动、压力/电容感应、灯效驱动等，SensorHub项目明确列示AI眼镜等IoT设备；另有AI眼镜客户导入音频功放、灯效驱动等公开信息。主板块保留AI眼镜模拟芯片，跟踪品牌客户放量和产品单机价值量。</t>
+          <t>证据强：2025年报/业绩快报披露AI眼镜影像与视觉算法持续升级，围绕复杂光照、动态场景、低照度和视频防抖推进平台适配；公开资料显示方案已在雷鸟、Rokid、夸克等AI眼镜落地。删减“端侧视觉AI底座”重复行，保留最直接的AI眼镜视觉算法。</t>
         </is>
       </c>
       <c r="E335" s="6" t="inlineStr">
@@ -10113,22 +10113,22 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>AI眼镜声学传感器</t>
+          <t>AI眼镜模拟芯片</t>
         </is>
       </c>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>688286</t>
+          <t>688798</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>敏芯股份</t>
+          <t>艾为电子</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>证据中：公司提质增效报告披露布局高信噪比、低功耗数字麦克风，部分型号已小批量出货，并布局应用于AI眼镜的骨传导声学传感器；删减“高信噪比数字麦克风”重复行，合并为AI眼镜声学传感器。风险是AI眼镜相关产品仍处研发/小批量阶段，收入贡献未充分披露。</t>
+          <t>证据中强：2025年报披露公司高性能数模混合芯片覆盖音频功放、触觉反馈、马达驱动、压力/电容感应、灯效驱动等，SensorHub项目明确列示AI眼镜等IoT设备；另有AI眼镜客户导入音频功放、灯效驱动等公开信息。主板块保留AI眼镜模拟芯片，跟踪品牌客户放量和产品单机价值量。</t>
         </is>
       </c>
       <c r="E336" s="6" t="inlineStr">
@@ -10140,22 +10140,22 @@
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>消费锂电池</t>
+          <t>AI眼镜声学传感器</t>
         </is>
       </c>
       <c r="B337" s="3" t="inlineStr">
         <is>
-          <t>688772</t>
+          <t>688286</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>珠海冠宇</t>
+          <t>敏芯股份</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露公司主营消费类锂离子电池，AI功能消费电子推出有望带来换机潮，消费类半固态电池已规模化量产；募集说明书提及智能手表、智能眼镜等可穿戴需求扩张。主板块保留消费锂电池，AI受益偏终端电池供能配套，直接度低于AI眼镜专用电池公司。</t>
+          <t>证据中：公司提质增效报告披露布局高信噪比、低功耗数字麦克风，部分型号已小批量出货，并布局应用于AI眼镜的骨传导声学传感器；删减“高信噪比数字麦克风”重复行，合并为AI眼镜声学传感器。风险是AI眼镜相关产品仍处研发/小批量阶段，收入贡献未充分披露。</t>
         </is>
       </c>
       <c r="E337" s="6" t="inlineStr">
@@ -10167,22 +10167,22 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>AI智能眼镜电池</t>
+          <t>消费锂电池</t>
         </is>
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>001283</t>
+          <t>688772</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>豪鹏科技</t>
+          <t>珠海冠宇</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报/公开资料披露公司布局AI智能眼镜电池，固态电池样品在AI终端、可穿戴设备等场景完成初步验证；删减“AI终端固态电池”重复行，当前主线仍是AI智能眼镜电池，固态电池属于下一代技术储备而非已验证主收入板块。</t>
+          <t>证据中：2025年报披露公司主营消费类锂离子电池，AI功能消费电子推出有望带来换机潮，消费类半固态电池已规模化量产；募集说明书提及智能手表、智能眼镜等可穿戴需求扩张。主板块保留消费锂电池，AI受益偏终端电池供能配套，直接度低于AI眼镜专用电池公司。</t>
         </is>
       </c>
       <c r="E338" s="6" t="inlineStr">
@@ -10194,22 +10194,22 @@
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>AI眼镜结构件</t>
+          <t>AI智能眼镜电池</t>
         </is>
       </c>
       <c r="B339" s="3" t="inlineStr">
         <is>
-          <t>300115</t>
+          <t>001283</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>长盈精密</t>
+          <t>豪鹏科技</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报摘要披露公司抓住AI硬件迭代机遇，持续开发AI笔记本和可穿戴产品关键零部件，轻量化金属及非金属结构件取得突破；AI眼镜结构件面向头部客户是主要弹性来源。主板块保留AI眼镜结构件，风险是消费电子结构件仍具客户集中和价格压力。</t>
+          <t>证据中强：2025年报/公开资料披露公司布局AI智能眼镜电池，固态电池样品在AI终端、可穿戴设备等场景完成初步验证；删减“AI终端固态电池”重复行，当前主线仍是AI智能眼镜电池，固态电池属于下一代技术储备而非已验证主收入板块。</t>
         </is>
       </c>
       <c r="E339" s="6" t="inlineStr">
@@ -10221,22 +10221,22 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>AI智能眼镜整机</t>
+          <t>AI眼镜结构件</t>
         </is>
       </c>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>002241</t>
+          <t>300115</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>歌尔股份</t>
+          <t>长盈精密</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司研发围绕MEMS声学传感器、微系统模组、AI智能眼镜/AR光学器件、MR头显等，AI智能眼镜等新兴业务表现亮眼；作为精密零组件+整机制造平台，主板块保留AI智能眼镜整机，光学、声学、SiP模组作为支撑能力写入备注即可。风险是营收仍受传统消费电子/XR周期影响。</t>
+          <t>证据中强：2025年报摘要披露公司抓住AI硬件迭代机遇，持续开发AI笔记本和可穿戴产品关键零部件，轻量化金属及非金属结构件取得突破；AI眼镜结构件面向头部客户是主要弹性来源。主板块保留AI眼镜结构件，风险是消费电子结构件仍具客户集中和价格压力。</t>
         </is>
       </c>
       <c r="E340" s="6" t="inlineStr">
@@ -10248,22 +10248,22 @@
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>AI终端精密功能件</t>
+          <t>AI智能眼镜整机</t>
         </is>
       </c>
       <c r="B341" s="3" t="inlineStr">
         <is>
-          <t>002600</t>
+          <t>002241</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>领益智造</t>
+          <t>歌尔股份</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报摘要披露公司核心产品覆盖AI手机、AIPC、AI眼镜及XR可穿戴、AI服务器、机器人等硬件，以2024年收入计在全球AI终端高精密功能件行业排名第一；半年报披露AR眼镜项目含MicroOLED显示、Insert Molding金属件增强等。主板块从精密结构件扩展为AI终端精密功能件。</t>
+          <t>证据中强：2025年报披露公司研发围绕MEMS声学传感器、微系统模组、AI智能眼镜/AR光学器件、MR头显等，AI智能眼镜等新兴业务表现亮眼；作为精密零组件+整机制造平台，主板块保留AI智能眼镜整机，光学、声学、SiP模组作为支撑能力写入备注即可。风险是营收仍受传统消费电子/XR周期影响。</t>
         </is>
       </c>
       <c r="E341" s="6" t="inlineStr">
@@ -10275,22 +10275,22 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>机器人3D视觉</t>
+          <t>AI终端精密功能件</t>
         </is>
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>688322</t>
+          <t>002600</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>奥比中光</t>
+          <t>领益智造</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司专注3D视觉感知，在人工智能与机器人时代打造“机器人之眼”和机器人与AI视觉产业中台；产品和生态围绕机器人、AI视觉、3D相机矩阵推进。删减泛化的“3D视觉传感器”重复表述，主板块保留机器人3D视觉。风险是机器人需求仍处导入期，短期收入仍含AIoT/生物识别等多场景。</t>
+          <t>证据强：2025年报摘要披露公司核心产品覆盖AI手机、AIPC、AI眼镜及XR可穿戴、AI服务器、机器人等硬件，以2024年收入计在全球AI终端高精密功能件行业排名第一；半年报披露AR眼镜项目含MicroOLED显示、Insert Molding金属件增强等。主板块从精密结构件扩展为AI终端精密功能件。</t>
         </is>
       </c>
       <c r="E342" s="6" t="inlineStr">
@@ -10302,22 +10302,22 @@
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>机器人力传感器</t>
+          <t>机器人3D视觉</t>
         </is>
       </c>
       <c r="B343" s="3" t="inlineStr">
         <is>
-          <t>603662</t>
+          <t>688322</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>柯力传感</t>
+          <t>奥比中光</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司围绕人形、协作和工业机器人加快六维力/力矩、一维至三维力、触觉、IMU等产品研发认证及批量交付；半年报披露以六维力/力矩为核心融合触觉、IMU的机器人传感方案。删减“触觉传感器-IMU”重复行，保留最能解释AI机器人弹性的机器人力传感器。</t>
+          <t>证据强：2025年报披露公司专注3D视觉感知，在人工智能与机器人时代打造“机器人之眼”和机器人与AI视觉产业中台；产品和生态围绕机器人、AI视觉、3D相机矩阵推进。删减泛化的“3D视觉传感器”重复表述，主板块保留机器人3D视觉。风险是机器人需求仍处导入期，短期收入仍含AIoT/生物识别等多场景。</t>
         </is>
       </c>
       <c r="E343" s="6" t="inlineStr">
@@ -10334,17 +10334,17 @@
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>301413</t>
+          <t>603662</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>安培龙</t>
+          <t>柯力传感</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报/投资者关系披露公司机器人力传感器包括单向力、力矩及六维力传感器，基于MEMS硅基应变片和玻璃微熔工艺的单向力及力矩传感器已开发完成并向多家机器人客户送样。主板块保留机器人力传感器，但公告提示相关收入占比仍低，六维力部分仍需验证批量订单。</t>
+          <t>证据强：2025年报披露公司围绕人形、协作和工业机器人加快六维力/力矩、一维至三维力、触觉、IMU等产品研发认证及批量交付；半年报披露以六维力/力矩为核心融合触觉、IMU的机器人传感方案。删减“触觉传感器-IMU”重复行，保留最能解释AI机器人弹性的机器人力传感器。</t>
         </is>
       </c>
       <c r="E344" s="6" t="inlineStr">
@@ -10361,17 +10361,17 @@
       </c>
       <c r="B345" s="3" t="inlineStr">
         <is>
-          <t>300354</t>
+          <t>301413</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>东华测试</t>
+          <t>安培龙</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025投资者关系记录披露六维力传感器处于小批量试制阶段，下游包括工业机器人、人形机器人、航空航天、汽车、电子、医疗等；公司主业仍以结构力学性能测试、PHM、电化学工作站等为基础，机器人收入贡献尚未充分披露，跟踪送样转批量和标定/测试体系能力。</t>
+          <t>证据中：2025年报/投资者关系披露公司机器人力传感器包括单向力、力矩及六维力传感器，基于MEMS硅基应变片和玻璃微熔工艺的单向力及力矩传感器已开发完成并向多家机器人客户送样。主板块保留机器人力传感器，但公告提示相关收入占比仍低，六维力部分仍需验证批量订单。</t>
         </is>
       </c>
       <c r="E345" s="6" t="inlineStr">
@@ -10383,22 +10383,22 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>机器人电子皮肤</t>
+          <t>机器人力传感器</t>
         </is>
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>300007</t>
+          <t>300354</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>汉威科技</t>
+          <t>东华测试</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露柔性传感电子皮肤入选2025具身智能十大创新产品和技术，机器人相关电子皮肤和触觉传感器已小批量供货；公司官网披露具备年产1000万支柔性传感器产线和柔性压阻/压电/电容/汗液四大技术。主板块从电子皮肤规范为机器人电子皮肤，风险是整体业务仍以气体/仪表等传感平台为主。</t>
+          <t>证据中：2025投资者关系记录披露六维力传感器处于小批量试制阶段，下游包括工业机器人、人形机器人、航空航天、汽车、电子、医疗等；公司主业仍以结构力学性能测试、PHM、电化学工作站等为基础，机器人收入贡献尚未充分披露，跟踪送样转批量和标定/测试体系能力。</t>
         </is>
       </c>
       <c r="E346" s="6" t="inlineStr">
@@ -10410,22 +10410,22 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>机器人谐波减速器</t>
+          <t>机器人电子皮肤</t>
         </is>
       </c>
       <c r="B347" s="3" t="inlineStr">
         <is>
-          <t>688017</t>
+          <t>300007</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>绿的谐波</t>
+          <t>汉威科技</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司巩固具身智能场景谐波减速器领先地位，并围绕轻量化、微型化、低噪音、精度、刚性和寿命持续攻关；同时突破行星滚柱丝杠规模化制造并扩展直线伺服关节。主板块从泛机器人执行器收敛为机器人谐波减速器，丝杠和机电一体化作为增量能力跟踪。</t>
+          <t>证据强：2025年报披露柔性传感电子皮肤入选2025具身智能十大创新产品和技术，机器人相关电子皮肤和触觉传感器已小批量供货；公司官网披露具备年产1000万支柔性传感器产线和柔性压阻/压电/电容/汗液四大技术。主板块从电子皮肤规范为机器人电子皮肤，风险是整体业务仍以气体/仪表等传感平台为主。</t>
         </is>
       </c>
       <c r="E347" s="6" t="inlineStr">
@@ -10437,22 +10437,22 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>机器人精密减速器</t>
+          <t>机器人谐波减速器</t>
         </is>
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>002896</t>
+          <t>688017</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>中大力德</t>
+          <t>绿的谐波</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露精密减速器受工业机器人产量增长、人形机器人原型机批量落地等带动，公司具备行星、RV、谐波三大减速器布局，并通过减速器+电机+驱动一体化架构形成智能执行单元。主板块从机器人减速器规范为机器人精密减速器，跟踪人形机器人客户、型号验证和毛利率。</t>
+          <t>证据强：2025年报披露公司巩固具身智能场景谐波减速器领先地位，并围绕轻量化、微型化、低噪音、精度、刚性和寿命持续攻关；同时突破行星滚柱丝杠规模化制造并扩展直线伺服关节。主板块从泛机器人执行器收敛为机器人谐波减速器，丝杠和机电一体化作为增量能力跟踪。</t>
         </is>
       </c>
       <c r="E348" s="6" t="inlineStr">
@@ -10469,17 +10469,17 @@
       </c>
       <c r="B349" s="3" t="inlineStr">
         <is>
-          <t>002472</t>
+          <t>002896</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>双环传动</t>
+          <t>中大力德</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露工业机器人核心零部件减速器趋势向好，公司在重载RV精密减速器领域攻克高精度、长寿命核心技术；控股子公司从事机器人关节高精密减速器研发生产，产品包括RV减速器、精密配件及谐波减速器。主板块从机器人减速器细化为机器人高精密减速器，风险是汽车齿轮仍是主要利润来源。</t>
+          <t>证据中强：2025年报披露精密减速器受工业机器人产量增长、人形机器人原型机批量落地等带动，公司具备行星、RV、谐波三大减速器布局，并通过减速器+电机+驱动一体化架构形成智能执行单元。主板块从机器人减速器规范为机器人精密减速器，跟踪人形机器人客户、型号验证和毛利率。</t>
         </is>
       </c>
       <c r="E349" s="6" t="inlineStr">
@@ -10491,22 +10491,22 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>行星滚柱丝杠</t>
+          <t>机器人精密减速器</t>
         </is>
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>603667</t>
+          <t>002472</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>五洲新春</t>
+          <t>双环传动</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025定增预案披露具身智能机器人和汽车智驾核心零部件项目，达产后规划年产98万套行星滚柱丝杠、210万套微型滚珠丝杠和7万组通用机器人专用轴承；删减机器人专用轴承重复行，保留最能解释人形机器人弹性的行星滚柱丝杠。风险是募投建设周期较长，当前丝杠收入基数仍小。</t>
+          <t>证据中强：2025年报披露工业机器人核心零部件减速器趋势向好，公司在重载RV精密减速器领域攻克高精度、长寿命核心技术；控股子公司从事机器人关节高精密减速器研发生产，产品包括RV减速器、精密配件及谐波减速器。主板块从机器人减速器细化为机器人高精密减速器，风险是汽车齿轮仍是主要利润来源。</t>
         </is>
       </c>
       <c r="E350" s="6" t="inlineStr">
@@ -10523,17 +10523,17 @@
       </c>
       <c r="B351" s="3" t="inlineStr">
         <is>
-          <t>601100</t>
+          <t>603667</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>恒立液压</t>
+          <t>五洲新春</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露线性驱动项目投产，精密丝杠、直线导轨、电动缸等产品拓展；行星滚柱丝杠已完成送样和初步量产，为精密传动业务开拓机器人等多元下游市场。主板块保留行星滚柱丝杠，但公司基本盘仍是液压件，机器人弹性需看丝杠客户验证、量产节奏和收入占比。</t>
+          <t>证据中强：2025定增预案披露具身智能机器人和汽车智驾核心零部件项目，达产后规划年产98万套行星滚柱丝杠、210万套微型滚珠丝杠和7万组通用机器人专用轴承；删减机器人专用轴承重复行，保留最能解释人形机器人弹性的行星滚柱丝杠。风险是募投建设周期较长，当前丝杠收入基数仍小。</t>
         </is>
       </c>
       <c r="E351" s="6" t="inlineStr">
@@ -10550,17 +10550,17 @@
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>688678</t>
+          <t>601100</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>福立旺</t>
+          <t>恒立液压</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025提质增效评估/公开资料披露公司向人形机器人精密传动拓展，已开发5.0mm、6.5mm、9.0mm等螺母直径规格微型行星滚柱丝杠，并向多家头部客户送样；删减机器人关节结构件重复行，关节护罩、驱动器支架等结构件作为补充交付能力。风险是主业仍为精密金属零部件，丝杠商业化仍早期。</t>
+          <t>证据中：2025年报披露线性驱动项目投产，精密丝杠、直线导轨、电动缸等产品拓展；行星滚柱丝杠已完成送样和初步量产，为精密传动业务开拓机器人等多元下游市场。主板块保留行星滚柱丝杠，但公司基本盘仍是液压件，机器人弹性需看丝杠客户验证、量产节奏和收入占比。</t>
         </is>
       </c>
       <c r="E352" s="6" t="inlineStr">
@@ -10577,17 +10577,17 @@
       </c>
       <c r="B353" s="3" t="inlineStr">
         <is>
-          <t>603009</t>
+          <t>688678</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>北特科技</t>
+          <t>福立旺</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>证据中强：募集说明书披露差动式行星滚柱丝杠承载能力强、刚度大、磨损小和寿命长，适用于高负载线性执行场合；募投项目达产后规划年产80万套行星滚柱丝杠，主要应用于人形机器人肢体线性运动。主板块保留差动式行星滚柱丝杠，风险是募投产能释放和客户量产验证仍需跟踪。</t>
+          <t>证据中：2025提质增效评估/公开资料披露公司向人形机器人精密传动拓展，已开发5.0mm、6.5mm、9.0mm等螺母直径规格微型行星滚柱丝杠，并向多家头部客户送样；删减机器人关节结构件重复行，关节护罩、驱动器支架等结构件作为补充交付能力。风险是主业仍为精密金属零部件，丝杠商业化仍早期。</t>
         </is>
       </c>
       <c r="E353" s="6" t="inlineStr">
@@ -10599,22 +10599,22 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>机器人执行器</t>
+          <t>行星滚柱丝杠</t>
         </is>
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>601689</t>
+          <t>603009</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>拓普集团</t>
+          <t>北特科技</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司已设立机器人执行器事业部，布局直线执行器、旋转执行器、灵巧手、传感器、躯体结构件、足部减震器、电子柔性皮肤等平台化产品；直线执行器获得客户认可后继续送样旋转执行器和灵巧手电机。主板块保留机器人执行器，风险是收入主体仍为汽车零部件且机器人客户/订单未完全披露。</t>
+          <t>证据中强：募集说明书披露差动式行星滚柱丝杠承载能力强、刚度大、磨损小和寿命长，适用于高负载线性执行场合；募投项目达产后规划年产80万套行星滚柱丝杠，主要应用于人形机器人肢体线性运动。主板块保留差动式行星滚柱丝杠，风险是募投产能释放和客户量产验证仍需跟踪。</t>
         </is>
       </c>
       <c r="E354" s="6" t="inlineStr">
@@ -10626,22 +10626,22 @@
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>机器人伺服驱动</t>
+          <t>机器人执行器</t>
         </is>
       </c>
       <c r="B355" s="3" t="inlineStr">
         <is>
-          <t>300124</t>
+          <t>601689</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>汇川技术</t>
+          <t>拓普集团</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露人形机器人业务已完成从预研到商业化突破，构建核心部件全栈能力，完成无框力矩电机、低压高功率伺服驱动器、关节模组、行星滚柱丝杠、编码器等第一代产品开发和交付；删减“机器人直线导轨-丝杠”重复行，保留最能体现汇川运动控制优势的机器人伺服驱动。</t>
+          <t>证据中强：2025年报披露公司已设立机器人执行器事业部，布局直线执行器、旋转执行器、灵巧手、传感器、躯体结构件、足部减震器、电子柔性皮肤等平台化产品；直线执行器获得客户认可后继续送样旋转执行器和灵巧手电机。主板块保留机器人执行器，风险是收入主体仍为汽车零部件且机器人客户/订单未完全披露。</t>
         </is>
       </c>
       <c r="E355" s="6" t="inlineStr">
@@ -10653,22 +10653,22 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>机器人驱控系统</t>
+          <t>机器人伺服驱动</t>
         </is>
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>002979</t>
+          <t>300124</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>雷赛智能</t>
+          <t>汇川技术</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司机器人核心部件覆盖高密度无框力矩电机、中空编码器、空心杯电机、微型伺服、谐波/行星关节模组、高中低自由度灵巧手，并布局运动控制“小脑”；关节模组与灵巧手已进入数十家主流客户批量供货。主板块从机器人关节运动控制收敛为机器人驱控系统。</t>
+          <t>证据强：2025年报披露人形机器人业务已完成从预研到商业化突破，构建核心部件全栈能力，完成无框力矩电机、低压高功率伺服驱动器、关节模组、行星滚柱丝杠、编码器等第一代产品开发和交付；删减“机器人直线导轨-丝杠”重复行，保留最能体现汇川运动控制优势的机器人伺服驱动。</t>
         </is>
       </c>
       <c r="E356" s="6" t="inlineStr">
@@ -10680,22 +10680,22 @@
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>空心杯电机</t>
+          <t>机器人驱控系统</t>
         </is>
       </c>
       <c r="B357" s="3" t="inlineStr">
         <is>
-          <t>603728</t>
+          <t>002979</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>鸣志电器</t>
+          <t>雷赛智能</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露无刷电机模组、无齿槽空心杯模组、无框/交流伺服电机及驱动控制系统、精密减速机和丝杠传动模组广泛适用于人形机器人灵巧手、关节、底盘等；删减“运动控制”重复行，保留最具人形机器人弹性的空心杯电机，运动控制平台作为配套能力。</t>
+          <t>证据强：2025年报披露公司机器人核心部件覆盖高密度无框力矩电机、中空编码器、空心杯电机、微型伺服、谐波/行星关节模组、高中低自由度灵巧手，并布局运动控制“小脑”；关节模组与灵巧手已进入数十家主流客户批量供货。主板块从机器人关节运动控制收敛为机器人驱控系统。</t>
         </is>
       </c>
       <c r="E357" s="6" t="inlineStr">
@@ -10707,22 +10707,22 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>行业大模型+Agent平台</t>
+          <t>空心杯电机</t>
         </is>
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>300229</t>
+          <t>603728</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>拓尔思</t>
+          <t>鸣志电器</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025半年报/公告披露高质量数据集系统、海贝搜索向量数据库、拓天链Agent平台及拓天大模型等；数据和向量数据库是底座，商业化主线为行业大模型+Agent平台。</t>
+          <t>证据强：2025年报披露无刷电机模组、无齿槽空心杯模组、无框/交流伺服电机及驱动控制系统、精密减速机和丝杠传动模组广泛适用于人形机器人灵巧手、关节、底盘等；删减“运动控制”重复行，保留最具人形机器人弹性的空心杯电机，运动控制平台作为配套能力。</t>
         </is>
       </c>
       <c r="E358" s="6" t="inlineStr">
@@ -10734,22 +10734,22 @@
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>行业大模型训推一体</t>
+          <t>行业大模型+Agent平台</t>
         </is>
       </c>
       <c r="B359" s="3" t="inlineStr">
         <is>
-          <t>688327</t>
+          <t>300229</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>云从科技</t>
+          <t>拓尔思</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司基于CWOS和从容多模态大模型推出大模型训推及智用一体机，并在工程、制造、政务等场景落地；多模态大模型是底座，主线收敛为行业大模型训推一体。</t>
+          <t>证据强：2025半年报/公告披露高质量数据集系统、海贝搜索向量数据库、拓天链Agent平台及拓天大模型等；数据和向量数据库是底座，商业化主线为行业大模型+Agent平台。</t>
         </is>
       </c>
       <c r="E359" s="6" t="inlineStr">
@@ -10761,22 +10761,22 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>国产算力大模型底座</t>
+          <t>行业大模型训推一体</t>
         </is>
       </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>002230</t>
+          <t>688327</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>科大讯飞</t>
+          <t>云从科技</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露讯飞星火持续基于全国产算力训练并推进X1/X1.5等推理模型，2025年大模型相关项目中标金额领先；行业大模型与AI开放平台是商业化路径，合并降级到备注。</t>
+          <t>证据中强：2025年报披露公司基于CWOS和从容多模态大模型推出大模型训推及智用一体机，并在工程、制造、政务等场景落地；多模态大模型是底座，主线收敛为行业大模型训推一体。</t>
         </is>
       </c>
       <c r="E360" s="6" t="inlineStr">
@@ -10788,22 +10788,22 @@
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>企业AI平台</t>
+          <t>国产算力大模型底座</t>
         </is>
       </c>
       <c r="B361" s="3" t="inlineStr">
         <is>
-          <t>600588</t>
+          <t>002230</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>用友网络</t>
+          <t>科大讯飞</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露用友BIP以AI×数据×流程原生一体，将企业AI融入财务、人力、供应链、制造等核心业务；但公司仍亏损，主线保留企业AI平台并提示盈利修复风险。</t>
+          <t>证据强：2025年报披露讯飞星火持续基于全国产算力训练并推进X1/X1.5等推理模型，2025年大模型相关项目中标金额领先；行业大模型与AI开放平台是商业化路径，合并降级到备注。</t>
         </is>
       </c>
       <c r="E361" s="6" t="inlineStr">
@@ -10815,22 +10815,22 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>企业级AI应用平台</t>
+          <t>企业AI平台</t>
         </is>
       </c>
       <c r="B362" s="3" t="inlineStr">
         <is>
-          <t>300170</t>
+          <t>600588</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>汉得信息</t>
+          <t>用友网络</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司加大行业大模型和垂类智能体研发，基于H-ZERO、H-ONE构建企业级AI基础设施并打造AI应用工厂；AI业务收入放量，主板块由企业AI中台升级为企业级AI应用平台。</t>
+          <t>证据中强：2025年报披露用友BIP以AI×数据×流程原生一体，将企业AI融入财务、人力、供应链、制造等核心业务；但公司仍亏损，主线保留企业AI平台并提示盈利修复风险。</t>
         </is>
       </c>
       <c r="E362" s="6" t="inlineStr">
@@ -10842,22 +10842,22 @@
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>行业AI智能体平台</t>
+          <t>企业级AI应用平台</t>
         </is>
       </c>
       <c r="B363" s="3" t="inlineStr">
         <is>
-          <t>301236</t>
+          <t>300170</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>软通动力</t>
+          <t>汉得信息</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司以软通天璇AutoAgent等平台为引擎，提供从AI咨询、模型部署、智能体开发到持续运营的全流程智能化升级服务；主板块保留行业AI平台并细化为行业AI智能体平台。</t>
+          <t>证据强：2025年报披露公司加大行业大模型和垂类智能体研发，基于H-ZERO、H-ONE构建企业级AI基础设施并打造AI应用工厂；AI业务收入放量，主板块由企业AI中台升级为企业级AI应用平台。</t>
         </is>
       </c>
       <c r="E363" s="6" t="inlineStr">
@@ -10869,22 +10869,22 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>制造业AI智能体平台</t>
+          <t>行业AI智能体平台</t>
         </is>
       </c>
       <c r="B364" s="3" t="inlineStr">
         <is>
-          <t>300378</t>
+          <t>301236</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>鼎捷数智</t>
+          <t>软通动力</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司持续升级鼎捷雅典娜数智底座并丰富AI智能体矩阵，AI相关业务签约金额近2亿元，覆盖生产、销售、财务等制造场景；主板块由工业AI细化为制造业AI智能体平台。</t>
+          <t>证据强：2025年报披露公司以软通天璇AutoAgent等平台为引擎，提供从AI咨询、模型部署、智能体开发到持续运营的全流程智能化升级服务；主板块保留行业AI平台并细化为行业AI智能体平台。</t>
         </is>
       </c>
       <c r="E364" s="6" t="inlineStr">
@@ -10896,22 +10896,22 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>行业AI交付</t>
+          <t>制造业AI智能体平台</t>
         </is>
       </c>
       <c r="B365" s="3" t="inlineStr">
         <is>
-          <t>002649</t>
+          <t>300378</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>博彦科技</t>
+          <t>鼎捷数智</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司以AI、大数据为技术底座，依托人工智能计算平台和AI Agent平台，在金融、能源、化工等行业提供AI咨询、解决方案、实施与运营；AI中台是能力底座，合并到行业AI交付。</t>
+          <t>证据强：2025年报披露公司持续升级鼎捷雅典娜数智底座并丰富AI智能体矩阵，AI相关业务签约金额近2亿元，覆盖生产、销售、财务等制造场景；主板块由工业AI细化为制造业AI智能体平台。</t>
         </is>
       </c>
       <c r="E365" s="6" t="inlineStr">
@@ -10923,22 +10923,22 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>AI数据基础设施软件</t>
+          <t>行业AI交付</t>
         </is>
       </c>
       <c r="B366" s="3" t="inlineStr">
         <is>
-          <t>688031</t>
+          <t>002649</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>星环科技</t>
+          <t>博彦科技</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报显示公司定位企业级AI和大数据基础设施软件，覆盖大数据平台、分布式数据库、数据开发工具和AI平台，并参与向量数据库标准；AI加速卡池化更像数据库/GPU加速能力，合并降级到备注。</t>
+          <t>证据中强：2025年报披露公司以AI、大数据为技术底座，依托人工智能计算平台和AI Agent平台，在金融、能源、化工等行业提供AI咨询、解决方案、实施与运营；AI中台是能力底座，合并到行业AI交付。</t>
         </is>
       </c>
       <c r="E366" s="6" t="inlineStr">
@@ -10950,22 +10950,22 @@
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>向量数据库</t>
+          <t>AI数据基础设施软件</t>
         </is>
       </c>
       <c r="B367" s="3" t="inlineStr">
         <is>
-          <t>603138</t>
+          <t>688031</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>海量数据</t>
+          <t>星环科技</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露公司专注数据库，Vastbase与向量数据库等AI相关能力是大模型开发和智能问答等场景底座；但收入仍以国产数据库替代为主，向量数据库商业化占比未充分拆分。</t>
+          <t>证据中强：2025年报显示公司定位企业级AI和大数据基础设施软件，覆盖大数据平台、分布式数据库、数据开发工具和AI平台，并参与向量数据库标准；AI加速卡池化更像数据库/GPU加速能力，合并降级到备注。</t>
         </is>
       </c>
       <c r="E367" s="6" t="inlineStr">
@@ -10977,22 +10977,22 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>AI数据库</t>
+          <t>向量数据库</t>
         </is>
       </c>
       <c r="B368" s="3" t="inlineStr">
         <is>
-          <t>688692</t>
+          <t>603138</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>达梦数据</t>
+          <t>海量数据</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报显示软件产品使用授权仍是核心收入引擎，公司围绕数据库、云计算、大数据、AI相关产品和数据库一体机形成全栈布局；合并“全栈数据产品”，主板块保留AI数据库。</t>
+          <t>证据中：2025年报披露公司专注数据库，Vastbase与向量数据库等AI相关能力是大模型开发和智能问答等场景底座；但收入仍以国产数据库替代为主，向量数据库商业化占比未充分拆分。</t>
         </is>
       </c>
       <c r="E368" s="6" t="inlineStr">
@@ -11004,22 +11004,22 @@
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>多模态训练数据</t>
+          <t>AI数据库</t>
         </is>
       </c>
       <c r="B369" s="3" t="inlineStr">
         <is>
-          <t>688787</t>
+          <t>688692</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>海天瑞声</t>
+          <t>达梦数据</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露全球AI渗透和多模态大模型需求推动训练数据服务扩容，公司持续投入语音、视觉、NLP、3D点云及大模型数据清洗/自动标注能力；主板块由训练数据细化为多模态训练数据。</t>
+          <t>证据强：2025年报显示软件产品使用授权仍是核心收入引擎，公司围绕数据库、云计算、大数据、AI相关产品和数据库一体机形成全栈布局；合并“全栈数据产品”，主板块保留AI数据库。</t>
         </is>
       </c>
       <c r="E369" s="6" t="inlineStr">
@@ -11031,22 +11031,22 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>中文数据语料</t>
+          <t>多模态训练数据</t>
         </is>
       </c>
       <c r="B370" s="3" t="inlineStr">
         <is>
-          <t>688228</t>
+          <t>688787</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>开普云</t>
+          <t>海天瑞声</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露公司积累PB级数据并参与中文互联网基础语料3.0，专题数据语料平台仍处产品开发阶段；AI链逻辑存在，但商业化确定性低于成熟软件/SaaS。</t>
+          <t>证据强：2025年报披露全球AI渗透和多模态大模型需求推动训练数据服务扩容，公司持续投入语音、视觉、NLP、3D点云及大模型数据清洗/自动标注能力；主板块由训练数据细化为多模态训练数据。</t>
         </is>
       </c>
       <c r="E370" s="6" t="inlineStr">
@@ -11058,22 +11058,22 @@
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>AI安全</t>
+          <t>中文数据语料</t>
         </is>
       </c>
       <c r="B371" s="3" t="inlineStr">
         <is>
-          <t>002439</t>
+          <t>688228</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>启明星辰</t>
+          <t>开普云</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露以AI+安全为核心，推出大模型应用防火墙、访问安全代理、评估系统、脱敏罩、水印及拦截清洗等矩阵；由泛AI安全收敛为大模型应用安全防护。</t>
+          <t>证据中：2025年报披露公司积累PB级数据并参与中文互联网基础语料3.0，专题数据语料平台仍处产品开发阶段；AI链逻辑存在，但商业化确定性低于成熟软件/SaaS。</t>
         </is>
       </c>
       <c r="E371" s="6" t="inlineStr">
@@ -11090,17 +11090,17 @@
       </c>
       <c r="B372" s="3" t="inlineStr">
         <is>
-          <t>300454</t>
+          <t>002439</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>深信服</t>
+          <t>启明星辰</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露AI安全平台以安全数据和模型底座为核心，结合安全GPT大模型，覆盖安全运营、零信任、数据安全、终端安全；AI算力网关和办公助手为辅线。</t>
+          <t>证据强：2025年报披露以AI+安全为核心，推出大模型应用防火墙、访问安全代理、评估系统、脱敏罩、水印及拦截清洗等矩阵；由泛AI安全收敛为大模型应用安全防护。</t>
         </is>
       </c>
       <c r="E372" s="6" t="inlineStr">
@@ -11117,17 +11117,17 @@
       </c>
       <c r="B373" s="3" t="inlineStr">
         <is>
-          <t>688561</t>
+          <t>300454</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>奇安信</t>
+          <t>深信服</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露AISOC、AI+代码卫士、大模型卫士等AI安全新品在客户侧验证并转化收入，覆盖安全运营、检测、数据、代码、攻防智能体；由泛AI安全收敛为AI安全智能体。</t>
+          <t>证据强：2025年报披露AI安全平台以安全数据和模型底座为核心，结合安全GPT大模型，覆盖安全运营、零信任、数据安全、终端安全；AI算力网关和办公助手为辅线。</t>
         </is>
       </c>
       <c r="E373" s="6" t="inlineStr">
@@ -11144,17 +11144,17 @@
       </c>
       <c r="B374" s="3" t="inlineStr">
         <is>
-          <t>688023</t>
+          <t>688561</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>安恒信息</t>
+          <t>奇安信</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露恒脑安全垂域大模型支持多参数模型、量化、软硬一体/SaaS交付并上线智能体商城；AI数据分类分级是恒脑体系的应用场景，合并降级到备注。</t>
+          <t>证据强：2025年报披露AISOC、AI+代码卫士、大模型卫士等AI安全新品在客户侧验证并转化收入，覆盖安全运营、检测、数据、代码、攻防智能体；由泛AI安全收敛为AI安全智能体。</t>
         </is>
       </c>
       <c r="E374" s="6" t="inlineStr">
@@ -11171,17 +11171,17 @@
       </c>
       <c r="B375" s="3" t="inlineStr">
         <is>
-          <t>601360</t>
+          <t>688023</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>三六零</t>
+          <t>安恒信息</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报/半年报披露自研AI大模型驱动互联网产品，同时360安全大模型已在大量用户真实环境测试、应用与交付；主板块由宽泛360大模型收敛为360安全大模型。</t>
+          <t>证据强：2025年报披露恒脑安全垂域大模型支持多参数模型、量化、软硬一体/SaaS交付并上线智能体商城；AI数据分类分级是恒脑体系的应用场景，合并降级到备注。</t>
         </is>
       </c>
       <c r="E375" s="6" t="inlineStr">
@@ -11198,17 +11198,17 @@
       </c>
       <c r="B376" s="3" t="inlineStr">
         <is>
-          <t>300369</t>
+          <t>601360</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>绿盟科技</t>
+          <t>三六零</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露清风卫AI安全系列覆盖评估、防护、响应，并推出AI全生命周期安全测评和备案服务，国家级攻防演练AI内容安全赛道表现突出；保留清风卫AI安全。</t>
+          <t>证据中强：2025年报/半年报披露自研AI大模型驱动互联网产品，同时360安全大模型已在大量用户真实环境测试、应用与交付；主板块由宽泛360大模型收敛为360安全大模型。</t>
         </is>
       </c>
       <c r="E376" s="6" t="inlineStr">
@@ -11220,22 +11220,22 @@
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>AI办公Agent</t>
+          <t>AI安全</t>
         </is>
       </c>
       <c r="B377" s="3" t="inlineStr">
         <is>
-          <t>688111</t>
+          <t>300369</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>金山办公</t>
+          <t>绿盟科技</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露WPS AI政务版、企业知识库、可信溯源和私有化部署等能力，WPS 365持续向企业级智能办公平台演进；企业知识库是AI办公Agent底座能力，合并到备注。</t>
+          <t>证据强：2025年报披露清风卫AI安全系列覆盖评估、防护、响应，并推出AI全生命周期安全测评和备案服务，国家级攻防演练AI内容安全赛道表现突出；保留清风卫AI安全。</t>
         </is>
       </c>
       <c r="E377" s="6" t="inlineStr">
@@ -11247,22 +11247,22 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>PDF文档AI</t>
+          <t>AI办公Agent</t>
         </is>
       </c>
       <c r="B378" s="3" t="inlineStr">
         <is>
-          <t>688095</t>
+          <t>688111</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>福昕软件</t>
+          <t>金山办公</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>证据中强：公司核心仍是PDF/OFD版式文档软件，2025年营收高增并推进AI-Powered Research Agent、智能文档解析、结构化提取和私域知识库；主板块保留PDF文档AI。</t>
+          <t>证据强：2025年报披露WPS AI政务版、企业知识库、可信溯源和私有化部署等能力，WPS 365持续向企业级智能办公平台演进；企业知识库是AI办公Agent底座能力，合并到备注。</t>
         </is>
       </c>
       <c r="E378" s="6" t="inlineStr">
@@ -11274,22 +11274,22 @@
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>问财金融投研AI</t>
+          <t>PDF文档AI</t>
         </is>
       </c>
       <c r="B379" s="3" t="inlineStr">
         <is>
-          <t>300033</t>
+          <t>688095</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>同花顺</t>
+          <t>福昕软件</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025财务决算披露公司持续加大AI研发、自研大模型并提升金融专业场景准确性，叠加营收和净利高增；AI变现依托问财/投研助手和金融信息服务，主线细化为问财金融投研AI。</t>
+          <t>证据中强：公司核心仍是PDF/OFD版式文档软件，2025年营收高增并推进AI-Powered Research Agent、智能文档解析、结构化提取和私域知识库；主板块保留PDF文档AI。</t>
         </is>
       </c>
       <c r="E379" s="6" t="inlineStr">
@@ -11301,22 +11301,22 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>保险IT AI应用</t>
+          <t>问财金融投研AI</t>
         </is>
       </c>
       <c r="B380" s="3" t="inlineStr">
         <is>
-          <t>603927</t>
+          <t>300033</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>中科软</t>
+          <t>同花顺</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司聚焦行业应用软件开发，保险IT解决方案市场占有率持续领先，并继续深耕保险、医疗卫生及政务等重点行业AI应用；主线保留保险IT AI应用，政务AI办公智能体并入备注不单列。</t>
+          <t>证据强：2025财务决算披露公司持续加大AI研发、自研大模型并提升金融专业场景准确性，叠加营收和净利高增；AI变现依托问财/投研助手和金融信息服务，主线细化为问财金融投研AI。</t>
         </is>
       </c>
       <c r="E380" s="6" t="inlineStr">
@@ -11328,22 +11328,22 @@
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>AI多媒体创作平台</t>
+          <t>保险IT AI应用</t>
         </is>
       </c>
       <c r="B381" s="3" t="inlineStr">
         <is>
-          <t>300624</t>
+          <t>603927</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>万兴科技</t>
+          <t>中科软</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露万兴天幕2.0音视频多媒体大模型、AI漫剧/视频创作工作流，全年AI原生应用收入超1.3亿元、同比超90%；主板块由多媒体创作AI收敛为AI多媒体创作平台。</t>
+          <t>证据中强：2025年报披露公司聚焦行业应用软件开发，保险IT解决方案市场占有率持续领先，并继续深耕保险、医疗卫生及政务等重点行业AI应用；主线保留保险IT AI应用，政务AI办公智能体并入备注不单列。</t>
         </is>
       </c>
       <c r="E381" s="6" t="inlineStr">
@@ -11355,22 +11355,22 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>AI+CAx工业设计软件</t>
+          <t>AI多媒体创作平台</t>
         </is>
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>688083</t>
+          <t>300624</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>中望软件</t>
+          <t>万兴科技</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司持续探索AI与CAx软件深度融合，ZWCAD 2026集成相似图形检索等AI功能并以API赋能生态；核心仍是研发设计类工业软件，主板块由工业设计AI细化为AI+CAx工业设计软件。</t>
+          <t>证据强：2025年报披露万兴天幕2.0音视频多媒体大模型、AI漫剧/视频创作工作流，全年AI原生应用收入超1.3亿元、同比超90%；主板块由多媒体创作AI收敛为AI多媒体创作平台。</t>
         </is>
       </c>
       <c r="E382" s="6" t="inlineStr">
@@ -11382,22 +11382,22 @@
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>物理AI工业仿真</t>
+          <t>AI+CAx工业设计软件</t>
         </is>
       </c>
       <c r="B383" s="3" t="inlineStr">
         <is>
-          <t>688507</t>
+          <t>688083</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>索辰科技</t>
+          <t>中望软件</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司以CAE为核心并新增开物系列物理AI平台，物理AI聚焦工业场景机理建模与精准计算，产品矩阵从CAE延伸至工业软件全链条；主板块由工业仿真AI升级为物理AI工业仿真。</t>
+          <t>证据中强：2025年报披露公司持续探索AI与CAx软件深度融合，ZWCAD 2026集成相似图形检索等AI功能并以API赋能生态；核心仍是研发设计类工业软件，主板块由工业设计AI细化为AI+CAx工业设计软件。</t>
         </is>
       </c>
       <c r="E383" s="6" t="inlineStr">
@@ -11409,22 +11409,22 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>流程工业AI</t>
+          <t>物理AI工业仿真</t>
         </is>
       </c>
       <c r="B384" s="3" t="inlineStr">
         <is>
-          <t>688777</t>
+          <t>688507</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>中控技术</t>
+          <t>索辰科技</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>证据强：公司持续深化All in AI战略，将AI能力融入流程工业控制、数据与场景体系；客户和控制系统部署基础集中在石化、化工、电力、冶金、制药等流程工业，主板块由工业AI收敛为流程工业AI。</t>
+          <t>证据强：2025年报披露公司以CAE为核心并新增开物系列物理AI平台，物理AI聚焦工业场景机理建模与精准计算，产品矩阵从CAE延伸至工业软件全链条；主板块由工业仿真AI升级为物理AI工业仿真。</t>
         </is>
       </c>
       <c r="E384" s="6" t="inlineStr">
@@ -11436,22 +11436,22 @@
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>激光加工AI工艺优化</t>
+          <t>流程工业AI</t>
         </is>
       </c>
       <c r="B385" s="3" t="inlineStr">
         <is>
-          <t>688188</t>
+          <t>688777</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>柏楚电子</t>
+          <t>中控技术</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司在金属成型中基于自研AI模型实现切割断面自动采集与闭环工艺调试，并推进智能焊接、视觉识别和多机协同；主板块由工艺专家库细化为激光加工AI工艺优化。</t>
+          <t>证据强：公司持续深化All in AI战略，将AI能力融入流程工业控制、数据与场景体系；客户和控制系统部署基础集中在石化、化工、电力、冶金、制药等流程工业，主板块由工业AI收敛为流程工业AI。</t>
         </is>
       </c>
       <c r="E385" s="6" t="inlineStr">
@@ -11463,22 +11463,22 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>AI分子砌块设计</t>
+          <t>激光加工AI工艺优化</t>
         </is>
       </c>
       <c r="B386" s="3" t="inlineStr">
         <is>
-          <t>300725</t>
+          <t>688188</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>药石科技</t>
+          <t>柏楚电子</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年投资者交流披露公司在前端分子砌块研发中应用AI生成8,000多万个新颖分子砌块，筛选后产品已陆续上线；核心仍是分子砌块+CDMO，主板块由AI分子砌块筛选细化为AI分子砌块设计。</t>
+          <t>证据强：2025年报披露公司在金属成型中基于自研AI模型实现切割断面自动采集与闭环工艺调试，并推进智能焊接、视觉识别和多机协同；主板块由工艺专家库细化为激光加工AI工艺优化。</t>
         </is>
       </c>
       <c r="E386" s="6" t="inlineStr">
@@ -11490,22 +11490,22 @@
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>AI片段分子库</t>
+          <t>AI分子砌块设计</t>
         </is>
       </c>
       <c r="B387" s="3" t="inlineStr">
         <is>
-          <t>688131</t>
+          <t>300725</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>皓元医药</t>
+          <t>药石科技</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露公司开发药物片段分子库，完成1万多种可用于药物筛选的小分子及类似物，并指出片段分子库结合人工智能大数据和实验筛选模型用于先导化合物发现；AI化合物库收敛为AI片段分子库。</t>
+          <t>证据中强：2025年投资者交流披露公司在前端分子砌块研发中应用AI生成8,000多万个新颖分子砌块，筛选后产品已陆续上线；核心仍是分子砌块+CDMO，主板块由AI分子砌块筛选细化为AI分子砌块设计。</t>
         </is>
       </c>
       <c r="E387" s="6" t="inlineStr">
@@ -11517,22 +11517,22 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>AI药物发现</t>
+          <t>AI片段分子库</t>
         </is>
       </c>
       <c r="B388" s="3" t="inlineStr">
         <is>
-          <t>688222</t>
+          <t>688131</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>成都先导</t>
+          <t>皓元医药</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司以DEL技术为核心，并自主研发DEL+AI+自动化一体化分子优化平台HAILO，覆盖计算科学/AI数据分析与分子设计；主板块由AI制药收敛为AI药物发现。</t>
+          <t>证据中：2025年报披露公司开发药物片段分子库，完成1万多种可用于药物筛选的小分子及类似物，并指出片段分子库结合人工智能大数据和实验筛选模型用于先导化合物发现；AI化合物库收敛为AI片段分子库。</t>
         </is>
       </c>
       <c r="E388" s="6" t="inlineStr">
@@ -11544,22 +11544,22 @@
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>AI辅助药物设计</t>
+          <t>AI药物发现</t>
         </is>
       </c>
       <c r="B389" s="3" t="inlineStr">
         <is>
-          <t>301230</t>
+          <t>688222</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>泓博医药</t>
+          <t>成都先导</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司以药物设计为核心驱动，在先导化合物发现阶段使用计算机/人工智能辅助药物设计，并覆盖靶点识别、虚拟筛选、结构预测、分子对接、分子动力学和ADME预测；AI是CRO/CDMO服务能力，不单列泛AI制药。</t>
+          <t>证据中强：2025年报披露公司以DEL技术为核心，并自主研发DEL+AI+自动化一体化分子优化平台HAILO，覆盖计算科学/AI数据分析与分子设计；主板块由AI制药收敛为AI药物发现。</t>
         </is>
       </c>
       <c r="E389" s="6" t="inlineStr">
@@ -11571,22 +11571,22 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>AI患者追踪系统</t>
+          <t>AI辅助药物设计</t>
         </is>
       </c>
       <c r="B390" s="3" t="inlineStr">
         <is>
-          <t>300451</t>
+          <t>301230</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>创业慧康</t>
+          <t>泓博医药</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>证据中强但基本面承压：2025年报披露公司以AI技术创新驱动医疗场景落地，AI关键患者追踪系统APTS以医疗大模型为底座筛查高危患者并开展分级追踪；医疗大模型概念收敛为更具体的AI患者追踪系统。</t>
+          <t>证据中强：2025年报披露公司以药物设计为核心驱动，在先导化合物发现阶段使用计算机/人工智能辅助药物设计，并覆盖靶点识别、虚拟筛选、结构预测、分子对接、分子动力学和ADME预测；AI是CRO/CDMO服务能力，不单列泛AI制药。</t>
         </is>
       </c>
       <c r="E390" s="6" t="inlineStr">
@@ -11598,22 +11598,22 @@
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>AI医学影像设备</t>
+          <t>AI患者追踪系统</t>
         </is>
       </c>
       <c r="B391" s="3" t="inlineStr">
         <is>
-          <t>688271</t>
+          <t>300451</t>
         </is>
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>联影医疗</t>
+          <t>创业慧康</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司医学影像与放疗设备收入创新高，并推进设备+AI在医学影像诊疗和治疗场景落地，原生智能超声、光子计数CT、双宽体双源CT等高端产品放量；主板块保留医疗影像AI并细化为AI医学影像设备。</t>
+          <t>证据中强但基本面承压：2025年报披露公司以AI技术创新驱动医疗场景落地，AI关键患者追踪系统APTS以医疗大模型为底座筛查高危患者并开展分级追踪；医疗大模型概念收敛为更具体的AI患者追踪系统。</t>
         </is>
       </c>
       <c r="E391" s="6" t="inlineStr">
@@ -11625,22 +11625,22 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>医疗信息化大模型</t>
+          <t>AI医学影像设备</t>
         </is>
       </c>
       <c r="B392" s="3" t="inlineStr">
         <is>
-          <t>300253</t>
+          <t>688271</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>卫宁健康</t>
+          <t>联影医疗</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>证据强但业绩承压：2025年报/半年报披露公司发布WiNGPT医疗大模型和WiNEX Copilot，覆盖文书生成、病历质控、诊中决策、报告解读、护理评估等场景，并在多家医疗机构部署；主线为医疗信息化大模型而非通用医疗AI。</t>
+          <t>证据强：2025年报披露公司医学影像与放疗设备收入创新高，并推进设备+AI在医学影像诊疗和治疗场景落地，原生智能超声、光子计数CT、双宽体双源CT等高端产品放量；主板块保留医疗影像AI并细化为AI医学影像设备。</t>
         </is>
       </c>
       <c r="E392" s="6" t="inlineStr">
@@ -11652,25 +11652,52 @@
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
+          <t>医疗信息化大模型</t>
+        </is>
+      </c>
+      <c r="B393" s="3" t="inlineStr">
+        <is>
+          <t>300253</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>卫宁健康</t>
+        </is>
+      </c>
+      <c r="D393" s="2" t="inlineStr">
+        <is>
+          <t>证据强但业绩承压：2025年报/半年报披露公司发布WiNGPT医疗大模型和WiNEX Copilot，覆盖文书生成、病历质控、诊中决策、报告解读、护理评估等场景，并在多家医疗机构部署；主线为医疗信息化大模型而非通用医疗AI。</t>
+        </is>
+      </c>
+      <c r="E393" s="6" t="inlineStr">
+        <is>
+          <t>已处理</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
           <t>医学检验AI服务</t>
         </is>
       </c>
-      <c r="B393" s="3" t="inlineStr">
+      <c r="B394" s="3" t="inlineStr">
         <is>
           <t>603108</t>
         </is>
       </c>
-      <c r="C393" s="2" t="inlineStr">
+      <c r="C394" s="2" t="inlineStr">
         <is>
           <t>润达医疗</t>
         </is>
       </c>
-      <c r="D393" s="2" t="inlineStr">
+      <c r="D394" s="2" t="inlineStr">
         <is>
           <t>证据中强但业绩弱：2025年报披露公司推出大模型产品CDx良医晓慧，覆盖数据基座、医生助理和健康智能体，已在华西、南方、齐鲁等医院落地；核心仍是IVD流通/实验室服务，主板块由IVD检验AI细化为医学检验AI服务。</t>
         </is>
       </c>
-      <c r="E393" s="6" t="inlineStr">
+      <c r="E394" s="6" t="inlineStr">
         <is>
           <t>已处理</t>
         </is>

--- a/watchlists/AI产业链.xlsx
+++ b/watchlists/AI产业链.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI产业链" sheetId="1" r:id="Ra745c65ac7ac4598"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI产业链" sheetId="1" r:id="Rd1f8d500f6a04c04"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7404,10 +7404,8 @@
           <x:t xml:space="preserve">半导体测试服务</x:t>
         </x:is>
       </x:c>
-      <x:c r="B241" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">430139</x:t>
-        </x:is>
+      <x:c r="B241" s="3" t="str">
+        <x:v>920139</x:v>
       </x:c>
       <x:c r="C241" s="2" t="inlineStr">
         <x:is>
@@ -11526,6 +11524,6 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd72c834f64724eb1"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4cd08c757d024d8b"/>
 </x:worksheet>
 </file>
--- a/watchlists/AI产业链.xlsx
+++ b/watchlists/AI产业链.xlsx
@@ -1606,7 +1606,7 @@
     <row r="26" ht="90" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>FAU</t>
+          <t>新型光纤/无源内连光器件</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1621,12 +1621,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>并表子公司生一升的无源内连光器件覆盖AWG、MT-FA/FA-REC、光纤阵列；2026H1正式披露用于100G–800G高速光模块、数据中心/云计算，且无源内连产品交付增加。1.6T MT-FA+Lens项目已完成工艺研发并称实现产品量产，但未披露CPO客户、订单、出货或独立收入。重点复核：器件保偏光纤仅处客户验证，公司称其适配CPO/硅光互连；2026-08-15公告称业务体量有限、在手订单少、通信领域未新增重大客户，不能按CPO规模应用、AI订单或收入处理。证据A：上交所2026-08-15、2026-08-25。</t>
+          <t>2026H1官方：无源内连光器件需求增加；器件级保偏光纤（PMF）面向AI服务器/智算集群，披露称匹配CPO/硅光；“FAU型器件保偏光纤”只列为FAU多芯阵列应用。CPO、PMF、PM-FAU均为条件性观察（产品方向/验证与产能表述，非商业闭环）；具名客户、CPO/PMF/PM-FAU量产订单、独立AI收入均=evidence_absent。证据A：上交所《2026年半年度报告》2026-08-25。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>新增；2026-08-31重点复核：无源内连=收入，器件保偏=验证/观察</t>
+          <t>已复核；2026H1官方披露；条件性观察（CPO/PMF/PM-FAU），客户/订单/独立AI收入=evidence_absent</t>
         </is>
       </c>
     </row>

--- a/watchlists/AI产业链.xlsx
+++ b/watchlists/AI产业链.xlsx
@@ -934,7 +934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E395"/>
+  <dimension ref="A1:E396"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -8155,49 +8155,49 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>内存接口芯片</t>
+          <t>DRAM存储制造</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>688008</t>
+          <t>688825</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>澜起科技</t>
+          <t>长鑫科技</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>DDR5 RCD/DB、MRCD/MDB、CKD是AI服务器高带宽内存互连核心节点，PCIe Retimer、CXL MXC扩展高速互连第二曲线；主板块收敛为内存接口芯片，HBM、DDR5 SPD、SOCAMM、CXL和CXL内存扩展模组均并入备注或删除，避免误当存储模组/HBM厂商。风险是海外竞争、服务器平台迭代和新品放量节奏。证据A。</t>
+          <t>证据A：DRAM IDM，DDR5已量产并用于服务器，属于AI服务器/数据中心的通用DRAM节点。招股书披露报告期内用于AI算力服务器的DRAM收入占比仍低；不以HBM受益逻辑纳入，HBM量产、客户、订单、收入及独立AI收入均为evidence_absent。来源：上交所招股书（2026-07-22）、公司产品页（2026-09-05复核）。</t>
         </is>
       </c>
       <c r="E269" s="6" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>已复核；2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>DDR5 SPD</t>
+          <t>内存接口芯片</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>688123</t>
+          <t>688008</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>聚辰股份</t>
+          <t>澜起科技</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>公司具备DDR2/3/4/5内存模组配套SPD、TS等芯片产品，DDR5 SPD受益AI服务器内存模组数量提升，是明确的小芯片弹性节点；主板块保留DDR5 SPD，SOCAMM作为下游内存模组形态并入备注，不单列。风险是DDR5渗透节奏、客户导入、EEPROM周期和价格竞争。证据A。</t>
+          <t>DDR5 RCD/DB、MRCD/MDB、CKD是AI服务器高带宽内存互连核心节点，PCIe Retimer、CXL MXC扩展高速互连第二曲线；主板块收敛为内存接口芯片，HBM、DDR5 SPD、SOCAMM、CXL和CXL内存扩展模组均并入备注或删除，避免误当存储模组/HBM厂商。风险是海外竞争、服务器平台迭代和新品放量节奏。证据A。</t>
         </is>
       </c>
       <c r="E270" s="6" t="inlineStr">
@@ -8209,22 +8209,22 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>高端存储分销</t>
+          <t>DDR5 SPD</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>300475</t>
+          <t>688123</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>香农芯创</t>
+          <t>聚辰股份</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>公司以SK海力士核心代理分销为基本盘，向国内云服务器龙头和大型ODM提供存储解决方案；HBM/DDR5紧缺带来强周期弹性，但本质不是HBM制造商。自主海普存储企业级SSD/DRAM开始贡献增量。主板块由HBM改为高端存储分销，风险是存储价格周期、供应商授权、分销毛利和库存。证据A/B。</t>
+          <t>公司具备DDR2/3/4/5内存模组配套SPD、TS等芯片产品，DDR5 SPD受益AI服务器内存模组数量提升，是明确的小芯片弹性节点；主板块保留DDR5 SPD，SOCAMM作为下游内存模组形态并入备注，不单列。风险是DDR5渗透节奏、客户导入、EEPROM周期和价格竞争。证据A。</t>
         </is>
       </c>
       <c r="E271" s="6" t="inlineStr">
@@ -8236,22 +8236,22 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>企业级存储模组</t>
+          <t>高端存储分销</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>688525</t>
+          <t>300475</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>佰维存储</t>
+          <t>香农芯创</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>公司企业级存储方案覆盖PCIe/SATA SSD、DDR4/DDR5 RDIMM和CXL内存扩展模组，服务数据中心、服务器和AI工作负载；主板块由DDR5 SPD改为企业级存储模组，SOCAMM、企业级SSD、SSD主控、UFS、晶圆级封测和CXL并入备注或降级。风险是NAND/DRAM价格周期、库存、客户认证和自研控制器/封测兑现。证据B。</t>
+          <t>公司以SK海力士核心代理分销为基本盘，向国内云服务器龙头和大型ODM提供存储解决方案；HBM/DDR5紧缺带来强周期弹性，但本质不是HBM制造商。自主海普存储企业级SSD/DRAM开始贡献增量。主板块由HBM改为高端存储分销，风险是存储价格周期、供应商授权、分销毛利和库存。证据A/B。</t>
         </is>
       </c>
       <c r="E272" s="6" t="inlineStr">
@@ -8268,17 +8268,17 @@
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>301308</t>
+          <t>688525</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>佰维存储</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>公司企业级eSSD和RDIMM已在互联网、运营商等客户完成验证并批量出货，SOCAMM2、CXL内存扩展、MRDIMM等构成AI服务器存储升级可选项；主板块由SOCAMM改为企业级存储模组，端侧UFS、eMMC、SSD主控、SPU、HLC-iSA、mSSD和CXL并入备注。SOCAMM2仍需收入贡献验证。证据A/B。</t>
+          <t>公司企业级存储方案覆盖PCIe/SATA SSD、DDR4/DDR5 RDIMM和CXL内存扩展模组，服务数据中心、服务器和AI工作负载；主板块由DDR5 SPD改为企业级存储模组，SOCAMM、企业级SSD、SSD主控、UFS、晶圆级封测和CXL并入备注或降级。风险是NAND/DRAM价格周期、库存、客户认证和自研控制器/封测兑现。证据B。</t>
         </is>
       </c>
       <c r="E273" s="6" t="inlineStr">
@@ -8290,22 +8290,22 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>企业级SSD</t>
+          <t>企业级存储模组</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>001309</t>
+          <t>301308</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报摘要披露AI浪潮下公司加快向高容量、高性能固态硬盘拓展，重点聚焦QLC NAND企业级应用方向；自研主控是能力基础，但表格保留最贴近收入承载的“企业级SSD”，删减企业级SSD主控、QLC SSD、AI场景化存储方案重复行。风险是存储价格周期和经营现金流波动。</t>
+          <t>公司企业级eSSD和RDIMM已在互联网、运营商等客户完成验证并批量出货，SOCAMM2、CXL内存扩展、MRDIMM等构成AI服务器存储升级可选项；主板块由SOCAMM改为企业级存储模组，端侧UFS、eMMC、SSD主控、SPU、HLC-iSA、mSSD和CXL并入备注。SOCAMM2仍需收入贡献验证。证据A/B。</t>
         </is>
       </c>
       <c r="E274" s="6" t="inlineStr">
@@ -8317,22 +8317,22 @@
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>企业级SSD主控</t>
+          <t>企业级SSD</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>300672</t>
+          <t>001309</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>国科微</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>证据中偏弱：公司固态存储主控芯片实现国产替代，同时布局端侧AI、车载电子、智慧视觉等多条芯片线；AI数据中心企业级SSD客户、收入占比和订单仍未充分披露，保留为SSD主控国产替代观察，基本面需关注2025亏损后毛利修复和研发投入转化。</t>
+          <t>证据中强：2025年报摘要披露AI浪潮下公司加快向高容量、高性能固态硬盘拓展，重点聚焦QLC NAND企业级应用方向；自研主控是能力基础，但表格保留最贴近收入承载的“企业级SSD”，删减企业级SSD主控、QLC SSD、AI场景化存储方案重复行。风险是存储价格周期和经营现金流波动。</t>
         </is>
       </c>
       <c r="E275" s="6" t="inlineStr">
@@ -8349,17 +8349,17 @@
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>688449</t>
+          <t>300672</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>联芸科技</t>
+          <t>国科微</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露SSD主控覆盖SATA、PCIe3.0/4.0/5.0，企业级PCIe Gen5 SSD主控已进入量产测试阶段，并规划PCIe Gen6/Gen7切入数据中心；删减UFS主控重复行，UFS偏终端嵌入式，AI算力弹性以企业级SSD主控为主。</t>
+          <t>证据中偏弱：公司固态存储主控芯片实现国产替代，同时布局端侧AI、车载电子、智慧视觉等多条芯片线；AI数据中心企业级SSD客户、收入占比和订单仍未充分披露，保留为SSD主控国产替代观察，基本面需关注2025亏损后毛利修复和研发投入转化。</t>
         </is>
       </c>
       <c r="E276" s="6" t="inlineStr">
@@ -8371,22 +8371,22 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>AI存储</t>
+          <t>企业级SSD主控</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>300302</t>
+          <t>688449</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>同有科技</t>
+          <t>联芸科技</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露高端存储在AI智算中心、高性能计算等核心场景推进，NVMe/RDMA高性能分布式文件存储用于智算领域高并发、低延迟需求；主板块保留AI存储，跟踪标杆方案复制、国产化替代和毛利率。</t>
+          <t>证据强：2025年报披露SSD主控覆盖SATA、PCIe3.0/4.0/5.0，企业级PCIe Gen5 SSD主控已进入量产测试阶段，并规划PCIe Gen6/Gen7切入数据中心；删减UFS主控重复行，UFS偏终端嵌入式，AI算力弹性以企业级SSD主控为主。</t>
         </is>
       </c>
       <c r="E277" s="6" t="inlineStr">
@@ -8398,30 +8398,34 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>HBF高带宽闪存</t>
+          <t>AI存储</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>300302</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>暂无成熟A股纯标的</t>
+          <t>同有科技</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>德明利2025半年报提到闪迪HBF结合3D NAND与HBM、适合读取密集型AI推理任务；A股暂无成熟高带宽闪存纯标的。</t>
-        </is>
-      </c>
-      <c r="E278" s="6" t="n"/>
+          <t>证据强：2025年报披露高端存储在AI智算中心、高性能计算等核心场景推进，NVMe/RDMA高性能分布式文件存储用于智算领域高并发、低延迟需求；主板块保留AI存储，跟踪标杆方案复制、国产化替代和毛利率。</t>
+        </is>
+      </c>
+      <c r="E278" s="6" t="inlineStr">
+        <is>
+          <t>已处理</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>Nearline HDD</t>
+          <t>HBF高带宽闪存</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -8436,7 +8440,7 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>希捷和西部数据官方披露AI数据增长推动数据中心exabyte级低成本存储需求；近线HDD仍主要由海外双寡头主导。</t>
+          <t>德明利2025半年报提到闪迪HBF结合3D NAND与HBM、适合读取密集型AI推理任务；A股暂无成熟高带宽闪存纯标的。</t>
         </is>
       </c>
       <c r="E279" s="6" t="n"/>
@@ -8444,7 +8448,7 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>HAMR-ePMR高容量HDD</t>
+          <t>Nearline HDD</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -8459,7 +8463,7 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>希捷披露HAMR Mozaic放量，西部数据披露40TB UltraSMR ePMR验证和HAMR 100TB路线；A股暂无成熟HDD主线标的。</t>
+          <t>希捷和西部数据官方披露AI数据增长推动数据中心exabyte级低成本存储需求；近线HDD仍主要由海外双寡头主导。</t>
         </is>
       </c>
       <c r="E280" s="6" t="n"/>
@@ -8467,7 +8471,7 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>高带宽HDD</t>
+          <t>HAMR-ePMR高容量HDD</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
@@ -8482,7 +8486,7 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>西部数据2026 Innovation Day披露High Bandwidth Drive与Dual Pivot提升HDD带宽/IO，服务AI温冷数据层，A股暂无对应纯标的。</t>
+          <t>希捷披露HAMR Mozaic放量，西部数据披露40TB UltraSMR ePMR验证和HAMR 100TB路线；A股暂无成熟HDD主线标的。</t>
         </is>
       </c>
       <c r="E281" s="6" t="n"/>
@@ -8490,7 +8494,7 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>CXL</t>
+          <t>高带宽HDD</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -8505,7 +8509,7 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Astera/Broadcom/Marvell主导高速互连芯片，A股除澜起接口芯片外不宜硬凑纯Retimer/PCIe switch标的。</t>
+          <t>西部数据2026 Innovation Day披露High Bandwidth Drive与Dual Pivot提升HDD带宽/IO，服务AI温冷数据层，A股暂无对应纯标的。</t>
         </is>
       </c>
       <c r="E282" s="6" t="n"/>
@@ -8513,22 +8517,22 @@
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>CXL内存扩展模组</t>
+          <t>CXL</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
           <t>暂无成熟A股纯标的</t>
         </is>
       </c>
-      <c r="C283" s="2" t="inlineStr">
-        <is>
-          <t>CXL Switch暂无成熟A股纯标的</t>
-        </is>
-      </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>CXL交换/池化控制仍主要由Marvell等海外厂商推进，A股目前缺成熟CXL Switch纯标的。</t>
+          <t>Astera/Broadcom/Marvell主导高速互连芯片，A股除澜起接口芯片外不宜硬凑纯Retimer/PCIe switch标的。</t>
         </is>
       </c>
       <c r="E283" s="6" t="n"/>
@@ -8536,49 +8540,45 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>HBM BI</t>
+          <t>CXL内存扩展模组</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>300567</t>
+          <t>暂无成熟A股纯标的</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>精测电子</t>
+          <t>CXL Switch暂无成熟A股纯标的</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>检测设备平台，2025年报摘要披露推出JH5520 HBM BI测试系统以满足HBM高端存储测试需求，半导体量检测覆盖前道、后道电测和先进封装；主板块改为HBM BI，PCB AOI、半导体量测和先进封装X-Ray并入备注，风险是半导体业务收入占比、客户认证和设备订单兑现。证据A/B。</t>
-        </is>
-      </c>
-      <c r="E284" s="6" t="inlineStr">
-        <is>
-          <t>已处理</t>
-        </is>
-      </c>
+          <t>CXL交换/池化控制仍主要由Marvell等海外厂商推进，A股目前缺成熟CXL Switch纯标的。</t>
+        </is>
+      </c>
+      <c r="E284" s="6" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>AI服务器整机</t>
+          <t>HBM BI</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>603019</t>
+          <t>300567</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>精测电子</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>证据中强：公司核心是高端计算机、智能计算和算力服务，2025年报披露继续围绕AI算力、液冷散热、高速互联等核心领域投入；AI存储和推理板卡只是配套能力，删减AI存储、AI推理板卡、AI服务器ODM重复行，保留更准确的AI服务器整机/智算底座定位。</t>
+          <t>检测设备平台，2025年报摘要披露推出JH5520 HBM BI测试系统以满足HBM高端存储测试需求，半导体量检测覆盖前道、后道电测和先进封装；主板块改为HBM BI，PCB AOI、半导体量测和先进封装X-Ray并入备注，风险是半导体业务收入占比、客户认证和设备订单兑现。证据A/B。</t>
         </is>
       </c>
       <c r="E285" s="6" t="inlineStr">
@@ -8595,17 +8595,17 @@
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>000977</t>
+          <t>603019</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>浪潮信息</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露总营收1647.82亿元、同比增长43.25%，主要由服务器产品销售增长驱动；存储交换类收入占比小，删减AI存储重复行，主板块改为AI服务器整机。风险是服务器高增但毛利率偏低，GPU/核心器件供应和价格压力影响利润弹性。</t>
+          <t>证据中强：公司核心是高端计算机、智能计算和算力服务，2025年报披露继续围绕AI算力、液冷散热、高速互联等核心领域投入；AI存储和推理板卡只是配套能力，删减AI存储、AI推理板卡、AI服务器ODM重复行，保留更准确的AI服务器整机/智算底座定位。</t>
         </is>
       </c>
       <c r="E286" s="6" t="inlineStr">
@@ -8622,17 +8622,17 @@
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>000034</t>
+          <t>000977</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>神州数码</t>
+          <t>浪潮信息</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露AI相关业务收入330.3亿元、同比增长47.7%，神州鲲泰服务器基于鲲鹏CPU+昇腾NPU支持DeepSeek等大模型私有化部署，并开放国产技术栈AI智算OpenLab；主线是国产算力整机和方案。</t>
+          <t>证据强：2025年报披露总营收1647.82亿元、同比增长43.25%，主要由服务器产品销售增长驱动；存储交换类收入占比小，删减AI存储重复行，主板块改为AI服务器整机。风险是服务器高增但毛利率偏低，GPU/核心器件供应和价格压力影响利润弹性。</t>
         </is>
       </c>
       <c r="E287" s="6" t="inlineStr">
@@ -8649,17 +8649,17 @@
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>002261</t>
+          <t>000034</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>拓维信息</t>
+          <t>神州数码</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报摘要披露公司基于“鲲鹏+昇腾AI”算力底座，推出中心侧高性能服务器、推理服务器和边端终端侧产品；主板块从国产AI服务器收敛为昇腾AI服务器，风险是收入下滑、利润体量仍小。</t>
+          <t>证据中强：2025年报披露AI相关业务收入330.3亿元、同比增长47.7%，神州鲲泰服务器基于鲲鹏CPU+昇腾NPU支持DeepSeek等大模型私有化部署，并开放国产技术栈AI智算OpenLab；主线是国产算力整机和方案。</t>
         </is>
       </c>
       <c r="E288" s="6" t="inlineStr">
@@ -8671,22 +8671,22 @@
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>AI服务器ODM</t>
+          <t>AI服务器整机</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>601138</t>
+          <t>002261</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>工业富联</t>
+          <t>拓维信息</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司与全球头部客户协同下一代AI服务器及液冷技术，云服务商AI服务器收入同比大增，GPU与ASIC方案产品快速增长；删减“AI服务器机柜”重复行，机柜/液冷作为ODM系统能力纳入备注。</t>
+          <t>证据中：2025年报摘要披露公司基于“鲲鹏+昇腾AI”算力底座，推出中心侧高性能服务器、推理服务器和边端终端侧产品；主板块从国产AI服务器收敛为昇腾AI服务器，风险是收入下滑、利润体量仍小。</t>
         </is>
       </c>
       <c r="E289" s="6" t="inlineStr">
@@ -8703,17 +8703,17 @@
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>603296</t>
+          <t>601138</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>华勤技术</t>
+          <t>工业富联</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露华勤数据中心业务形成AI服务器、通用服务器、交换机等全栈产品组合，数据中心业务收入754.75亿元、同比增长51.93%；主板块保留AI服务器ODM，AI PC和终端ODM作为附属受益。</t>
+          <t>证据强：2025年报披露公司与全球头部客户协同下一代AI服务器及液冷技术，云服务商AI服务器收入同比大增，GPU与ASIC方案产品快速增长；删减“AI服务器机柜”重复行，机柜/液冷作为ODM系统能力纳入备注。</t>
         </is>
       </c>
       <c r="E290" s="6" t="inlineStr">
@@ -8725,22 +8725,22 @@
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>算力服务器结构件</t>
+          <t>AI服务器ODM</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>002965</t>
+          <t>603296</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>祥鑫科技</t>
+          <t>华勤技术</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>证据中弱：2025年报披露公司在通信设备领域可供应通讯插箱、交换机箱、算力服务器等产品和服务，但汽车业务仍占收入主体且净利润下滑；主板块由AI服务器机柜收敛为算力服务器结构件，AI订单强度需继续验证。</t>
+          <t>证据强：2025年报披露华勤数据中心业务形成AI服务器、通用服务器、交换机等全栈产品组合，数据中心业务收入754.75亿元、同比增长51.93%；主板块保留AI服务器ODM，AI PC和终端ODM作为附属受益。</t>
         </is>
       </c>
       <c r="E291" s="6" t="inlineStr">
@@ -8752,22 +8752,22 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>智能算力产品及服务</t>
+          <t>算力服务器结构件</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>300857</t>
+          <t>002965</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>协创数据</t>
+          <t>祥鑫科技</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露智能算力产品及服务收入27.61亿元、同比增长1727.17%、占总收入22.57%，成为第二大收入支柱；原IDC标签不准确，改为智能算力产品及服务。</t>
+          <t>证据中弱：2025年报披露公司在通信设备领域可供应通讯插箱、交换机箱、算力服务器等产品和服务，但汽车业务仍占收入主体且净利润下滑；主板块由AI服务器机柜收敛为算力服务器结构件，AI订单强度需继续验证。</t>
         </is>
       </c>
       <c r="E292" s="6" t="inlineStr">
@@ -8779,22 +8779,22 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>国产AI加速芯片</t>
+          <t>智能算力产品及服务</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>688256</t>
+          <t>300857</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>寒武纪</t>
+          <t>协创数据</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司云边端智能芯片及板卡矩阵，云端产品线面向服务器和数据中心AI处理，收入大增并首次全年盈利；删减“AI推理板卡”重复行，板卡是产品形态，主板块归入国产AI加速芯片。</t>
+          <t>证据强：2025年报披露智能算力产品及服务收入27.61亿元、同比增长1727.17%、占总收入22.57%，成为第二大收入支柱；原IDC标签不准确，改为智能算力产品及服务。</t>
         </is>
       </c>
       <c r="E293" s="6" t="inlineStr">
@@ -8806,22 +8806,22 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>国产CPU-DCU芯片</t>
+          <t>国产AI加速芯片</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>688041</t>
+          <t>688256</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>寒武纪</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报及公开资料显示海光坚持CPU+DCU双芯战略，DCU软件栈适配大模型训练推理并在多行业场景落地；删减“AI推理板卡”重复行，核心价值在国产高端处理器和DCU算力平台。</t>
+          <t>证据强：2025年报披露公司云边端智能芯片及板卡矩阵，云端产品线面向服务器和数据中心AI处理，收入大增并首次全年盈利；删减“AI推理板卡”重复行，板卡是产品形态，主板块归入国产AI加速芯片。</t>
         </is>
       </c>
       <c r="E294" s="6" t="inlineStr">
@@ -8833,22 +8833,22 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>国产GPU芯片</t>
+          <t>国产CPU-DCU芯片</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>300474</t>
+          <t>688041</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>景嘉微</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露公司推进“高性能GPU+边端侧AI SoC芯片”双轮驱动，景宏系列智算模块及整机产品瞄准AI训练和推理；删减“AI推理板卡”重复行，当前仍以国产GPU芯片为主线，亏损和商业化规模是主要风险。</t>
+          <t>证据强：2025年报及公开资料显示海光坚持CPU+DCU双芯战略，DCU软件栈适配大模型训练推理并在多行业场景落地；删减“AI推理板卡”重复行，核心价值在国产高端处理器和DCU算力平台。</t>
         </is>
       </c>
       <c r="E295" s="6" t="inlineStr">
@@ -8860,22 +8860,22 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>AI推理芯片</t>
+          <t>国产GPU芯片</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>688343</t>
+          <t>300474</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>云天励飞</t>
+          <t>景嘉微</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司构建应用、算法、芯片全栈能力，自研AI推理芯片适配国产大模型、操作系统和推理框架，并推出大模型一体机；一体机为产品化形态，主板块保留AI推理芯片。</t>
+          <t>证据中：2025年报披露公司推进“高性能GPU+边端侧AI SoC芯片”双轮驱动，景宏系列智算模块及整机产品瞄准AI训练和推理；删减“AI推理板卡”重复行，当前仍以国产GPU芯片为主线，亏损和商业化规模是主要风险。</t>
         </is>
       </c>
       <c r="E296" s="6" t="inlineStr">
@@ -8887,22 +8887,22 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>智算网络设备</t>
+          <t>AI推理芯片</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>000938</t>
+          <t>688343</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>紫光股份</t>
+          <t>云天励飞</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>证据强：新华三深度覆盖云、网、安、算、存、端，但公司披露中国数据中心交换机份额居前，并在智算网络、800G/CPO交换机和AI算力基础设施上持续推进；删减AI存储、AI服务器ODM重复行，主板块保留最能体现差异化和份额优势的智算交换机。</t>
+          <t>证据中强：2025年报披露公司构建应用、算法、芯片全栈能力，自研AI推理芯片适配国产大模型、操作系统和推理框架，并推出大模型一体机；一体机为产品化形态，主板块保留AI推理芯片。</t>
         </is>
       </c>
       <c r="E297" s="6" t="inlineStr">
@@ -8919,17 +8919,17 @@
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>301165</t>
+          <t>000938</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>锐捷网络</t>
+          <t>紫光股份</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露AI智算中心网络方案已服务中国移动、阿里、字节、百度、腾讯等训练/推理大模型场景，数据中心交换机订单加速交付；IDC数据显示中国数据中心交换机市占率第三。</t>
+          <t>证据强：新华三深度覆盖云、网、安、算、存、端，但公司披露中国数据中心交换机份额居前，并在智算网络、800G/CPO交换机和AI算力基础设施上持续推进；删减AI存储、AI服务器ODM重复行，主板块保留最能体现差异化和份额优势的智算交换机。</t>
         </is>
       </c>
       <c r="E298" s="6" t="inlineStr">
@@ -8946,17 +8946,17 @@
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>000063</t>
+          <t>301165</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>中兴通讯</t>
+          <t>锐捷网络</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报及公司新闻披露算力业务收入同比约150%，服务器及存储同比超200%，数据中心产品同比增长；公司以自研AI大容量交换芯片支撑智算超节点和万卡级智算中心，主板块从交换机扩展为智算网络设备。</t>
+          <t>证据强：2025年报披露AI智算中心网络方案已服务中国移动、阿里、字节、百度、腾讯等训练/推理大模型场景，数据中心交换机订单加速交付；IDC数据显示中国数据中心交换机市占率第三。</t>
         </is>
       </c>
       <c r="E299" s="6" t="inlineStr">
@@ -8968,22 +8968,22 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>以太网交换芯片</t>
+          <t>智算网络设备</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>688702</t>
+          <t>000063</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>盛科通信-U</t>
+          <t>中兴通讯</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司主营以太网交换芯片及配套产品，交换芯片收入8.31亿元、占营收72.26%，交换机收入占比较低；删减“智算交换机”重复行，保留最能体现价值量的以太网交换芯片，风险是亏损扩大和高端产品放量节奏。</t>
+          <t>证据强：2025年报及公司新闻披露算力业务收入同比约150%，服务器及存储同比超200%，数据中心产品同比增长；公司以自研AI大容量交换芯片支撑智算超节点和万卡级智算中心，主板块从交换机扩展为智算网络设备。</t>
         </is>
       </c>
       <c r="E300" s="6" t="inlineStr">
@@ -8995,22 +8995,22 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>以太网PHY-交换芯片</t>
+          <t>以太网交换芯片</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>688515</t>
+          <t>688702</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>裕太微</t>
+          <t>盛科通信-U</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露公司专注高速有线通信芯片，网通PHY、交换机芯片、网卡芯片已规模量产，网通类产品销量约1.4亿颗，并向数据中心与基站等高价值场景延伸；AI数据中心直接收入仍需跟踪。</t>
+          <t>证据中强：2025年报披露公司主营以太网交换芯片及配套产品，交换芯片收入8.31亿元、占营收72.26%，交换机收入占比较低；删减“智算交换机”重复行，保留最能体现价值量的以太网交换芯片，风险是亏损扩大和高端产品放量节奏。</t>
         </is>
       </c>
       <c r="E301" s="6" t="inlineStr">
@@ -9022,30 +9022,34 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>PCIe Switch</t>
+          <t>以太网PHY-交换芯片</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>暂无成熟A股纯标的</t>
+          <t>688515</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>暂无成熟A股纯标的</t>
+          <t>裕太微</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>GPU集群内PCIe Switch、NVSwitch和高端交换ASIC主要由NVIDIA、Broadcom、Microchip、Astera等海外厂商主导，A股不硬凑。</t>
-        </is>
-      </c>
-      <c r="E302" s="6" t="n"/>
+          <t>证据中：2025年报披露公司专注高速有线通信芯片，网通PHY、交换机芯片、网卡芯片已规模量产，网通类产品销量约1.4亿颗，并向数据中心与基站等高价值场景延伸；AI数据中心直接收入仍需跟踪。</t>
+        </is>
+      </c>
+      <c r="E302" s="6" t="inlineStr">
+        <is>
+          <t>已处理</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>BMC</t>
+          <t>PCIe Switch</t>
         </is>
       </c>
       <c r="B303" s="3" t="inlineStr">
@@ -9060,7 +9064,7 @@
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>AI服务器BMC/远程管理芯片以海外和台湾厂商为主，A股目前缺成熟纯标的，先列系统级空白。</t>
+          <t>GPU集群内PCIe Switch、NVSwitch和高端交换ASIC主要由NVIDIA、Broadcom、Microchip、Astera等海外厂商主导，A股不硬凑。</t>
         </is>
       </c>
       <c r="E303" s="6" t="n"/>
@@ -9068,49 +9072,45 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>Edge BMC管理芯片</t>
+          <t>BMC</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>688595</t>
+          <t>暂无成熟A股纯标的</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>芯海科技</t>
+          <t>暂无成熟A股纯标的</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报摘要披露面向边缘计算及服务器市场的轻量级edge BMC管理芯片已上市并量产销售，同时EC芯片在AI PC量产；保留BMC但改为Edge BMC管理芯片，风险是公司仍亏损且BMC收入规模未单列。</t>
-        </is>
-      </c>
-      <c r="E304" s="6" t="inlineStr">
-        <is>
-          <t>已处理</t>
-        </is>
-      </c>
+          <t>AI服务器BMC/远程管理芯片以海外和台湾厂商为主，A股目前缺成熟纯标的，先列系统级空白。</t>
+        </is>
+      </c>
+      <c r="E304" s="6" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>低抖动时钟源</t>
+          <t>Edge BMC管理芯片</t>
         </is>
       </c>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>603738</t>
+          <t>688595</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>泰晶科技</t>
+          <t>芯海科技</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报/半年报披露公司开发面向AI数据中心基础设施的312.5MHz差分输出温补振荡器和低抖动可编程振荡器，满足AI数据中心、3.2T光模块、AI算力等需求；主板块保留低抖动时钟源。</t>
+          <t>证据中：2025年报摘要披露面向边缘计算及服务器市场的轻量级edge BMC管理芯片已上市并量产销售，同时EC芯片在AI PC量产；保留BMC但改为Edge BMC管理芯片，风险是公司仍亏损且BMC收入规模未单列。</t>
         </is>
       </c>
       <c r="E305" s="6" t="inlineStr">
@@ -9122,22 +9122,22 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>高频晶振</t>
+          <t>低抖动时钟源</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>300460</t>
+          <t>603738</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>惠伦晶体</t>
+          <t>泰晶科技</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>证据弱：2025半年报披露公司主营石英晶体元器件，高频产品和服务器等领域方案商认证具备基础支撑价值；但2025年仍亏损且未见明确AI服务器低抖动订单，主板块由低抖动时钟源降级为高频晶振观察。</t>
+          <t>证据中强：2025年报/半年报披露公司开发面向AI数据中心基础设施的312.5MHz差分输出温补振荡器和低抖动可编程振荡器，满足AI数据中心、3.2T光模块、AI算力等需求；主板块保留低抖动时钟源。</t>
         </is>
       </c>
       <c r="E306" s="6" t="inlineStr">
@@ -9149,22 +9149,22 @@
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>IDC</t>
+          <t>高频晶振</t>
         </is>
       </c>
       <c r="B307" s="3" t="inlineStr">
         <is>
-          <t>600845</t>
+          <t>300460</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>宝信软件</t>
+          <t>惠伦晶体</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>工业软件和IDC双主业，宝之云IDC、华北基地、人工智能算力资源池等资产构成算力基础设施运营侧真实映射；DCIM不是公司最核心的AI受益解释。主板块由DCIM改为IDC，原IDC重复行合并删除。风险是钢铁行业软件需求承压、IDC资本开支和上架率、电力成本、AI算力资源池回报周期。证据A/B。</t>
+          <t>证据弱：2025半年报披露公司主营石英晶体元器件，高频产品和服务器等领域方案商认证具备基础支撑价值；但2025年仍亏损且未见明确AI服务器低抖动订单，主板块由低抖动时钟源降级为高频晶振观察。</t>
         </is>
       </c>
       <c r="E307" s="6" t="inlineStr">
@@ -9176,22 +9176,22 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>AIDC智算中心</t>
+          <t>IDC</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>300442</t>
+          <t>600845</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>润泽科技</t>
+          <t>宝信软件</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报显示AIDC收入25.1亿元、占总收入44.24%，新增交付算力规模220MW且含单体100MW智算中心；合并IDC/算力中心运维，主线改为AIDC智算中心。</t>
+          <t>工业软件和IDC双主业，宝之云IDC、华北基地、人工智能算力资源池等资产构成算力基础设施运营侧真实映射；DCIM不是公司最核心的AI受益解释。主板块由DCIM改为IDC，原IDC重复行合并删除。风险是钢铁行业软件需求承压、IDC资本开支和上架率、电力成本、AI算力资源池回报周期。证据A/B。</t>
         </is>
       </c>
       <c r="E308" s="6" t="inlineStr">
@@ -9203,22 +9203,22 @@
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>IDC及算力租赁</t>
+          <t>AIDC智算中心</t>
         </is>
       </c>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>300738</t>
+          <t>300442</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>奥飞数据</t>
+          <t>润泽科技</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露业务为IDC及互联网综合服务，报告期新项目投产并继续推进算力租赁和相关设备销售；AI链受益来自机柜上架和算力需求，保留IDC及算力租赁。</t>
+          <t>证据强：2025年报显示AIDC收入25.1亿元、占总收入44.24%，新增交付算力规模220MW且含单体100MW智算中心；合并IDC/算力中心运维，主线改为AIDC智算中心。</t>
         </is>
       </c>
       <c r="E309" s="6" t="inlineStr">
@@ -9230,22 +9230,22 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>IDC云计算基础设施</t>
+          <t>IDC及算力租赁</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>300383</t>
+          <t>300738</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>光环新网</t>
+          <t>奥飞数据</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露主营仍是IDC及云计算，AI爆发带动数据中心与云计算需求，并与格灵深瞳合作AI+行业智算云；直接算力运营收入未充分拆分，保留IDC云计算基础设施。</t>
+          <t>证据中：2025年报披露业务为IDC及互联网综合服务，报告期新项目投产并继续推进算力租赁和相关设备销售；AI链受益来自机柜上架和算力需求，保留IDC及算力租赁。</t>
         </is>
       </c>
       <c r="E310" s="6" t="inlineStr">
@@ -9257,22 +9257,22 @@
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>算力中心运维</t>
+          <t>IDC云计算基础设施</t>
         </is>
       </c>
       <c r="B311" s="3" t="inlineStr">
         <is>
-          <t>002929</t>
+          <t>300383</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>润建股份</t>
+          <t>光环新网</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露算力网络业务增长、算力中心管理运维和智算云服务推进，但AI及算力收入占比仍较小且归母净利下滑；保留算力中心运维并下调盈利确定性。</t>
+          <t>证据中：2025年报披露主营仍是IDC及云计算，AI爆发带动数据中心与云计算需求，并与格灵深瞳合作AI+行业智算云；直接算力运营收入未充分拆分，保留IDC云计算基础设施。</t>
         </is>
       </c>
       <c r="E311" s="6" t="inlineStr">
@@ -9284,22 +9284,22 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>算力设备交付运维</t>
+          <t>算力中心运维</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>301085</t>
+          <t>002929</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>亚康股份</t>
+          <t>润建股份</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报摘要披露向富士康、英业达、华勤、浪潮等算力服务器制造商提供交付及售后维保，并从传统数据中心向AI智算中心运维升级；公司亏损，主线为算力设备交付运维。</t>
+          <t>证据中：2025年报披露算力网络业务增长、算力中心管理运维和智算云服务推进，但AI及算力收入占比仍较小且归母净利下滑；保留算力中心运维并下调盈利确定性。</t>
         </is>
       </c>
       <c r="E312" s="6" t="inlineStr">
@@ -9311,22 +9311,22 @@
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>AI智能终端ODM</t>
+          <t>算力设备交付运维</t>
         </is>
       </c>
       <c r="B313" s="3" t="inlineStr">
         <is>
-          <t>603341</t>
+          <t>301085</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>龙旗科技</t>
+          <t>亚康股份</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露AI PC实现全平台产品设计与量产落地并获得全球头部客户订单，智能眼镜实现多场景、多品类规模化量产，AIoT业务覆盖智能手表/手环和智能眼镜；主板块从智能终端ODM细化为AI智能终端ODM。风险是手机/平板仍占大盘，新业务弹性需看AI PC、智能眼镜收入占比和毛利。</t>
+          <t>证据中：2025年报摘要披露向富士康、英业达、华勤、浪潮等算力服务器制造商提供交付及售后维保，并从传统数据中心向AI智算中心运维升级；公司亏损，主线为算力设备交付运维。</t>
         </is>
       </c>
       <c r="E313" s="6" t="inlineStr">
@@ -9338,27 +9338,27 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>端侧AI SoC</t>
+          <t>AI智能终端ODM</t>
         </is>
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>603893</t>
+          <t>603341</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>瑞芯微</t>
+          <t>龙旗科技</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>证据强：2026年一季报及2026年半年度业绩预告显示，公司采用“AIoT SoC算力平台+AI协处理器”双轨路线，RK3588、RK3576、RV11系列持续高速增长，RK182X已量产并预计下半年开始放量；以RK3588为例，芯片集成CPU、GPU、6TOPS自研NPU、ISP及8K音视频编解码能力，终端覆盖机器人、机器视觉/安防、工业控制、智能座舱、商显/办公、智能家居及教育娱乐等消费电子。2026H1预告营收28.70—29.10亿元、归母净利润8.50—9.10亿元、扣非净利润8.30—8.90亿元（均未经审计）。主板块归入端侧AI SoC；风险是存储及载板等原材料涨价/短缺、消费类终端承压，以及新品导入和放量不及预期。</t>
+          <t>证据中强：2025年报披露AI PC实现全平台产品设计与量产落地并获得全球头部客户订单，智能眼镜实现多场景、多品类规模化量产，AIoT业务覆盖智能手表/手环和智能眼镜；主板块从智能终端ODM细化为AI智能终端ODM。风险是手机/平板仍占大盘，新业务弹性需看AI PC、智能眼镜收入占比和毛利。</t>
         </is>
       </c>
       <c r="E314" s="6" t="inlineStr">
         <is>
-          <t>更新；2026-07-25</t>
+          <t>已处理</t>
         </is>
       </c>
     </row>
@@ -9370,22 +9370,22 @@
       </c>
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>300458</t>
+          <t>603893</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>全志科技</t>
+          <t>瑞芯微</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司实现CPU、GPU、NPU、DSP及RISC-V协处理器复杂异构芯片规模化量产，智能终端应用处理器是核心业务；删减AI眼镜应用处理器重复行，AI眼镜只是下游应用之一，主板块保留端侧AI SoC。</t>
+          <t>证据强：2026年一季报及2026年半年度业绩预告显示，公司采用“AIoT SoC算力平台+AI协处理器”双轨路线，RK3588、RK3576、RV11系列持续高速增长，RK182X已量产并预计下半年开始放量；以RK3588为例，芯片集成CPU、GPU、6TOPS自研NPU、ISP及8K音视频编解码能力，终端覆盖机器人、机器视觉/安防、工业控制、智能座舱、商显/办公、智能家居及教育娱乐等消费电子。2026H1预告营收28.70—29.10亿元、归母净利润8.50—9.10亿元、扣非净利润8.30—8.90亿元（均未经审计）。主板块归入端侧AI SoC；风险是存储及载板等原材料涨价/短缺、消费类终端承压，以及新品导入和放量不及预期。</t>
         </is>
       </c>
       <c r="E315" s="6" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>更新；2026-07-25</t>
         </is>
       </c>
     </row>
@@ -9397,17 +9397,17 @@
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>688099</t>
+          <t>300458</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>晶晨股份</t>
+          <t>全志科技</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露智能多媒体及显示SoC仍是核心收入来源，AIoT SoC收入16.40亿元、同比增长8.50%，AIoT SoC集成NPU、DSP、视觉处理单元、ISP及编解码器并获Google EDLA认证；主板块从端侧AIoT SoC收敛为端侧AI SoC，跟踪端侧大模型适配、头部客户新品和经营现金流修复。</t>
+          <t>证据中强：2025年报披露公司实现CPU、GPU、NPU、DSP及RISC-V协处理器复杂异构芯片规模化量产，智能终端应用处理器是核心业务；删减AI眼镜应用处理器重复行，AI眼镜只是下游应用之一，主板块保留端侧AI SoC。</t>
         </is>
       </c>
       <c r="E316" s="6" t="inlineStr">
@@ -9424,71 +9424,71 @@
       </c>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>301536</t>
+          <t>688099</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>星宸科技</t>
+          <t>晶晨股份</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>证据强（截至2026-07-25）：公司以视觉AI SoC为核心，核心芯片集成ISP、NPU、编解码、音频/显示等IP；主要产品/目标终端包括IPC/NVR（SSR670G）、家用服务及户外等机器人、智能家居/办公/工业、智能穿戴和车载记录仪/DMS/OMS/CMS/L0-L2辅助驾驶，另布局SPAD 3D感知与蓝牙。已形成收入：2025年智能安防19.35亿元/65.10%、智能物联6.58亿元/22.14%、智能车载3.18亿元/10.69%；2026H1预告收入26.2—27.2亿元、归母8.2—9.0亿元、扣非7.0—7.8亿元（未经审计；7月22日公告称无需修正），SSR670系列公司称已大规模商用。商业化边界：AI眼镜SSC309QL仅小规模量产，另有5—6家客户开发中，订单/独立收入N/A；机器人2025年出货超1,000万颗但独立收入N/A，具身“小脑/大脑”仍在研；SS901公司IR称已在国内一线自主品牌主力车型量产上车，其他车载/3D项目的导入或规划不等于订单/收入。PE(TTM，用户口径)=24.4—28.4x：总市值555.82亿元（东方财富，2026-07-24收盘）÷[(2026H1扣非预告7.0—7.8亿元−2026Q1扣非2.0998亿元)×4]，非标准近四季PE。证据状态：财务/分部=confirmed_official；产品/客户进展=company_claim；估值=market_data_vendor；annualized_core_gap_status=insufficient、formal_surprise_status=N/A（缺公告前FY归母点时共识）。风险：半年度预告待8月27日正式半年报验证，毛利率、现金流、存货、价量与新品放量持续性待核。</t>
+          <t>证据中强：2025年报披露智能多媒体及显示SoC仍是核心收入来源，AIoT SoC收入16.40亿元、同比增长8.50%，AIoT SoC集成NPU、DSP、视觉处理单元、ISP及编解码器并获Google EDLA认证；主板块从端侧AIoT SoC收敛为端侧AI SoC，跟踪端侧大模型适配、头部客户新品和经营现金流修复。</t>
         </is>
       </c>
       <c r="E317" s="6" t="inlineStr">
         <is>
-          <t>更新；2026-07-25</t>
+          <t>已处理</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>AI眼镜主控SoC</t>
+          <t>端侧AI SoC</t>
         </is>
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>688608</t>
+          <t>301536</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>恒玄科技</t>
+          <t>星宸科技</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司主营低功耗无线计算SoC，芯片集成CPU、嵌入式NPU、ISP、DSP、蓝牙/Wi-Fi等模块；BES6100面向智能眼镜等低功耗终端，6nm工艺，集成多核Cortex-A、NPU、GPU，可运行Linux/Android并支持端侧AI推理。风险是AI眼镜SoC仍处放量早期，需跟踪客户导入和量产节奏。</t>
+          <t>证据强（截至2026-07-25）：公司以视觉AI SoC为核心，核心芯片集成ISP、NPU、编解码、音频/显示等IP；主要产品/目标终端包括IPC/NVR（SSR670G）、家用服务及户外等机器人、智能家居/办公/工业、智能穿戴和车载记录仪/DMS/OMS/CMS/L0-L2辅助驾驶，另布局SPAD 3D感知与蓝牙。已形成收入：2025年智能安防19.35亿元/65.10%、智能物联6.58亿元/22.14%、智能车载3.18亿元/10.69%；2026H1预告收入26.2—27.2亿元、归母8.2—9.0亿元、扣非7.0—7.8亿元（未经审计；7月22日公告称无需修正），SSR670系列公司称已大规模商用。商业化边界：AI眼镜SSC309QL仅小规模量产，另有5—6家客户开发中，订单/独立收入N/A；机器人2025年出货超1,000万颗但独立收入N/A，具身“小脑/大脑”仍在研；SS901公司IR称已在国内一线自主品牌主力车型量产上车，其他车载/3D项目的导入或规划不等于订单/收入。PE(TTM，用户口径)=24.4—28.4x：总市值555.82亿元（东方财富，2026-07-24收盘）÷[(2026H1扣非预告7.0—7.8亿元−2026Q1扣非2.0998亿元)×4]，非标准近四季PE。证据状态：财务/分部=confirmed_official；产品/客户进展=company_claim；估值=market_data_vendor；annualized_core_gap_status=insufficient、formal_surprise_status=N/A（缺公告前FY归母点时共识）。风险：半年度预告待8月27日正式半年报验证，毛利率、现金流、存货、价量与新品放量持续性待核。</t>
         </is>
       </c>
       <c r="E318" s="6" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>更新；2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>智能穿戴SoC</t>
+          <t>AI眼镜主控SoC</t>
         </is>
       </c>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>688049</t>
+          <t>688608</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>炬芯科技</t>
+          <t>恒玄科技</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报摘要披露公司构建低功耗大算力芯片硬件架构、端侧AI开发工具和存内计算CIM，CPU+DSP+NPU架构提升端侧AI能效；智能穿戴SoC覆盖手表/手环、AI眼镜等，主板块保留智能穿戴SoC，AI眼镜属于穿戴场景扩展而非单独主线。</t>
+          <t>证据强：2025年报披露公司主营低功耗无线计算SoC，芯片集成CPU、嵌入式NPU、ISP、DSP、蓝牙/Wi-Fi等模块；BES6100面向智能眼镜等低功耗终端，6nm工艺，集成多核Cortex-A、NPU、GPU，可运行Linux/Android并支持端侧AI推理。风险是AI眼镜SoC仍处放量早期，需跟踪客户导入和量产节奏。</t>
         </is>
       </c>
       <c r="E319" s="6" t="inlineStr">
@@ -9500,22 +9500,22 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>端侧音视频SoC</t>
+          <t>智能穿戴SoC</t>
         </is>
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>688332</t>
+          <t>688049</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>中科蓝讯</t>
+          <t>炬芯科技</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>证据中：公司专注低功耗无线音频SoC，2025年报披露形成蓝牙耳机、智能穿戴、AIoT、AI语音识别、Wi-Fi、视频芯片等产品线，并向AI玩具、AI眼镜、AI音箱扩展；主板块保留端侧音视频SoC。风险是2025净利高增主要受投资公允价值影响，扣非和主业毛利需单独跟踪。</t>
+          <t>证据中强：2025年报摘要披露公司构建低功耗大算力芯片硬件架构、端侧AI开发工具和存内计算CIM，CPU+DSP+NPU架构提升端侧AI能效；智能穿戴SoC覆盖手表/手环、AI眼镜等，主板块保留智能穿戴SoC，AI眼镜属于穿戴场景扩展而非单独主线。</t>
         </is>
       </c>
       <c r="E320" s="6" t="inlineStr">
@@ -9527,22 +9527,22 @@
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>端侧AI MCU</t>
+          <t>端侧音视频SoC</t>
         </is>
       </c>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>688018</t>
+          <t>688332</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>乐鑫科技</t>
+          <t>中科蓝讯</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司以AIoT为核心，芯片、模组和开发套件保持增长；官方ESP32-P4为双核RISC-V高性能MCU，具备AI指令扩展、先进内存子系统和高速外设，面向HMI、边缘计算、视觉AI等嵌入式场景。风险是AI算力较SoC/NPU平台更轻量，需跟踪高端新品放量和客户结构。</t>
+          <t>证据中：公司专注低功耗无线音频SoC，2025年报披露形成蓝牙耳机、智能穿戴、AIoT、AI语音识别、Wi-Fi、视频芯片等产品线，并向AI玩具、AI眼镜、AI音箱扩展；主板块保留端侧音视频SoC。风险是2025净利高增主要受投资公允价值影响，扣非和主业毛利需单独跟踪。</t>
         </is>
       </c>
       <c r="E321" s="6" t="inlineStr">
@@ -9554,22 +9554,22 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>端侧AI蜂窝模组</t>
+          <t>端侧AI MCU</t>
         </is>
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>603236</t>
+          <t>688018</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>移远通信</t>
+          <t>乐鑫科技</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露物联网需求回暖，边缘计算、混合现实、大模型与物联网融合加速；公司推出支持主流AI大模型端侧部署的5G智能座舱模组，并依托智能模组、AI大模型、主控板、算力卡和自研算法打造多层级端侧AI方案。主板块保留端侧AI蜂窝模组，跟踪AI模组收入占比和毛利提升。</t>
+          <t>证据中强：2025年报披露公司以AIoT为核心，芯片、模组和开发套件保持增长；官方ESP32-P4为双核RISC-V高性能MCU，具备AI指令扩展、先进内存子系统和高速外设，面向HMI、边缘计算、视觉AI等嵌入式场景。风险是AI算力较SoC/NPU平台更轻量，需跟踪高端新品放量和客户结构。</t>
         </is>
       </c>
       <c r="E322" s="6" t="inlineStr">
@@ -9581,22 +9581,22 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>高算力智能模组</t>
+          <t>端侧AI蜂窝模组</t>
         </is>
       </c>
       <c r="B323" s="3" t="inlineStr">
         <is>
-          <t>002881</t>
+          <t>603236</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>美格智能</t>
+          <t>移远通信</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露无线通信模组正向智能模组、高算力模组升级，公司的智能模组和高算力模组是物联网终端侧、边缘侧计算能力承载平台，并推动端侧AI在物联网领域落地；主板块从端侧AI蜂窝模组细化为高算力智能模组，跟踪海外收入、车载/AR/VR等大颗粒市场和毛利修复。</t>
+          <t>证据强：2025年报披露物联网需求回暖，边缘计算、混合现实、大模型与物联网融合加速；公司推出支持主流AI大模型端侧部署的5G智能座舱模组，并依托智能模组、AI大模型、主控板、算力卡和自研算法打造多层级端侧AI方案。主板块保留端侧AI蜂窝模组，跟踪AI模组收入占比和毛利提升。</t>
         </is>
       </c>
       <c r="E323" s="6" t="inlineStr">
@@ -9608,22 +9608,22 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>端侧AI模组</t>
+          <t>高算力智能模组</t>
         </is>
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>300638</t>
+          <t>002881</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>广和通</t>
+          <t>美格智能</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司发布Fibocom AI Stack端侧AI解决方案及覆盖1T-50T算力的“星云”AI模组矩阵，支持不同参数端侧大模型部署，应用于AI玩具、机器人等终端；主板块保留端侧AI模组，跟踪星云系列出货、AI解决方案收入占比和客户落地。</t>
+          <t>证据中强：2025年报披露无线通信模组正向智能模组、高算力模组升级，公司的智能模组和高算力模组是物联网终端侧、边缘侧计算能力承载平台，并推动端侧AI在物联网领域落地；主板块从端侧AI蜂窝模组细化为高算力智能模组，跟踪海外收入、车载/AR/VR等大颗粒市场和毛利修复。</t>
         </is>
       </c>
       <c r="E324" s="6" t="inlineStr">
@@ -9635,22 +9635,22 @@
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>AIOS端侧智能</t>
+          <t>端侧AI模组</t>
         </is>
       </c>
       <c r="B325" s="3" t="inlineStr">
         <is>
-          <t>300496</t>
+          <t>300638</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>中科创达</t>
+          <t>广和通</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司以AIOS为核心战略，覆盖端云协同、AI智能体和行业AI，并在智能汽车、AI眼镜、机器人等端侧场景落地；主板块由端侧智能OS升级为AIOS端侧智能。</t>
+          <t>证据强：2025年报披露公司发布Fibocom AI Stack端侧AI解决方案及覆盖1T-50T算力的“星云”AI模组矩阵，支持不同参数端侧大模型部署，应用于AI玩具、机器人等终端；主板块保留端侧AI模组，跟踪星云系列出货、AI解决方案收入占比和客户落地。</t>
         </is>
       </c>
       <c r="E325" s="6" t="inlineStr">
@@ -9662,22 +9662,22 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>AR光波导</t>
+          <t>AIOS端侧智能</t>
         </is>
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>002273</t>
+          <t>300496</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>水晶光电</t>
+          <t>中科创达</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>精密镀膜、微纳光学和光电封测能力较强，AR/VR领域反射光波导及核心光学元件为公司重点工程，AI眼镜是更直接的未来映射；主板块改为AR光波导，微透镜并入备注，CPO硅透镜研发仅作远期观察，风险是AR大客户量产节奏、消费电子大客户依赖和光通信收入兑现。证据B。</t>
+          <t>证据强：2025年报披露公司以AIOS为核心战略，覆盖端云协同、AI智能体和行业AI，并在智能汽车、AI眼镜、机器人等端侧场景落地；主板块由端侧智能OS升级为AIOS端侧智能。</t>
         </is>
       </c>
       <c r="E326" s="6" t="inlineStr">
@@ -9689,22 +9689,22 @@
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>AI眼镜光学模组</t>
+          <t>AR光波导</t>
         </is>
       </c>
       <c r="B327" s="3" t="inlineStr">
         <is>
-          <t>300433</t>
+          <t>002273</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>蓝思科技</t>
+          <t>水晶光电</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司是AI硬件全产业链一站式精密制造解决方案提供商，AI眼镜领域具备材料、光学、结构件到整机组装全栈能力，已实现国内头部客户整机组装和海外头部客户精密零组件规模化交付，并在光波导镜片高精度自动化组装等领域突破；主板块从AI眼镜光波导扩展为AI眼镜光学模组。</t>
+          <t>精密镀膜、微纳光学和光电封测能力较强，AR/VR领域反射光波导及核心光学元件为公司重点工程，AI眼镜是更直接的未来映射；主板块改为AR光波导，微透镜并入备注，CPO硅透镜研发仅作远期观察，风险是AR大客户量产节奏、消费电子大客户依赖和光通信收入兑现。证据B。</t>
         </is>
       </c>
       <c r="E327" s="6" t="inlineStr">
@@ -9716,22 +9716,22 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>AR投影光机</t>
+          <t>AI眼镜光学模组</t>
         </is>
       </c>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>688010</t>
+          <t>300433</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>福光股份</t>
+          <t>蓝思科技</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露公司主营特种及民用光学镜头、光电系统和光学元组件，研发项目中M003 MicroLED AR显示模组处于产业化推广，应用于AR领域；投影光机可用于AR/可穿戴设备。主板块保留AR投影光机，但AI眼镜收入纯度和客户放量仍需继续验证，扣非盈利仍承压。</t>
+          <t>证据强：2025年报披露公司是AI硬件全产业链一站式精密制造解决方案提供商，AI眼镜领域具备材料、光学、结构件到整机组装全栈能力，已实现国内头部客户整机组装和海外头部客户精密零组件规模化交付，并在光波导镜片高精度自动化组装等领域突破；主板块从AI眼镜光波导扩展为AI眼镜光学模组。</t>
         </is>
       </c>
       <c r="E328" s="6" t="inlineStr">
@@ -9743,22 +9743,22 @@
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>硅基OLED微显示</t>
+          <t>AR投影光机</t>
         </is>
       </c>
       <c r="B329" s="3" t="inlineStr">
         <is>
-          <t>688496</t>
+          <t>688010</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>清越科技</t>
+          <t>福光股份</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露公司形成PMOLED、电子纸模组与硅基OLED微显示器三大业务，硅基OLED用于AR智能眼镜、VR头显等近眼显示；Micro-OLED高亮高效结构器件等项目继续推进。主板块保留硅基OLED微显示，但公司2025亏损扩大，需跟踪硅基OLED量产客户和盈利拐点。</t>
+          <t>证据中：2025年报披露公司主营特种及民用光学镜头、光电系统和光学元组件，研发项目中M003 MicroLED AR显示模组处于产业化推广，应用于AR领域；投影光机可用于AR/可穿戴设备。主板块保留AR投影光机，但AI眼镜收入纯度和客户放量仍需继续验证，扣非盈利仍承压。</t>
         </is>
       </c>
       <c r="E329" s="6" t="inlineStr">
@@ -9770,22 +9770,22 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>AI眼镜MicroLED光机</t>
+          <t>硅基OLED微显示</t>
         </is>
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>300296</t>
+          <t>688496</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>利亚德</t>
+          <t>清越科技</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年度总经理工作报告披露公司已推出基于MicroLED光机的AR眼镜，并发布AI玩具等大众消费AI创新产品；MicroLED仍是新战略周期重点增长方向。主板块保留AI眼镜MicroLED光机，风险是公司收入主体仍为LED显示和文旅，AI眼镜商业化仍早期。</t>
+          <t>证据中：2025年报披露公司形成PMOLED、电子纸模组与硅基OLED微显示器三大业务，硅基OLED用于AR智能眼镜、VR头显等近眼显示；Micro-OLED高亮高效结构器件等项目继续推进。主板块保留硅基OLED微显示，但公司2025亏损扩大，需跟踪硅基OLED量产客户和盈利拐点。</t>
         </is>
       </c>
       <c r="E330" s="6" t="inlineStr">
@@ -9797,22 +9797,22 @@
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>AI眼镜MicroLED微显示</t>
+          <t>AI眼镜MicroLED光机</t>
         </is>
       </c>
       <c r="B331" s="3" t="inlineStr">
         <is>
-          <t>300323</t>
+          <t>300296</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>京东方华灿</t>
+          <t>利亚德</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025投资者关系记录披露MicroLED技术可用于具备显示功能的AI眼镜，公司配合不同客户需求提供解决方案并提升性能与良率；2025年报披露MicroLED技术研发及产业化项目推进高亮度、高对比度、高色彩饱和度芯片。主板块保留AI眼镜MicroLED微显示，风险是公司仍亏损，产业化和客户放量需跟踪。</t>
+          <t>证据中强：2025年度总经理工作报告披露公司已推出基于MicroLED光机的AR眼镜，并发布AI玩具等大众消费AI创新产品；MicroLED仍是新战略周期重点增长方向。主板块保留AI眼镜MicroLED光机，风险是公司收入主体仍为LED显示和文旅，AI眼镜商业化仍早期。</t>
         </is>
       </c>
       <c r="E331" s="6" t="inlineStr">
@@ -9824,22 +9824,22 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>MicroLED芯片</t>
+          <t>AI眼镜MicroLED微显示</t>
         </is>
       </c>
       <c r="B332" s="3" t="inlineStr">
         <is>
-          <t>600703</t>
+          <t>300323</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>三安光电</t>
+          <t>京东方华灿</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露Mini/Micro LED高端产品占比提升，Micro LED芯片在中大型显示增长，并切入AR眼镜、AI数据中心光互连等应用；删减“化合物半导体”重复行，SiC/GaN等平台能力在备注降级说明。</t>
+          <t>证据中：2025投资者关系记录披露MicroLED技术可用于具备显示功能的AI眼镜，公司配合不同客户需求提供解决方案并提升性能与良率；2025年报披露MicroLED技术研发及产业化项目推进高亮度、高对比度、高色彩饱和度芯片。主板块保留AI眼镜MicroLED微显示，风险是公司仍亏损，产业化和客户放量需跟踪。</t>
         </is>
       </c>
       <c r="E332" s="6" t="inlineStr">
@@ -9851,22 +9851,22 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>OLED-MicroLED显示</t>
+          <t>MicroLED芯片</t>
         </is>
       </c>
       <c r="B333" s="3" t="inlineStr">
         <is>
-          <t>002387</t>
+          <t>600703</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>维信诺</t>
+          <t>三安光电</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露维信诺围绕AI新场景推进智能终端、智能影像、智慧家居等显示供货，并持续推进ViP、Micro-LED等显示技术；真实受益节点是AI终端显示，MicroLED更多体现技术储备和参股生态。</t>
+          <t>证据中强：2025年报披露Mini/Micro LED高端产品占比提升，Micro LED芯片在中大型显示增长，并切入AR眼镜、AI数据中心光互连等应用；删减“化合物半导体”重复行，SiC/GaN等平台能力在备注降级说明。</t>
         </is>
       </c>
       <c r="E333" s="6" t="inlineStr">
@@ -9878,22 +9878,22 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>AI眼镜CIS</t>
+          <t>OLED-MicroLED显示</t>
         </is>
       </c>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>688213</t>
+          <t>002387</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>思特威</t>
+          <t>维信诺</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司推出1200万像素AI眼镜应用CMOS图像传感器SC1200IOT，官网还披露SC1200IOT/SC1220IOT具备小封装、低功耗、高感度、Always-On等特性，适用于AI眼镜及AR/VR微型摄像头模组；主板块保留AI眼镜CIS，跟踪量产客户和高像素新品。</t>
+          <t>证据中：2025年报披露维信诺围绕AI新场景推进智能终端、智能影像、智慧家居等显示供货，并持续推进ViP、Micro-LED等显示技术；真实受益节点是AI终端显示，MicroLED更多体现技术储备和参股生态。</t>
         </is>
       </c>
       <c r="E334" s="6" t="inlineStr">
@@ -9910,17 +9910,17 @@
       </c>
       <c r="B335" s="3" t="inlineStr">
         <is>
-          <t>688728</t>
+          <t>688213</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>格科微</t>
+          <t>思特威</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司主营CIS与DDIC，高像素CIS放量；公告口径显示公司持续关注AI眼镜等新兴市场，500万和800万像素CIS已在AI眼镜项目量产。主板块保留AI眼镜CIS，但整体利润承压，需跟踪AI眼镜CIS是否能改善产品结构和毛利。</t>
+          <t>证据强：2025年报披露公司推出1200万像素AI眼镜应用CMOS图像传感器SC1200IOT，官网还披露SC1200IOT/SC1220IOT具备小封装、低功耗、高感度、Always-On等特性，适用于AI眼镜及AR/VR微型摄像头模组；主板块保留AI眼镜CIS，跟踪量产客户和高像素新品。</t>
         </is>
       </c>
       <c r="E335" s="6" t="inlineStr">
@@ -9932,22 +9932,22 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>AI眼镜视觉算法</t>
+          <t>AI眼镜CIS</t>
         </is>
       </c>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>688088</t>
+          <t>688728</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>虹软科技</t>
+          <t>格科微</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报/业绩快报披露AI眼镜影像与视觉算法持续升级，围绕复杂光照、动态场景、低照度和视频防抖推进平台适配；公开资料显示方案已在雷鸟、Rokid、夸克等AI眼镜落地。删减“端侧视觉AI底座”重复行，保留最直接的AI眼镜视觉算法。</t>
+          <t>证据中强：2025年报披露公司主营CIS与DDIC，高像素CIS放量；公告口径显示公司持续关注AI眼镜等新兴市场，500万和800万像素CIS已在AI眼镜项目量产。主板块保留AI眼镜CIS，但整体利润承压，需跟踪AI眼镜CIS是否能改善产品结构和毛利。</t>
         </is>
       </c>
       <c r="E336" s="6" t="inlineStr">
@@ -9959,22 +9959,22 @@
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>AI眼镜模拟芯片</t>
+          <t>AI眼镜视觉算法</t>
         </is>
       </c>
       <c r="B337" s="3" t="inlineStr">
         <is>
-          <t>688798</t>
+          <t>688088</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>艾为电子</t>
+          <t>虹软科技</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司高性能数模混合芯片覆盖音频功放、触觉反馈、马达驱动、压力/电容感应、灯效驱动等，SensorHub项目明确列示AI眼镜等IoT设备；另有AI眼镜客户导入音频功放、灯效驱动等公开信息。主板块保留AI眼镜模拟芯片，跟踪品牌客户放量和产品单机价值量。</t>
+          <t>证据强：2025年报/业绩快报披露AI眼镜影像与视觉算法持续升级，围绕复杂光照、动态场景、低照度和视频防抖推进平台适配；公开资料显示方案已在雷鸟、Rokid、夸克等AI眼镜落地。删减“端侧视觉AI底座”重复行，保留最直接的AI眼镜视觉算法。</t>
         </is>
       </c>
       <c r="E337" s="6" t="inlineStr">
@@ -9986,22 +9986,22 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>AI眼镜声学传感器</t>
+          <t>AI眼镜模拟芯片</t>
         </is>
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>688286</t>
+          <t>688798</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>敏芯股份</t>
+          <t>艾为电子</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>证据中：公司提质增效报告披露布局高信噪比、低功耗数字麦克风，部分型号已小批量出货，并布局应用于AI眼镜的骨传导声学传感器；删减“高信噪比数字麦克风”重复行，合并为AI眼镜声学传感器。风险是AI眼镜相关产品仍处研发/小批量阶段，收入贡献未充分披露。</t>
+          <t>证据中强：2025年报披露公司高性能数模混合芯片覆盖音频功放、触觉反馈、马达驱动、压力/电容感应、灯效驱动等，SensorHub项目明确列示AI眼镜等IoT设备；另有AI眼镜客户导入音频功放、灯效驱动等公开信息。主板块保留AI眼镜模拟芯片，跟踪品牌客户放量和产品单机价值量。</t>
         </is>
       </c>
       <c r="E338" s="6" t="inlineStr">
@@ -10013,22 +10013,22 @@
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>消费锂电池</t>
+          <t>AI眼镜声学传感器</t>
         </is>
       </c>
       <c r="B339" s="3" t="inlineStr">
         <is>
-          <t>688772</t>
+          <t>688286</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>珠海冠宇</t>
+          <t>敏芯股份</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露公司主营消费类锂离子电池，AI功能消费电子推出有望带来换机潮，消费类半固态电池已规模化量产；募集说明书提及智能手表、智能眼镜等可穿戴需求扩张。主板块保留消费锂电池，AI受益偏终端电池供能配套，直接度低于AI眼镜专用电池公司。</t>
+          <t>证据中：公司提质增效报告披露布局高信噪比、低功耗数字麦克风，部分型号已小批量出货，并布局应用于AI眼镜的骨传导声学传感器；删减“高信噪比数字麦克风”重复行，合并为AI眼镜声学传感器。风险是AI眼镜相关产品仍处研发/小批量阶段，收入贡献未充分披露。</t>
         </is>
       </c>
       <c r="E339" s="6" t="inlineStr">
@@ -10040,22 +10040,22 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>AI智能眼镜电池</t>
+          <t>消费锂电池</t>
         </is>
       </c>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>001283</t>
+          <t>688772</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>豪鹏科技</t>
+          <t>珠海冠宇</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报/公开资料披露公司布局AI智能眼镜电池，固态电池样品在AI终端、可穿戴设备等场景完成初步验证；删减“AI终端固态电池”重复行，当前主线仍是AI智能眼镜电池，固态电池属于下一代技术储备而非已验证主收入板块。</t>
+          <t>证据中：2025年报披露公司主营消费类锂离子电池，AI功能消费电子推出有望带来换机潮，消费类半固态电池已规模化量产；募集说明书提及智能手表、智能眼镜等可穿戴需求扩张。主板块保留消费锂电池，AI受益偏终端电池供能配套，直接度低于AI眼镜专用电池公司。</t>
         </is>
       </c>
       <c r="E340" s="6" t="inlineStr">
@@ -10067,22 +10067,22 @@
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>AI眼镜结构件</t>
+          <t>AI智能眼镜电池</t>
         </is>
       </c>
       <c r="B341" s="3" t="inlineStr">
         <is>
-          <t>300115</t>
+          <t>001283</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>长盈精密</t>
+          <t>豪鹏科技</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报摘要披露公司抓住AI硬件迭代机遇，持续开发AI笔记本和可穿戴产品关键零部件，轻量化金属及非金属结构件取得突破；AI眼镜结构件面向头部客户是主要弹性来源。主板块保留AI眼镜结构件，风险是消费电子结构件仍具客户集中和价格压力。</t>
+          <t>证据中强：2025年报/公开资料披露公司布局AI智能眼镜电池，固态电池样品在AI终端、可穿戴设备等场景完成初步验证；删减“AI终端固态电池”重复行，当前主线仍是AI智能眼镜电池，固态电池属于下一代技术储备而非已验证主收入板块。</t>
         </is>
       </c>
       <c r="E341" s="6" t="inlineStr">
@@ -10094,22 +10094,22 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>AI智能眼镜整机</t>
+          <t>AI眼镜结构件</t>
         </is>
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>002241</t>
+          <t>300115</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>歌尔股份</t>
+          <t>长盈精密</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司研发围绕MEMS声学传感器、微系统模组、AI智能眼镜/AR光学器件、MR头显等，AI智能眼镜等新兴业务表现亮眼；作为精密零组件+整机制造平台，主板块保留AI智能眼镜整机，光学、声学、SiP模组作为支撑能力写入备注即可。风险是营收仍受传统消费电子/XR周期影响。</t>
+          <t>证据中强：2025年报摘要披露公司抓住AI硬件迭代机遇，持续开发AI笔记本和可穿戴产品关键零部件，轻量化金属及非金属结构件取得突破；AI眼镜结构件面向头部客户是主要弹性来源。主板块保留AI眼镜结构件，风险是消费电子结构件仍具客户集中和价格压力。</t>
         </is>
       </c>
       <c r="E342" s="6" t="inlineStr">
@@ -10121,22 +10121,22 @@
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>AI终端精密功能件</t>
+          <t>AI智能眼镜整机</t>
         </is>
       </c>
       <c r="B343" s="3" t="inlineStr">
         <is>
-          <t>002600</t>
+          <t>002241</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>领益智造</t>
+          <t>歌尔股份</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报摘要披露公司核心产品覆盖AI手机、AIPC、AI眼镜及XR可穿戴、AI服务器、机器人等硬件，以2024年收入计在全球AI终端高精密功能件行业排名第一；半年报披露AR眼镜项目含MicroOLED显示、Insert Molding金属件增强等。主板块从精密结构件扩展为AI终端精密功能件。</t>
+          <t>证据中强：2025年报披露公司研发围绕MEMS声学传感器、微系统模组、AI智能眼镜/AR光学器件、MR头显等，AI智能眼镜等新兴业务表现亮眼；作为精密零组件+整机制造平台，主板块保留AI智能眼镜整机，光学、声学、SiP模组作为支撑能力写入备注即可。风险是营收仍受传统消费电子/XR周期影响。</t>
         </is>
       </c>
       <c r="E343" s="6" t="inlineStr">
@@ -10148,22 +10148,22 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>机器人3D视觉</t>
+          <t>AI终端精密功能件</t>
         </is>
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>688322</t>
+          <t>002600</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>奥比中光</t>
+          <t>领益智造</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司专注3D视觉感知，在人工智能与机器人时代打造“机器人之眼”和机器人与AI视觉产业中台；产品和生态围绕机器人、AI视觉、3D相机矩阵推进。删减泛化的“3D视觉传感器”重复表述，主板块保留机器人3D视觉。风险是机器人需求仍处导入期，短期收入仍含AIoT/生物识别等多场景。</t>
+          <t>证据强：2025年报摘要披露公司核心产品覆盖AI手机、AIPC、AI眼镜及XR可穿戴、AI服务器、机器人等硬件，以2024年收入计在全球AI终端高精密功能件行业排名第一；半年报披露AR眼镜项目含MicroOLED显示、Insert Molding金属件增强等。主板块从精密结构件扩展为AI终端精密功能件。</t>
         </is>
       </c>
       <c r="E344" s="6" t="inlineStr">
@@ -10175,22 +10175,22 @@
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>机器人力传感器</t>
+          <t>机器人3D视觉</t>
         </is>
       </c>
       <c r="B345" s="3" t="inlineStr">
         <is>
-          <t>603662</t>
+          <t>688322</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>柯力传感</t>
+          <t>奥比中光</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司围绕人形、协作和工业机器人加快六维力/力矩、一维至三维力、触觉、IMU等产品研发认证及批量交付；半年报披露以六维力/力矩为核心融合触觉、IMU的机器人传感方案。删减“触觉传感器-IMU”重复行，保留最能解释AI机器人弹性的机器人力传感器。</t>
+          <t>证据强：2025年报披露公司专注3D视觉感知，在人工智能与机器人时代打造“机器人之眼”和机器人与AI视觉产业中台；产品和生态围绕机器人、AI视觉、3D相机矩阵推进。删减泛化的“3D视觉传感器”重复表述，主板块保留机器人3D视觉。风险是机器人需求仍处导入期，短期收入仍含AIoT/生物识别等多场景。</t>
         </is>
       </c>
       <c r="E345" s="6" t="inlineStr">
@@ -10207,17 +10207,17 @@
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>301413</t>
+          <t>603662</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>安培龙</t>
+          <t>柯力传感</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报/投资者关系披露公司机器人力传感器包括单向力、力矩及六维力传感器，基于MEMS硅基应变片和玻璃微熔工艺的单向力及力矩传感器已开发完成并向多家机器人客户送样。主板块保留机器人力传感器，但公告提示相关收入占比仍低，六维力部分仍需验证批量订单。</t>
+          <t>证据强：2025年报披露公司围绕人形、协作和工业机器人加快六维力/力矩、一维至三维力、触觉、IMU等产品研发认证及批量交付；半年报披露以六维力/力矩为核心融合触觉、IMU的机器人传感方案。删减“触觉传感器-IMU”重复行，保留最能解释AI机器人弹性的机器人力传感器。</t>
         </is>
       </c>
       <c r="E346" s="6" t="inlineStr">
@@ -10234,17 +10234,17 @@
       </c>
       <c r="B347" s="3" t="inlineStr">
         <is>
-          <t>300354</t>
+          <t>301413</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>东华测试</t>
+          <t>安培龙</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025投资者关系记录披露六维力传感器处于小批量试制阶段，下游包括工业机器人、人形机器人、航空航天、汽车、电子、医疗等；公司主业仍以结构力学性能测试、PHM、电化学工作站等为基础，机器人收入贡献尚未充分披露，跟踪送样转批量和标定/测试体系能力。</t>
+          <t>证据中：2025年报/投资者关系披露公司机器人力传感器包括单向力、力矩及六维力传感器，基于MEMS硅基应变片和玻璃微熔工艺的单向力及力矩传感器已开发完成并向多家机器人客户送样。主板块保留机器人力传感器，但公告提示相关收入占比仍低，六维力部分仍需验证批量订单。</t>
         </is>
       </c>
       <c r="E347" s="6" t="inlineStr">
@@ -10256,22 +10256,22 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>机器人电子皮肤</t>
+          <t>机器人力传感器</t>
         </is>
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>300007</t>
+          <t>300354</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>汉威科技</t>
+          <t>东华测试</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露柔性传感电子皮肤入选2025具身智能十大创新产品和技术，机器人相关电子皮肤和触觉传感器已小批量供货；公司官网披露具备年产1000万支柔性传感器产线和柔性压阻/压电/电容/汗液四大技术。主板块从电子皮肤规范为机器人电子皮肤，风险是整体业务仍以气体/仪表等传感平台为主。</t>
+          <t>证据中：2025投资者关系记录披露六维力传感器处于小批量试制阶段，下游包括工业机器人、人形机器人、航空航天、汽车、电子、医疗等；公司主业仍以结构力学性能测试、PHM、电化学工作站等为基础，机器人收入贡献尚未充分披露，跟踪送样转批量和标定/测试体系能力。</t>
         </is>
       </c>
       <c r="E348" s="6" t="inlineStr">
@@ -10283,22 +10283,22 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>机器人谐波减速器</t>
+          <t>机器人电子皮肤</t>
         </is>
       </c>
       <c r="B349" s="3" t="inlineStr">
         <is>
-          <t>688017</t>
+          <t>300007</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>绿的谐波</t>
+          <t>汉威科技</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司巩固具身智能场景谐波减速器领先地位，并围绕轻量化、微型化、低噪音、精度、刚性和寿命持续攻关；同时突破行星滚柱丝杠规模化制造并扩展直线伺服关节。主板块从泛机器人执行器收敛为机器人谐波减速器，丝杠和机电一体化作为增量能力跟踪。</t>
+          <t>证据强：2025年报披露柔性传感电子皮肤入选2025具身智能十大创新产品和技术，机器人相关电子皮肤和触觉传感器已小批量供货；公司官网披露具备年产1000万支柔性传感器产线和柔性压阻/压电/电容/汗液四大技术。主板块从电子皮肤规范为机器人电子皮肤，风险是整体业务仍以气体/仪表等传感平台为主。</t>
         </is>
       </c>
       <c r="E349" s="6" t="inlineStr">
@@ -10310,22 +10310,22 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>机器人精密减速器</t>
+          <t>机器人谐波减速器</t>
         </is>
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>002896</t>
+          <t>688017</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>中大力德</t>
+          <t>绿的谐波</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露精密减速器受工业机器人产量增长、人形机器人原型机批量落地等带动，公司具备行星、RV、谐波三大减速器布局，并通过减速器+电机+驱动一体化架构形成智能执行单元。主板块从机器人减速器规范为机器人精密减速器，跟踪人形机器人客户、型号验证和毛利率。</t>
+          <t>证据强：2025年报披露公司巩固具身智能场景谐波减速器领先地位，并围绕轻量化、微型化、低噪音、精度、刚性和寿命持续攻关；同时突破行星滚柱丝杠规模化制造并扩展直线伺服关节。主板块从泛机器人执行器收敛为机器人谐波减速器，丝杠和机电一体化作为增量能力跟踪。</t>
         </is>
       </c>
       <c r="E350" s="6" t="inlineStr">
@@ -10342,17 +10342,17 @@
       </c>
       <c r="B351" s="3" t="inlineStr">
         <is>
-          <t>002472</t>
+          <t>002896</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>双环传动</t>
+          <t>中大力德</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露工业机器人核心零部件减速器趋势向好，公司在重载RV精密减速器领域攻克高精度、长寿命核心技术；控股子公司从事机器人关节高精密减速器研发生产，产品包括RV减速器、精密配件及谐波减速器。主板块从机器人减速器细化为机器人高精密减速器，风险是汽车齿轮仍是主要利润来源。</t>
+          <t>证据中强：2025年报披露精密减速器受工业机器人产量增长、人形机器人原型机批量落地等带动，公司具备行星、RV、谐波三大减速器布局，并通过减速器+电机+驱动一体化架构形成智能执行单元。主板块从机器人减速器规范为机器人精密减速器，跟踪人形机器人客户、型号验证和毛利率。</t>
         </is>
       </c>
       <c r="E351" s="6" t="inlineStr">
@@ -10364,22 +10364,22 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>行星滚柱丝杠</t>
+          <t>机器人精密减速器</t>
         </is>
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>603667</t>
+          <t>002472</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>五洲新春</t>
+          <t>双环传动</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025定增预案披露具身智能机器人和汽车智驾核心零部件项目，达产后规划年产98万套行星滚柱丝杠、210万套微型滚珠丝杠和7万组通用机器人专用轴承；删减机器人专用轴承重复行，保留最能解释人形机器人弹性的行星滚柱丝杠。风险是募投建设周期较长，当前丝杠收入基数仍小。</t>
+          <t>证据中强：2025年报披露工业机器人核心零部件减速器趋势向好，公司在重载RV精密减速器领域攻克高精度、长寿命核心技术；控股子公司从事机器人关节高精密减速器研发生产，产品包括RV减速器、精密配件及谐波减速器。主板块从机器人减速器细化为机器人高精密减速器，风险是汽车齿轮仍是主要利润来源。</t>
         </is>
       </c>
       <c r="E352" s="6" t="inlineStr">
@@ -10396,17 +10396,17 @@
       </c>
       <c r="B353" s="3" t="inlineStr">
         <is>
-          <t>601100</t>
+          <t>603667</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>恒立液压</t>
+          <t>五洲新春</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露线性驱动项目投产，精密丝杠、直线导轨、电动缸等产品拓展；行星滚柱丝杠已完成送样和初步量产，为精密传动业务开拓机器人等多元下游市场。主板块保留行星滚柱丝杠，但公司基本盘仍是液压件，机器人弹性需看丝杠客户验证、量产节奏和收入占比。</t>
+          <t>证据中强：2025定增预案披露具身智能机器人和汽车智驾核心零部件项目，达产后规划年产98万套行星滚柱丝杠、210万套微型滚珠丝杠和7万组通用机器人专用轴承；删减机器人专用轴承重复行，保留最能解释人形机器人弹性的行星滚柱丝杠。风险是募投建设周期较长，当前丝杠收入基数仍小。</t>
         </is>
       </c>
       <c r="E353" s="6" t="inlineStr">
@@ -10423,17 +10423,17 @@
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>688678</t>
+          <t>601100</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>福立旺</t>
+          <t>恒立液压</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025提质增效评估/公开资料披露公司向人形机器人精密传动拓展，已开发5.0mm、6.5mm、9.0mm等螺母直径规格微型行星滚柱丝杠，并向多家头部客户送样；删减机器人关节结构件重复行，关节护罩、驱动器支架等结构件作为补充交付能力。风险是主业仍为精密金属零部件，丝杠商业化仍早期。</t>
+          <t>证据中：2025年报披露线性驱动项目投产，精密丝杠、直线导轨、电动缸等产品拓展；行星滚柱丝杠已完成送样和初步量产，为精密传动业务开拓机器人等多元下游市场。主板块保留行星滚柱丝杠，但公司基本盘仍是液压件，机器人弹性需看丝杠客户验证、量产节奏和收入占比。</t>
         </is>
       </c>
       <c r="E354" s="6" t="inlineStr">
@@ -10450,17 +10450,17 @@
       </c>
       <c r="B355" s="3" t="inlineStr">
         <is>
-          <t>603009</t>
+          <t>688678</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>北特科技</t>
+          <t>福立旺</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>证据中强：募集说明书披露差动式行星滚柱丝杠承载能力强、刚度大、磨损小和寿命长，适用于高负载线性执行场合；募投项目达产后规划年产80万套行星滚柱丝杠，主要应用于人形机器人肢体线性运动。主板块保留差动式行星滚柱丝杠，风险是募投产能释放和客户量产验证仍需跟踪。</t>
+          <t>证据中：2025提质增效评估/公开资料披露公司向人形机器人精密传动拓展，已开发5.0mm、6.5mm、9.0mm等螺母直径规格微型行星滚柱丝杠，并向多家头部客户送样；删减机器人关节结构件重复行，关节护罩、驱动器支架等结构件作为补充交付能力。风险是主业仍为精密金属零部件，丝杠商业化仍早期。</t>
         </is>
       </c>
       <c r="E355" s="6" t="inlineStr">
@@ -10472,22 +10472,22 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>机器人执行器</t>
+          <t>行星滚柱丝杠</t>
         </is>
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>601689</t>
+          <t>603009</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>拓普集团</t>
+          <t>北特科技</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司已设立机器人执行器事业部，布局直线执行器、旋转执行器、灵巧手、传感器、躯体结构件、足部减震器、电子柔性皮肤等平台化产品；直线执行器获得客户认可后继续送样旋转执行器和灵巧手电机。主板块保留机器人执行器，风险是收入主体仍为汽车零部件且机器人客户/订单未完全披露。</t>
+          <t>证据中强：募集说明书披露差动式行星滚柱丝杠承载能力强、刚度大、磨损小和寿命长，适用于高负载线性执行场合；募投项目达产后规划年产80万套行星滚柱丝杠，主要应用于人形机器人肢体线性运动。主板块保留差动式行星滚柱丝杠，风险是募投产能释放和客户量产验证仍需跟踪。</t>
         </is>
       </c>
       <c r="E356" s="6" t="inlineStr">
@@ -10499,22 +10499,22 @@
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>机器人伺服驱动</t>
+          <t>机器人执行器</t>
         </is>
       </c>
       <c r="B357" s="3" t="inlineStr">
         <is>
-          <t>300124</t>
+          <t>601689</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>汇川技术</t>
+          <t>拓普集团</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露人形机器人业务已完成从预研到商业化突破，构建核心部件全栈能力，完成无框力矩电机、低压高功率伺服驱动器、关节模组、行星滚柱丝杠、编码器等第一代产品开发和交付；删减“机器人直线导轨-丝杠”重复行，保留最能体现汇川运动控制优势的机器人伺服驱动。</t>
+          <t>证据中强：2025年报披露公司已设立机器人执行器事业部，布局直线执行器、旋转执行器、灵巧手、传感器、躯体结构件、足部减震器、电子柔性皮肤等平台化产品；直线执行器获得客户认可后继续送样旋转执行器和灵巧手电机。主板块保留机器人执行器，风险是收入主体仍为汽车零部件且机器人客户/订单未完全披露。</t>
         </is>
       </c>
       <c r="E357" s="6" t="inlineStr">
@@ -10526,22 +10526,22 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>机器人驱控系统</t>
+          <t>机器人伺服驱动</t>
         </is>
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>002979</t>
+          <t>300124</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>雷赛智能</t>
+          <t>汇川技术</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司机器人核心部件覆盖高密度无框力矩电机、中空编码器、空心杯电机、微型伺服、谐波/行星关节模组、高中低自由度灵巧手，并布局运动控制“小脑”；关节模组与灵巧手已进入数十家主流客户批量供货。主板块从机器人关节运动控制收敛为机器人驱控系统。</t>
+          <t>证据强：2025年报披露人形机器人业务已完成从预研到商业化突破，构建核心部件全栈能力，完成无框力矩电机、低压高功率伺服驱动器、关节模组、行星滚柱丝杠、编码器等第一代产品开发和交付；删减“机器人直线导轨-丝杠”重复行，保留最能体现汇川运动控制优势的机器人伺服驱动。</t>
         </is>
       </c>
       <c r="E358" s="6" t="inlineStr">
@@ -10553,22 +10553,22 @@
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>空心杯电机</t>
+          <t>机器人驱控系统</t>
         </is>
       </c>
       <c r="B359" s="3" t="inlineStr">
         <is>
-          <t>603728</t>
+          <t>002979</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>鸣志电器</t>
+          <t>雷赛智能</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露无刷电机模组、无齿槽空心杯模组、无框/交流伺服电机及驱动控制系统、精密减速机和丝杠传动模组广泛适用于人形机器人灵巧手、关节、底盘等；删减“运动控制”重复行，保留最具人形机器人弹性的空心杯电机，运动控制平台作为配套能力。</t>
+          <t>证据强：2025年报披露公司机器人核心部件覆盖高密度无框力矩电机、中空编码器、空心杯电机、微型伺服、谐波/行星关节模组、高中低自由度灵巧手，并布局运动控制“小脑”；关节模组与灵巧手已进入数十家主流客户批量供货。主板块从机器人关节运动控制收敛为机器人驱控系统。</t>
         </is>
       </c>
       <c r="E359" s="6" t="inlineStr">
@@ -10580,22 +10580,22 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>行业大模型+Agent平台</t>
+          <t>空心杯电机</t>
         </is>
       </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>300229</t>
+          <t>603728</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>拓尔思</t>
+          <t>鸣志电器</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025半年报/公告披露高质量数据集系统、海贝搜索向量数据库、拓天链Agent平台及拓天大模型等；数据和向量数据库是底座，商业化主线为行业大模型+Agent平台。</t>
+          <t>证据强：2025年报披露无刷电机模组、无齿槽空心杯模组、无框/交流伺服电机及驱动控制系统、精密减速机和丝杠传动模组广泛适用于人形机器人灵巧手、关节、底盘等；删减“运动控制”重复行，保留最具人形机器人弹性的空心杯电机，运动控制平台作为配套能力。</t>
         </is>
       </c>
       <c r="E360" s="6" t="inlineStr">
@@ -10607,22 +10607,22 @@
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>行业大模型训推一体</t>
+          <t>行业大模型+Agent平台</t>
         </is>
       </c>
       <c r="B361" s="3" t="inlineStr">
         <is>
-          <t>688327</t>
+          <t>300229</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>云从科技</t>
+          <t>拓尔思</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司基于CWOS和从容多模态大模型推出大模型训推及智用一体机，并在工程、制造、政务等场景落地；多模态大模型是底座，主线收敛为行业大模型训推一体。</t>
+          <t>证据强：2025半年报/公告披露高质量数据集系统、海贝搜索向量数据库、拓天链Agent平台及拓天大模型等；数据和向量数据库是底座，商业化主线为行业大模型+Agent平台。</t>
         </is>
       </c>
       <c r="E361" s="6" t="inlineStr">
@@ -10634,22 +10634,22 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>国产算力大模型底座</t>
+          <t>行业大模型训推一体</t>
         </is>
       </c>
       <c r="B362" s="3" t="inlineStr">
         <is>
-          <t>002230</t>
+          <t>688327</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>科大讯飞</t>
+          <t>云从科技</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露讯飞星火持续基于全国产算力训练并推进X1/X1.5等推理模型，2025年大模型相关项目中标金额领先；行业大模型与AI开放平台是商业化路径，合并降级到备注。</t>
+          <t>证据中强：2025年报披露公司基于CWOS和从容多模态大模型推出大模型训推及智用一体机，并在工程、制造、政务等场景落地；多模态大模型是底座，主线收敛为行业大模型训推一体。</t>
         </is>
       </c>
       <c r="E362" s="6" t="inlineStr">
@@ -10661,22 +10661,22 @@
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>企业AI平台</t>
+          <t>国产算力大模型底座</t>
         </is>
       </c>
       <c r="B363" s="3" t="inlineStr">
         <is>
-          <t>600588</t>
+          <t>002230</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>用友网络</t>
+          <t>科大讯飞</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露用友BIP以AI×数据×流程原生一体，将企业AI融入财务、人力、供应链、制造等核心业务；但公司仍亏损，主线保留企业AI平台并提示盈利修复风险。</t>
+          <t>证据强：2025年报披露讯飞星火持续基于全国产算力训练并推进X1/X1.5等推理模型，2025年大模型相关项目中标金额领先；行业大模型与AI开放平台是商业化路径，合并降级到备注。</t>
         </is>
       </c>
       <c r="E363" s="6" t="inlineStr">
@@ -10688,22 +10688,22 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>企业级AI应用平台</t>
+          <t>企业AI平台</t>
         </is>
       </c>
       <c r="B364" s="3" t="inlineStr">
         <is>
-          <t>300170</t>
+          <t>600588</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>汉得信息</t>
+          <t>用友网络</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司加大行业大模型和垂类智能体研发，基于H-ZERO、H-ONE构建企业级AI基础设施并打造AI应用工厂；AI业务收入放量，主板块由企业AI中台升级为企业级AI应用平台。</t>
+          <t>证据中强：2025年报披露用友BIP以AI×数据×流程原生一体，将企业AI融入财务、人力、供应链、制造等核心业务；但公司仍亏损，主线保留企业AI平台并提示盈利修复风险。</t>
         </is>
       </c>
       <c r="E364" s="6" t="inlineStr">
@@ -10715,22 +10715,22 @@
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>行业AI智能体平台</t>
+          <t>企业级AI应用平台</t>
         </is>
       </c>
       <c r="B365" s="3" t="inlineStr">
         <is>
-          <t>301236</t>
+          <t>300170</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>软通动力</t>
+          <t>汉得信息</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司以软通天璇AutoAgent等平台为引擎，提供从AI咨询、模型部署、智能体开发到持续运营的全流程智能化升级服务；主板块保留行业AI平台并细化为行业AI智能体平台。</t>
+          <t>证据强：2025年报披露公司加大行业大模型和垂类智能体研发，基于H-ZERO、H-ONE构建企业级AI基础设施并打造AI应用工厂；AI业务收入放量，主板块由企业AI中台升级为企业级AI应用平台。</t>
         </is>
       </c>
       <c r="E365" s="6" t="inlineStr">
@@ -10742,22 +10742,22 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>制造业AI智能体平台</t>
+          <t>行业AI智能体平台</t>
         </is>
       </c>
       <c r="B366" s="3" t="inlineStr">
         <is>
-          <t>300378</t>
+          <t>301236</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>鼎捷数智</t>
+          <t>软通动力</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司持续升级鼎捷雅典娜数智底座并丰富AI智能体矩阵，AI相关业务签约金额近2亿元，覆盖生产、销售、财务等制造场景；主板块由工业AI细化为制造业AI智能体平台。</t>
+          <t>证据强：2025年报披露公司以软通天璇AutoAgent等平台为引擎，提供从AI咨询、模型部署、智能体开发到持续运营的全流程智能化升级服务；主板块保留行业AI平台并细化为行业AI智能体平台。</t>
         </is>
       </c>
       <c r="E366" s="6" t="inlineStr">
@@ -10769,22 +10769,22 @@
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>行业AI交付</t>
+          <t>制造业AI智能体平台</t>
         </is>
       </c>
       <c r="B367" s="3" t="inlineStr">
         <is>
-          <t>002649</t>
+          <t>300378</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>博彦科技</t>
+          <t>鼎捷数智</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司以AI、大数据为技术底座，依托人工智能计算平台和AI Agent平台，在金融、能源、化工等行业提供AI咨询、解决方案、实施与运营；AI中台是能力底座，合并到行业AI交付。</t>
+          <t>证据强：2025年报披露公司持续升级鼎捷雅典娜数智底座并丰富AI智能体矩阵，AI相关业务签约金额近2亿元，覆盖生产、销售、财务等制造场景；主板块由工业AI细化为制造业AI智能体平台。</t>
         </is>
       </c>
       <c r="E367" s="6" t="inlineStr">
@@ -10796,22 +10796,22 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>AI数据基础设施软件</t>
+          <t>行业AI交付</t>
         </is>
       </c>
       <c r="B368" s="3" t="inlineStr">
         <is>
-          <t>688031</t>
+          <t>002649</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>星环科技</t>
+          <t>博彦科技</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报显示公司定位企业级AI和大数据基础设施软件，覆盖大数据平台、分布式数据库、数据开发工具和AI平台，并参与向量数据库标准；AI加速卡池化更像数据库/GPU加速能力，合并降级到备注。</t>
+          <t>证据中强：2025年报披露公司以AI、大数据为技术底座，依托人工智能计算平台和AI Agent平台，在金融、能源、化工等行业提供AI咨询、解决方案、实施与运营；AI中台是能力底座，合并到行业AI交付。</t>
         </is>
       </c>
       <c r="E368" s="6" t="inlineStr">
@@ -10823,22 +10823,22 @@
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>向量数据库</t>
+          <t>AI数据基础设施软件</t>
         </is>
       </c>
       <c r="B369" s="3" t="inlineStr">
         <is>
-          <t>603138</t>
+          <t>688031</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>海量数据</t>
+          <t>星环科技</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露公司专注数据库，Vastbase与向量数据库等AI相关能力是大模型开发和智能问答等场景底座；但收入仍以国产数据库替代为主，向量数据库商业化占比未充分拆分。</t>
+          <t>证据中强：2025年报显示公司定位企业级AI和大数据基础设施软件，覆盖大数据平台、分布式数据库、数据开发工具和AI平台，并参与向量数据库标准；AI加速卡池化更像数据库/GPU加速能力，合并降级到备注。</t>
         </is>
       </c>
       <c r="E369" s="6" t="inlineStr">
@@ -10850,22 +10850,22 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>AI数据库</t>
+          <t>向量数据库</t>
         </is>
       </c>
       <c r="B370" s="3" t="inlineStr">
         <is>
-          <t>688692</t>
+          <t>603138</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>达梦数据</t>
+          <t>海量数据</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报显示软件产品使用授权仍是核心收入引擎，公司围绕数据库、云计算、大数据、AI相关产品和数据库一体机形成全栈布局；合并“全栈数据产品”，主板块保留AI数据库。</t>
+          <t>证据中：2025年报披露公司专注数据库，Vastbase与向量数据库等AI相关能力是大模型开发和智能问答等场景底座；但收入仍以国产数据库替代为主，向量数据库商业化占比未充分拆分。</t>
         </is>
       </c>
       <c r="E370" s="6" t="inlineStr">
@@ -10877,22 +10877,22 @@
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>多模态训练数据</t>
+          <t>AI数据库</t>
         </is>
       </c>
       <c r="B371" s="3" t="inlineStr">
         <is>
-          <t>688787</t>
+          <t>688692</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>海天瑞声</t>
+          <t>达梦数据</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露全球AI渗透和多模态大模型需求推动训练数据服务扩容，公司持续投入语音、视觉、NLP、3D点云及大模型数据清洗/自动标注能力；主板块由训练数据细化为多模态训练数据。</t>
+          <t>证据强：2025年报显示软件产品使用授权仍是核心收入引擎，公司围绕数据库、云计算、大数据、AI相关产品和数据库一体机形成全栈布局；合并“全栈数据产品”，主板块保留AI数据库。</t>
         </is>
       </c>
       <c r="E371" s="6" t="inlineStr">
@@ -10904,22 +10904,22 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>中文数据语料</t>
+          <t>多模态训练数据</t>
         </is>
       </c>
       <c r="B372" s="3" t="inlineStr">
         <is>
-          <t>688228</t>
+          <t>688787</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>开普云</t>
+          <t>海天瑞声</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露公司积累PB级数据并参与中文互联网基础语料3.0，专题数据语料平台仍处产品开发阶段；AI链逻辑存在，但商业化确定性低于成熟软件/SaaS。</t>
+          <t>证据强：2025年报披露全球AI渗透和多模态大模型需求推动训练数据服务扩容，公司持续投入语音、视觉、NLP、3D点云及大模型数据清洗/自动标注能力；主板块由训练数据细化为多模态训练数据。</t>
         </is>
       </c>
       <c r="E372" s="6" t="inlineStr">
@@ -10931,22 +10931,22 @@
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>AI安全</t>
+          <t>中文数据语料</t>
         </is>
       </c>
       <c r="B373" s="3" t="inlineStr">
         <is>
-          <t>002439</t>
+          <t>688228</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>启明星辰</t>
+          <t>开普云</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露以AI+安全为核心，推出大模型应用防火墙、访问安全代理、评估系统、脱敏罩、水印及拦截清洗等矩阵；由泛AI安全收敛为大模型应用安全防护。</t>
+          <t>证据中：2025年报披露公司积累PB级数据并参与中文互联网基础语料3.0，专题数据语料平台仍处产品开发阶段；AI链逻辑存在，但商业化确定性低于成熟软件/SaaS。</t>
         </is>
       </c>
       <c r="E373" s="6" t="inlineStr">
@@ -10963,17 +10963,17 @@
       </c>
       <c r="B374" s="3" t="inlineStr">
         <is>
-          <t>300454</t>
+          <t>002439</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>深信服</t>
+          <t>启明星辰</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露AI安全平台以安全数据和模型底座为核心，结合安全GPT大模型，覆盖安全运营、零信任、数据安全、终端安全；AI算力网关和办公助手为辅线。</t>
+          <t>证据强：2025年报披露以AI+安全为核心，推出大模型应用防火墙、访问安全代理、评估系统、脱敏罩、水印及拦截清洗等矩阵；由泛AI安全收敛为大模型应用安全防护。</t>
         </is>
       </c>
       <c r="E374" s="6" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="B375" s="3" t="inlineStr">
         <is>
-          <t>688561</t>
+          <t>300454</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>奇安信</t>
+          <t>深信服</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露AISOC、AI+代码卫士、大模型卫士等AI安全新品在客户侧验证并转化收入，覆盖安全运营、检测、数据、代码、攻防智能体；由泛AI安全收敛为AI安全智能体。</t>
+          <t>证据强：2025年报披露AI安全平台以安全数据和模型底座为核心，结合安全GPT大模型，覆盖安全运营、零信任、数据安全、终端安全；AI算力网关和办公助手为辅线。</t>
         </is>
       </c>
       <c r="E375" s="6" t="inlineStr">
@@ -11017,17 +11017,17 @@
       </c>
       <c r="B376" s="3" t="inlineStr">
         <is>
-          <t>688023</t>
+          <t>688561</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>安恒信息</t>
+          <t>奇安信</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露恒脑安全垂域大模型支持多参数模型、量化、软硬一体/SaaS交付并上线智能体商城；AI数据分类分级是恒脑体系的应用场景，合并降级到备注。</t>
+          <t>证据强：2025年报披露AISOC、AI+代码卫士、大模型卫士等AI安全新品在客户侧验证并转化收入，覆盖安全运营、检测、数据、代码、攻防智能体；由泛AI安全收敛为AI安全智能体。</t>
         </is>
       </c>
       <c r="E376" s="6" t="inlineStr">
@@ -11044,17 +11044,17 @@
       </c>
       <c r="B377" s="3" t="inlineStr">
         <is>
-          <t>601360</t>
+          <t>688023</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>三六零</t>
+          <t>安恒信息</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报/半年报披露自研AI大模型驱动互联网产品，同时360安全大模型已在大量用户真实环境测试、应用与交付；主板块由宽泛360大模型收敛为360安全大模型。</t>
+          <t>证据强：2025年报披露恒脑安全垂域大模型支持多参数模型、量化、软硬一体/SaaS交付并上线智能体商城；AI数据分类分级是恒脑体系的应用场景，合并降级到备注。</t>
         </is>
       </c>
       <c r="E377" s="6" t="inlineStr">
@@ -11071,17 +11071,17 @@
       </c>
       <c r="B378" s="3" t="inlineStr">
         <is>
-          <t>300369</t>
+          <t>601360</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>绿盟科技</t>
+          <t>三六零</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露清风卫AI安全系列覆盖评估、防护、响应，并推出AI全生命周期安全测评和备案服务，国家级攻防演练AI内容安全赛道表现突出；保留清风卫AI安全。</t>
+          <t>证据中强：2025年报/半年报披露自研AI大模型驱动互联网产品，同时360安全大模型已在大量用户真实环境测试、应用与交付；主板块由宽泛360大模型收敛为360安全大模型。</t>
         </is>
       </c>
       <c r="E378" s="6" t="inlineStr">
@@ -11093,22 +11093,22 @@
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>AI办公Agent</t>
+          <t>AI安全</t>
         </is>
       </c>
       <c r="B379" s="3" t="inlineStr">
         <is>
-          <t>688111</t>
+          <t>300369</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>金山办公</t>
+          <t>绿盟科技</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露WPS AI政务版、企业知识库、可信溯源和私有化部署等能力，WPS 365持续向企业级智能办公平台演进；企业知识库是AI办公Agent底座能力，合并到备注。</t>
+          <t>证据强：2025年报披露清风卫AI安全系列覆盖评估、防护、响应，并推出AI全生命周期安全测评和备案服务，国家级攻防演练AI内容安全赛道表现突出；保留清风卫AI安全。</t>
         </is>
       </c>
       <c r="E379" s="6" t="inlineStr">
@@ -11120,22 +11120,22 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>PDF文档AI</t>
+          <t>AI办公Agent</t>
         </is>
       </c>
       <c r="B380" s="3" t="inlineStr">
         <is>
-          <t>688095</t>
+          <t>688111</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>福昕软件</t>
+          <t>金山办公</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>证据中强：公司核心仍是PDF/OFD版式文档软件，2025年营收高增并推进AI-Powered Research Agent、智能文档解析、结构化提取和私域知识库；主板块保留PDF文档AI。</t>
+          <t>证据强：2025年报披露WPS AI政务版、企业知识库、可信溯源和私有化部署等能力，WPS 365持续向企业级智能办公平台演进；企业知识库是AI办公Agent底座能力，合并到备注。</t>
         </is>
       </c>
       <c r="E380" s="6" t="inlineStr">
@@ -11147,22 +11147,22 @@
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>问财金融投研AI</t>
+          <t>PDF文档AI</t>
         </is>
       </c>
       <c r="B381" s="3" t="inlineStr">
         <is>
-          <t>300033</t>
+          <t>688095</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>同花顺</t>
+          <t>福昕软件</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025财务决算披露公司持续加大AI研发、自研大模型并提升金融专业场景准确性，叠加营收和净利高增；AI变现依托问财/投研助手和金融信息服务，主线细化为问财金融投研AI。</t>
+          <t>证据中强：公司核心仍是PDF/OFD版式文档软件，2025年营收高增并推进AI-Powered Research Agent、智能文档解析、结构化提取和私域知识库；主板块保留PDF文档AI。</t>
         </is>
       </c>
       <c r="E381" s="6" t="inlineStr">
@@ -11174,22 +11174,22 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>保险IT AI应用</t>
+          <t>问财金融投研AI</t>
         </is>
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>603927</t>
+          <t>300033</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>中科软</t>
+          <t>同花顺</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司聚焦行业应用软件开发，保险IT解决方案市场占有率持续领先，并继续深耕保险、医疗卫生及政务等重点行业AI应用；主线保留保险IT AI应用，政务AI办公智能体并入备注不单列。</t>
+          <t>证据强：2025财务决算披露公司持续加大AI研发、自研大模型并提升金融专业场景准确性，叠加营收和净利高增；AI变现依托问财/投研助手和金融信息服务，主线细化为问财金融投研AI。</t>
         </is>
       </c>
       <c r="E382" s="6" t="inlineStr">
@@ -11201,22 +11201,22 @@
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>AI多媒体创作平台</t>
+          <t>保险IT AI应用</t>
         </is>
       </c>
       <c r="B383" s="3" t="inlineStr">
         <is>
-          <t>300624</t>
+          <t>603927</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>万兴科技</t>
+          <t>中科软</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露万兴天幕2.0音视频多媒体大模型、AI漫剧/视频创作工作流，全年AI原生应用收入超1.3亿元、同比超90%；主板块由多媒体创作AI收敛为AI多媒体创作平台。</t>
+          <t>证据中强：2025年报披露公司聚焦行业应用软件开发，保险IT解决方案市场占有率持续领先，并继续深耕保险、医疗卫生及政务等重点行业AI应用；主线保留保险IT AI应用，政务AI办公智能体并入备注不单列。</t>
         </is>
       </c>
       <c r="E383" s="6" t="inlineStr">
@@ -11228,22 +11228,22 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>AI+CAx工业设计软件</t>
+          <t>AI多媒体创作平台</t>
         </is>
       </c>
       <c r="B384" s="3" t="inlineStr">
         <is>
-          <t>688083</t>
+          <t>300624</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>中望软件</t>
+          <t>万兴科技</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司持续探索AI与CAx软件深度融合，ZWCAD 2026集成相似图形检索等AI功能并以API赋能生态；核心仍是研发设计类工业软件，主板块由工业设计AI细化为AI+CAx工业设计软件。</t>
+          <t>证据强：2025年报披露万兴天幕2.0音视频多媒体大模型、AI漫剧/视频创作工作流，全年AI原生应用收入超1.3亿元、同比超90%；主板块由多媒体创作AI收敛为AI多媒体创作平台。</t>
         </is>
       </c>
       <c r="E384" s="6" t="inlineStr">
@@ -11255,22 +11255,22 @@
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>物理AI工业仿真</t>
+          <t>AI+CAx工业设计软件</t>
         </is>
       </c>
       <c r="B385" s="3" t="inlineStr">
         <is>
-          <t>688507</t>
+          <t>688083</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>索辰科技</t>
+          <t>中望软件</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司以CAE为核心并新增开物系列物理AI平台，物理AI聚焦工业场景机理建模与精准计算，产品矩阵从CAE延伸至工业软件全链条；主板块由工业仿真AI升级为物理AI工业仿真。</t>
+          <t>证据中强：2025年报披露公司持续探索AI与CAx软件深度融合，ZWCAD 2026集成相似图形检索等AI功能并以API赋能生态；核心仍是研发设计类工业软件，主板块由工业设计AI细化为AI+CAx工业设计软件。</t>
         </is>
       </c>
       <c r="E385" s="6" t="inlineStr">
@@ -11282,22 +11282,22 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>流程工业AI</t>
+          <t>物理AI工业仿真</t>
         </is>
       </c>
       <c r="B386" s="3" t="inlineStr">
         <is>
-          <t>688777</t>
+          <t>688507</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>中控技术</t>
+          <t>索辰科技</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>证据强：公司持续深化All in AI战略，将AI能力融入流程工业控制、数据与场景体系；客户和控制系统部署基础集中在石化、化工、电力、冶金、制药等流程工业，主板块由工业AI收敛为流程工业AI。</t>
+          <t>证据强：2025年报披露公司以CAE为核心并新增开物系列物理AI平台，物理AI聚焦工业场景机理建模与精准计算，产品矩阵从CAE延伸至工业软件全链条；主板块由工业仿真AI升级为物理AI工业仿真。</t>
         </is>
       </c>
       <c r="E386" s="6" t="inlineStr">
@@ -11309,22 +11309,22 @@
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>激光加工AI工艺优化</t>
+          <t>流程工业AI</t>
         </is>
       </c>
       <c r="B387" s="3" t="inlineStr">
         <is>
-          <t>688188</t>
+          <t>688777</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>柏楚电子</t>
+          <t>中控技术</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司在金属成型中基于自研AI模型实现切割断面自动采集与闭环工艺调试，并推进智能焊接、视觉识别和多机协同；主板块由工艺专家库细化为激光加工AI工艺优化。</t>
+          <t>证据强：公司持续深化All in AI战略，将AI能力融入流程工业控制、数据与场景体系；客户和控制系统部署基础集中在石化、化工、电力、冶金、制药等流程工业，主板块由工业AI收敛为流程工业AI。</t>
         </is>
       </c>
       <c r="E387" s="6" t="inlineStr">
@@ -11336,22 +11336,22 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>AI分子砌块设计</t>
+          <t>激光加工AI工艺优化</t>
         </is>
       </c>
       <c r="B388" s="3" t="inlineStr">
         <is>
-          <t>300725</t>
+          <t>688188</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>药石科技</t>
+          <t>柏楚电子</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年投资者交流披露公司在前端分子砌块研发中应用AI生成8,000多万个新颖分子砌块，筛选后产品已陆续上线；核心仍是分子砌块+CDMO，主板块由AI分子砌块筛选细化为AI分子砌块设计。</t>
+          <t>证据强：2025年报披露公司在金属成型中基于自研AI模型实现切割断面自动采集与闭环工艺调试，并推进智能焊接、视觉识别和多机协同；主板块由工艺专家库细化为激光加工AI工艺优化。</t>
         </is>
       </c>
       <c r="E388" s="6" t="inlineStr">
@@ -11363,22 +11363,22 @@
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>AI片段分子库</t>
+          <t>AI分子砌块设计</t>
         </is>
       </c>
       <c r="B389" s="3" t="inlineStr">
         <is>
-          <t>688131</t>
+          <t>300725</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>皓元医药</t>
+          <t>药石科技</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>证据中：2025年报披露公司开发药物片段分子库，完成1万多种可用于药物筛选的小分子及类似物，并指出片段分子库结合人工智能大数据和实验筛选模型用于先导化合物发现；AI化合物库收敛为AI片段分子库。</t>
+          <t>证据中强：2025年投资者交流披露公司在前端分子砌块研发中应用AI生成8,000多万个新颖分子砌块，筛选后产品已陆续上线；核心仍是分子砌块+CDMO，主板块由AI分子砌块筛选细化为AI分子砌块设计。</t>
         </is>
       </c>
       <c r="E389" s="6" t="inlineStr">
@@ -11390,22 +11390,22 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>AI药物发现</t>
+          <t>AI片段分子库</t>
         </is>
       </c>
       <c r="B390" s="3" t="inlineStr">
         <is>
-          <t>688222</t>
+          <t>688131</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>成都先导</t>
+          <t>皓元医药</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司以DEL技术为核心，并自主研发DEL+AI+自动化一体化分子优化平台HAILO，覆盖计算科学/AI数据分析与分子设计；主板块由AI制药收敛为AI药物发现。</t>
+          <t>证据中：2025年报披露公司开发药物片段分子库，完成1万多种可用于药物筛选的小分子及类似物，并指出片段分子库结合人工智能大数据和实验筛选模型用于先导化合物发现；AI化合物库收敛为AI片段分子库。</t>
         </is>
       </c>
       <c r="E390" s="6" t="inlineStr">
@@ -11417,22 +11417,22 @@
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>AI辅助药物设计</t>
+          <t>AI药物发现</t>
         </is>
       </c>
       <c r="B391" s="3" t="inlineStr">
         <is>
-          <t>301230</t>
+          <t>688222</t>
         </is>
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>泓博医药</t>
+          <t>成都先导</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>证据中强：2025年报披露公司以药物设计为核心驱动，在先导化合物发现阶段使用计算机/人工智能辅助药物设计，并覆盖靶点识别、虚拟筛选、结构预测、分子对接、分子动力学和ADME预测；AI是CRO/CDMO服务能力，不单列泛AI制药。</t>
+          <t>证据中强：2025年报披露公司以DEL技术为核心，并自主研发DEL+AI+自动化一体化分子优化平台HAILO，覆盖计算科学/AI数据分析与分子设计；主板块由AI制药收敛为AI药物发现。</t>
         </is>
       </c>
       <c r="E391" s="6" t="inlineStr">
@@ -11444,22 +11444,22 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>AI患者追踪系统</t>
+          <t>AI辅助药物设计</t>
         </is>
       </c>
       <c r="B392" s="3" t="inlineStr">
         <is>
-          <t>300451</t>
+          <t>301230</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>创业慧康</t>
+          <t>泓博医药</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>证据中强但基本面承压：2025年报披露公司以AI技术创新驱动医疗场景落地，AI关键患者追踪系统APTS以医疗大模型为底座筛查高危患者并开展分级追踪；医疗大模型概念收敛为更具体的AI患者追踪系统。</t>
+          <t>证据中强：2025年报披露公司以药物设计为核心驱动，在先导化合物发现阶段使用计算机/人工智能辅助药物设计，并覆盖靶点识别、虚拟筛选、结构预测、分子对接、分子动力学和ADME预测；AI是CRO/CDMO服务能力，不单列泛AI制药。</t>
         </is>
       </c>
       <c r="E392" s="6" t="inlineStr">
@@ -11471,22 +11471,22 @@
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>AI医学影像设备</t>
+          <t>AI患者追踪系统</t>
         </is>
       </c>
       <c r="B393" s="3" t="inlineStr">
         <is>
-          <t>688271</t>
+          <t>300451</t>
         </is>
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>联影医疗</t>
+          <t>创业慧康</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>证据强：2025年报披露公司医学影像与放疗设备收入创新高，并推进设备+AI在医学影像诊疗和治疗场景落地，原生智能超声、光子计数CT、双宽体双源CT等高端产品放量；主板块保留医疗影像AI并细化为AI医学影像设备。</t>
+          <t>证据中强但基本面承压：2025年报披露公司以AI技术创新驱动医疗场景落地，AI关键患者追踪系统APTS以医疗大模型为底座筛查高危患者并开展分级追踪；医疗大模型概念收敛为更具体的AI患者追踪系统。</t>
         </is>
       </c>
       <c r="E393" s="6" t="inlineStr">
@@ -11498,22 +11498,22 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>医疗信息化大模型</t>
+          <t>AI医学影像设备</t>
         </is>
       </c>
       <c r="B394" s="3" t="inlineStr">
         <is>
-          <t>300253</t>
+          <t>688271</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>卫宁健康</t>
+          <t>联影医疗</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>证据强但业绩承压：2025年报/半年报披露公司发布WiNGPT医疗大模型和WiNEX Copilot，覆盖文书生成、病历质控、诊中决策、报告解读、护理评估等场景，并在多家医疗机构部署；主线为医疗信息化大模型而非通用医疗AI。</t>
+          <t>证据强：2025年报披露公司医学影像与放疗设备收入创新高，并推进设备+AI在医学影像诊疗和治疗场景落地，原生智能超声、光子计数CT、双宽体双源CT等高端产品放量；主板块保留医疗影像AI并细化为AI医学影像设备。</t>
         </is>
       </c>
       <c r="E394" s="6" t="inlineStr">
@@ -11525,25 +11525,52 @@
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
+          <t>医疗信息化大模型</t>
+        </is>
+      </c>
+      <c r="B395" s="3" t="inlineStr">
+        <is>
+          <t>300253</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>卫宁健康</t>
+        </is>
+      </c>
+      <c r="D395" s="2" t="inlineStr">
+        <is>
+          <t>证据强但业绩承压：2025年报/半年报披露公司发布WiNGPT医疗大模型和WiNEX Copilot，覆盖文书生成、病历质控、诊中决策、报告解读、护理评估等场景，并在多家医疗机构部署；主线为医疗信息化大模型而非通用医疗AI。</t>
+        </is>
+      </c>
+      <c r="E395" s="6" t="inlineStr">
+        <is>
+          <t>已处理</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
           <t>医学检验AI服务</t>
         </is>
       </c>
-      <c r="B395" s="3" t="inlineStr">
+      <c r="B396" s="3" t="inlineStr">
         <is>
           <t>603108</t>
         </is>
       </c>
-      <c r="C395" s="2" t="inlineStr">
+      <c r="C396" s="2" t="inlineStr">
         <is>
           <t>润达医疗</t>
         </is>
       </c>
-      <c r="D395" s="2" t="inlineStr">
+      <c r="D396" s="2" t="inlineStr">
         <is>
           <t>证据中强但业绩弱：2025年报披露公司推出大模型产品CDx良医晓慧，覆盖数据基座、医生助理和健康智能体，已在华西、南方、齐鲁等医院落地；核心仍是IVD流通/实验室服务，主板块由IVD检验AI细化为医学检验AI服务。</t>
         </is>
       </c>
-      <c r="E395" s="6" t="inlineStr">
+      <c r="E396" s="6" t="inlineStr">
         <is>
           <t>已处理</t>
         </is>
